--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -218,10 +218,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -243,10 +243,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -268,10 +268,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3524250" cy="666750"/>
+    <ext cx="4762500" cy="952500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -293,10 +293,10 @@
     <from>
       <col>33</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2476500" cy="1333500"/>
+    <ext cx="2476500" cy="1143000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK51"/>
+  <dimension ref="A1:AK53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="59" customWidth="1" min="1" max="1"/>
@@ -642,504 +642,284 @@
     <col width="7" customWidth="1" min="31" max="31"/>
     <col width="7" customWidth="1" min="32" max="32"/>
     <col width="7" customWidth="1" min="33" max="33"/>
-    <col width="19" customWidth="1" min="34" max="34"/>
-    <col width="22" customWidth="1" min="35" max="35"/>
-    <col width="42" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="23" customWidth="1" min="35" max="35"/>
+    <col width="23" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
+          <t>INFORME DE CONTROL TÉCNICO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>COORDINACIÓN ZONAL 6</t>
+          <t>No. IT-CZ06-R-2025-00XX</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:CAÑAR</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE FM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:CAÑAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>FRECUENCIA (MHz)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Frecuencia (MHz)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M10" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="N10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O8" s="3" t="n">
+      <c r="O10" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P8" s="3" t="n">
+      <c r="P10" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q10" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S8" s="3" t="n">
+      <c r="S10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T10" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W10" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X10" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y10" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA8" s="3" t="n">
+      <c r="AA10" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB8" s="3" t="n">
+      <c r="AB10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AC10" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD8" s="3" t="n">
+      <c r="AD10" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE8" s="3" t="n">
+      <c r="AE10" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF8" s="3" t="n">
+      <c r="AF10" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG8" s="3" t="n">
+      <c r="AG10" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
+      <c r="AH10" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI8" s="3" t="inlineStr">
+      <c r="AI10" s="3" t="inlineStr">
         <is>
           <t>Ancho de Banda
 (KHz)</t>
         </is>
       </c>
-      <c r="AJ8" s="3" t="inlineStr">
+      <c r="AJ10" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AK8" s="4" t="inlineStr">
+      <c r="AK10" s="4" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>SUSCAL RADIO DIGITAL FM</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>88.09999999999999</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>70.81</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>71.16</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>71.81</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>71.39</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>70.87</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>70.81</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>70.62</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>70.94</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>70.63</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>70.95999999999999</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>70.73999999999999</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>71.27</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>70.76000000000001</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>70.81</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>70.42</v>
-      </c>
-      <c r="T9" s="6" t="n">
-        <v>70.84999999999999</v>
-      </c>
-      <c r="U9" s="6" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>70.27</v>
-      </c>
-      <c r="W9" s="6" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="X9" s="6" t="n">
-        <v>70.22</v>
-      </c>
-      <c r="Y9" s="6" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="Z9" s="6" t="n">
-        <v>70.48999999999999</v>
-      </c>
-      <c r="AA9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC9" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD9" s="6" t="n">
-        <v>70.68000000000001</v>
-      </c>
-      <c r="AE9" s="6" t="n">
-        <v>70.78</v>
-      </c>
-      <c r="AF9" s="6" t="n">
-        <v>70.73999999999999</v>
-      </c>
-      <c r="AG9" s="6" t="n">
-        <v>71.11</v>
-      </c>
-      <c r="AH9" s="6" t="n">
-        <v>70.79000000000001</v>
-      </c>
-      <c r="AI9" s="6" t="n">
-        <v>339.89</v>
-      </c>
-      <c r="AJ9" s="6" t="inlineStr"/>
-      <c r="AK9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>LA VOZ DEL TAMBO</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>93.28</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>94.11</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>93.97</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>93.48999999999999</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>93.52</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>93.55</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>92.95999999999999</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>93.36</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>93.75</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>93.52</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>93.93000000000001</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>94.01000000000001</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>93.66</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>93.38</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>92.72</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>92.98</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>93.42</v>
-      </c>
-      <c r="T10" s="6" t="n">
-        <v>93.75</v>
-      </c>
-      <c r="U10" s="6" t="n">
-        <v>93.36</v>
-      </c>
-      <c r="V10" s="6" t="n">
-        <v>92.31999999999999</v>
-      </c>
-      <c r="W10" s="6" t="n">
-        <v>93.09</v>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>93.06999999999999</v>
-      </c>
-      <c r="Y10" s="6" t="n">
-        <v>92.84</v>
-      </c>
-      <c r="Z10" s="6" t="n">
-        <v>93.28</v>
-      </c>
-      <c r="AA10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC10" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD10" s="6" t="n">
-        <v>92.72</v>
-      </c>
-      <c r="AE10" s="6" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="AF10" s="6" t="n">
-        <v>93.08</v>
-      </c>
-      <c r="AG10" s="6" t="n">
-        <v>93.13</v>
-      </c>
-      <c r="AH10" s="6" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="AI10" s="6" t="n">
-        <v>215.38</v>
-      </c>
-      <c r="AJ10" s="6" t="inlineStr"/>
-      <c r="AK10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>W RADIO</t>
+          <t>SUSCAL RADIO DIGITAL FM</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>90.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>75.98</v>
+        <v>70.81</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>74.91</v>
+        <v>71.16</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>78.88</v>
+        <v>71.81</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>75.26000000000001</v>
+        <v>71.39</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>74.39</v>
+        <v>70.94</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>74.59999999999999</v>
+        <v>70.87</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>73.68000000000001</v>
+        <v>70.81</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>74.56999999999999</v>
+        <v>70.62</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>74.68000000000001</v>
+        <v>70.94</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>74.41</v>
+        <v>70.63</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>74.92</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>74.76000000000001</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>74.81999999999999</v>
+        <v>71.27</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>73.83</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>74.08</v>
+        <v>70.81</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>72.84999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="S11" s="6" t="n">
-        <v>74.43000000000001</v>
+        <v>70.42</v>
       </c>
       <c r="T11" s="6" t="n">
-        <v>74.48</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>74.27</v>
+        <v>70.55</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>74.08</v>
+        <v>70.27</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>73.83</v>
+        <v>70.75</v>
       </c>
       <c r="X11" s="6" t="n">
-        <v>74.39</v>
+        <v>70.22</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>74.2</v>
+        <v>70.5</v>
       </c>
       <c r="Z11" s="6" t="n">
-        <v>73.31999999999999</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="AA11" s="6" t="inlineStr">
         <is>
@@ -1157,22 +937,22 @@
         </is>
       </c>
       <c r="AD11" s="6" t="n">
-        <v>74.47</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="AE11" s="6" t="n">
-        <v>73.42</v>
+        <v>70.78</v>
       </c>
       <c r="AF11" s="6" t="n">
-        <v>72.95999999999999</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="AG11" s="6" t="n">
-        <v>73.36</v>
+        <v>71.11</v>
       </c>
       <c r="AH11" s="6" t="n">
-        <v>74.42</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="AI11" s="6" t="n">
-        <v>381.82</v>
+        <v>339.89</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
       <c r="AK11" s="7" t="inlineStr"/>
@@ -1180,83 +960,83 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SUPER S</t>
+          <t>LA VOZ DEL TAMBO</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>90.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>96.93000000000001</v>
+        <v>93.28</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>97.09</v>
+        <v>94.11</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>96.54000000000001</v>
+        <v>93.97</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>97.12</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>97.09</v>
+        <v>93.52</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>97.7</v>
+        <v>93.55</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>97.28</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>97.02</v>
+        <v>93.36</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>97.08</v>
+        <v>93.75</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>96.45</v>
+        <v>93.52</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>96.55</v>
+        <v>93.93000000000001</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>96.68000000000001</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>97.84999999999999</v>
+        <v>93.66</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>97.26000000000001</v>
+        <v>93.38</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>97.52</v>
+        <v>92.72</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>96.83</v>
+        <v>92.98</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>95.88</v>
+        <v>93.42</v>
       </c>
       <c r="T12" s="6" t="n">
-        <v>96.89</v>
+        <v>93.75</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>96.91</v>
+        <v>93.36</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>96.95</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>97.84</v>
+        <v>93.09</v>
       </c>
       <c r="X12" s="6" t="n">
-        <v>96.5</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="Y12" s="6" t="n">
-        <v>96.29000000000001</v>
+        <v>92.84</v>
       </c>
       <c r="Z12" s="6" t="n">
-        <v>97.41</v>
+        <v>93.28</v>
       </c>
       <c r="AA12" s="6" t="inlineStr">
         <is>
@@ -1274,22 +1054,22 @@
         </is>
       </c>
       <c r="AD12" s="6" t="n">
-        <v>97.31999999999999</v>
+        <v>92.72</v>
       </c>
       <c r="AE12" s="6" t="n">
-        <v>96.86</v>
+        <v>92.87</v>
       </c>
       <c r="AF12" s="6" t="n">
-        <v>97.02</v>
+        <v>93.08</v>
       </c>
       <c r="AG12" s="6" t="n">
-        <v>96.36</v>
+        <v>93.13</v>
       </c>
       <c r="AH12" s="6" t="n">
-        <v>96.97</v>
+        <v>93.33</v>
       </c>
       <c r="AI12" s="6" t="n">
-        <v>394.82</v>
+        <v>215.38</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
       <c r="AK12" s="7" t="inlineStr"/>
@@ -1297,83 +1077,83 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>LA SUPER DEPORTIVA</t>
+          <t>W RADIO</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>91.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>51.91</v>
+        <v>75.98</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>51.91</v>
+        <v>74.91</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>53.71</v>
+        <v>78.88</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>53.19</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>52.31</v>
+        <v>74.39</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>52.02</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>51.63</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>51.38</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>52.8</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>52.85</v>
+        <v>74.41</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>52.05</v>
+        <v>74.92</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>51.7</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>51.64</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>51.52</v>
+        <v>73.83</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>51.34</v>
+        <v>74.08</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>51.23</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="S13" s="6" t="n">
-        <v>51.05</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="T13" s="6" t="n">
-        <v>51.93</v>
+        <v>74.48</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>51.36</v>
+        <v>74.27</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>51.27</v>
+        <v>74.08</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>51.31</v>
+        <v>73.83</v>
       </c>
       <c r="X13" s="6" t="n">
-        <v>51.83</v>
+        <v>74.39</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>51.24</v>
+        <v>74.2</v>
       </c>
       <c r="Z13" s="6" t="n">
-        <v>52.94</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="AA13" s="6" t="inlineStr">
         <is>
@@ -1391,22 +1171,22 @@
         </is>
       </c>
       <c r="AD13" s="6" t="n">
-        <v>51.04</v>
+        <v>74.47</v>
       </c>
       <c r="AE13" s="6" t="n">
-        <v>50.71</v>
+        <v>73.42</v>
       </c>
       <c r="AF13" s="6" t="n">
-        <v>50.56</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="AG13" s="6" t="n">
-        <v>51.09</v>
+        <v>73.36</v>
       </c>
       <c r="AH13" s="6" t="n">
-        <v>51.77</v>
+        <v>74.42</v>
       </c>
       <c r="AI13" s="6" t="n">
-        <v>489.28</v>
+        <v>381.82</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
       <c r="AK13" s="7" t="inlineStr"/>
@@ -1414,83 +1194,83 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>GCG MAGICA FM</t>
+          <t>SUPER S</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>92.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>87.31</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>87.98999999999999</v>
+        <v>97.09</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>88.61</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>88.18000000000001</v>
+        <v>97.12</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>87.95999999999999</v>
+        <v>97.09</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>87.73</v>
+        <v>97.7</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>87.54000000000001</v>
+        <v>97.28</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>88.2</v>
+        <v>97.02</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>89.23</v>
+        <v>97.08</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>89.13</v>
+        <v>96.45</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>89.14</v>
+        <v>96.55</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>89.18000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>88.27</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>88.66</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>88.20999999999999</v>
+        <v>97.52</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>87.81999999999999</v>
+        <v>96.83</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>88.15000000000001</v>
+        <v>95.88</v>
       </c>
       <c r="T14" s="6" t="n">
-        <v>88.48</v>
+        <v>96.89</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>87.94</v>
+        <v>96.91</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>87.94</v>
+        <v>96.95</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>88.13</v>
+        <v>97.84</v>
       </c>
       <c r="X14" s="6" t="n">
-        <v>88.29000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>88.23</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="Z14" s="6" t="n">
-        <v>87.55</v>
+        <v>97.41</v>
       </c>
       <c r="AA14" s="6" t="inlineStr">
         <is>
@@ -1508,22 +1288,22 @@
         </is>
       </c>
       <c r="AD14" s="6" t="n">
-        <v>88.03</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="AE14" s="6" t="n">
-        <v>88.34</v>
+        <v>96.86</v>
       </c>
       <c r="AF14" s="6" t="n">
-        <v>88.09999999999999</v>
+        <v>97.02</v>
       </c>
       <c r="AG14" s="6" t="n">
-        <v>87.69</v>
+        <v>96.36</v>
       </c>
       <c r="AH14" s="6" t="n">
-        <v>88.22</v>
+        <v>96.97</v>
       </c>
       <c r="AI14" s="6" t="n">
-        <v>214.98</v>
+        <v>394.82</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
       <c r="AK14" s="7" t="inlineStr"/>
@@ -1531,83 +1311,83 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>RADIO K1</t>
+          <t>LA SUPER DEPORTIVA</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>92.5</v>
+        <v>91.7</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>82</v>
+        <v>51.91</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>83.66</v>
+        <v>51.91</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>82.89</v>
+        <v>53.71</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>79.54000000000001</v>
+        <v>53.19</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>78.98999999999999</v>
+        <v>52.31</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>78.14</v>
+        <v>52.02</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>77.03</v>
+        <v>51.63</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>78.29000000000001</v>
+        <v>51.38</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>78.98</v>
+        <v>52.8</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>78.91</v>
+        <v>52.85</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>79.91</v>
+        <v>52.05</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>79.66</v>
+        <v>51.7</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>78.11</v>
+        <v>51.64</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>78.31</v>
+        <v>51.52</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>78.04000000000001</v>
+        <v>51.34</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>77.95</v>
+        <v>51.23</v>
       </c>
       <c r="S15" s="6" t="n">
-        <v>79.06</v>
+        <v>51.05</v>
       </c>
       <c r="T15" s="6" t="n">
-        <v>79.84</v>
+        <v>51.93</v>
       </c>
       <c r="U15" s="6" t="n">
-        <v>78.34</v>
+        <v>51.36</v>
       </c>
       <c r="V15" s="6" t="n">
-        <v>79.08</v>
+        <v>51.27</v>
       </c>
       <c r="W15" s="6" t="n">
-        <v>79.27</v>
+        <v>51.31</v>
       </c>
       <c r="X15" s="6" t="n">
-        <v>78.29000000000001</v>
+        <v>51.83</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>78.43000000000001</v>
+        <v>51.24</v>
       </c>
       <c r="Z15" s="6" t="n">
-        <v>77.91</v>
+        <v>52.94</v>
       </c>
       <c r="AA15" s="6" t="inlineStr">
         <is>
@@ -1625,22 +1405,22 @@
         </is>
       </c>
       <c r="AD15" s="6" t="n">
-        <v>78.19</v>
+        <v>51.04</v>
       </c>
       <c r="AE15" s="6" t="n">
-        <v>78.01000000000001</v>
+        <v>50.71</v>
       </c>
       <c r="AF15" s="6" t="n">
-        <v>77.29000000000001</v>
+        <v>50.56</v>
       </c>
       <c r="AG15" s="6" t="n">
-        <v>77.31</v>
+        <v>51.09</v>
       </c>
       <c r="AH15" s="6" t="n">
-        <v>78.98</v>
+        <v>51.77</v>
       </c>
       <c r="AI15" s="6" t="n">
-        <v>362.77</v>
+        <v>489.28</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
       <c r="AK15" s="7" t="inlineStr"/>
@@ -1648,83 +1428,83 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RADIO GENESIS</t>
+          <t>GCG MAGICA FM</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>93.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>87.48999999999999</v>
+        <v>87.31</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>89.48</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>87.59999999999999</v>
+        <v>88.61</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>82.76000000000001</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>82.14</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>83.81999999999999</v>
+        <v>87.73</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>82.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>82.92</v>
+        <v>88.2</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>82.92</v>
+        <v>89.23</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>83.93000000000001</v>
+        <v>89.13</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>81.26000000000001</v>
+        <v>89.14</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>79.93000000000001</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>77.94</v>
+        <v>88.27</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>77.83</v>
+        <v>88.66</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>77.65000000000001</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>76.88</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="S16" s="6" t="n">
-        <v>79.18000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="T16" s="6" t="n">
-        <v>81.59</v>
+        <v>88.48</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>77.73999999999999</v>
+        <v>87.94</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>78.68000000000001</v>
+        <v>87.94</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>77.12</v>
+        <v>88.13</v>
       </c>
       <c r="X16" s="6" t="n">
-        <v>78.59</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>78.06999999999999</v>
+        <v>88.23</v>
       </c>
       <c r="Z16" s="6" t="n">
-        <v>83.88</v>
+        <v>87.55</v>
       </c>
       <c r="AA16" s="6" t="inlineStr">
         <is>
@@ -1742,22 +1522,22 @@
         </is>
       </c>
       <c r="AD16" s="6" t="n">
-        <v>84.56</v>
+        <v>88.03</v>
       </c>
       <c r="AE16" s="6" t="n">
-        <v>83.56999999999999</v>
+        <v>88.34</v>
       </c>
       <c r="AF16" s="6" t="n">
-        <v>83.16</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AG16" s="6" t="n">
-        <v>84.08</v>
+        <v>87.69</v>
       </c>
       <c r="AH16" s="6" t="n">
-        <v>81.7</v>
+        <v>88.22</v>
       </c>
       <c r="AI16" s="6" t="n">
-        <v>219.91</v>
+        <v>214.98</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
       <c r="AK16" s="7" t="inlineStr"/>
@@ -1765,83 +1545,83 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>RADIO QUITUMBE (SIS NO AUTORI)</t>
+          <t>RADIO K1</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>94.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>63.41</v>
+        <v>82</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>60.13</v>
+        <v>83.66</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>59.7</v>
+        <v>82.89</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>57.16</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>56.34</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>57.07</v>
+        <v>78.14</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>57.27</v>
+        <v>77.03</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>56.95</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>55.98</v>
+        <v>78.98</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>54.59</v>
+        <v>78.91</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>58.17</v>
+        <v>79.91</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>57.62</v>
+        <v>79.66</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>56.08</v>
+        <v>78.11</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>55.72</v>
+        <v>78.31</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>54.92</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>54.94</v>
+        <v>77.95</v>
       </c>
       <c r="S17" s="6" t="n">
-        <v>59.31</v>
+        <v>79.06</v>
       </c>
       <c r="T17" s="6" t="n">
-        <v>57.59</v>
+        <v>79.84</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>56.86</v>
+        <v>78.34</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>57.49</v>
+        <v>79.08</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>55.42</v>
+        <v>79.27</v>
       </c>
       <c r="X17" s="6" t="n">
-        <v>56.76</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="Y17" s="6" t="n">
-        <v>56.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="Z17" s="6" t="n">
-        <v>53.79</v>
+        <v>77.91</v>
       </c>
       <c r="AA17" s="6" t="inlineStr">
         <is>
@@ -1859,22 +1639,22 @@
         </is>
       </c>
       <c r="AD17" s="6" t="n">
-        <v>52.48</v>
+        <v>78.19</v>
       </c>
       <c r="AE17" s="6" t="n">
-        <v>54.38</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="AF17" s="6" t="n">
-        <v>55.62</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="AG17" s="6" t="n">
-        <v>55.96</v>
+        <v>77.31</v>
       </c>
       <c r="AH17" s="6" t="n">
-        <v>56.71</v>
+        <v>78.98</v>
       </c>
       <c r="AI17" s="6" t="n">
-        <v>489.91</v>
+        <v>362.77</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
       <c r="AK17" s="7" t="inlineStr"/>
@@ -1882,83 +1662,83 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>LA VOZ DE INGAPIRCA FM</t>
+          <t>RADIO GENESIS</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>94.5</v>
+        <v>93.3</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>87.01000000000001</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>87.55</v>
+        <v>89.48</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>87.76000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>87.17</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>87.51000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>87.17</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>87.18000000000001</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>87.56999999999999</v>
+        <v>82.92</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>87.29000000000001</v>
+        <v>82.92</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>87.41</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>87.76000000000001</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>87.13</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>87.53</v>
+        <v>77.94</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>87.48999999999999</v>
+        <v>77.83</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>87.55</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>87.04000000000001</v>
+        <v>76.88</v>
       </c>
       <c r="S18" s="6" t="n">
-        <v>87.28</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="T18" s="6" t="n">
-        <v>87.66</v>
+        <v>81.59</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>87.26000000000001</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>87.17</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>88.13</v>
+        <v>77.12</v>
       </c>
       <c r="X18" s="6" t="n">
-        <v>86.91</v>
+        <v>78.59</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>87.19</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="Z18" s="6" t="n">
-        <v>87.05</v>
+        <v>83.88</v>
       </c>
       <c r="AA18" s="6" t="inlineStr">
         <is>
@@ -1976,22 +1756,22 @@
         </is>
       </c>
       <c r="AD18" s="6" t="n">
-        <v>87.63</v>
+        <v>84.56</v>
       </c>
       <c r="AE18" s="6" t="n">
-        <v>87.11</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="AF18" s="6" t="n">
-        <v>87.04000000000001</v>
+        <v>83.16</v>
       </c>
       <c r="AG18" s="6" t="n">
-        <v>87.14</v>
+        <v>84.08</v>
       </c>
       <c r="AH18" s="6" t="n">
-        <v>87.34</v>
+        <v>81.7</v>
       </c>
       <c r="AI18" s="6" t="n">
-        <v>196.8</v>
+        <v>219.91</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
       <c r="AK18" s="7" t="inlineStr"/>
@@ -1999,83 +1779,83 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ONDAS CAÑARIS FM</t>
+          <t>RADIO QUITUMBE (SIS NO AUTORI)</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>95.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>94.31999999999999</v>
+        <v>63.41</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>94.76000000000001</v>
+        <v>60.13</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>94.06999999999999</v>
+        <v>59.7</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>94.17</v>
+        <v>57.16</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>94.72</v>
+        <v>56.34</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>94.16</v>
+        <v>57.07</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>94.15000000000001</v>
+        <v>57.27</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>94.31</v>
+        <v>56.95</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>94.03</v>
+        <v>55.98</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>93.81</v>
+        <v>54.59</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>93.7</v>
+        <v>58.17</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>94.93000000000001</v>
+        <v>57.62</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>94.28</v>
+        <v>56.08</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>94.02</v>
+        <v>55.72</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>94.45</v>
+        <v>54.92</v>
       </c>
       <c r="R19" s="6" t="n">
-        <v>93.68000000000001</v>
+        <v>54.94</v>
       </c>
       <c r="S19" s="6" t="n">
-        <v>94.22</v>
+        <v>59.31</v>
       </c>
       <c r="T19" s="6" t="n">
-        <v>94.33</v>
+        <v>57.59</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>94.87</v>
+        <v>56.86</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>94.43000000000001</v>
+        <v>57.49</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>94.41</v>
+        <v>55.42</v>
       </c>
       <c r="X19" s="6" t="n">
-        <v>93.66</v>
+        <v>56.76</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>94.48</v>
+        <v>56.06</v>
       </c>
       <c r="Z19" s="6" t="n">
-        <v>94.44</v>
+        <v>53.79</v>
       </c>
       <c r="AA19" s="6" t="inlineStr">
         <is>
@@ -2093,22 +1873,22 @@
         </is>
       </c>
       <c r="AD19" s="6" t="n">
-        <v>94.86</v>
+        <v>52.48</v>
       </c>
       <c r="AE19" s="6" t="n">
-        <v>93.95999999999999</v>
+        <v>54.38</v>
       </c>
       <c r="AF19" s="6" t="n">
-        <v>93.87</v>
+        <v>55.62</v>
       </c>
       <c r="AG19" s="6" t="n">
-        <v>94.06999999999999</v>
+        <v>55.96</v>
       </c>
       <c r="AH19" s="6" t="n">
-        <v>94.26000000000001</v>
+        <v>56.71</v>
       </c>
       <c r="AI19" s="6" t="n">
-        <v>230.95</v>
+        <v>489.91</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
       <c r="AK19" s="7" t="inlineStr"/>
@@ -2116,83 +1896,83 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>RADIO CATEDRAL 95.7</t>
+          <t>LA VOZ DE INGAPIRCA FM</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>95.7</v>
+        <v>94.5</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>79.19</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>78.02</v>
+        <v>87.55</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>76.98999999999999</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>78.19</v>
+        <v>87.17</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>77.61</v>
+        <v>87.51000000000001</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>78.34</v>
+        <v>87.17</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>77.91</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>77.88</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>77.90000000000001</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>78.09</v>
+        <v>87.41</v>
       </c>
       <c r="M20" s="6" t="n">
-        <v>76.56</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>78.29000000000001</v>
+        <v>87.13</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>78.41</v>
+        <v>87.53</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>76.47</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>75.29000000000001</v>
+        <v>87.55</v>
       </c>
       <c r="R20" s="6" t="n">
-        <v>76.73999999999999</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="S20" s="6" t="n">
-        <v>77.23</v>
+        <v>87.28</v>
       </c>
       <c r="T20" s="6" t="n">
-        <v>78.43000000000001</v>
+        <v>87.66</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>78.76000000000001</v>
+        <v>87.26000000000001</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>78.73</v>
+        <v>87.17</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>77.31999999999999</v>
+        <v>88.13</v>
       </c>
       <c r="X20" s="6" t="n">
-        <v>77.84999999999999</v>
+        <v>86.91</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>76.91</v>
+        <v>87.19</v>
       </c>
       <c r="Z20" s="6" t="n">
-        <v>77.48999999999999</v>
+        <v>87.05</v>
       </c>
       <c r="AA20" s="6" t="inlineStr">
         <is>
@@ -2210,22 +1990,22 @@
         </is>
       </c>
       <c r="AD20" s="6" t="n">
-        <v>76.88</v>
+        <v>87.63</v>
       </c>
       <c r="AE20" s="6" t="n">
-        <v>76.61</v>
+        <v>87.11</v>
       </c>
       <c r="AF20" s="6" t="n">
-        <v>77.09999999999999</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="AG20" s="6" t="n">
-        <v>76.23</v>
+        <v>87.14</v>
       </c>
       <c r="AH20" s="6" t="n">
-        <v>77.55</v>
+        <v>87.34</v>
       </c>
       <c r="AI20" s="6" t="n">
-        <v>436.64</v>
+        <v>196.8</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
       <c r="AK20" s="7" t="inlineStr"/>
@@ -2233,83 +2013,83 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>RADIO COSMOS</t>
+          <t>ONDAS CAÑARIS FM</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>97.3</v>
+        <v>95.3</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>70.97</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>71.63</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>70.72</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>72.53</v>
+        <v>94.17</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>70.94</v>
+        <v>94.72</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>71.58</v>
+        <v>94.16</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>70.19</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>71.95999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>71.48999999999999</v>
+        <v>94.03</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>72.37</v>
+        <v>93.81</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>68.65000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>69.26000000000001</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>69.84</v>
+        <v>94.28</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>70.48</v>
+        <v>94.02</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>69.34999999999999</v>
+        <v>94.45</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>69.12</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>68.91</v>
+        <v>94.22</v>
       </c>
       <c r="T21" s="6" t="n">
-        <v>71.76000000000001</v>
+        <v>94.33</v>
       </c>
       <c r="U21" s="6" t="n">
-        <v>71.72</v>
+        <v>94.87</v>
       </c>
       <c r="V21" s="6" t="n">
-        <v>73.87</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="W21" s="6" t="n">
-        <v>72.70999999999999</v>
+        <v>94.41</v>
       </c>
       <c r="X21" s="6" t="n">
-        <v>69.89</v>
+        <v>93.66</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>72.15000000000001</v>
+        <v>94.48</v>
       </c>
       <c r="Z21" s="6" t="n">
-        <v>69.72</v>
+        <v>94.44</v>
       </c>
       <c r="AA21" s="6" t="inlineStr">
         <is>
@@ -2327,22 +2107,22 @@
         </is>
       </c>
       <c r="AD21" s="6" t="n">
-        <v>75.16</v>
+        <v>94.86</v>
       </c>
       <c r="AE21" s="6" t="n">
-        <v>77.33</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="AF21" s="6" t="n">
-        <v>76.20999999999999</v>
+        <v>93.87</v>
       </c>
       <c r="AG21" s="6" t="n">
-        <v>84.45</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
-        <v>71.95999999999999</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="AI21" s="6" t="n">
-        <v>257.14</v>
+        <v>230.95</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
       <c r="AK21" s="7" t="inlineStr"/>
@@ -2350,83 +2130,83 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>RADIOHIT FM</t>
+          <t>RADIO CATEDRAL 95.7</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>98.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>82.16</v>
+        <v>79.19</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>82.04000000000001</v>
+        <v>78.02</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>82</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>83.72</v>
+        <v>78.19</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>81.56</v>
+        <v>77.61</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>82.06999999999999</v>
+        <v>78.34</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>81.31999999999999</v>
+        <v>77.91</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>81.45999999999999</v>
+        <v>77.88</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>82.41</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>82.11</v>
+        <v>78.09</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>81.54000000000001</v>
+        <v>76.56</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>81.65000000000001</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>81.03</v>
+        <v>78.41</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>79.18000000000001</v>
+        <v>76.47</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>80.03</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>80.20999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>80.44</v>
+        <v>77.23</v>
       </c>
       <c r="T22" s="6" t="n">
-        <v>82.08</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>80.15000000000001</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>80.55</v>
+        <v>78.73</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>79.08</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="X22" s="6" t="n">
-        <v>80.90000000000001</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>81.37</v>
+        <v>76.91</v>
       </c>
       <c r="Z22" s="6" t="n">
-        <v>80.8</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="AA22" s="6" t="inlineStr">
         <is>
@@ -2444,22 +2224,22 @@
         </is>
       </c>
       <c r="AD22" s="6" t="n">
-        <v>80.97</v>
+        <v>76.88</v>
       </c>
       <c r="AE22" s="6" t="n">
-        <v>80.06</v>
+        <v>76.61</v>
       </c>
       <c r="AF22" s="6" t="n">
-        <v>80.63</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="AG22" s="6" t="n">
-        <v>81.16</v>
+        <v>76.23</v>
       </c>
       <c r="AH22" s="6" t="n">
-        <v>81.17</v>
+        <v>77.55</v>
       </c>
       <c r="AI22" s="6" t="n">
-        <v>197.27</v>
+        <v>436.64</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
       <c r="AK22" s="7" t="inlineStr"/>
@@ -2467,83 +2247,83 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>LA RADIO DE LA ASAMBLEA NACIONA</t>
+          <t>RADIO COSMOS</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>98.5</v>
+        <v>97.3</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>46.88</v>
+        <v>70.97</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>46.81</v>
+        <v>71.63</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>45.97</v>
+        <v>70.72</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>47.78</v>
+        <v>72.53</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>48.08</v>
+        <v>70.94</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>47.05</v>
+        <v>71.58</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>46.67</v>
+        <v>70.19</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>47.12</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>46.84</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>46.88</v>
+        <v>72.37</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>46.33</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>49.66</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>48.7</v>
+        <v>69.84</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>49.31</v>
+        <v>70.48</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>47.73</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>49.23</v>
+        <v>69.12</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>47.98</v>
+        <v>68.91</v>
       </c>
       <c r="T23" s="6" t="n">
-        <v>46.88</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>45.82</v>
+        <v>71.72</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>46.52</v>
+        <v>73.87</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>47.44</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="X23" s="6" t="n">
-        <v>46.51</v>
+        <v>69.89</v>
       </c>
       <c r="Y23" s="6" t="n">
-        <v>46.15</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="Z23" s="6" t="n">
-        <v>45.64</v>
+        <v>69.72</v>
       </c>
       <c r="AA23" s="6" t="inlineStr">
         <is>
@@ -2561,22 +2341,22 @@
         </is>
       </c>
       <c r="AD23" s="6" t="n">
-        <v>44.54</v>
+        <v>75.16</v>
       </c>
       <c r="AE23" s="6" t="n">
-        <v>46.63</v>
+        <v>77.33</v>
       </c>
       <c r="AF23" s="6" t="n">
-        <v>46.59</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="AG23" s="6" t="n">
-        <v>47.18</v>
+        <v>84.45</v>
       </c>
       <c r="AH23" s="6" t="n">
-        <v>47.1</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="AI23" s="6" t="n">
-        <v>490</v>
+        <v>257.14</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
       <c r="AK23" s="7" t="inlineStr"/>
@@ -2584,83 +2364,83 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>RADIO ESTELAR</t>
+          <t>RADIOHIT FM</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>99.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>91.44</v>
+        <v>82.16</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>91.90000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>90.98999999999999</v>
+        <v>82</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>92.53</v>
+        <v>83.72</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>90.17</v>
+        <v>81.56</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>92.02</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>89</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>89.87</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>91.92</v>
+        <v>82.41</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>91.45</v>
+        <v>82.11</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>91.73999999999999</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>90.67</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>82.06999999999999</v>
+        <v>81.03</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>89.36</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>89.47</v>
+        <v>80.03</v>
       </c>
       <c r="R24" s="6" t="n">
-        <v>89.79000000000001</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="S24" s="6" t="n">
-        <v>91.56999999999999</v>
+        <v>80.44</v>
       </c>
       <c r="T24" s="6" t="n">
-        <v>91.59</v>
+        <v>82.08</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>91.81</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>90.04000000000001</v>
+        <v>80.55</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>87.87</v>
+        <v>79.08</v>
       </c>
       <c r="X24" s="6" t="n">
-        <v>91.38</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Y24" s="6" t="n">
-        <v>91.56999999999999</v>
+        <v>81.37</v>
       </c>
       <c r="Z24" s="6" t="n">
-        <v>91.66</v>
+        <v>80.8</v>
       </c>
       <c r="AA24" s="6" t="inlineStr">
         <is>
@@ -2678,22 +2458,22 @@
         </is>
       </c>
       <c r="AD24" s="6" t="n">
-        <v>89.04000000000001</v>
+        <v>80.97</v>
       </c>
       <c r="AE24" s="6" t="n">
-        <v>90.68000000000001</v>
+        <v>80.06</v>
       </c>
       <c r="AF24" s="6" t="n">
-        <v>89.98</v>
+        <v>80.63</v>
       </c>
       <c r="AG24" s="6" t="n">
-        <v>91.37</v>
+        <v>81.16</v>
       </c>
       <c r="AH24" s="6" t="n">
-        <v>90.45999999999999</v>
+        <v>81.17</v>
       </c>
       <c r="AI24" s="6" t="n">
-        <v>371.19</v>
+        <v>197.27</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
       <c r="AK24" s="7" t="inlineStr"/>
@@ -2701,83 +2481,83 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>RADIO COMPLICE FM</t>
+          <t>LA RADIO DE LA ASAMBLEA NACIONA</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>99.7</v>
+        <v>98.5</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>88.66</v>
+        <v>46.88</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>89.05</v>
+        <v>46.81</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>88.14</v>
+        <v>45.97</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>90.59999999999999</v>
+        <v>47.78</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>88.63</v>
+        <v>48.08</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>89.48999999999999</v>
+        <v>47.05</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>88.69</v>
+        <v>46.67</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>88.92</v>
+        <v>47.12</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>90.20999999999999</v>
+        <v>46.84</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>89.76000000000001</v>
+        <v>46.88</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>89.08</v>
+        <v>46.33</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>89.7</v>
+        <v>49.66</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>89.31999999999999</v>
+        <v>48.7</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>88.95999999999999</v>
+        <v>49.31</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>89.70999999999999</v>
+        <v>47.73</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>89.22</v>
+        <v>49.23</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>89.31999999999999</v>
+        <v>47.98</v>
       </c>
       <c r="T25" s="6" t="n">
-        <v>90.02</v>
+        <v>46.88</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>90.06</v>
+        <v>45.82</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>89.88</v>
+        <v>46.52</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>89.81</v>
+        <v>47.44</v>
       </c>
       <c r="X25" s="6" t="n">
-        <v>89.81999999999999</v>
+        <v>46.51</v>
       </c>
       <c r="Y25" s="6" t="n">
-        <v>89.81</v>
+        <v>46.15</v>
       </c>
       <c r="Z25" s="6" t="n">
-        <v>89.56</v>
+        <v>45.64</v>
       </c>
       <c r="AA25" s="6" t="inlineStr">
         <is>
@@ -2795,22 +2575,22 @@
         </is>
       </c>
       <c r="AD25" s="6" t="n">
-        <v>90.26000000000001</v>
+        <v>44.54</v>
       </c>
       <c r="AE25" s="6" t="n">
-        <v>89.19</v>
+        <v>46.63</v>
       </c>
       <c r="AF25" s="6" t="n">
-        <v>89.26000000000001</v>
+        <v>46.59</v>
       </c>
       <c r="AG25" s="6" t="n">
-        <v>89.41</v>
+        <v>47.18</v>
       </c>
       <c r="AH25" s="6" t="n">
-        <v>89.45</v>
+        <v>47.1</v>
       </c>
       <c r="AI25" s="6" t="n">
-        <v>315.07</v>
+        <v>490</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
       <c r="AK25" s="7" t="inlineStr"/>
@@ -2818,83 +2598,83 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>RADIO ROJA DEL CAÑAR</t>
+          <t>RADIO ESTELAR</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>101.7</v>
+        <v>99.3</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>95.06999999999999</v>
+        <v>91.44</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>95.45</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>95.17</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>96.01000000000001</v>
+        <v>92.53</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>95.23999999999999</v>
+        <v>90.17</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>95.89</v>
+        <v>92.02</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>95.45999999999999</v>
+        <v>89</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>95.34</v>
+        <v>89.87</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>95.73999999999999</v>
+        <v>91.92</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>95.16</v>
+        <v>91.45</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>93.95999999999999</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>94.33</v>
+        <v>90.67</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>94.28</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>93.86</v>
+        <v>89.36</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>93.70999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="R26" s="6" t="n">
-        <v>93.66</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="S26" s="6" t="n">
-        <v>93.48</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="T26" s="6" t="n">
-        <v>92.98999999999999</v>
+        <v>91.59</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>93.19</v>
+        <v>91.81</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>93.31999999999999</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>93.22</v>
+        <v>87.87</v>
       </c>
       <c r="X26" s="6" t="n">
-        <v>92.98</v>
+        <v>91.38</v>
       </c>
       <c r="Y26" s="6" t="n">
-        <v>93.08</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="Z26" s="6" t="n">
-        <v>92.95999999999999</v>
+        <v>91.66</v>
       </c>
       <c r="AA26" s="6" t="inlineStr">
         <is>
@@ -2912,22 +2692,22 @@
         </is>
       </c>
       <c r="AD26" s="6" t="n">
-        <v>88.22</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="AE26" s="6" t="n">
-        <v>94.93000000000001</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="AF26" s="6" t="n">
-        <v>95.78</v>
+        <v>89.98</v>
       </c>
       <c r="AG26" s="6" t="n">
-        <v>95.53</v>
+        <v>91.37</v>
       </c>
       <c r="AH26" s="6" t="n">
-        <v>94.22</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="AI26" s="6" t="n">
-        <v>244.12</v>
+        <v>371.19</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
       <c r="AK26" s="7" t="inlineStr"/>
@@ -2935,83 +2715,83 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>RADIO SONORAMA FM</t>
+          <t>RADIO COMPLICE FM</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>105.7</v>
+        <v>99.7</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>44.26</v>
+        <v>88.66</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>43.4</v>
+        <v>89.05</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>42.87</v>
+        <v>88.14</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>43.78</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>45.04</v>
+        <v>88.63</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>43.91</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>44.14</v>
+        <v>88.69</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>42.84</v>
+        <v>88.92</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>44.14</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>43.75</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>48.48</v>
+        <v>89.08</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>47.18</v>
+        <v>89.7</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>44.35</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>45.84</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>46.76</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="R27" s="6" t="n">
-        <v>47.58</v>
+        <v>89.22</v>
       </c>
       <c r="S27" s="6" t="n">
-        <v>45.74</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="T27" s="6" t="n">
-        <v>42.89</v>
+        <v>90.02</v>
       </c>
       <c r="U27" s="6" t="n">
-        <v>41.15</v>
+        <v>90.06</v>
       </c>
       <c r="V27" s="6" t="n">
-        <v>42.51</v>
+        <v>89.88</v>
       </c>
       <c r="W27" s="6" t="n">
-        <v>43.88</v>
+        <v>89.81</v>
       </c>
       <c r="X27" s="6" t="n">
-        <v>43.55</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="Y27" s="6" t="n">
-        <v>42.28</v>
+        <v>89.81</v>
       </c>
       <c r="Z27" s="6" t="n">
-        <v>44.64</v>
+        <v>89.56</v>
       </c>
       <c r="AA27" s="6" t="inlineStr">
         <is>
@@ -3029,22 +2809,22 @@
         </is>
       </c>
       <c r="AD27" s="6" t="n">
-        <v>41.87</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="AE27" s="6" t="n">
-        <v>42.42</v>
+        <v>89.19</v>
       </c>
       <c r="AF27" s="6" t="n">
-        <v>41.86</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="AG27" s="6" t="n">
-        <v>43.46</v>
+        <v>89.41</v>
       </c>
       <c r="AH27" s="6" t="n">
-        <v>44.09</v>
+        <v>89.45</v>
       </c>
       <c r="AI27" s="6" t="n">
-        <v>483.6</v>
+        <v>315.07</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
       <c r="AK27" s="7" t="inlineStr"/>
@@ -3052,83 +2832,83 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>RADIO VISION CUENCA 106.1 FM</t>
+          <t>RADIO ROJA DEL CAÑAR</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>106.1</v>
+        <v>101.7</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>93.23</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>93.48999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>93.69</v>
+        <v>95.17</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>93.81</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>93.94</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>94.40000000000001</v>
+        <v>95.89</v>
       </c>
       <c r="I28" s="6" t="n">
+        <v>95.45999999999999</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>95.73999999999999</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>93.95999999999999</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="P28" s="6" t="n">
         <v>93.86</v>
       </c>
-      <c r="J28" s="6" t="n">
-        <v>93.83</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>93.98999999999999</v>
-      </c>
-      <c r="L28" s="6" t="n">
+      <c r="Q28" s="6" t="n">
         <v>93.70999999999999</v>
       </c>
-      <c r="M28" s="6" t="n">
-        <v>93.76000000000001</v>
-      </c>
-      <c r="N28" s="6" t="n">
-        <v>93.42</v>
-      </c>
-      <c r="O28" s="6" t="n">
-        <v>93.77</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>94.01000000000001</v>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v>93.72</v>
-      </c>
       <c r="R28" s="6" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="S28" s="6" t="n">
         <v>93.48</v>
       </c>
-      <c r="S28" s="6" t="n">
-        <v>93.78</v>
-      </c>
       <c r="T28" s="6" t="n">
-        <v>93.89</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>94.01000000000001</v>
+        <v>93.19</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>93.81999999999999</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>94.14</v>
+        <v>93.22</v>
       </c>
       <c r="X28" s="6" t="n">
-        <v>93.48999999999999</v>
+        <v>92.98</v>
       </c>
       <c r="Y28" s="6" t="n">
-        <v>93.56</v>
+        <v>93.08</v>
       </c>
       <c r="Z28" s="6" t="n">
-        <v>93.34999999999999</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="AA28" s="6" t="inlineStr">
         <is>
@@ -3146,22 +2926,22 @@
         </is>
       </c>
       <c r="AD28" s="6" t="n">
-        <v>93.14</v>
+        <v>88.22</v>
       </c>
       <c r="AE28" s="6" t="n">
-        <v>93.41</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="AF28" s="6" t="n">
-        <v>93.56999999999999</v>
+        <v>95.78</v>
       </c>
       <c r="AG28" s="6" t="n">
-        <v>93.66</v>
+        <v>95.53</v>
       </c>
       <c r="AH28" s="6" t="n">
-        <v>93.70999999999999</v>
+        <v>94.22</v>
       </c>
       <c r="AI28" s="6" t="n">
-        <v>165.25</v>
+        <v>244.12</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
       <c r="AK28" s="7" t="inlineStr"/>
@@ -3169,83 +2949,83 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>CUMBRES FM</t>
+          <t>RADIO SONORAMA FM</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>106.9</v>
+        <v>105.7</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>95.87</v>
+        <v>44.26</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>92.8</v>
+        <v>43.4</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>89.73</v>
+        <v>42.87</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>95.20999999999999</v>
+        <v>43.78</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>91.89</v>
+        <v>45.04</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>91.70999999999999</v>
+        <v>43.91</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>92.11</v>
+        <v>44.14</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>91.36</v>
+        <v>42.84</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>91.63</v>
+        <v>44.14</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>91.56999999999999</v>
+        <v>43.75</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>91.55</v>
+        <v>48.48</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>92.47</v>
+        <v>47.18</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>92.87</v>
+        <v>44.35</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>92.89</v>
+        <v>45.84</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>92.98</v>
+        <v>46.76</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>92.31999999999999</v>
+        <v>47.58</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>92.94</v>
+        <v>45.74</v>
       </c>
       <c r="T29" s="6" t="n">
-        <v>95.68000000000001</v>
+        <v>42.89</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>92.73999999999999</v>
+        <v>41.15</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>92.45999999999999</v>
+        <v>42.51</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>92.95</v>
+        <v>43.88</v>
       </c>
       <c r="X29" s="6" t="n">
-        <v>92.76000000000001</v>
+        <v>43.55</v>
       </c>
       <c r="Y29" s="6" t="n">
-        <v>92.53</v>
+        <v>42.28</v>
       </c>
       <c r="Z29" s="6" t="n">
-        <v>95.41</v>
+        <v>44.64</v>
       </c>
       <c r="AA29" s="6" t="inlineStr">
         <is>
@@ -3263,22 +3043,22 @@
         </is>
       </c>
       <c r="AD29" s="6" t="n">
-        <v>95.22</v>
+        <v>41.87</v>
       </c>
       <c r="AE29" s="6" t="n">
-        <v>92.56999999999999</v>
+        <v>42.42</v>
       </c>
       <c r="AF29" s="6" t="n">
-        <v>92.39</v>
+        <v>41.86</v>
       </c>
       <c r="AG29" s="6" t="n">
-        <v>92.54000000000001</v>
+        <v>43.46</v>
       </c>
       <c r="AH29" s="6" t="n">
-        <v>92.83</v>
+        <v>44.09</v>
       </c>
       <c r="AI29" s="6" t="n">
-        <v>243.85</v>
+        <v>483.6</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
       <c r="AK29" s="7" t="inlineStr"/>
@@ -3286,83 +3066,83 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>CANELA AUSTRO</t>
+          <t>RADIO VISION CUENCA 106.1 FM</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>107.3</v>
+        <v>106.1</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>89.27</v>
+        <v>93.23</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>88.7</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>88.43000000000001</v>
+        <v>93.69</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>88.98999999999999</v>
+        <v>93.81</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>88.98999999999999</v>
+        <v>93.94</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>89.02</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>68.03</v>
+        <v>93.86</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>46.18</v>
+        <v>93.83</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>88.91</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>88.97</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>88.75</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>88.88</v>
+        <v>93.42</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>89.19</v>
+        <v>93.77</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>89.51000000000001</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>89.79000000000001</v>
+        <v>93.72</v>
       </c>
       <c r="R30" s="6" t="n">
-        <v>89.64</v>
+        <v>93.48</v>
       </c>
       <c r="S30" s="6" t="n">
-        <v>89.63</v>
+        <v>93.78</v>
       </c>
       <c r="T30" s="6" t="n">
-        <v>89.18000000000001</v>
+        <v>93.89</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>89.20999999999999</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>89.44</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>90.08</v>
+        <v>94.14</v>
       </c>
       <c r="X30" s="6" t="n">
-        <v>89.84999999999999</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="Y30" s="6" t="n">
-        <v>89.40000000000001</v>
+        <v>93.56</v>
       </c>
       <c r="Z30" s="6" t="n">
-        <v>89.25</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="AA30" s="6" t="inlineStr">
         <is>
@@ -3380,628 +3160,632 @@
         </is>
       </c>
       <c r="AD30" s="6" t="n">
-        <v>89.64</v>
+        <v>93.14</v>
       </c>
       <c r="AE30" s="6" t="n">
-        <v>89.58</v>
+        <v>93.41</v>
       </c>
       <c r="AF30" s="6" t="n">
-        <v>90.16</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="AG30" s="6" t="n">
-        <v>89.7</v>
+        <v>93.66</v>
       </c>
       <c r="AH30" s="6" t="n">
-        <v>87.01000000000001</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="AI30" s="6" t="n">
-        <v>332.07</v>
+        <v>165.25</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
       <c r="AK30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>CUMBRES FM</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>95.87</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>95.20999999999999</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>91.89</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>91.36</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>91.63</v>
+      </c>
+      <c r="L31" s="6" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>92.47</v>
+      </c>
+      <c r="O31" s="6" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v>92.89</v>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>92.98</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v>92.31999999999999</v>
+      </c>
+      <c r="S31" s="6" t="n">
+        <v>92.94</v>
+      </c>
+      <c r="T31" s="6" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="U31" s="6" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="V31" s="6" t="n">
+        <v>92.45999999999999</v>
+      </c>
+      <c r="W31" s="6" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="X31" s="6" t="n">
+        <v>92.76000000000001</v>
+      </c>
+      <c r="Y31" s="6" t="n">
+        <v>92.53</v>
+      </c>
+      <c r="Z31" s="6" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="AA31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC31" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD31" s="6" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="AE31" s="6" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="AF31" s="6" t="n">
+        <v>92.39</v>
+      </c>
+      <c r="AG31" s="6" t="n">
+        <v>92.54000000000001</v>
+      </c>
+      <c r="AH31" s="6" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="AI31" s="6" t="n">
+        <v>243.85</v>
+      </c>
+      <c r="AJ31" s="6" t="inlineStr"/>
+      <c r="AK31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>CANELA AUSTRO</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>89.02</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>68.03</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>88.91</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>88.97</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>89.79000000000001</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>89.18000000000001</v>
+      </c>
+      <c r="U32" s="6" t="n">
+        <v>89.20999999999999</v>
+      </c>
+      <c r="V32" s="6" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="W32" s="6" t="n">
+        <v>90.08</v>
+      </c>
+      <c r="X32" s="6" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="Y32" s="6" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="Z32" s="6" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="AA32" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" s="6" t="n">
+        <v>89.64</v>
+      </c>
+      <c r="AE32" s="6" t="n">
+        <v>89.58</v>
+      </c>
+      <c r="AF32" s="6" t="n">
+        <v>90.16</v>
+      </c>
+      <c r="AG32" s="6" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="AH32" s="6" t="n">
+        <v>87.01000000000001</v>
+      </c>
+      <c r="AI32" s="6" t="n">
+        <v>332.07</v>
+      </c>
+      <c r="AJ32" s="6" t="inlineStr"/>
+      <c r="AK32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>RADIO CAÑARI</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B33" s="9" t="n">
         <v>107.7</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C33" s="9" t="n">
         <v>92.8</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D33" s="9" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E33" s="9" t="n">
         <v>91.36</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F33" s="9" t="n">
         <v>91.81</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G33" s="9" t="n">
         <v>92.20999999999999</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H33" s="9" t="n">
         <v>92.84999999999999</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I33" s="9" t="n">
         <v>92.97</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J33" s="9" t="n">
         <v>92.06</v>
       </c>
-      <c r="K31" s="9" t="n">
+      <c r="K33" s="9" t="n">
         <v>92.05</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L33" s="9" t="n">
         <v>91.97</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M33" s="9" t="n">
         <v>91.98</v>
       </c>
-      <c r="N31" s="9" t="n">
+      <c r="N33" s="9" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O33" s="9" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="P31" s="9" t="n">
+      <c r="P33" s="9" t="n">
         <v>92.14</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q33" s="9" t="n">
         <v>92.78</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R33" s="9" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S33" s="9" t="n">
         <v>92.78</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T33" s="9" t="n">
         <v>92.92</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U33" s="9" t="n">
         <v>91.84</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V33" s="9" t="n">
         <v>92.84</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W33" s="9" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="X31" s="9" t="n">
+      <c r="X33" s="9" t="n">
         <v>92.89</v>
       </c>
-      <c r="Y31" s="9" t="n">
+      <c r="Y33" s="9" t="n">
         <v>92.36</v>
       </c>
-      <c r="Z31" s="9" t="n">
+      <c r="Z33" s="9" t="n">
         <v>93.11</v>
       </c>
-      <c r="AA31" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB31" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC31" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD31" s="9" t="n">
+      <c r="AA33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="9" t="n">
         <v>93.01000000000001</v>
       </c>
-      <c r="AE31" s="9" t="n">
+      <c r="AE33" s="9" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="AF31" s="9" t="n">
+      <c r="AF33" s="9" t="n">
         <v>92.98</v>
       </c>
-      <c r="AG31" s="9" t="n">
+      <c r="AG33" s="9" t="n">
         <v>93.02</v>
       </c>
-      <c r="AH31" s="9" t="n">
+      <c r="AH33" s="9" t="n">
         <v>92.45</v>
       </c>
-      <c r="AI31" s="9" t="n">
+      <c r="AI33" s="9" t="n">
         <v>269.05</v>
       </c>
-      <c r="AJ31" s="9" t="inlineStr"/>
-      <c r="AK31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>COORDINACIÓN ZONAL 6</t>
-        </is>
-      </c>
-    </row>
+      <c r="AJ33" s="9" t="inlineStr"/>
+      <c r="AK33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34"/>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
+          <t>AGENCIA DE REGULACIÓN Y CONTROL DE LAS TELECOMUNICACIONES</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
+          <t>COORDINACIÓN ZONAL 6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:CAÑAR</t>
+          <t>ESTACIÓN DE COMPROBACIÓN TÉCNICA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>PERIODO: JULIO</t>
+          <t>FORMULARIO DE CONTROL MENSUAL DE TV</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
+          <t>CIUDAD:CAÑAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>PERIODO: JULIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="45" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>ESTACION</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Frecuencia (MHz)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="C43" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G43" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H43" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I43" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="J43" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K43" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L43" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M43" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N41" s="3" t="n">
+      <c r="N43" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="O41" s="3" t="n">
+      <c r="O43" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="P41" s="3" t="n">
+      <c r="P43" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q43" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R43" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S41" s="3" t="n">
+      <c r="S43" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="T41" s="3" t="n">
+      <c r="T43" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U41" s="3" t="n">
+      <c r="U43" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V43" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W43" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X41" s="3" t="n">
+      <c r="X43" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="Y41" s="3" t="n">
+      <c r="Y43" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="Z41" s="3" t="n">
+      <c r="Z43" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="AA41" s="3" t="n">
+      <c r="AA43" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="AB41" s="3" t="n">
+      <c r="AB43" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="AC41" s="3" t="n">
+      <c r="AC43" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="AD41" s="3" t="n">
+      <c r="AD43" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="AE41" s="3" t="n">
+      <c r="AE43" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="AF41" s="3" t="n">
+      <c r="AF43" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="AG41" s="3" t="n">
+      <c r="AG43" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="AH41" s="3" t="inlineStr">
+      <c r="AH43" s="3" t="inlineStr">
         <is>
           <t>Promedio
 (dBuV/m)</t>
         </is>
       </c>
-      <c r="AI41" s="3" t="inlineStr">
+      <c r="AI43" s="3" t="inlineStr">
         <is>
           <t>Medición Manual
 AB(KHz) o NIVEL
 (dBµV/m)</t>
         </is>
       </c>
-      <c r="AJ41" s="3" t="inlineStr">
+      <c r="AJ43" s="3" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>TELEAMAZONAS</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n">
-        <v>61.25</v>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>54.45</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>54.48</v>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>57.77</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>54.82</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>55.26</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>56.32</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="L42" s="6" t="n">
-        <v>56.89</v>
-      </c>
-      <c r="M42" s="6" t="n">
-        <v>56.92</v>
-      </c>
-      <c r="N42" s="6" t="n">
-        <v>57.59</v>
-      </c>
-      <c r="O42" s="6" t="n">
-        <v>57.66</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v>56.31</v>
-      </c>
-      <c r="S42" s="6" t="n">
-        <v>55.18</v>
-      </c>
-      <c r="T42" s="6" t="n">
-        <v>56.62</v>
-      </c>
-      <c r="U42" s="6" t="n">
-        <v>55.28</v>
-      </c>
-      <c r="V42" s="6" t="n">
-        <v>54.73</v>
-      </c>
-      <c r="W42" s="6" t="n">
-        <v>55.07</v>
-      </c>
-      <c r="X42" s="6" t="n">
-        <v>54.94</v>
-      </c>
-      <c r="Y42" s="6" t="n">
-        <v>57.08</v>
-      </c>
-      <c r="Z42" s="6" t="n">
-        <v>54.75</v>
-      </c>
-      <c r="AA42" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB42" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC42" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD42" s="6" t="n">
-        <v>52.19</v>
-      </c>
-      <c r="AE42" s="6" t="n">
-        <v>54.52</v>
-      </c>
-      <c r="AF42" s="6" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="AG42" s="6" t="n">
-        <v>54.43</v>
-      </c>
-      <c r="AH42" s="6" t="n">
-        <v>55.55</v>
-      </c>
-      <c r="AI42" s="6" t="inlineStr"/>
-      <c r="AJ42" s="6" t="inlineStr"/>
-      <c r="AK42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>TELERAMA</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>62.47</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>60.99</v>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>61.95</v>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>61.42</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>61.35</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>60.27</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>59.26</v>
-      </c>
-      <c r="L43" s="6" t="n">
-        <v>59.13</v>
-      </c>
-      <c r="M43" s="6" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v>57.83</v>
-      </c>
-      <c r="O43" s="6" t="n">
-        <v>58.15</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v>62.37</v>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v>62.44</v>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v>59.07</v>
-      </c>
-      <c r="S43" s="6" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="T43" s="6" t="n">
-        <v>58.95</v>
-      </c>
-      <c r="U43" s="6" t="n">
-        <v>61.47</v>
-      </c>
-      <c r="V43" s="6" t="n">
-        <v>62.25</v>
-      </c>
-      <c r="W43" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="X43" s="6" t="n">
-        <v>62.32</v>
-      </c>
-      <c r="Y43" s="6" t="n">
-        <v>60.83</v>
-      </c>
-      <c r="Z43" s="6" t="n">
-        <v>62.26</v>
-      </c>
-      <c r="AA43" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB43" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC43" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD43" s="6" t="n">
-        <v>62.62</v>
-      </c>
-      <c r="AE43" s="6" t="n">
-        <v>62.34</v>
-      </c>
-      <c r="AF43" s="6" t="n">
-        <v>62.65</v>
-      </c>
-      <c r="AG43" s="6" t="n">
-        <v>63.19</v>
-      </c>
-      <c r="AH43" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="AI43" s="6" t="inlineStr"/>
-      <c r="AJ43" s="6" t="inlineStr"/>
-      <c r="AK43" s="7" t="n"/>
+      <c r="AK43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>TELEVISION DEL PACIFICO</t>
+          <t>TELEAMAZONAS</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>181.25</v>
+        <v>61.25</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>30.76</v>
+        <v>54.45</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>31.32</v>
+        <v>54.48</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>32.11</v>
+        <v>57.77</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>30.86</v>
+        <v>54.82</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>28.58</v>
+        <v>55.26</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>29.81</v>
+        <v>56.32</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>27.63</v>
+        <v>56.04</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>31.39</v>
+        <v>55.54</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>31.98</v>
+        <v>56.45</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>31.91</v>
+        <v>56.89</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>33.47</v>
+        <v>56.92</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>31.81</v>
+        <v>57.59</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>28.62</v>
+        <v>57.66</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>24.98</v>
+        <v>55.07</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>27.11</v>
+        <v>54.17</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>27.55</v>
+        <v>56.31</v>
       </c>
       <c r="S44" s="6" t="n">
-        <v>29.39</v>
+        <v>55.18</v>
       </c>
       <c r="T44" s="6" t="n">
-        <v>30.03</v>
+        <v>56.62</v>
       </c>
       <c r="U44" s="6" t="n">
-        <v>29.37</v>
+        <v>55.28</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>27.43</v>
+        <v>54.73</v>
       </c>
       <c r="W44" s="6" t="n">
-        <v>24.95</v>
+        <v>55.07</v>
       </c>
       <c r="X44" s="6" t="n">
-        <v>28.58</v>
+        <v>54.94</v>
       </c>
       <c r="Y44" s="6" t="n">
-        <v>30.77</v>
+        <v>57.08</v>
       </c>
       <c r="Z44" s="6" t="n">
-        <v>28.12</v>
+        <v>54.75</v>
       </c>
       <c r="AA44" s="6" t="inlineStr">
         <is>
@@ -4019,19 +3803,19 @@
         </is>
       </c>
       <c r="AD44" s="6" t="n">
-        <v>27.18</v>
+        <v>52.19</v>
       </c>
       <c r="AE44" s="6" t="n">
-        <v>27.85</v>
+        <v>54.52</v>
       </c>
       <c r="AF44" s="6" t="n">
-        <v>26.6</v>
+        <v>54.88</v>
       </c>
       <c r="AG44" s="6" t="n">
-        <v>26.24</v>
+        <v>54.43</v>
       </c>
       <c r="AH44" s="6" t="n">
-        <v>29.16</v>
+        <v>55.55</v>
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
@@ -4040,83 +3824,83 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>RED TELESISTEMA (R.T.S)</t>
+          <t>TELERAMA</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>193.25</v>
+        <v>83.25</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>46.3</v>
+        <v>62.47</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>46.33</v>
+        <v>60.99</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>46.39</v>
+        <v>59.32</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>47.05</v>
+        <v>61.95</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>47.51</v>
+        <v>61.42</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>48.13</v>
+        <v>61.35</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>46.25</v>
+        <v>60.77</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>47.56</v>
+        <v>60.27</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>49.26</v>
+        <v>59.26</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>47.54</v>
+        <v>59.13</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>48.23</v>
+        <v>59.08</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>46.86</v>
+        <v>57.83</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>45.58</v>
+        <v>58.15</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>45.14</v>
+        <v>62.37</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>46.13</v>
+        <v>62.44</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>46.38</v>
+        <v>59.07</v>
       </c>
       <c r="S45" s="6" t="n">
-        <v>46.3</v>
+        <v>61.21</v>
       </c>
       <c r="T45" s="6" t="n">
-        <v>49.68</v>
+        <v>58.95</v>
       </c>
       <c r="U45" s="6" t="n">
-        <v>49.32</v>
+        <v>61.47</v>
       </c>
       <c r="V45" s="6" t="n">
-        <v>47.83</v>
+        <v>62.25</v>
       </c>
       <c r="W45" s="6" t="n">
-        <v>45.16</v>
+        <v>62</v>
       </c>
       <c r="X45" s="6" t="n">
-        <v>47.52</v>
+        <v>62.32</v>
       </c>
       <c r="Y45" s="6" t="n">
-        <v>48.44</v>
+        <v>60.83</v>
       </c>
       <c r="Z45" s="6" t="n">
-        <v>46.78</v>
+        <v>62.26</v>
       </c>
       <c r="AA45" s="6" t="inlineStr">
         <is>
@@ -4134,19 +3918,19 @@
         </is>
       </c>
       <c r="AD45" s="6" t="n">
-        <v>45.82</v>
+        <v>62.62</v>
       </c>
       <c r="AE45" s="6" t="n">
-        <v>47.77</v>
+        <v>62.34</v>
       </c>
       <c r="AF45" s="6" t="n">
-        <v>47.22</v>
+        <v>62.65</v>
       </c>
       <c r="AG45" s="6" t="n">
-        <v>47.83</v>
+        <v>63.19</v>
       </c>
       <c r="AH45" s="6" t="n">
-        <v>47.15</v>
+        <v>61</v>
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
@@ -4155,83 +3939,83 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>CADENA ECUATORIANA DE TELE</t>
+          <t>TELEVISION DEL PACIFICO</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>205.25</v>
+        <v>181.25</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>20.25</v>
+        <v>30.76</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>19.44</v>
+        <v>31.32</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>18.66</v>
+        <v>32.11</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>21.06</v>
+        <v>30.86</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>19.93</v>
+        <v>28.58</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>20.95</v>
+        <v>29.81</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>21.35</v>
+        <v>27.63</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>19.73</v>
+        <v>31.39</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>20.03</v>
+        <v>31.98</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>19.83</v>
+        <v>31.91</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>19.34</v>
+        <v>33.47</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>20.03</v>
+        <v>31.81</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>20.25</v>
+        <v>28.62</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>19.31</v>
+        <v>24.98</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>21.73</v>
+        <v>27.11</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>21.23</v>
+        <v>27.55</v>
       </c>
       <c r="S46" s="6" t="n">
-        <v>19.64</v>
+        <v>29.39</v>
       </c>
       <c r="T46" s="6" t="n">
-        <v>20.19</v>
+        <v>30.03</v>
       </c>
       <c r="U46" s="6" t="n">
-        <v>20.4</v>
+        <v>29.37</v>
       </c>
       <c r="V46" s="6" t="n">
-        <v>20.01</v>
+        <v>27.43</v>
       </c>
       <c r="W46" s="6" t="n">
-        <v>20.09</v>
+        <v>24.95</v>
       </c>
       <c r="X46" s="6" t="n">
-        <v>19.82</v>
+        <v>28.58</v>
       </c>
       <c r="Y46" s="6" t="n">
-        <v>20.22</v>
+        <v>30.77</v>
       </c>
       <c r="Z46" s="6" t="n">
-        <v>20.75</v>
+        <v>28.12</v>
       </c>
       <c r="AA46" s="6" t="inlineStr">
         <is>
@@ -4249,19 +4033,19 @@
         </is>
       </c>
       <c r="AD46" s="6" t="n">
-        <v>20.72</v>
+        <v>27.18</v>
       </c>
       <c r="AE46" s="6" t="n">
-        <v>19.91</v>
+        <v>27.85</v>
       </c>
       <c r="AF46" s="6" t="n">
-        <v>20.74</v>
+        <v>26.6</v>
       </c>
       <c r="AG46" s="6" t="n">
-        <v>20.32</v>
+        <v>26.24</v>
       </c>
       <c r="AH46" s="6" t="n">
-        <v>20.21</v>
+        <v>29.16</v>
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
@@ -4270,83 +4054,83 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>CANAL UNO (NO AUTORIZADO)</t>
+          <t>RED TELESISTEMA (R.T.S)</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>519.25</v>
+        <v>193.25</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>17.22</v>
+        <v>46.3</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>17.16</v>
+        <v>46.33</v>
       </c>
       <c r="E47" s="6" t="n">
-        <v>16.48</v>
+        <v>46.39</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>20.09</v>
+        <v>47.05</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>17.15</v>
+        <v>47.51</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>16.65</v>
+        <v>48.13</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>17.38</v>
+        <v>46.25</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>17.17</v>
+        <v>47.56</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>16.77</v>
+        <v>49.26</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>16.8</v>
+        <v>47.54</v>
       </c>
       <c r="M47" s="6" t="n">
-        <v>16.85</v>
+        <v>48.23</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>16.67</v>
+        <v>46.86</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>16.78</v>
+        <v>45.58</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>17</v>
+        <v>45.14</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>16.78</v>
+        <v>46.13</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>16.69</v>
+        <v>46.38</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>17.09</v>
+        <v>46.3</v>
       </c>
       <c r="T47" s="6" t="n">
-        <v>16.92</v>
+        <v>49.68</v>
       </c>
       <c r="U47" s="6" t="n">
-        <v>16.91</v>
+        <v>49.32</v>
       </c>
       <c r="V47" s="6" t="n">
-        <v>17.3</v>
+        <v>47.83</v>
       </c>
       <c r="W47" s="6" t="n">
-        <v>17.05</v>
+        <v>45.16</v>
       </c>
       <c r="X47" s="6" t="n">
-        <v>16.87</v>
+        <v>47.52</v>
       </c>
       <c r="Y47" s="6" t="n">
-        <v>16.7</v>
+        <v>48.44</v>
       </c>
       <c r="Z47" s="6" t="n">
-        <v>16.9</v>
+        <v>46.78</v>
       </c>
       <c r="AA47" s="6" t="inlineStr">
         <is>
@@ -4364,19 +4148,19 @@
         </is>
       </c>
       <c r="AD47" s="6" t="n">
-        <v>16.85</v>
+        <v>45.82</v>
       </c>
       <c r="AE47" s="6" t="n">
-        <v>16.5</v>
+        <v>47.77</v>
       </c>
       <c r="AF47" s="6" t="n">
-        <v>16.61</v>
+        <v>47.22</v>
       </c>
       <c r="AG47" s="6" t="n">
-        <v>16.54</v>
+        <v>47.83</v>
       </c>
       <c r="AH47" s="6" t="n">
-        <v>17</v>
+        <v>47.15</v>
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
@@ -4385,83 +4169,83 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>TELEVICENTRO</t>
+          <t>CADENA ECUATORIANA DE TELE</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>567.25</v>
+        <v>205.25</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>64.31999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>65.59</v>
+        <v>19.44</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>65.7</v>
+        <v>18.66</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>29.7</v>
+        <v>21.06</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>31.15</v>
+        <v>19.93</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>30.96</v>
+        <v>20.95</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>30.68</v>
+        <v>21.35</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>30.74</v>
+        <v>19.73</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>30.38</v>
+        <v>20.03</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>30.17</v>
+        <v>19.83</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>30.75</v>
+        <v>19.34</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>29.89</v>
+        <v>20.03</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>30.15</v>
+        <v>20.25</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>31.64</v>
+        <v>19.31</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>30.28</v>
+        <v>21.73</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>31.09</v>
+        <v>21.23</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>30.65</v>
+        <v>19.64</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>32.47</v>
+        <v>20.19</v>
       </c>
       <c r="U48" s="6" t="n">
-        <v>31.51</v>
+        <v>20.4</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>30.9</v>
+        <v>20.01</v>
       </c>
       <c r="W48" s="6" t="n">
-        <v>32.99</v>
+        <v>20.09</v>
       </c>
       <c r="X48" s="6" t="n">
-        <v>27.85</v>
+        <v>19.82</v>
       </c>
       <c r="Y48" s="6" t="n">
-        <v>28.3</v>
+        <v>20.22</v>
       </c>
       <c r="Z48" s="6" t="n">
-        <v>28.28</v>
+        <v>20.75</v>
       </c>
       <c r="AA48" s="6" t="inlineStr">
         <is>
@@ -4479,19 +4263,19 @@
         </is>
       </c>
       <c r="AD48" s="6" t="n">
-        <v>28.19</v>
+        <v>20.72</v>
       </c>
       <c r="AE48" s="6" t="n">
-        <v>44.75</v>
+        <v>19.91</v>
       </c>
       <c r="AF48" s="6" t="n">
-        <v>60.62</v>
+        <v>20.74</v>
       </c>
       <c r="AG48" s="6" t="n">
-        <v>61.05</v>
+        <v>20.32</v>
       </c>
       <c r="AH48" s="6" t="n">
-        <v>36.81</v>
+        <v>20.21</v>
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
@@ -4500,83 +4284,83 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>TV AUSTRAL</t>
+          <t>CANAL UNO (NO AUTORIZADO)</t>
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>579.25</v>
+        <v>519.25</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>22.82</v>
+        <v>17.22</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>19.78</v>
+        <v>17.16</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>19.33</v>
+        <v>16.48</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>20.23</v>
+        <v>20.09</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>20.96</v>
+        <v>17.15</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>21.43</v>
+        <v>16.65</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>20.83</v>
+        <v>17.38</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>20.46</v>
+        <v>17.17</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>20.8</v>
+        <v>16.77</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>19.84</v>
+        <v>16.8</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>19.92</v>
+        <v>16.85</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>20.16</v>
+        <v>16.67</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>20.13</v>
+        <v>16.78</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>22.75</v>
+        <v>17</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>20.9</v>
+        <v>16.78</v>
       </c>
       <c r="R49" s="6" t="n">
-        <v>20.58</v>
+        <v>16.69</v>
       </c>
       <c r="S49" s="6" t="n">
-        <v>20.58</v>
+        <v>17.09</v>
       </c>
       <c r="T49" s="6" t="n">
-        <v>22.65</v>
+        <v>16.92</v>
       </c>
       <c r="U49" s="6" t="n">
-        <v>21.7</v>
+        <v>16.91</v>
       </c>
       <c r="V49" s="6" t="n">
-        <v>19.97</v>
+        <v>17.3</v>
       </c>
       <c r="W49" s="6" t="n">
-        <v>20.77</v>
+        <v>17.05</v>
       </c>
       <c r="X49" s="6" t="n">
-        <v>20.33</v>
+        <v>16.87</v>
       </c>
       <c r="Y49" s="6" t="n">
-        <v>20.74</v>
+        <v>16.7</v>
       </c>
       <c r="Z49" s="6" t="n">
-        <v>21.79</v>
+        <v>16.9</v>
       </c>
       <c r="AA49" s="6" t="inlineStr">
         <is>
@@ -4594,19 +4378,19 @@
         </is>
       </c>
       <c r="AD49" s="6" t="n">
-        <v>20.5</v>
+        <v>16.85</v>
       </c>
       <c r="AE49" s="6" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AF49" s="6" t="n">
-        <v>20.99</v>
+        <v>16.61</v>
       </c>
       <c r="AG49" s="6" t="n">
-        <v>21.88</v>
+        <v>16.54</v>
       </c>
       <c r="AH49" s="6" t="n">
-        <v>20.81</v>
+        <v>17</v>
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
@@ -4615,83 +4399,83 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>UCSG TELEVISION</t>
+          <t>TELEVICENTRO</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>591.25</v>
+        <v>567.25</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>18.53</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>18</v>
+        <v>65.59</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>17.98</v>
+        <v>65.7</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>18.24</v>
+        <v>29.7</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>18.19</v>
+        <v>31.15</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>17.79</v>
+        <v>30.96</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>18.05</v>
+        <v>30.68</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>18.3</v>
+        <v>30.74</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>18.22</v>
+        <v>30.38</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>17.98</v>
+        <v>30.17</v>
       </c>
       <c r="M50" s="6" t="n">
-        <v>18.44</v>
+        <v>30.75</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>18.26</v>
+        <v>29.89</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>18.29</v>
+        <v>30.15</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>18.67</v>
+        <v>31.64</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>18.47</v>
+        <v>30.28</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>18.01</v>
+        <v>31.09</v>
       </c>
       <c r="S50" s="6" t="n">
-        <v>18.22</v>
+        <v>30.65</v>
       </c>
       <c r="T50" s="6" t="n">
-        <v>18.26</v>
+        <v>32.47</v>
       </c>
       <c r="U50" s="6" t="n">
-        <v>17.86</v>
+        <v>31.51</v>
       </c>
       <c r="V50" s="6" t="n">
-        <v>18.4</v>
+        <v>30.9</v>
       </c>
       <c r="W50" s="6" t="n">
-        <v>18.1</v>
+        <v>32.99</v>
       </c>
       <c r="X50" s="6" t="n">
-        <v>17.84</v>
+        <v>27.85</v>
       </c>
       <c r="Y50" s="6" t="n">
-        <v>18.21</v>
+        <v>28.3</v>
       </c>
       <c r="Z50" s="6" t="n">
-        <v>18.21</v>
+        <v>28.28</v>
       </c>
       <c r="AA50" s="6" t="inlineStr">
         <is>
@@ -4709,154 +4493,386 @@
         </is>
       </c>
       <c r="AD50" s="6" t="n">
-        <v>18.28</v>
+        <v>28.19</v>
       </c>
       <c r="AE50" s="6" t="n">
-        <v>17.92</v>
+        <v>44.75</v>
       </c>
       <c r="AF50" s="6" t="n">
-        <v>19.01</v>
+        <v>60.62</v>
       </c>
       <c r="AG50" s="6" t="n">
-        <v>17.87</v>
+        <v>61.05</v>
       </c>
       <c r="AH50" s="6" t="n">
-        <v>18.2</v>
+        <v>36.81</v>
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
       <c r="AK50" s="7" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>TV AUSTRAL</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>579.25</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="L51" s="6" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="S51" s="6" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="T51" s="6" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="U51" s="6" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V51" s="6" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="W51" s="6" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="X51" s="6" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="Y51" s="6" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="Z51" s="6" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="AA51" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB51" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC51" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD51" s="6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="AE51" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF51" s="6" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AG51" s="6" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="AH51" s="6" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="AI51" s="6" t="inlineStr"/>
+      <c r="AJ51" s="6" t="inlineStr"/>
+      <c r="AK51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>UCSG TELEVISION</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>591.25</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="L52" s="6" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="N52" s="6" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="S52" s="6" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="T52" s="6" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="U52" s="6" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="V52" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W52" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X52" s="6" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="Y52" s="6" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="Z52" s="6" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="AA52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC52" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD52" s="6" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="AE52" s="6" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="AF52" s="6" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="AG52" s="6" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="AH52" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AI52" s="6" t="inlineStr"/>
+      <c r="AJ52" s="6" t="inlineStr"/>
+      <c r="AK52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n">
+      <c r="B53" s="9" t="n">
         <v>621.25</v>
       </c>
-      <c r="C51" s="9" t="n">
+      <c r="C53" s="9" t="n">
         <v>17.95</v>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D53" s="9" t="n">
         <v>18.92</v>
       </c>
-      <c r="E51" s="9" t="n">
+      <c r="E53" s="9" t="n">
         <v>18.01</v>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F53" s="9" t="n">
         <v>19.62</v>
       </c>
-      <c r="G51" s="9" t="n">
+      <c r="G53" s="9" t="n">
         <v>18.31</v>
       </c>
-      <c r="H51" s="9" t="n">
+      <c r="H53" s="9" t="n">
         <v>18.65</v>
       </c>
-      <c r="I51" s="9" t="n">
+      <c r="I53" s="9" t="n">
         <v>17.95</v>
       </c>
-      <c r="J51" s="9" t="n">
+      <c r="J53" s="9" t="n">
         <v>18.35</v>
       </c>
-      <c r="K51" s="9" t="n">
+      <c r="K53" s="9" t="n">
         <v>17.77</v>
       </c>
-      <c r="L51" s="9" t="n">
+      <c r="L53" s="9" t="n">
         <v>17.89</v>
       </c>
-      <c r="M51" s="9" t="n">
+      <c r="M53" s="9" t="n">
         <v>18.63</v>
       </c>
-      <c r="N51" s="9" t="n">
+      <c r="N53" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="O51" s="9" t="n">
+      <c r="O53" s="9" t="n">
         <v>18.66</v>
       </c>
-      <c r="P51" s="9" t="n">
+      <c r="P53" s="9" t="n">
         <v>18.17</v>
       </c>
-      <c r="Q51" s="9" t="n">
+      <c r="Q53" s="9" t="n">
         <v>17.78</v>
       </c>
-      <c r="R51" s="9" t="n">
+      <c r="R53" s="9" t="n">
         <v>17.77</v>
       </c>
-      <c r="S51" s="9" t="n">
+      <c r="S53" s="9" t="n">
         <v>18.17</v>
       </c>
-      <c r="T51" s="9" t="n">
+      <c r="T53" s="9" t="n">
         <v>18.65</v>
       </c>
-      <c r="U51" s="9" t="n">
+      <c r="U53" s="9" t="n">
         <v>18.15</v>
       </c>
-      <c r="V51" s="9" t="n">
+      <c r="V53" s="9" t="n">
         <v>18.39</v>
       </c>
-      <c r="W51" s="9" t="n">
+      <c r="W53" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="X51" s="9" t="n">
+      <c r="X53" s="9" t="n">
         <v>17.88</v>
       </c>
-      <c r="Y51" s="9" t="n">
+      <c r="Y53" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="Z51" s="9" t="n">
+      <c r="Z53" s="9" t="n">
         <v>17.42</v>
       </c>
-      <c r="AA51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC51" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD51" s="9" t="n">
+      <c r="AA53" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD53" s="9" t="n">
         <v>17.28</v>
       </c>
-      <c r="AE51" s="9" t="n">
+      <c r="AE53" s="9" t="n">
         <v>17.95</v>
       </c>
-      <c r="AF51" s="9" t="n">
+      <c r="AF53" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="AG51" s="9" t="n">
+      <c r="AG53" s="9" t="n">
         <v>17.93</v>
       </c>
-      <c r="AH51" s="9" t="n">
+      <c r="AH53" s="9" t="n">
         <v>18.18</v>
       </c>
-      <c r="AI51" s="9" t="inlineStr"/>
-      <c r="AJ51" s="9" t="inlineStr"/>
-      <c r="AK51" s="10" t="n"/>
+      <c r="AI53" s="9" t="inlineStr"/>
+      <c r="AJ53" s="9" t="inlineStr"/>
+      <c r="AK53" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A34:AK34"/>
+  <mergeCells count="16">
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="A4:AK4"/>
-    <mergeCell ref="A35:AK35"/>
+    <mergeCell ref="A40:AK40"/>
     <mergeCell ref="A3:AK3"/>
-    <mergeCell ref="A40:AK40"/>
     <mergeCell ref="A39:AK39"/>
     <mergeCell ref="A7:AK7"/>
     <mergeCell ref="A38:AK38"/>
     <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="A41:AK41"/>
+    <mergeCell ref="A42:AK42"/>
     <mergeCell ref="A36:AK36"/>
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="A37:AK37"/>
+    <mergeCell ref="A9:AK9"/>
+    <mergeCell ref="A8:AK8"/>
     <mergeCell ref="A6:AK6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -218,7 +218,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -268,7 +268,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -38,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -100,11 +100,60 @@
       <top style="thin"/>
       <bottom style="medium"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +185,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -644,7 +696,7 @@
     <col width="7" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
     <col width="23" customWidth="1" min="35" max="35"/>
-    <col width="23" customWidth="1" min="36" max="36"/>
+    <col width="38" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
@@ -3704,7 +3756,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK43" s="4" t="n"/>
+      <c r="AK43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3819,7 +3871,7 @@
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="7" t="n"/>
+      <c r="AK44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3934,7 +3986,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="7" t="n"/>
+      <c r="AK45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4049,7 +4101,7 @@
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="7" t="n"/>
+      <c r="AK46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4164,7 +4216,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="7" t="n"/>
+      <c r="AK47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4279,7 +4331,7 @@
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="7" t="n"/>
+      <c r="AK48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4394,7 +4446,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="7" t="n"/>
+      <c r="AK49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4509,7 +4561,7 @@
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="7" t="n"/>
+      <c r="AK50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -4624,7 +4676,7 @@
       </c>
       <c r="AI51" s="6" t="inlineStr"/>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="7" t="n"/>
+      <c r="AK51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -4739,7 +4791,7 @@
       </c>
       <c r="AI52" s="6" t="inlineStr"/>
       <c r="AJ52" s="6" t="inlineStr"/>
-      <c r="AK52" s="7" t="n"/>
+      <c r="AK52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -4854,26 +4906,37 @@
       </c>
       <c r="AI53" s="9" t="inlineStr"/>
       <c r="AJ53" s="9" t="inlineStr"/>
-      <c r="AK53" s="10" t="n"/>
+      <c r="AK53" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="27">
+    <mergeCell ref="AJ47:AK47"/>
+    <mergeCell ref="A3:AK3"/>
+    <mergeCell ref="AJ43:AK43"/>
+    <mergeCell ref="AJ50:AK50"/>
+    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="AJ51:AK51"/>
+    <mergeCell ref="AJ46:AK46"/>
+    <mergeCell ref="A42:AK42"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="AJ52:AK52"/>
+    <mergeCell ref="A8:AK8"/>
     <mergeCell ref="A4:AK4"/>
+    <mergeCell ref="A38:AK38"/>
+    <mergeCell ref="AJ48:AK48"/>
     <mergeCell ref="A40:AK40"/>
-    <mergeCell ref="A3:AK3"/>
+    <mergeCell ref="A9:AK9"/>
     <mergeCell ref="A39:AK39"/>
-    <mergeCell ref="A7:AK7"/>
-    <mergeCell ref="A38:AK38"/>
-    <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="A41:AK41"/>
-    <mergeCell ref="A42:AK42"/>
+    <mergeCell ref="AJ53:AK53"/>
+    <mergeCell ref="AJ49:AK49"/>
     <mergeCell ref="A36:AK36"/>
     <mergeCell ref="A1:AK1"/>
+    <mergeCell ref="AJ45:AK45"/>
+    <mergeCell ref="A6:AK6"/>
+    <mergeCell ref="A7:AK7"/>
+    <mergeCell ref="A41:AK41"/>
+    <mergeCell ref="AJ44:AK44"/>
     <mergeCell ref="A37:AK37"/>
-    <mergeCell ref="A9:AK9"/>
-    <mergeCell ref="A8:AK8"/>
-    <mergeCell ref="A6:AK6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -30,12 +30,30 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDFECE"/>
+        <bgColor rgb="FFCDFECE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFE9F"/>
+        <bgColor rgb="FFFFFE9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFD9BCB"/>
+        <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -153,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,7 +191,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,11 +209,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -745,7 +778,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:CAÑAR</t>
+          <t>CIUDAD:tambo</t>
         </is>
       </c>
     </row>
@@ -759,7 +792,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -901,76 +934,76 @@
       <c r="B11" s="6" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>70.81</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <v>71.16</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>71.81</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>71.39</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>70.94</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>70.87</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>70.81</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="7" t="n">
         <v>70.62</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="K11" s="7" t="n">
         <v>70.94</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="7" t="n">
         <v>70.63</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="N11" s="7" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="O11" s="7" t="n">
         <v>71.27</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="P11" s="7" t="n">
         <v>70.76000000000001</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="Q11" s="7" t="n">
         <v>70.81</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="R11" s="7" t="n">
         <v>70.2</v>
       </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="7" t="n">
         <v>70.42</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="T11" s="7" t="n">
         <v>70.84999999999999</v>
       </c>
-      <c r="U11" s="6" t="n">
+      <c r="U11" s="7" t="n">
         <v>70.55</v>
       </c>
-      <c r="V11" s="6" t="n">
+      <c r="V11" s="7" t="n">
         <v>70.27</v>
       </c>
-      <c r="W11" s="6" t="n">
+      <c r="W11" s="7" t="n">
         <v>70.75</v>
       </c>
-      <c r="X11" s="6" t="n">
+      <c r="X11" s="7" t="n">
         <v>70.22</v>
       </c>
-      <c r="Y11" s="6" t="n">
+      <c r="Y11" s="7" t="n">
         <v>70.5</v>
       </c>
-      <c r="Z11" s="6" t="n">
+      <c r="Z11" s="7" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="AA11" s="6" t="inlineStr">
@@ -988,16 +1021,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD11" s="6" t="n">
+      <c r="AD11" s="7" t="n">
         <v>70.68000000000001</v>
       </c>
-      <c r="AE11" s="6" t="n">
+      <c r="AE11" s="7" t="n">
         <v>70.78</v>
       </c>
-      <c r="AF11" s="6" t="n">
+      <c r="AF11" s="7" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="AG11" s="6" t="n">
+      <c r="AG11" s="7" t="n">
         <v>71.11</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1007,7 +1040,7 @@
         <v>339.89</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="7" t="inlineStr"/>
+      <c r="AK11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1018,76 +1051,76 @@
       <c r="B12" s="6" t="n">
         <v>89.3</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>93.28</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <v>94.11</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <v>93.97</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>93.48999999999999</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>93.52</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>93.55</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>92.95999999999999</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="7" t="n">
         <v>93.36</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K12" s="7" t="n">
         <v>93.75</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="L12" s="7" t="n">
         <v>93.52</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="M12" s="7" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="N12" s="7" t="n">
         <v>94.01000000000001</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="O12" s="7" t="n">
         <v>93.66</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="P12" s="7" t="n">
         <v>93.38</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="Q12" s="7" t="n">
         <v>92.72</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="R12" s="7" t="n">
         <v>92.98</v>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="S12" s="7" t="n">
         <v>93.42</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="T12" s="7" t="n">
         <v>93.75</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="U12" s="7" t="n">
         <v>93.36</v>
       </c>
-      <c r="V12" s="6" t="n">
+      <c r="V12" s="7" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="W12" s="6" t="n">
+      <c r="W12" s="7" t="n">
         <v>93.09</v>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="X12" s="7" t="n">
         <v>93.06999999999999</v>
       </c>
-      <c r="Y12" s="6" t="n">
+      <c r="Y12" s="7" t="n">
         <v>92.84</v>
       </c>
-      <c r="Z12" s="6" t="n">
+      <c r="Z12" s="7" t="n">
         <v>93.28</v>
       </c>
       <c r="AA12" s="6" t="inlineStr">
@@ -1105,16 +1138,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD12" s="6" t="n">
+      <c r="AD12" s="7" t="n">
         <v>92.72</v>
       </c>
-      <c r="AE12" s="6" t="n">
+      <c r="AE12" s="7" t="n">
         <v>92.87</v>
       </c>
-      <c r="AF12" s="6" t="n">
+      <c r="AF12" s="7" t="n">
         <v>93.08</v>
       </c>
-      <c r="AG12" s="6" t="n">
+      <c r="AG12" s="7" t="n">
         <v>93.13</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1124,7 +1157,7 @@
         <v>215.38</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="7" t="inlineStr"/>
+      <c r="AK12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1135,76 +1168,76 @@
       <c r="B13" s="6" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>75.98</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <v>74.91</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>78.88</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>75.26000000000001</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>74.39</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>73.68000000000001</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="7" t="n">
         <v>74.56999999999999</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="K13" s="7" t="n">
         <v>74.68000000000001</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="7" t="n">
         <v>74.41</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="M13" s="7" t="n">
         <v>74.92</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="N13" s="7" t="n">
         <v>74.76000000000001</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="O13" s="7" t="n">
         <v>74.81999999999999</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="P13" s="7" t="n">
         <v>73.83</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="Q13" s="7" t="n">
         <v>74.08</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="R13" s="7" t="n">
         <v>72.84999999999999</v>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="S13" s="7" t="n">
         <v>74.43000000000001</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="T13" s="7" t="n">
         <v>74.48</v>
       </c>
-      <c r="U13" s="6" t="n">
+      <c r="U13" s="7" t="n">
         <v>74.27</v>
       </c>
-      <c r="V13" s="6" t="n">
+      <c r="V13" s="7" t="n">
         <v>74.08</v>
       </c>
-      <c r="W13" s="6" t="n">
+      <c r="W13" s="7" t="n">
         <v>73.83</v>
       </c>
-      <c r="X13" s="6" t="n">
+      <c r="X13" s="7" t="n">
         <v>74.39</v>
       </c>
-      <c r="Y13" s="6" t="n">
+      <c r="Y13" s="7" t="n">
         <v>74.2</v>
       </c>
-      <c r="Z13" s="6" t="n">
+      <c r="Z13" s="7" t="n">
         <v>73.31999999999999</v>
       </c>
       <c r="AA13" s="6" t="inlineStr">
@@ -1222,16 +1255,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD13" s="6" t="n">
+      <c r="AD13" s="7" t="n">
         <v>74.47</v>
       </c>
-      <c r="AE13" s="6" t="n">
+      <c r="AE13" s="7" t="n">
         <v>73.42</v>
       </c>
-      <c r="AF13" s="6" t="n">
+      <c r="AF13" s="7" t="n">
         <v>72.95999999999999</v>
       </c>
-      <c r="AG13" s="6" t="n">
+      <c r="AG13" s="7" t="n">
         <v>73.36</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1241,7 +1274,7 @@
         <v>381.82</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="7" t="inlineStr"/>
+      <c r="AK13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1252,76 +1285,76 @@
       <c r="B14" s="6" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>96.93000000000001</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <v>97.09</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>96.54000000000001</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>97.12</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>97.09</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>97.7</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>97.28</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="7" t="n">
         <v>97.02</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K14" s="7" t="n">
         <v>97.08</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="7" t="n">
         <v>96.45</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>96.55</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="N14" s="7" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="O14" s="6" t="n">
+      <c r="O14" s="7" t="n">
         <v>97.84999999999999</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="P14" s="7" t="n">
         <v>97.26000000000001</v>
       </c>
-      <c r="Q14" s="6" t="n">
+      <c r="Q14" s="7" t="n">
         <v>97.52</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="R14" s="7" t="n">
         <v>96.83</v>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>95.88</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="T14" s="7" t="n">
         <v>96.89</v>
       </c>
-      <c r="U14" s="6" t="n">
+      <c r="U14" s="7" t="n">
         <v>96.91</v>
       </c>
-      <c r="V14" s="6" t="n">
+      <c r="V14" s="7" t="n">
         <v>96.95</v>
       </c>
-      <c r="W14" s="6" t="n">
+      <c r="W14" s="7" t="n">
         <v>97.84</v>
       </c>
-      <c r="X14" s="6" t="n">
+      <c r="X14" s="7" t="n">
         <v>96.5</v>
       </c>
-      <c r="Y14" s="6" t="n">
+      <c r="Y14" s="7" t="n">
         <v>96.29000000000001</v>
       </c>
-      <c r="Z14" s="6" t="n">
+      <c r="Z14" s="7" t="n">
         <v>97.41</v>
       </c>
       <c r="AA14" s="6" t="inlineStr">
@@ -1339,16 +1372,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD14" s="6" t="n">
+      <c r="AD14" s="7" t="n">
         <v>97.31999999999999</v>
       </c>
-      <c r="AE14" s="6" t="n">
+      <c r="AE14" s="7" t="n">
         <v>96.86</v>
       </c>
-      <c r="AF14" s="6" t="n">
+      <c r="AF14" s="7" t="n">
         <v>97.02</v>
       </c>
-      <c r="AG14" s="6" t="n">
+      <c r="AG14" s="7" t="n">
         <v>96.36</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1358,7 +1391,7 @@
         <v>394.82</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="7" t="inlineStr"/>
+      <c r="AK14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1369,76 +1402,76 @@
       <c r="B15" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="9" t="n">
         <v>51.91</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="9" t="n">
         <v>51.91</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="9" t="n">
         <v>53.71</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>53.19</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>52.31</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>52.02</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>51.63</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="9" t="n">
         <v>51.38</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L15" s="9" t="n">
         <v>52.85</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>52.05</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="N15" s="9" t="n">
         <v>51.7</v>
       </c>
-      <c r="O15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>51.64</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="P15" s="9" t="n">
         <v>51.52</v>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>51.34</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="R15" s="9" t="n">
         <v>51.23</v>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>51.05</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="T15" s="9" t="n">
         <v>51.93</v>
       </c>
-      <c r="U15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>51.36</v>
       </c>
-      <c r="V15" s="6" t="n">
+      <c r="V15" s="9" t="n">
         <v>51.27</v>
       </c>
-      <c r="W15" s="6" t="n">
+      <c r="W15" s="9" t="n">
         <v>51.31</v>
       </c>
-      <c r="X15" s="6" t="n">
+      <c r="X15" s="9" t="n">
         <v>51.83</v>
       </c>
-      <c r="Y15" s="6" t="n">
+      <c r="Y15" s="9" t="n">
         <v>51.24</v>
       </c>
-      <c r="Z15" s="6" t="n">
+      <c r="Z15" s="9" t="n">
         <v>52.94</v>
       </c>
       <c r="AA15" s="6" t="inlineStr">
@@ -1456,16 +1489,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD15" s="6" t="n">
+      <c r="AD15" s="9" t="n">
         <v>51.04</v>
       </c>
-      <c r="AE15" s="6" t="n">
+      <c r="AE15" s="9" t="n">
         <v>50.71</v>
       </c>
-      <c r="AF15" s="6" t="n">
+      <c r="AF15" s="9" t="n">
         <v>50.56</v>
       </c>
-      <c r="AG15" s="6" t="n">
+      <c r="AG15" s="9" t="n">
         <v>51.09</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1475,7 +1508,7 @@
         <v>489.28</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="7" t="inlineStr"/>
+      <c r="AK15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1486,76 +1519,76 @@
       <c r="B16" s="6" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="7" t="n">
         <v>87.31</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="7" t="n">
         <v>87.98999999999999</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>88.61</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>88.18000000000001</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>87.95999999999999</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>87.73</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>87.54000000000001</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="7" t="n">
         <v>88.2</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K16" s="7" t="n">
         <v>89.23</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L16" s="7" t="n">
         <v>89.13</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M16" s="7" t="n">
         <v>89.14</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="N16" s="7" t="n">
         <v>89.18000000000001</v>
       </c>
-      <c r="O16" s="6" t="n">
+      <c r="O16" s="7" t="n">
         <v>88.27</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="P16" s="7" t="n">
         <v>88.66</v>
       </c>
-      <c r="Q16" s="6" t="n">
+      <c r="Q16" s="7" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="R16" s="7" t="n">
         <v>87.81999999999999</v>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <v>88.15000000000001</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="T16" s="7" t="n">
         <v>88.48</v>
       </c>
-      <c r="U16" s="6" t="n">
+      <c r="U16" s="7" t="n">
         <v>87.94</v>
       </c>
-      <c r="V16" s="6" t="n">
+      <c r="V16" s="7" t="n">
         <v>87.94</v>
       </c>
-      <c r="W16" s="6" t="n">
+      <c r="W16" s="7" t="n">
         <v>88.13</v>
       </c>
-      <c r="X16" s="6" t="n">
+      <c r="X16" s="7" t="n">
         <v>88.29000000000001</v>
       </c>
-      <c r="Y16" s="6" t="n">
+      <c r="Y16" s="7" t="n">
         <v>88.23</v>
       </c>
-      <c r="Z16" s="6" t="n">
+      <c r="Z16" s="7" t="n">
         <v>87.55</v>
       </c>
       <c r="AA16" s="6" t="inlineStr">
@@ -1573,16 +1606,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD16" s="6" t="n">
+      <c r="AD16" s="7" t="n">
         <v>88.03</v>
       </c>
-      <c r="AE16" s="6" t="n">
+      <c r="AE16" s="7" t="n">
         <v>88.34</v>
       </c>
-      <c r="AF16" s="6" t="n">
+      <c r="AF16" s="7" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="AG16" s="6" t="n">
+      <c r="AG16" s="7" t="n">
         <v>87.69</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1592,7 +1625,7 @@
         <v>214.98</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="7" t="inlineStr"/>
+      <c r="AK16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1603,76 +1636,76 @@
       <c r="B17" s="6" t="n">
         <v>92.5</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="7" t="n">
         <v>83.66</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="7" t="n">
         <v>82.89</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>79.54000000000001</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <v>78.98999999999999</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>78.14</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>77.03</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="7" t="n">
         <v>78.29000000000001</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K17" s="7" t="n">
         <v>78.98</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L17" s="7" t="n">
         <v>78.91</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M17" s="7" t="n">
         <v>79.91</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="7" t="n">
         <v>79.66</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="O17" s="7" t="n">
         <v>78.11</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="P17" s="7" t="n">
         <v>78.31</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="Q17" s="7" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="R17" s="7" t="n">
         <v>77.95</v>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <v>79.06</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="T17" s="7" t="n">
         <v>79.84</v>
       </c>
-      <c r="U17" s="6" t="n">
+      <c r="U17" s="7" t="n">
         <v>78.34</v>
       </c>
-      <c r="V17" s="6" t="n">
+      <c r="V17" s="7" t="n">
         <v>79.08</v>
       </c>
-      <c r="W17" s="6" t="n">
+      <c r="W17" s="7" t="n">
         <v>79.27</v>
       </c>
-      <c r="X17" s="6" t="n">
+      <c r="X17" s="7" t="n">
         <v>78.29000000000001</v>
       </c>
-      <c r="Y17" s="6" t="n">
+      <c r="Y17" s="7" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="Z17" s="6" t="n">
+      <c r="Z17" s="7" t="n">
         <v>77.91</v>
       </c>
       <c r="AA17" s="6" t="inlineStr">
@@ -1690,16 +1723,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD17" s="6" t="n">
+      <c r="AD17" s="7" t="n">
         <v>78.19</v>
       </c>
-      <c r="AE17" s="6" t="n">
+      <c r="AE17" s="7" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="AF17" s="6" t="n">
+      <c r="AF17" s="7" t="n">
         <v>77.29000000000001</v>
       </c>
-      <c r="AG17" s="6" t="n">
+      <c r="AG17" s="7" t="n">
         <v>77.31</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1709,7 +1742,7 @@
         <v>362.77</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="7" t="inlineStr"/>
+      <c r="AK17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1720,76 +1753,76 @@
       <c r="B18" s="6" t="n">
         <v>93.3</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="7" t="n">
         <v>87.48999999999999</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <v>89.48</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <v>82.76000000000001</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>82.14</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>83.81999999999999</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="7" t="n">
         <v>82.84999999999999</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="7" t="n">
         <v>82.92</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="7" t="n">
         <v>82.92</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="L18" s="7" t="n">
         <v>83.93000000000001</v>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="M18" s="7" t="n">
         <v>81.26000000000001</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="N18" s="7" t="n">
         <v>79.93000000000001</v>
       </c>
-      <c r="O18" s="6" t="n">
+      <c r="O18" s="7" t="n">
         <v>77.94</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="P18" s="7" t="n">
         <v>77.83</v>
       </c>
-      <c r="Q18" s="6" t="n">
+      <c r="Q18" s="7" t="n">
         <v>77.65000000000001</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="R18" s="7" t="n">
         <v>76.88</v>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="7" t="n">
         <v>79.18000000000001</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="T18" s="7" t="n">
         <v>81.59</v>
       </c>
-      <c r="U18" s="6" t="n">
+      <c r="U18" s="7" t="n">
         <v>77.73999999999999</v>
       </c>
-      <c r="V18" s="6" t="n">
+      <c r="V18" s="7" t="n">
         <v>78.68000000000001</v>
       </c>
-      <c r="W18" s="6" t="n">
+      <c r="W18" s="7" t="n">
         <v>77.12</v>
       </c>
-      <c r="X18" s="6" t="n">
+      <c r="X18" s="7" t="n">
         <v>78.59</v>
       </c>
-      <c r="Y18" s="6" t="n">
+      <c r="Y18" s="7" t="n">
         <v>78.06999999999999</v>
       </c>
-      <c r="Z18" s="6" t="n">
+      <c r="Z18" s="7" t="n">
         <v>83.88</v>
       </c>
       <c r="AA18" s="6" t="inlineStr">
@@ -1807,16 +1840,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD18" s="6" t="n">
+      <c r="AD18" s="7" t="n">
         <v>84.56</v>
       </c>
-      <c r="AE18" s="6" t="n">
+      <c r="AE18" s="7" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="AF18" s="6" t="n">
+      <c r="AF18" s="7" t="n">
         <v>83.16</v>
       </c>
-      <c r="AG18" s="6" t="n">
+      <c r="AG18" s="7" t="n">
         <v>84.08</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -1826,7 +1859,7 @@
         <v>219.91</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="7" t="inlineStr"/>
+      <c r="AK18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1837,76 +1870,76 @@
       <c r="B19" s="6" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>63.41</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <v>60.13</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>59.7</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>57.16</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>56.34</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>57.07</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="7" t="n">
         <v>57.27</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="7" t="n">
         <v>56.95</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="K19" s="7" t="n">
         <v>55.98</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="7" t="n">
         <v>54.59</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="M19" s="7" t="n">
         <v>58.17</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="N19" s="7" t="n">
         <v>57.62</v>
       </c>
-      <c r="O19" s="6" t="n">
+      <c r="O19" s="7" t="n">
         <v>56.08</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="P19" s="7" t="n">
         <v>55.72</v>
       </c>
-      <c r="Q19" s="6" t="n">
+      <c r="Q19" s="7" t="n">
         <v>54.92</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="R19" s="7" t="n">
         <v>54.94</v>
       </c>
-      <c r="S19" s="6" t="n">
+      <c r="S19" s="7" t="n">
         <v>59.31</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="T19" s="7" t="n">
         <v>57.59</v>
       </c>
-      <c r="U19" s="6" t="n">
+      <c r="U19" s="7" t="n">
         <v>56.86</v>
       </c>
-      <c r="V19" s="6" t="n">
+      <c r="V19" s="7" t="n">
         <v>57.49</v>
       </c>
-      <c r="W19" s="6" t="n">
+      <c r="W19" s="7" t="n">
         <v>55.42</v>
       </c>
-      <c r="X19" s="6" t="n">
+      <c r="X19" s="7" t="n">
         <v>56.76</v>
       </c>
-      <c r="Y19" s="6" t="n">
+      <c r="Y19" s="7" t="n">
         <v>56.06</v>
       </c>
-      <c r="Z19" s="6" t="n">
+      <c r="Z19" s="9" t="n">
         <v>53.79</v>
       </c>
       <c r="AA19" s="6" t="inlineStr">
@@ -1924,16 +1957,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD19" s="6" t="n">
+      <c r="AD19" s="9" t="n">
         <v>52.48</v>
       </c>
-      <c r="AE19" s="6" t="n">
+      <c r="AE19" s="7" t="n">
         <v>54.38</v>
       </c>
-      <c r="AF19" s="6" t="n">
+      <c r="AF19" s="7" t="n">
         <v>55.62</v>
       </c>
-      <c r="AG19" s="6" t="n">
+      <c r="AG19" s="7" t="n">
         <v>55.96</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -1943,7 +1976,7 @@
         <v>489.91</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="7" t="inlineStr"/>
+      <c r="AK19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1954,76 +1987,76 @@
       <c r="B20" s="6" t="n">
         <v>94.5</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="7" t="n">
         <v>87.55</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="7" t="n">
         <v>87.76000000000001</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>87.17</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>87.51000000000001</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>87.17</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>87.18000000000001</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="7" t="n">
         <v>87.56999999999999</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="K20" s="7" t="n">
         <v>87.29000000000001</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="L20" s="7" t="n">
         <v>87.41</v>
       </c>
-      <c r="M20" s="6" t="n">
+      <c r="M20" s="7" t="n">
         <v>87.76000000000001</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="N20" s="7" t="n">
         <v>87.13</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="O20" s="7" t="n">
         <v>87.53</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="P20" s="7" t="n">
         <v>87.48999999999999</v>
       </c>
-      <c r="Q20" s="6" t="n">
+      <c r="Q20" s="7" t="n">
         <v>87.55</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="R20" s="7" t="n">
         <v>87.04000000000001</v>
       </c>
-      <c r="S20" s="6" t="n">
+      <c r="S20" s="7" t="n">
         <v>87.28</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="T20" s="7" t="n">
         <v>87.66</v>
       </c>
-      <c r="U20" s="6" t="n">
+      <c r="U20" s="7" t="n">
         <v>87.26000000000001</v>
       </c>
-      <c r="V20" s="6" t="n">
+      <c r="V20" s="7" t="n">
         <v>87.17</v>
       </c>
-      <c r="W20" s="6" t="n">
+      <c r="W20" s="7" t="n">
         <v>88.13</v>
       </c>
-      <c r="X20" s="6" t="n">
+      <c r="X20" s="7" t="n">
         <v>86.91</v>
       </c>
-      <c r="Y20" s="6" t="n">
+      <c r="Y20" s="7" t="n">
         <v>87.19</v>
       </c>
-      <c r="Z20" s="6" t="n">
+      <c r="Z20" s="7" t="n">
         <v>87.05</v>
       </c>
       <c r="AA20" s="6" t="inlineStr">
@@ -2041,16 +2074,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD20" s="6" t="n">
+      <c r="AD20" s="7" t="n">
         <v>87.63</v>
       </c>
-      <c r="AE20" s="6" t="n">
+      <c r="AE20" s="7" t="n">
         <v>87.11</v>
       </c>
-      <c r="AF20" s="6" t="n">
+      <c r="AF20" s="7" t="n">
         <v>87.04000000000001</v>
       </c>
-      <c r="AG20" s="6" t="n">
+      <c r="AG20" s="7" t="n">
         <v>87.14</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2060,7 +2093,7 @@
         <v>196.8</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="7" t="inlineStr"/>
+      <c r="AK20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2071,76 +2104,76 @@
       <c r="B21" s="6" t="n">
         <v>95.3</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <v>94.76000000000001</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>94.06999999999999</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>94.17</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>94.72</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>94.16</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <v>94.15000000000001</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <v>94.31</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <v>94.03</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="L21" s="7" t="n">
         <v>93.81</v>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="M21" s="7" t="n">
         <v>93.7</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="N21" s="7" t="n">
         <v>94.93000000000001</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="O21" s="7" t="n">
         <v>94.28</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="P21" s="7" t="n">
         <v>94.02</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="Q21" s="7" t="n">
         <v>94.45</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="R21" s="7" t="n">
         <v>93.68000000000001</v>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <v>94.22</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="T21" s="7" t="n">
         <v>94.33</v>
       </c>
-      <c r="U21" s="6" t="n">
+      <c r="U21" s="7" t="n">
         <v>94.87</v>
       </c>
-      <c r="V21" s="6" t="n">
+      <c r="V21" s="7" t="n">
         <v>94.43000000000001</v>
       </c>
-      <c r="W21" s="6" t="n">
+      <c r="W21" s="7" t="n">
         <v>94.41</v>
       </c>
-      <c r="X21" s="6" t="n">
+      <c r="X21" s="7" t="n">
         <v>93.66</v>
       </c>
-      <c r="Y21" s="6" t="n">
+      <c r="Y21" s="7" t="n">
         <v>94.48</v>
       </c>
-      <c r="Z21" s="6" t="n">
+      <c r="Z21" s="7" t="n">
         <v>94.44</v>
       </c>
       <c r="AA21" s="6" t="inlineStr">
@@ -2158,16 +2191,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD21" s="6" t="n">
+      <c r="AD21" s="7" t="n">
         <v>94.86</v>
       </c>
-      <c r="AE21" s="6" t="n">
+      <c r="AE21" s="7" t="n">
         <v>93.95999999999999</v>
       </c>
-      <c r="AF21" s="6" t="n">
+      <c r="AF21" s="7" t="n">
         <v>93.87</v>
       </c>
-      <c r="AG21" s="6" t="n">
+      <c r="AG21" s="7" t="n">
         <v>94.06999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2177,7 +2210,7 @@
         <v>230.95</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="7" t="inlineStr"/>
+      <c r="AK21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2188,76 +2221,76 @@
       <c r="B22" s="6" t="n">
         <v>95.7</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>79.19</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="7" t="n">
         <v>78.02</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="7" t="n">
         <v>78.19</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>77.61</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>78.34</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <v>77.91</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <v>77.88</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K22" s="7" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="L22" s="7" t="n">
         <v>78.09</v>
       </c>
-      <c r="M22" s="6" t="n">
+      <c r="M22" s="7" t="n">
         <v>76.56</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="N22" s="7" t="n">
         <v>78.29000000000001</v>
       </c>
-      <c r="O22" s="6" t="n">
+      <c r="O22" s="7" t="n">
         <v>78.41</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="P22" s="7" t="n">
         <v>76.47</v>
       </c>
-      <c r="Q22" s="6" t="n">
+      <c r="Q22" s="7" t="n">
         <v>75.29000000000001</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="R22" s="7" t="n">
         <v>76.73999999999999</v>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="S22" s="7" t="n">
         <v>77.23</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="T22" s="7" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="U22" s="6" t="n">
+      <c r="U22" s="7" t="n">
         <v>78.76000000000001</v>
       </c>
-      <c r="V22" s="6" t="n">
+      <c r="V22" s="7" t="n">
         <v>78.73</v>
       </c>
-      <c r="W22" s="6" t="n">
+      <c r="W22" s="7" t="n">
         <v>77.31999999999999</v>
       </c>
-      <c r="X22" s="6" t="n">
+      <c r="X22" s="7" t="n">
         <v>77.84999999999999</v>
       </c>
-      <c r="Y22" s="6" t="n">
+      <c r="Y22" s="7" t="n">
         <v>76.91</v>
       </c>
-      <c r="Z22" s="6" t="n">
+      <c r="Z22" s="7" t="n">
         <v>77.48999999999999</v>
       </c>
       <c r="AA22" s="6" t="inlineStr">
@@ -2275,16 +2308,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD22" s="6" t="n">
+      <c r="AD22" s="7" t="n">
         <v>76.88</v>
       </c>
-      <c r="AE22" s="6" t="n">
+      <c r="AE22" s="7" t="n">
         <v>76.61</v>
       </c>
-      <c r="AF22" s="6" t="n">
+      <c r="AF22" s="7" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="AG22" s="6" t="n">
+      <c r="AG22" s="7" t="n">
         <v>76.23</v>
       </c>
       <c r="AH22" s="6" t="n">
@@ -2294,7 +2327,7 @@
         <v>436.64</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="7" t="inlineStr"/>
+      <c r="AK22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2305,76 +2338,76 @@
       <c r="B23" s="6" t="n">
         <v>97.3</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="7" t="n">
         <v>70.97</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="7" t="n">
         <v>71.63</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>70.72</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F23" s="7" t="n">
         <v>72.53</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <v>70.94</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H23" s="7" t="n">
         <v>71.58</v>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="7" t="n">
         <v>70.19</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="J23" s="7" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="K23" s="6" t="n">
+      <c r="K23" s="7" t="n">
         <v>71.48999999999999</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="L23" s="7" t="n">
         <v>72.37</v>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M23" s="7" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="N23" s="7" t="n">
         <v>69.26000000000001</v>
       </c>
-      <c r="O23" s="6" t="n">
+      <c r="O23" s="7" t="n">
         <v>69.84</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="P23" s="7" t="n">
         <v>70.48</v>
       </c>
-      <c r="Q23" s="6" t="n">
+      <c r="Q23" s="7" t="n">
         <v>69.34999999999999</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="R23" s="7" t="n">
         <v>69.12</v>
       </c>
-      <c r="S23" s="6" t="n">
+      <c r="S23" s="7" t="n">
         <v>68.91</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="T23" s="7" t="n">
         <v>71.76000000000001</v>
       </c>
-      <c r="U23" s="6" t="n">
+      <c r="U23" s="7" t="n">
         <v>71.72</v>
       </c>
-      <c r="V23" s="6" t="n">
+      <c r="V23" s="7" t="n">
         <v>73.87</v>
       </c>
-      <c r="W23" s="6" t="n">
+      <c r="W23" s="7" t="n">
         <v>72.70999999999999</v>
       </c>
-      <c r="X23" s="6" t="n">
+      <c r="X23" s="7" t="n">
         <v>69.89</v>
       </c>
-      <c r="Y23" s="6" t="n">
+      <c r="Y23" s="7" t="n">
         <v>72.15000000000001</v>
       </c>
-      <c r="Z23" s="6" t="n">
+      <c r="Z23" s="7" t="n">
         <v>69.72</v>
       </c>
       <c r="AA23" s="6" t="inlineStr">
@@ -2392,16 +2425,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD23" s="6" t="n">
+      <c r="AD23" s="7" t="n">
         <v>75.16</v>
       </c>
-      <c r="AE23" s="6" t="n">
+      <c r="AE23" s="7" t="n">
         <v>77.33</v>
       </c>
-      <c r="AF23" s="6" t="n">
+      <c r="AF23" s="7" t="n">
         <v>76.20999999999999</v>
       </c>
-      <c r="AG23" s="6" t="n">
+      <c r="AG23" s="7" t="n">
         <v>84.45</v>
       </c>
       <c r="AH23" s="6" t="n">
@@ -2411,7 +2444,7 @@
         <v>257.14</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="7" t="inlineStr"/>
+      <c r="AK23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2422,76 +2455,76 @@
       <c r="B24" s="6" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="7" t="n">
         <v>82.16</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="7" t="n">
         <v>82.04000000000001</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>82</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="7" t="n">
         <v>83.72</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <v>81.56</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="7" t="n">
         <v>82.06999999999999</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="7" t="n">
         <v>81.31999999999999</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="7" t="n">
         <v>81.45999999999999</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="K24" s="7" t="n">
         <v>82.41</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="L24" s="7" t="n">
         <v>82.11</v>
       </c>
-      <c r="M24" s="6" t="n">
+      <c r="M24" s="7" t="n">
         <v>81.54000000000001</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="N24" s="7" t="n">
         <v>81.65000000000001</v>
       </c>
-      <c r="O24" s="6" t="n">
+      <c r="O24" s="7" t="n">
         <v>81.03</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="P24" s="7" t="n">
         <v>79.18000000000001</v>
       </c>
-      <c r="Q24" s="6" t="n">
+      <c r="Q24" s="7" t="n">
         <v>80.03</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="R24" s="7" t="n">
         <v>80.20999999999999</v>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="S24" s="7" t="n">
         <v>80.44</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="T24" s="7" t="n">
         <v>82.08</v>
       </c>
-      <c r="U24" s="6" t="n">
+      <c r="U24" s="7" t="n">
         <v>80.15000000000001</v>
       </c>
-      <c r="V24" s="6" t="n">
+      <c r="V24" s="7" t="n">
         <v>80.55</v>
       </c>
-      <c r="W24" s="6" t="n">
+      <c r="W24" s="7" t="n">
         <v>79.08</v>
       </c>
-      <c r="X24" s="6" t="n">
+      <c r="X24" s="7" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="Y24" s="6" t="n">
+      <c r="Y24" s="7" t="n">
         <v>81.37</v>
       </c>
-      <c r="Z24" s="6" t="n">
+      <c r="Z24" s="7" t="n">
         <v>80.8</v>
       </c>
       <c r="AA24" s="6" t="inlineStr">
@@ -2509,16 +2542,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD24" s="6" t="n">
+      <c r="AD24" s="7" t="n">
         <v>80.97</v>
       </c>
-      <c r="AE24" s="6" t="n">
+      <c r="AE24" s="7" t="n">
         <v>80.06</v>
       </c>
-      <c r="AF24" s="6" t="n">
+      <c r="AF24" s="7" t="n">
         <v>80.63</v>
       </c>
-      <c r="AG24" s="6" t="n">
+      <c r="AG24" s="7" t="n">
         <v>81.16</v>
       </c>
       <c r="AH24" s="6" t="n">
@@ -2528,7 +2561,7 @@
         <v>197.27</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="7" t="inlineStr"/>
+      <c r="AK24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2539,76 +2572,76 @@
       <c r="B25" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="9" t="n">
         <v>46.88</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="9" t="n">
         <v>46.81</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="9" t="n">
         <v>45.97</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>47.78</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>48.08</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>47.05</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>46.67</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="9" t="n">
         <v>47.12</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>46.84</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="L25" s="9" t="n">
         <v>46.88</v>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>46.33</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="N25" s="9" t="n">
         <v>49.66</v>
       </c>
-      <c r="O25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>48.7</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="P25" s="9" t="n">
         <v>49.31</v>
       </c>
-      <c r="Q25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>47.73</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="R25" s="9" t="n">
         <v>49.23</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>47.98</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="T25" s="9" t="n">
         <v>46.88</v>
       </c>
-      <c r="U25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>45.82</v>
       </c>
-      <c r="V25" s="6" t="n">
+      <c r="V25" s="9" t="n">
         <v>46.52</v>
       </c>
-      <c r="W25" s="6" t="n">
+      <c r="W25" s="9" t="n">
         <v>47.44</v>
       </c>
-      <c r="X25" s="6" t="n">
+      <c r="X25" s="9" t="n">
         <v>46.51</v>
       </c>
-      <c r="Y25" s="6" t="n">
+      <c r="Y25" s="9" t="n">
         <v>46.15</v>
       </c>
-      <c r="Z25" s="6" t="n">
+      <c r="Z25" s="9" t="n">
         <v>45.64</v>
       </c>
       <c r="AA25" s="6" t="inlineStr">
@@ -2626,16 +2659,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD25" s="6" t="n">
+      <c r="AD25" s="9" t="n">
         <v>44.54</v>
       </c>
-      <c r="AE25" s="6" t="n">
+      <c r="AE25" s="9" t="n">
         <v>46.63</v>
       </c>
-      <c r="AF25" s="6" t="n">
+      <c r="AF25" s="9" t="n">
         <v>46.59</v>
       </c>
-      <c r="AG25" s="6" t="n">
+      <c r="AG25" s="9" t="n">
         <v>47.18</v>
       </c>
       <c r="AH25" s="6" t="n">
@@ -2645,7 +2678,7 @@
         <v>490</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="7" t="inlineStr"/>
+      <c r="AK25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2656,76 +2689,76 @@
       <c r="B26" s="6" t="n">
         <v>99.3</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="7" t="n">
         <v>91.44</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="7" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>90.98999999999999</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>92.53</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <v>90.17</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>92.02</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="7" t="n">
         <v>89.87</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="K26" s="7" t="n">
         <v>91.92</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="L26" s="7" t="n">
         <v>91.45</v>
       </c>
-      <c r="M26" s="6" t="n">
+      <c r="M26" s="7" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="N26" s="7" t="n">
         <v>90.67</v>
       </c>
-      <c r="O26" s="6" t="n">
+      <c r="O26" s="7" t="n">
         <v>82.06999999999999</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="P26" s="7" t="n">
         <v>89.36</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="Q26" s="7" t="n">
         <v>89.47</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="R26" s="7" t="n">
         <v>89.79000000000001</v>
       </c>
-      <c r="S26" s="6" t="n">
+      <c r="S26" s="7" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="T26" s="7" t="n">
         <v>91.59</v>
       </c>
-      <c r="U26" s="6" t="n">
+      <c r="U26" s="7" t="n">
         <v>91.81</v>
       </c>
-      <c r="V26" s="6" t="n">
+      <c r="V26" s="7" t="n">
         <v>90.04000000000001</v>
       </c>
-      <c r="W26" s="6" t="n">
+      <c r="W26" s="7" t="n">
         <v>87.87</v>
       </c>
-      <c r="X26" s="6" t="n">
+      <c r="X26" s="7" t="n">
         <v>91.38</v>
       </c>
-      <c r="Y26" s="6" t="n">
+      <c r="Y26" s="7" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="Z26" s="6" t="n">
+      <c r="Z26" s="7" t="n">
         <v>91.66</v>
       </c>
       <c r="AA26" s="6" t="inlineStr">
@@ -2743,16 +2776,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD26" s="6" t="n">
+      <c r="AD26" s="7" t="n">
         <v>89.04000000000001</v>
       </c>
-      <c r="AE26" s="6" t="n">
+      <c r="AE26" s="7" t="n">
         <v>90.68000000000001</v>
       </c>
-      <c r="AF26" s="6" t="n">
+      <c r="AF26" s="7" t="n">
         <v>89.98</v>
       </c>
-      <c r="AG26" s="6" t="n">
+      <c r="AG26" s="7" t="n">
         <v>91.37</v>
       </c>
       <c r="AH26" s="6" t="n">
@@ -2762,7 +2795,7 @@
         <v>371.19</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="7" t="inlineStr"/>
+      <c r="AK26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2773,76 +2806,76 @@
       <c r="B27" s="6" t="n">
         <v>99.7</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="7" t="n">
         <v>88.66</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="7" t="n">
         <v>89.05</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>88.14</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <v>88.63</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="7" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="7" t="n">
         <v>88.69</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="7" t="n">
         <v>88.92</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="K27" s="7" t="n">
         <v>90.20999999999999</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="L27" s="7" t="n">
         <v>89.76000000000001</v>
       </c>
-      <c r="M27" s="6" t="n">
+      <c r="M27" s="7" t="n">
         <v>89.08</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="N27" s="7" t="n">
         <v>89.7</v>
       </c>
-      <c r="O27" s="6" t="n">
+      <c r="O27" s="7" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="P27" s="7" t="n">
         <v>88.95999999999999</v>
       </c>
-      <c r="Q27" s="6" t="n">
+      <c r="Q27" s="7" t="n">
         <v>89.70999999999999</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="R27" s="7" t="n">
         <v>89.22</v>
       </c>
-      <c r="S27" s="6" t="n">
+      <c r="S27" s="7" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="T27" s="7" t="n">
         <v>90.02</v>
       </c>
-      <c r="U27" s="6" t="n">
+      <c r="U27" s="7" t="n">
         <v>90.06</v>
       </c>
-      <c r="V27" s="6" t="n">
+      <c r="V27" s="7" t="n">
         <v>89.88</v>
       </c>
-      <c r="W27" s="6" t="n">
+      <c r="W27" s="7" t="n">
         <v>89.81</v>
       </c>
-      <c r="X27" s="6" t="n">
+      <c r="X27" s="7" t="n">
         <v>89.81999999999999</v>
       </c>
-      <c r="Y27" s="6" t="n">
+      <c r="Y27" s="7" t="n">
         <v>89.81</v>
       </c>
-      <c r="Z27" s="6" t="n">
+      <c r="Z27" s="7" t="n">
         <v>89.56</v>
       </c>
       <c r="AA27" s="6" t="inlineStr">
@@ -2860,16 +2893,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD27" s="6" t="n">
+      <c r="AD27" s="7" t="n">
         <v>90.26000000000001</v>
       </c>
-      <c r="AE27" s="6" t="n">
+      <c r="AE27" s="7" t="n">
         <v>89.19</v>
       </c>
-      <c r="AF27" s="6" t="n">
+      <c r="AF27" s="7" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="AG27" s="6" t="n">
+      <c r="AG27" s="7" t="n">
         <v>89.41</v>
       </c>
       <c r="AH27" s="6" t="n">
@@ -2879,7 +2912,7 @@
         <v>315.07</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="7" t="inlineStr"/>
+      <c r="AK27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2890,76 +2923,76 @@
       <c r="B28" s="6" t="n">
         <v>101.7</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="7" t="n">
         <v>95.06999999999999</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="7" t="n">
         <v>95.45</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>95.17</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="7" t="n">
         <v>96.01000000000001</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="7" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="7" t="n">
         <v>95.89</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="7" t="n">
         <v>95.45999999999999</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J28" s="7" t="n">
         <v>95.34</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="K28" s="7" t="n">
         <v>95.73999999999999</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="L28" s="7" t="n">
         <v>95.16</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="M28" s="7" t="n">
         <v>93.95999999999999</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N28" s="7" t="n">
         <v>94.33</v>
       </c>
-      <c r="O28" s="6" t="n">
+      <c r="O28" s="7" t="n">
         <v>94.28</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="P28" s="7" t="n">
         <v>93.86</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q28" s="7" t="n">
         <v>93.70999999999999</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="R28" s="7" t="n">
         <v>93.66</v>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="S28" s="7" t="n">
         <v>93.48</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="T28" s="7" t="n">
         <v>92.98999999999999</v>
       </c>
-      <c r="U28" s="6" t="n">
+      <c r="U28" s="7" t="n">
         <v>93.19</v>
       </c>
-      <c r="V28" s="6" t="n">
+      <c r="V28" s="7" t="n">
         <v>93.31999999999999</v>
       </c>
-      <c r="W28" s="6" t="n">
+      <c r="W28" s="7" t="n">
         <v>93.22</v>
       </c>
-      <c r="X28" s="6" t="n">
+      <c r="X28" s="7" t="n">
         <v>92.98</v>
       </c>
-      <c r="Y28" s="6" t="n">
+      <c r="Y28" s="7" t="n">
         <v>93.08</v>
       </c>
-      <c r="Z28" s="6" t="n">
+      <c r="Z28" s="7" t="n">
         <v>92.95999999999999</v>
       </c>
       <c r="AA28" s="6" t="inlineStr">
@@ -2977,16 +3010,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD28" s="6" t="n">
+      <c r="AD28" s="7" t="n">
         <v>88.22</v>
       </c>
-      <c r="AE28" s="6" t="n">
+      <c r="AE28" s="7" t="n">
         <v>94.93000000000001</v>
       </c>
-      <c r="AF28" s="6" t="n">
+      <c r="AF28" s="7" t="n">
         <v>95.78</v>
       </c>
-      <c r="AG28" s="6" t="n">
+      <c r="AG28" s="7" t="n">
         <v>95.53</v>
       </c>
       <c r="AH28" s="6" t="n">
@@ -2996,7 +3029,7 @@
         <v>244.12</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="7" t="inlineStr"/>
+      <c r="AK28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3007,76 +3040,76 @@
       <c r="B29" s="6" t="n">
         <v>105.7</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C29" s="9" t="n">
         <v>44.26</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="9" t="n">
         <v>43.4</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="E29" s="10" t="n">
         <v>42.87</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>43.78</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>45.04</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>43.91</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>44.14</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="10" t="n">
         <v>42.84</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>44.14</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="L29" s="9" t="n">
         <v>43.75</v>
       </c>
-      <c r="M29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>48.48</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="N29" s="9" t="n">
         <v>47.18</v>
       </c>
-      <c r="O29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>44.35</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="P29" s="9" t="n">
         <v>45.84</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>46.76</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="R29" s="9" t="n">
         <v>47.58</v>
       </c>
-      <c r="S29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>45.74</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="T29" s="10" t="n">
         <v>42.89</v>
       </c>
-      <c r="U29" s="6" t="n">
+      <c r="U29" s="10" t="n">
         <v>41.15</v>
       </c>
-      <c r="V29" s="6" t="n">
+      <c r="V29" s="10" t="n">
         <v>42.51</v>
       </c>
-      <c r="W29" s="6" t="n">
+      <c r="W29" s="9" t="n">
         <v>43.88</v>
       </c>
-      <c r="X29" s="6" t="n">
+      <c r="X29" s="9" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y29" s="6" t="n">
+      <c r="Y29" s="10" t="n">
         <v>42.28</v>
       </c>
-      <c r="Z29" s="6" t="n">
+      <c r="Z29" s="9" t="n">
         <v>44.64</v>
       </c>
       <c r="AA29" s="6" t="inlineStr">
@@ -3094,16 +3127,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD29" s="6" t="n">
+      <c r="AD29" s="10" t="n">
         <v>41.87</v>
       </c>
-      <c r="AE29" s="6" t="n">
+      <c r="AE29" s="10" t="n">
         <v>42.42</v>
       </c>
-      <c r="AF29" s="6" t="n">
+      <c r="AF29" s="10" t="n">
         <v>41.86</v>
       </c>
-      <c r="AG29" s="6" t="n">
+      <c r="AG29" s="9" t="n">
         <v>43.46</v>
       </c>
       <c r="AH29" s="6" t="n">
@@ -3113,7 +3146,7 @@
         <v>483.6</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="7" t="inlineStr"/>
+      <c r="AK29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3124,76 +3157,76 @@
       <c r="B30" s="6" t="n">
         <v>106.1</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="7" t="n">
         <v>93.23</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <v>93.48999999999999</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="7" t="n">
         <v>93.69</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="7" t="n">
         <v>93.81</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>93.94</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="H30" s="7" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="7" t="n">
         <v>93.86</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="7" t="n">
         <v>93.83</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="K30" s="7" t="n">
         <v>93.98999999999999</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="L30" s="7" t="n">
         <v>93.70999999999999</v>
       </c>
-      <c r="M30" s="6" t="n">
+      <c r="M30" s="7" t="n">
         <v>93.76000000000001</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="N30" s="7" t="n">
         <v>93.42</v>
       </c>
-      <c r="O30" s="6" t="n">
+      <c r="O30" s="7" t="n">
         <v>93.77</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="P30" s="7" t="n">
         <v>94.01000000000001</v>
       </c>
-      <c r="Q30" s="6" t="n">
+      <c r="Q30" s="7" t="n">
         <v>93.72</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="R30" s="7" t="n">
         <v>93.48</v>
       </c>
-      <c r="S30" s="6" t="n">
+      <c r="S30" s="7" t="n">
         <v>93.78</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="T30" s="7" t="n">
         <v>93.89</v>
       </c>
-      <c r="U30" s="6" t="n">
+      <c r="U30" s="7" t="n">
         <v>94.01000000000001</v>
       </c>
-      <c r="V30" s="6" t="n">
+      <c r="V30" s="7" t="n">
         <v>93.81999999999999</v>
       </c>
-      <c r="W30" s="6" t="n">
+      <c r="W30" s="7" t="n">
         <v>94.14</v>
       </c>
-      <c r="X30" s="6" t="n">
+      <c r="X30" s="7" t="n">
         <v>93.48999999999999</v>
       </c>
-      <c r="Y30" s="6" t="n">
+      <c r="Y30" s="7" t="n">
         <v>93.56</v>
       </c>
-      <c r="Z30" s="6" t="n">
+      <c r="Z30" s="7" t="n">
         <v>93.34999999999999</v>
       </c>
       <c r="AA30" s="6" t="inlineStr">
@@ -3211,16 +3244,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD30" s="6" t="n">
+      <c r="AD30" s="7" t="n">
         <v>93.14</v>
       </c>
-      <c r="AE30" s="6" t="n">
+      <c r="AE30" s="7" t="n">
         <v>93.41</v>
       </c>
-      <c r="AF30" s="6" t="n">
+      <c r="AF30" s="7" t="n">
         <v>93.56999999999999</v>
       </c>
-      <c r="AG30" s="6" t="n">
+      <c r="AG30" s="7" t="n">
         <v>93.66</v>
       </c>
       <c r="AH30" s="6" t="n">
@@ -3230,7 +3263,7 @@
         <v>165.25</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="7" t="inlineStr"/>
+      <c r="AK30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3241,76 +3274,76 @@
       <c r="B31" s="6" t="n">
         <v>106.9</v>
       </c>
-      <c r="C31" s="6" t="n">
+      <c r="C31" s="7" t="n">
         <v>95.87</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="7" t="n">
         <v>92.8</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>89.73</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>95.20999999999999</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="G31" s="7" t="n">
         <v>91.89</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="H31" s="7" t="n">
         <v>91.70999999999999</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="7" t="n">
         <v>92.11</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="7" t="n">
         <v>91.36</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="K31" s="7" t="n">
         <v>91.63</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="L31" s="7" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="M31" s="6" t="n">
+      <c r="M31" s="7" t="n">
         <v>91.55</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="N31" s="7" t="n">
         <v>92.47</v>
       </c>
-      <c r="O31" s="6" t="n">
+      <c r="O31" s="7" t="n">
         <v>92.87</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="P31" s="7" t="n">
         <v>92.89</v>
       </c>
-      <c r="Q31" s="6" t="n">
+      <c r="Q31" s="7" t="n">
         <v>92.98</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="R31" s="7" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="S31" s="6" t="n">
+      <c r="S31" s="7" t="n">
         <v>92.94</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="T31" s="7" t="n">
         <v>95.68000000000001</v>
       </c>
-      <c r="U31" s="6" t="n">
+      <c r="U31" s="7" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="V31" s="6" t="n">
+      <c r="V31" s="7" t="n">
         <v>92.45999999999999</v>
       </c>
-      <c r="W31" s="6" t="n">
+      <c r="W31" s="7" t="n">
         <v>92.95</v>
       </c>
-      <c r="X31" s="6" t="n">
+      <c r="X31" s="7" t="n">
         <v>92.76000000000001</v>
       </c>
-      <c r="Y31" s="6" t="n">
+      <c r="Y31" s="7" t="n">
         <v>92.53</v>
       </c>
-      <c r="Z31" s="6" t="n">
+      <c r="Z31" s="7" t="n">
         <v>95.41</v>
       </c>
       <c r="AA31" s="6" t="inlineStr">
@@ -3328,16 +3361,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD31" s="6" t="n">
+      <c r="AD31" s="7" t="n">
         <v>95.22</v>
       </c>
-      <c r="AE31" s="6" t="n">
+      <c r="AE31" s="7" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="AF31" s="6" t="n">
+      <c r="AF31" s="7" t="n">
         <v>92.39</v>
       </c>
-      <c r="AG31" s="6" t="n">
+      <c r="AG31" s="7" t="n">
         <v>92.54000000000001</v>
       </c>
       <c r="AH31" s="6" t="n">
@@ -3347,7 +3380,7 @@
         <v>243.85</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="7" t="inlineStr"/>
+      <c r="AK31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3358,76 +3391,76 @@
       <c r="B32" s="6" t="n">
         <v>107.3</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="7" t="n">
         <v>89.27</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="7" t="n">
         <v>88.7</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>88.43000000000001</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="7" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="7" t="n">
         <v>89.02</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="7" t="n">
         <v>68.03</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="9" t="n">
         <v>46.18</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="K32" s="7" t="n">
         <v>88.91</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="L32" s="7" t="n">
         <v>88.97</v>
       </c>
-      <c r="M32" s="6" t="n">
+      <c r="M32" s="7" t="n">
         <v>88.75</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="N32" s="7" t="n">
         <v>88.88</v>
       </c>
-      <c r="O32" s="6" t="n">
+      <c r="O32" s="7" t="n">
         <v>89.19</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="P32" s="7" t="n">
         <v>89.51000000000001</v>
       </c>
-      <c r="Q32" s="6" t="n">
+      <c r="Q32" s="7" t="n">
         <v>89.79000000000001</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="R32" s="7" t="n">
         <v>89.64</v>
       </c>
-      <c r="S32" s="6" t="n">
+      <c r="S32" s="7" t="n">
         <v>89.63</v>
       </c>
-      <c r="T32" s="6" t="n">
+      <c r="T32" s="7" t="n">
         <v>89.18000000000001</v>
       </c>
-      <c r="U32" s="6" t="n">
+      <c r="U32" s="7" t="n">
         <v>89.20999999999999</v>
       </c>
-      <c r="V32" s="6" t="n">
+      <c r="V32" s="7" t="n">
         <v>89.44</v>
       </c>
-      <c r="W32" s="6" t="n">
+      <c r="W32" s="7" t="n">
         <v>90.08</v>
       </c>
-      <c r="X32" s="6" t="n">
+      <c r="X32" s="7" t="n">
         <v>89.84999999999999</v>
       </c>
-      <c r="Y32" s="6" t="n">
+      <c r="Y32" s="7" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="Z32" s="6" t="n">
+      <c r="Z32" s="7" t="n">
         <v>89.25</v>
       </c>
       <c r="AA32" s="6" t="inlineStr">
@@ -3445,16 +3478,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD32" s="6" t="n">
+      <c r="AD32" s="7" t="n">
         <v>89.64</v>
       </c>
-      <c r="AE32" s="6" t="n">
+      <c r="AE32" s="7" t="n">
         <v>89.58</v>
       </c>
-      <c r="AF32" s="6" t="n">
+      <c r="AF32" s="7" t="n">
         <v>90.16</v>
       </c>
-      <c r="AG32" s="6" t="n">
+      <c r="AG32" s="7" t="n">
         <v>89.7</v>
       </c>
       <c r="AH32" s="6" t="n">
@@ -3464,124 +3497,124 @@
         <v>332.07</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="7" t="inlineStr"/>
+      <c r="AK32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>RADIO CAÑARI</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n">
+      <c r="B33" s="12" t="n">
         <v>107.7</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="13" t="n">
         <v>92.8</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="13" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="13" t="n">
         <v>91.36</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="13" t="n">
         <v>91.81</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="13" t="n">
         <v>92.20999999999999</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="13" t="n">
         <v>92.84999999999999</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="13" t="n">
         <v>92.97</v>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" s="13" t="n">
         <v>92.06</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="13" t="n">
         <v>92.05</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="13" t="n">
         <v>91.97</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="13" t="n">
         <v>91.98</v>
       </c>
-      <c r="N33" s="9" t="n">
+      <c r="N33" s="13" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="O33" s="13" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="P33" s="9" t="n">
+      <c r="P33" s="13" t="n">
         <v>92.14</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="13" t="n">
         <v>92.78</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="13" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="S33" s="9" t="n">
+      <c r="S33" s="13" t="n">
         <v>92.78</v>
       </c>
-      <c r="T33" s="9" t="n">
+      <c r="T33" s="13" t="n">
         <v>92.92</v>
       </c>
-      <c r="U33" s="9" t="n">
+      <c r="U33" s="13" t="n">
         <v>91.84</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="13" t="n">
         <v>92.84</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="13" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" s="13" t="n">
         <v>92.89</v>
       </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Y33" s="13" t="n">
         <v>92.36</v>
       </c>
-      <c r="Z33" s="9" t="n">
+      <c r="Z33" s="13" t="n">
         <v>93.11</v>
       </c>
-      <c r="AA33" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB33" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC33" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD33" s="9" t="n">
+      <c r="AA33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="13" t="n">
         <v>93.01000000000001</v>
       </c>
-      <c r="AE33" s="9" t="n">
+      <c r="AE33" s="13" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="AF33" s="9" t="n">
+      <c r="AF33" s="13" t="n">
         <v>92.98</v>
       </c>
-      <c r="AG33" s="9" t="n">
+      <c r="AG33" s="13" t="n">
         <v>93.02</v>
       </c>
-      <c r="AH33" s="9" t="n">
+      <c r="AH33" s="12" t="n">
         <v>92.45</v>
       </c>
-      <c r="AI33" s="9" t="n">
+      <c r="AI33" s="12" t="n">
         <v>269.05</v>
       </c>
-      <c r="AJ33" s="9" t="inlineStr"/>
-      <c r="AK33" s="10" t="inlineStr"/>
+      <c r="AJ33" s="12" t="inlineStr"/>
+      <c r="AK33" s="14" t="inlineStr"/>
     </row>
     <row r="34"/>
     <row r="35"/>
@@ -3616,7 +3649,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:CAÑAR</t>
+          <t>CIUDAD:tambo</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3663,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3789,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK43" s="11" t="n"/>
+      <c r="AK43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3767,76 +3800,76 @@
       <c r="B44" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C44" s="6" t="n">
+      <c r="C44" s="7" t="n">
         <v>54.45</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="7" t="n">
         <v>54.48</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="E44" s="7" t="n">
         <v>57.77</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F44" s="7" t="n">
         <v>54.82</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="G44" s="7" t="n">
         <v>55.26</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="H44" s="7" t="n">
         <v>56.32</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I44" s="7" t="n">
         <v>56.04</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="7" t="n">
         <v>55.54</v>
       </c>
-      <c r="K44" s="6" t="n">
+      <c r="K44" s="7" t="n">
         <v>56.45</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="L44" s="7" t="n">
         <v>56.89</v>
       </c>
-      <c r="M44" s="6" t="n">
+      <c r="M44" s="7" t="n">
         <v>56.92</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="N44" s="7" t="n">
         <v>57.59</v>
       </c>
-      <c r="O44" s="6" t="n">
+      <c r="O44" s="7" t="n">
         <v>57.66</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="P44" s="7" t="n">
         <v>55.07</v>
       </c>
-      <c r="Q44" s="6" t="n">
+      <c r="Q44" s="7" t="n">
         <v>54.17</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="R44" s="7" t="n">
         <v>56.31</v>
       </c>
-      <c r="S44" s="6" t="n">
+      <c r="S44" s="7" t="n">
         <v>55.18</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="T44" s="7" t="n">
         <v>56.62</v>
       </c>
-      <c r="U44" s="6" t="n">
+      <c r="U44" s="7" t="n">
         <v>55.28</v>
       </c>
-      <c r="V44" s="6" t="n">
+      <c r="V44" s="7" t="n">
         <v>54.73</v>
       </c>
-      <c r="W44" s="6" t="n">
+      <c r="W44" s="7" t="n">
         <v>55.07</v>
       </c>
-      <c r="X44" s="6" t="n">
+      <c r="X44" s="7" t="n">
         <v>54.94</v>
       </c>
-      <c r="Y44" s="6" t="n">
+      <c r="Y44" s="7" t="n">
         <v>57.08</v>
       </c>
-      <c r="Z44" s="6" t="n">
+      <c r="Z44" s="7" t="n">
         <v>54.75</v>
       </c>
       <c r="AA44" s="6" t="inlineStr">
@@ -3854,16 +3887,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD44" s="6" t="n">
+      <c r="AD44" s="9" t="n">
         <v>52.19</v>
       </c>
-      <c r="AE44" s="6" t="n">
+      <c r="AE44" s="7" t="n">
         <v>54.52</v>
       </c>
-      <c r="AF44" s="6" t="n">
+      <c r="AF44" s="7" t="n">
         <v>54.88</v>
       </c>
-      <c r="AG44" s="6" t="n">
+      <c r="AG44" s="7" t="n">
         <v>54.43</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -3871,7 +3904,7 @@
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="12" t="n"/>
+      <c r="AK44" s="16" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3882,76 +3915,76 @@
       <c r="B45" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C45" s="6" t="n">
+      <c r="C45" s="7" t="n">
         <v>62.47</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="7" t="n">
         <v>60.99</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="E45" s="7" t="n">
         <v>59.32</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="F45" s="7" t="n">
         <v>61.95</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="G45" s="7" t="n">
         <v>61.42</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="H45" s="7" t="n">
         <v>61.35</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" s="7" t="n">
         <v>60.77</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="7" t="n">
         <v>60.27</v>
       </c>
-      <c r="K45" s="6" t="n">
+      <c r="K45" s="7" t="n">
         <v>59.26</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="L45" s="7" t="n">
         <v>59.13</v>
       </c>
-      <c r="M45" s="6" t="n">
+      <c r="M45" s="7" t="n">
         <v>59.08</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="N45" s="7" t="n">
         <v>57.83</v>
       </c>
-      <c r="O45" s="6" t="n">
+      <c r="O45" s="7" t="n">
         <v>58.15</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="P45" s="7" t="n">
         <v>62.37</v>
       </c>
-      <c r="Q45" s="6" t="n">
+      <c r="Q45" s="7" t="n">
         <v>62.44</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="R45" s="7" t="n">
         <v>59.07</v>
       </c>
-      <c r="S45" s="6" t="n">
+      <c r="S45" s="7" t="n">
         <v>61.21</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="T45" s="7" t="n">
         <v>58.95</v>
       </c>
-      <c r="U45" s="6" t="n">
+      <c r="U45" s="7" t="n">
         <v>61.47</v>
       </c>
-      <c r="V45" s="6" t="n">
+      <c r="V45" s="7" t="n">
         <v>62.25</v>
       </c>
-      <c r="W45" s="6" t="n">
+      <c r="W45" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="X45" s="6" t="n">
+      <c r="X45" s="7" t="n">
         <v>62.32</v>
       </c>
-      <c r="Y45" s="6" t="n">
+      <c r="Y45" s="7" t="n">
         <v>60.83</v>
       </c>
-      <c r="Z45" s="6" t="n">
+      <c r="Z45" s="7" t="n">
         <v>62.26</v>
       </c>
       <c r="AA45" s="6" t="inlineStr">
@@ -3969,16 +4002,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD45" s="6" t="n">
+      <c r="AD45" s="7" t="n">
         <v>62.62</v>
       </c>
-      <c r="AE45" s="6" t="n">
+      <c r="AE45" s="7" t="n">
         <v>62.34</v>
       </c>
-      <c r="AF45" s="6" t="n">
+      <c r="AF45" s="7" t="n">
         <v>62.65</v>
       </c>
-      <c r="AG45" s="6" t="n">
+      <c r="AG45" s="7" t="n">
         <v>63.19</v>
       </c>
       <c r="AH45" s="6" t="n">
@@ -3986,7 +4019,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="12" t="n"/>
+      <c r="AK45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -3997,76 +4030,76 @@
       <c r="B46" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C46" s="6" t="n">
+      <c r="C46" s="10" t="n">
         <v>30.76</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="10" t="n">
         <v>31.32</v>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="E46" s="10" t="n">
         <v>32.11</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="F46" s="10" t="n">
         <v>30.86</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="G46" s="10" t="n">
         <v>28.58</v>
       </c>
-      <c r="H46" s="6" t="n">
+      <c r="H46" s="10" t="n">
         <v>29.81</v>
       </c>
-      <c r="I46" s="6" t="n">
+      <c r="I46" s="10" t="n">
         <v>27.63</v>
       </c>
-      <c r="J46" s="6" t="n">
+      <c r="J46" s="10" t="n">
         <v>31.39</v>
       </c>
-      <c r="K46" s="6" t="n">
+      <c r="K46" s="10" t="n">
         <v>31.98</v>
       </c>
-      <c r="L46" s="6" t="n">
+      <c r="L46" s="10" t="n">
         <v>31.91</v>
       </c>
-      <c r="M46" s="6" t="n">
+      <c r="M46" s="10" t="n">
         <v>33.47</v>
       </c>
-      <c r="N46" s="6" t="n">
+      <c r="N46" s="10" t="n">
         <v>31.81</v>
       </c>
-      <c r="O46" s="6" t="n">
+      <c r="O46" s="10" t="n">
         <v>28.62</v>
       </c>
-      <c r="P46" s="6" t="n">
+      <c r="P46" s="10" t="n">
         <v>24.98</v>
       </c>
-      <c r="Q46" s="6" t="n">
+      <c r="Q46" s="10" t="n">
         <v>27.11</v>
       </c>
-      <c r="R46" s="6" t="n">
+      <c r="R46" s="10" t="n">
         <v>27.55</v>
       </c>
-      <c r="S46" s="6" t="n">
+      <c r="S46" s="10" t="n">
         <v>29.39</v>
       </c>
-      <c r="T46" s="6" t="n">
+      <c r="T46" s="10" t="n">
         <v>30.03</v>
       </c>
-      <c r="U46" s="6" t="n">
+      <c r="U46" s="10" t="n">
         <v>29.37</v>
       </c>
-      <c r="V46" s="6" t="n">
+      <c r="V46" s="10" t="n">
         <v>27.43</v>
       </c>
-      <c r="W46" s="6" t="n">
+      <c r="W46" s="10" t="n">
         <v>24.95</v>
       </c>
-      <c r="X46" s="6" t="n">
+      <c r="X46" s="10" t="n">
         <v>28.58</v>
       </c>
-      <c r="Y46" s="6" t="n">
+      <c r="Y46" s="10" t="n">
         <v>30.77</v>
       </c>
-      <c r="Z46" s="6" t="n">
+      <c r="Z46" s="10" t="n">
         <v>28.12</v>
       </c>
       <c r="AA46" s="6" t="inlineStr">
@@ -4084,16 +4117,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD46" s="6" t="n">
+      <c r="AD46" s="10" t="n">
         <v>27.18</v>
       </c>
-      <c r="AE46" s="6" t="n">
+      <c r="AE46" s="10" t="n">
         <v>27.85</v>
       </c>
-      <c r="AF46" s="6" t="n">
+      <c r="AF46" s="10" t="n">
         <v>26.6</v>
       </c>
-      <c r="AG46" s="6" t="n">
+      <c r="AG46" s="10" t="n">
         <v>26.24</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4101,7 +4134,7 @@
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="12" t="n"/>
+      <c r="AK46" s="16" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4112,76 +4145,76 @@
       <c r="B47" s="6" t="n">
         <v>193.25</v>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="C47" s="9" t="n">
         <v>46.3</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="9" t="n">
         <v>46.33</v>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="E47" s="9" t="n">
         <v>46.39</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="F47" s="9" t="n">
         <v>47.05</v>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="G47" s="9" t="n">
         <v>47.51</v>
       </c>
-      <c r="H47" s="6" t="n">
+      <c r="H47" s="9" t="n">
         <v>48.13</v>
       </c>
-      <c r="I47" s="6" t="n">
+      <c r="I47" s="9" t="n">
         <v>46.25</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="J47" s="9" t="n">
         <v>47.56</v>
       </c>
-      <c r="K47" s="6" t="n">
+      <c r="K47" s="9" t="n">
         <v>49.26</v>
       </c>
-      <c r="L47" s="6" t="n">
+      <c r="L47" s="9" t="n">
         <v>47.54</v>
       </c>
-      <c r="M47" s="6" t="n">
+      <c r="M47" s="9" t="n">
         <v>48.23</v>
       </c>
-      <c r="N47" s="6" t="n">
+      <c r="N47" s="9" t="n">
         <v>46.86</v>
       </c>
-      <c r="O47" s="6" t="n">
+      <c r="O47" s="9" t="n">
         <v>45.58</v>
       </c>
-      <c r="P47" s="6" t="n">
+      <c r="P47" s="9" t="n">
         <v>45.14</v>
       </c>
-      <c r="Q47" s="6" t="n">
+      <c r="Q47" s="9" t="n">
         <v>46.13</v>
       </c>
-      <c r="R47" s="6" t="n">
+      <c r="R47" s="9" t="n">
         <v>46.38</v>
       </c>
-      <c r="S47" s="6" t="n">
+      <c r="S47" s="9" t="n">
         <v>46.3</v>
       </c>
-      <c r="T47" s="6" t="n">
+      <c r="T47" s="9" t="n">
         <v>49.68</v>
       </c>
-      <c r="U47" s="6" t="n">
+      <c r="U47" s="9" t="n">
         <v>49.32</v>
       </c>
-      <c r="V47" s="6" t="n">
+      <c r="V47" s="9" t="n">
         <v>47.83</v>
       </c>
-      <c r="W47" s="6" t="n">
+      <c r="W47" s="9" t="n">
         <v>45.16</v>
       </c>
-      <c r="X47" s="6" t="n">
+      <c r="X47" s="9" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y47" s="6" t="n">
+      <c r="Y47" s="9" t="n">
         <v>48.44</v>
       </c>
-      <c r="Z47" s="6" t="n">
+      <c r="Z47" s="9" t="n">
         <v>46.78</v>
       </c>
       <c r="AA47" s="6" t="inlineStr">
@@ -4199,16 +4232,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD47" s="6" t="n">
+      <c r="AD47" s="9" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE47" s="6" t="n">
+      <c r="AE47" s="9" t="n">
         <v>47.77</v>
       </c>
-      <c r="AF47" s="6" t="n">
+      <c r="AF47" s="9" t="n">
         <v>47.22</v>
       </c>
-      <c r="AG47" s="6" t="n">
+      <c r="AG47" s="9" t="n">
         <v>47.83</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -4216,7 +4249,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="12" t="n"/>
+      <c r="AK47" s="16" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4227,76 +4260,76 @@
       <c r="B48" s="6" t="n">
         <v>205.25</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C48" s="10" t="n">
         <v>20.25</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="10" t="n">
         <v>19.44</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E48" s="10" t="n">
         <v>18.66</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F48" s="10" t="n">
         <v>21.06</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G48" s="10" t="n">
         <v>19.93</v>
       </c>
-      <c r="H48" s="6" t="n">
+      <c r="H48" s="10" t="n">
         <v>20.95</v>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I48" s="10" t="n">
         <v>21.35</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" s="10" t="n">
         <v>19.73</v>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="K48" s="10" t="n">
         <v>20.03</v>
       </c>
-      <c r="L48" s="6" t="n">
+      <c r="L48" s="10" t="n">
         <v>19.83</v>
       </c>
-      <c r="M48" s="6" t="n">
+      <c r="M48" s="10" t="n">
         <v>19.34</v>
       </c>
-      <c r="N48" s="6" t="n">
+      <c r="N48" s="10" t="n">
         <v>20.03</v>
       </c>
-      <c r="O48" s="6" t="n">
+      <c r="O48" s="10" t="n">
         <v>20.25</v>
       </c>
-      <c r="P48" s="6" t="n">
+      <c r="P48" s="10" t="n">
         <v>19.31</v>
       </c>
-      <c r="Q48" s="6" t="n">
+      <c r="Q48" s="10" t="n">
         <v>21.73</v>
       </c>
-      <c r="R48" s="6" t="n">
+      <c r="R48" s="10" t="n">
         <v>21.23</v>
       </c>
-      <c r="S48" s="6" t="n">
+      <c r="S48" s="10" t="n">
         <v>19.64</v>
       </c>
-      <c r="T48" s="6" t="n">
+      <c r="T48" s="10" t="n">
         <v>20.19</v>
       </c>
-      <c r="U48" s="6" t="n">
+      <c r="U48" s="10" t="n">
         <v>20.4</v>
       </c>
-      <c r="V48" s="6" t="n">
+      <c r="V48" s="10" t="n">
         <v>20.01</v>
       </c>
-      <c r="W48" s="6" t="n">
+      <c r="W48" s="10" t="n">
         <v>20.09</v>
       </c>
-      <c r="X48" s="6" t="n">
+      <c r="X48" s="10" t="n">
         <v>19.82</v>
       </c>
-      <c r="Y48" s="6" t="n">
+      <c r="Y48" s="10" t="n">
         <v>20.22</v>
       </c>
-      <c r="Z48" s="6" t="n">
+      <c r="Z48" s="10" t="n">
         <v>20.75</v>
       </c>
       <c r="AA48" s="6" t="inlineStr">
@@ -4314,16 +4347,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD48" s="6" t="n">
+      <c r="AD48" s="10" t="n">
         <v>20.72</v>
       </c>
-      <c r="AE48" s="6" t="n">
+      <c r="AE48" s="10" t="n">
         <v>19.91</v>
       </c>
-      <c r="AF48" s="6" t="n">
+      <c r="AF48" s="10" t="n">
         <v>20.74</v>
       </c>
-      <c r="AG48" s="6" t="n">
+      <c r="AG48" s="10" t="n">
         <v>20.32</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -4331,7 +4364,7 @@
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="12" t="n"/>
+      <c r="AK48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4342,76 +4375,76 @@
       <c r="B49" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="C49" s="10" t="n">
         <v>17.22</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="10" t="n">
         <v>17.16</v>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="E49" s="10" t="n">
         <v>16.48</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="F49" s="10" t="n">
         <v>20.09</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="G49" s="10" t="n">
         <v>17.15</v>
       </c>
-      <c r="H49" s="6" t="n">
+      <c r="H49" s="10" t="n">
         <v>16.65</v>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" s="10" t="n">
         <v>17.38</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" s="10" t="n">
         <v>17.17</v>
       </c>
-      <c r="K49" s="6" t="n">
+      <c r="K49" s="10" t="n">
         <v>16.77</v>
       </c>
-      <c r="L49" s="6" t="n">
+      <c r="L49" s="10" t="n">
         <v>16.8</v>
       </c>
-      <c r="M49" s="6" t="n">
+      <c r="M49" s="10" t="n">
         <v>16.85</v>
       </c>
-      <c r="N49" s="6" t="n">
+      <c r="N49" s="10" t="n">
         <v>16.67</v>
       </c>
-      <c r="O49" s="6" t="n">
+      <c r="O49" s="10" t="n">
         <v>16.78</v>
       </c>
-      <c r="P49" s="6" t="n">
+      <c r="P49" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="Q49" s="6" t="n">
+      <c r="Q49" s="10" t="n">
         <v>16.78</v>
       </c>
-      <c r="R49" s="6" t="n">
+      <c r="R49" s="10" t="n">
         <v>16.69</v>
       </c>
-      <c r="S49" s="6" t="n">
+      <c r="S49" s="10" t="n">
         <v>17.09</v>
       </c>
-      <c r="T49" s="6" t="n">
+      <c r="T49" s="10" t="n">
         <v>16.92</v>
       </c>
-      <c r="U49" s="6" t="n">
+      <c r="U49" s="10" t="n">
         <v>16.91</v>
       </c>
-      <c r="V49" s="6" t="n">
+      <c r="V49" s="10" t="n">
         <v>17.3</v>
       </c>
-      <c r="W49" s="6" t="n">
+      <c r="W49" s="10" t="n">
         <v>17.05</v>
       </c>
-      <c r="X49" s="6" t="n">
+      <c r="X49" s="10" t="n">
         <v>16.87</v>
       </c>
-      <c r="Y49" s="6" t="n">
+      <c r="Y49" s="10" t="n">
         <v>16.7</v>
       </c>
-      <c r="Z49" s="6" t="n">
+      <c r="Z49" s="10" t="n">
         <v>16.9</v>
       </c>
       <c r="AA49" s="6" t="inlineStr">
@@ -4429,16 +4462,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD49" s="6" t="n">
+      <c r="AD49" s="10" t="n">
         <v>16.85</v>
       </c>
-      <c r="AE49" s="6" t="n">
+      <c r="AE49" s="10" t="n">
         <v>16.5</v>
       </c>
-      <c r="AF49" s="6" t="n">
+      <c r="AF49" s="10" t="n">
         <v>16.61</v>
       </c>
-      <c r="AG49" s="6" t="n">
+      <c r="AG49" s="10" t="n">
         <v>16.54</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -4446,7 +4479,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="12" t="n"/>
+      <c r="AK49" s="16" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4457,76 +4490,76 @@
       <c r="B50" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C50" s="7" t="n">
         <v>64.31999999999999</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="7" t="n">
         <v>65.59</v>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="E50" s="7" t="n">
         <v>65.7</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="10" t="n">
         <v>29.7</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="G50" s="10" t="n">
         <v>31.15</v>
       </c>
-      <c r="H50" s="6" t="n">
+      <c r="H50" s="10" t="n">
         <v>30.96</v>
       </c>
-      <c r="I50" s="6" t="n">
+      <c r="I50" s="10" t="n">
         <v>30.68</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" s="10" t="n">
         <v>30.74</v>
       </c>
-      <c r="K50" s="6" t="n">
+      <c r="K50" s="10" t="n">
         <v>30.38</v>
       </c>
-      <c r="L50" s="6" t="n">
+      <c r="L50" s="10" t="n">
         <v>30.17</v>
       </c>
-      <c r="M50" s="6" t="n">
+      <c r="M50" s="10" t="n">
         <v>30.75</v>
       </c>
-      <c r="N50" s="6" t="n">
+      <c r="N50" s="10" t="n">
         <v>29.89</v>
       </c>
-      <c r="O50" s="6" t="n">
+      <c r="O50" s="10" t="n">
         <v>30.15</v>
       </c>
-      <c r="P50" s="6" t="n">
+      <c r="P50" s="10" t="n">
         <v>31.64</v>
       </c>
-      <c r="Q50" s="6" t="n">
+      <c r="Q50" s="10" t="n">
         <v>30.28</v>
       </c>
-      <c r="R50" s="6" t="n">
+      <c r="R50" s="10" t="n">
         <v>31.09</v>
       </c>
-      <c r="S50" s="6" t="n">
+      <c r="S50" s="10" t="n">
         <v>30.65</v>
       </c>
-      <c r="T50" s="6" t="n">
+      <c r="T50" s="10" t="n">
         <v>32.47</v>
       </c>
-      <c r="U50" s="6" t="n">
+      <c r="U50" s="10" t="n">
         <v>31.51</v>
       </c>
-      <c r="V50" s="6" t="n">
+      <c r="V50" s="10" t="n">
         <v>30.9</v>
       </c>
-      <c r="W50" s="6" t="n">
+      <c r="W50" s="10" t="n">
         <v>32.99</v>
       </c>
-      <c r="X50" s="6" t="n">
+      <c r="X50" s="10" t="n">
         <v>27.85</v>
       </c>
-      <c r="Y50" s="6" t="n">
+      <c r="Y50" s="10" t="n">
         <v>28.3</v>
       </c>
-      <c r="Z50" s="6" t="n">
+      <c r="Z50" s="10" t="n">
         <v>28.28</v>
       </c>
       <c r="AA50" s="6" t="inlineStr">
@@ -4544,16 +4577,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD50" s="6" t="n">
+      <c r="AD50" s="10" t="n">
         <v>28.19</v>
       </c>
-      <c r="AE50" s="6" t="n">
+      <c r="AE50" s="9" t="n">
         <v>44.75</v>
       </c>
-      <c r="AF50" s="6" t="n">
+      <c r="AF50" s="7" t="n">
         <v>60.62</v>
       </c>
-      <c r="AG50" s="6" t="n">
+      <c r="AG50" s="7" t="n">
         <v>61.05</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -4561,7 +4594,7 @@
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="12" t="n"/>
+      <c r="AK50" s="16" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -4572,76 +4605,76 @@
       <c r="B51" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C51" s="6" t="n">
+      <c r="C51" s="10" t="n">
         <v>22.82</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="10" t="n">
         <v>19.78</v>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="E51" s="10" t="n">
         <v>19.33</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="10" t="n">
         <v>20.23</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="G51" s="10" t="n">
         <v>20.96</v>
       </c>
-      <c r="H51" s="6" t="n">
+      <c r="H51" s="10" t="n">
         <v>21.43</v>
       </c>
-      <c r="I51" s="6" t="n">
+      <c r="I51" s="10" t="n">
         <v>20.83</v>
       </c>
-      <c r="J51" s="6" t="n">
+      <c r="J51" s="10" t="n">
         <v>20.46</v>
       </c>
-      <c r="K51" s="6" t="n">
+      <c r="K51" s="10" t="n">
         <v>20.8</v>
       </c>
-      <c r="L51" s="6" t="n">
+      <c r="L51" s="10" t="n">
         <v>19.84</v>
       </c>
-      <c r="M51" s="6" t="n">
+      <c r="M51" s="10" t="n">
         <v>19.92</v>
       </c>
-      <c r="N51" s="6" t="n">
+      <c r="N51" s="10" t="n">
         <v>20.16</v>
       </c>
-      <c r="O51" s="6" t="n">
+      <c r="O51" s="10" t="n">
         <v>20.13</v>
       </c>
-      <c r="P51" s="6" t="n">
+      <c r="P51" s="10" t="n">
         <v>22.75</v>
       </c>
-      <c r="Q51" s="6" t="n">
+      <c r="Q51" s="10" t="n">
         <v>20.9</v>
       </c>
-      <c r="R51" s="6" t="n">
+      <c r="R51" s="10" t="n">
         <v>20.58</v>
       </c>
-      <c r="S51" s="6" t="n">
+      <c r="S51" s="10" t="n">
         <v>20.58</v>
       </c>
-      <c r="T51" s="6" t="n">
+      <c r="T51" s="10" t="n">
         <v>22.65</v>
       </c>
-      <c r="U51" s="6" t="n">
+      <c r="U51" s="10" t="n">
         <v>21.7</v>
       </c>
-      <c r="V51" s="6" t="n">
+      <c r="V51" s="10" t="n">
         <v>19.97</v>
       </c>
-      <c r="W51" s="6" t="n">
+      <c r="W51" s="10" t="n">
         <v>20.77</v>
       </c>
-      <c r="X51" s="6" t="n">
+      <c r="X51" s="10" t="n">
         <v>20.33</v>
       </c>
-      <c r="Y51" s="6" t="n">
+      <c r="Y51" s="10" t="n">
         <v>20.74</v>
       </c>
-      <c r="Z51" s="6" t="n">
+      <c r="Z51" s="10" t="n">
         <v>21.79</v>
       </c>
       <c r="AA51" s="6" t="inlineStr">
@@ -4659,16 +4692,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD51" s="6" t="n">
+      <c r="AD51" s="10" t="n">
         <v>20.5</v>
       </c>
-      <c r="AE51" s="6" t="n">
+      <c r="AE51" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="AF51" s="6" t="n">
+      <c r="AF51" s="10" t="n">
         <v>20.99</v>
       </c>
-      <c r="AG51" s="6" t="n">
+      <c r="AG51" s="10" t="n">
         <v>21.88</v>
       </c>
       <c r="AH51" s="6" t="n">
@@ -4676,7 +4709,7 @@
       </c>
       <c r="AI51" s="6" t="inlineStr"/>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="12" t="n"/>
+      <c r="AK51" s="16" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -4687,76 +4720,76 @@
       <c r="B52" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C52" s="10" t="n">
         <v>18.53</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E52" s="10" t="n">
         <v>17.98</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F52" s="10" t="n">
         <v>18.24</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G52" s="10" t="n">
         <v>18.19</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H52" s="10" t="n">
         <v>17.79</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I52" s="10" t="n">
         <v>18.05</v>
       </c>
-      <c r="J52" s="6" t="n">
+      <c r="J52" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="K52" s="6" t="n">
+      <c r="K52" s="10" t="n">
         <v>18.22</v>
       </c>
-      <c r="L52" s="6" t="n">
+      <c r="L52" s="10" t="n">
         <v>17.98</v>
       </c>
-      <c r="M52" s="6" t="n">
+      <c r="M52" s="10" t="n">
         <v>18.44</v>
       </c>
-      <c r="N52" s="6" t="n">
+      <c r="N52" s="10" t="n">
         <v>18.26</v>
       </c>
-      <c r="O52" s="6" t="n">
+      <c r="O52" s="10" t="n">
         <v>18.29</v>
       </c>
-      <c r="P52" s="6" t="n">
+      <c r="P52" s="10" t="n">
         <v>18.67</v>
       </c>
-      <c r="Q52" s="6" t="n">
+      <c r="Q52" s="10" t="n">
         <v>18.47</v>
       </c>
-      <c r="R52" s="6" t="n">
+      <c r="R52" s="10" t="n">
         <v>18.01</v>
       </c>
-      <c r="S52" s="6" t="n">
+      <c r="S52" s="10" t="n">
         <v>18.22</v>
       </c>
-      <c r="T52" s="6" t="n">
+      <c r="T52" s="10" t="n">
         <v>18.26</v>
       </c>
-      <c r="U52" s="6" t="n">
+      <c r="U52" s="10" t="n">
         <v>17.86</v>
       </c>
-      <c r="V52" s="6" t="n">
+      <c r="V52" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="W52" s="6" t="n">
+      <c r="W52" s="10" t="n">
         <v>18.1</v>
       </c>
-      <c r="X52" s="6" t="n">
+      <c r="X52" s="10" t="n">
         <v>17.84</v>
       </c>
-      <c r="Y52" s="6" t="n">
+      <c r="Y52" s="10" t="n">
         <v>18.21</v>
       </c>
-      <c r="Z52" s="6" t="n">
+      <c r="Z52" s="10" t="n">
         <v>18.21</v>
       </c>
       <c r="AA52" s="6" t="inlineStr">
@@ -4774,16 +4807,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD52" s="6" t="n">
+      <c r="AD52" s="10" t="n">
         <v>18.28</v>
       </c>
-      <c r="AE52" s="6" t="n">
+      <c r="AE52" s="10" t="n">
         <v>17.92</v>
       </c>
-      <c r="AF52" s="6" t="n">
+      <c r="AF52" s="10" t="n">
         <v>19.01</v>
       </c>
-      <c r="AG52" s="6" t="n">
+      <c r="AG52" s="10" t="n">
         <v>17.87</v>
       </c>
       <c r="AH52" s="6" t="n">
@@ -4791,122 +4824,122 @@
       </c>
       <c r="AI52" s="6" t="inlineStr"/>
       <c r="AJ52" s="6" t="inlineStr"/>
-      <c r="AK52" s="12" t="n"/>
+      <c r="AK52" s="16" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n">
+      <c r="B53" s="12" t="n">
         <v>621.25</v>
       </c>
-      <c r="C53" s="9" t="n">
+      <c r="C53" s="17" t="n">
         <v>17.95</v>
       </c>
-      <c r="D53" s="9" t="n">
+      <c r="D53" s="17" t="n">
         <v>18.92</v>
       </c>
-      <c r="E53" s="9" t="n">
+      <c r="E53" s="17" t="n">
         <v>18.01</v>
       </c>
-      <c r="F53" s="9" t="n">
+      <c r="F53" s="17" t="n">
         <v>19.62</v>
       </c>
-      <c r="G53" s="9" t="n">
+      <c r="G53" s="17" t="n">
         <v>18.31</v>
       </c>
-      <c r="H53" s="9" t="n">
+      <c r="H53" s="17" t="n">
         <v>18.65</v>
       </c>
-      <c r="I53" s="9" t="n">
+      <c r="I53" s="17" t="n">
         <v>17.95</v>
       </c>
-      <c r="J53" s="9" t="n">
+      <c r="J53" s="17" t="n">
         <v>18.35</v>
       </c>
-      <c r="K53" s="9" t="n">
+      <c r="K53" s="17" t="n">
         <v>17.77</v>
       </c>
-      <c r="L53" s="9" t="n">
+      <c r="L53" s="17" t="n">
         <v>17.89</v>
       </c>
-      <c r="M53" s="9" t="n">
+      <c r="M53" s="17" t="n">
         <v>18.63</v>
       </c>
-      <c r="N53" s="9" t="n">
+      <c r="N53" s="17" t="n">
         <v>18.2</v>
       </c>
-      <c r="O53" s="9" t="n">
+      <c r="O53" s="17" t="n">
         <v>18.66</v>
       </c>
-      <c r="P53" s="9" t="n">
+      <c r="P53" s="17" t="n">
         <v>18.17</v>
       </c>
-      <c r="Q53" s="9" t="n">
+      <c r="Q53" s="17" t="n">
         <v>17.78</v>
       </c>
-      <c r="R53" s="9" t="n">
+      <c r="R53" s="17" t="n">
         <v>17.77</v>
       </c>
-      <c r="S53" s="9" t="n">
+      <c r="S53" s="17" t="n">
         <v>18.17</v>
       </c>
-      <c r="T53" s="9" t="n">
+      <c r="T53" s="17" t="n">
         <v>18.65</v>
       </c>
-      <c r="U53" s="9" t="n">
+      <c r="U53" s="17" t="n">
         <v>18.15</v>
       </c>
-      <c r="V53" s="9" t="n">
+      <c r="V53" s="17" t="n">
         <v>18.39</v>
       </c>
-      <c r="W53" s="9" t="n">
+      <c r="W53" s="17" t="n">
         <v>18.8</v>
       </c>
-      <c r="X53" s="9" t="n">
+      <c r="X53" s="17" t="n">
         <v>17.88</v>
       </c>
-      <c r="Y53" s="9" t="n">
+      <c r="Y53" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="Z53" s="9" t="n">
+      <c r="Z53" s="17" t="n">
         <v>17.42</v>
       </c>
-      <c r="AA53" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB53" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC53" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD53" s="9" t="n">
+      <c r="AA53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD53" s="17" t="n">
         <v>17.28</v>
       </c>
-      <c r="AE53" s="9" t="n">
+      <c r="AE53" s="17" t="n">
         <v>17.95</v>
       </c>
-      <c r="AF53" s="9" t="n">
+      <c r="AF53" s="17" t="n">
         <v>17.8</v>
       </c>
-      <c r="AG53" s="9" t="n">
+      <c r="AG53" s="17" t="n">
         <v>17.93</v>
       </c>
-      <c r="AH53" s="9" t="n">
+      <c r="AH53" s="12" t="n">
         <v>18.18</v>
       </c>
-      <c r="AI53" s="9" t="inlineStr"/>
-      <c r="AJ53" s="9" t="inlineStr"/>
-      <c r="AK53" s="13" t="n"/>
+      <c r="AI53" s="12" t="inlineStr"/>
+      <c r="AJ53" s="12" t="inlineStr"/>
+      <c r="AK53" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -30,30 +30,12 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDFECE"/>
-        <bgColor rgb="FFCDFECE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFE9F"/>
-        <bgColor rgb="FFFFFE9F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFD9BCB"/>
-        <bgColor rgb="FFFD9BCB"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="17">
@@ -171,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,16 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,17 +182,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -778,7 +745,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:tambo</t>
+          <t>CIUDAD:CAÑAR</t>
         </is>
       </c>
     </row>
@@ -792,7 +759,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -934,76 +901,76 @@
       <c r="B11" s="6" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="6" t="n">
         <v>70.81</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="6" t="n">
         <v>71.16</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="6" t="n">
         <v>71.81</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="F11" s="6" t="n">
         <v>71.39</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="6" t="n">
         <v>70.94</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="6" t="n">
         <v>70.87</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="6" t="n">
         <v>70.81</v>
       </c>
-      <c r="J11" s="7" t="n">
+      <c r="J11" s="6" t="n">
         <v>70.62</v>
       </c>
-      <c r="K11" s="7" t="n">
+      <c r="K11" s="6" t="n">
         <v>70.94</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="6" t="n">
         <v>70.63</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="6" t="n">
         <v>70.95999999999999</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="N11" s="6" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="O11" s="7" t="n">
+      <c r="O11" s="6" t="n">
         <v>71.27</v>
       </c>
-      <c r="P11" s="7" t="n">
+      <c r="P11" s="6" t="n">
         <v>70.76000000000001</v>
       </c>
-      <c r="Q11" s="7" t="n">
+      <c r="Q11" s="6" t="n">
         <v>70.81</v>
       </c>
-      <c r="R11" s="7" t="n">
+      <c r="R11" s="6" t="n">
         <v>70.2</v>
       </c>
-      <c r="S11" s="7" t="n">
+      <c r="S11" s="6" t="n">
         <v>70.42</v>
       </c>
-      <c r="T11" s="7" t="n">
+      <c r="T11" s="6" t="n">
         <v>70.84999999999999</v>
       </c>
-      <c r="U11" s="7" t="n">
+      <c r="U11" s="6" t="n">
         <v>70.55</v>
       </c>
-      <c r="V11" s="7" t="n">
+      <c r="V11" s="6" t="n">
         <v>70.27</v>
       </c>
-      <c r="W11" s="7" t="n">
+      <c r="W11" s="6" t="n">
         <v>70.75</v>
       </c>
-      <c r="X11" s="7" t="n">
+      <c r="X11" s="6" t="n">
         <v>70.22</v>
       </c>
-      <c r="Y11" s="7" t="n">
+      <c r="Y11" s="6" t="n">
         <v>70.5</v>
       </c>
-      <c r="Z11" s="7" t="n">
+      <c r="Z11" s="6" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="AA11" s="6" t="inlineStr">
@@ -1021,16 +988,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD11" s="7" t="n">
+      <c r="AD11" s="6" t="n">
         <v>70.68000000000001</v>
       </c>
-      <c r="AE11" s="7" t="n">
+      <c r="AE11" s="6" t="n">
         <v>70.78</v>
       </c>
-      <c r="AF11" s="7" t="n">
+      <c r="AF11" s="6" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="AG11" s="7" t="n">
+      <c r="AG11" s="6" t="n">
         <v>71.11</v>
       </c>
       <c r="AH11" s="6" t="n">
@@ -1040,7 +1007,7 @@
         <v>339.89</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1051,76 +1018,76 @@
       <c r="B12" s="6" t="n">
         <v>89.3</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="6" t="n">
         <v>93.28</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="6" t="n">
         <v>94.11</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="6" t="n">
         <v>93.97</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="6" t="n">
         <v>93.48999999999999</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="6" t="n">
         <v>93.52</v>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="6" t="n">
         <v>93.55</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="6" t="n">
         <v>92.95999999999999</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="6" t="n">
         <v>93.36</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="K12" s="6" t="n">
         <v>93.75</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="6" t="n">
         <v>93.52</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="6" t="n">
         <v>93.93000000000001</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="N12" s="6" t="n">
         <v>94.01000000000001</v>
       </c>
-      <c r="O12" s="7" t="n">
+      <c r="O12" s="6" t="n">
         <v>93.66</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="P12" s="6" t="n">
         <v>93.38</v>
       </c>
-      <c r="Q12" s="7" t="n">
+      <c r="Q12" s="6" t="n">
         <v>92.72</v>
       </c>
-      <c r="R12" s="7" t="n">
+      <c r="R12" s="6" t="n">
         <v>92.98</v>
       </c>
-      <c r="S12" s="7" t="n">
+      <c r="S12" s="6" t="n">
         <v>93.42</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="T12" s="6" t="n">
         <v>93.75</v>
       </c>
-      <c r="U12" s="7" t="n">
+      <c r="U12" s="6" t="n">
         <v>93.36</v>
       </c>
-      <c r="V12" s="7" t="n">
+      <c r="V12" s="6" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="W12" s="7" t="n">
+      <c r="W12" s="6" t="n">
         <v>93.09</v>
       </c>
-      <c r="X12" s="7" t="n">
+      <c r="X12" s="6" t="n">
         <v>93.06999999999999</v>
       </c>
-      <c r="Y12" s="7" t="n">
+      <c r="Y12" s="6" t="n">
         <v>92.84</v>
       </c>
-      <c r="Z12" s="7" t="n">
+      <c r="Z12" s="6" t="n">
         <v>93.28</v>
       </c>
       <c r="AA12" s="6" t="inlineStr">
@@ -1138,16 +1105,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD12" s="7" t="n">
+      <c r="AD12" s="6" t="n">
         <v>92.72</v>
       </c>
-      <c r="AE12" s="7" t="n">
+      <c r="AE12" s="6" t="n">
         <v>92.87</v>
       </c>
-      <c r="AF12" s="7" t="n">
+      <c r="AF12" s="6" t="n">
         <v>93.08</v>
       </c>
-      <c r="AG12" s="7" t="n">
+      <c r="AG12" s="6" t="n">
         <v>93.13</v>
       </c>
       <c r="AH12" s="6" t="n">
@@ -1157,7 +1124,7 @@
         <v>215.38</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1168,76 +1135,76 @@
       <c r="B13" s="6" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="6" t="n">
         <v>75.98</v>
       </c>
-      <c r="D13" s="7" t="n">
+      <c r="D13" s="6" t="n">
         <v>74.91</v>
       </c>
-      <c r="E13" s="7" t="n">
+      <c r="E13" s="6" t="n">
         <v>78.88</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F13" s="6" t="n">
         <v>75.26000000000001</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="6" t="n">
         <v>74.39</v>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="6" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="6" t="n">
         <v>73.68000000000001</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="J13" s="6" t="n">
         <v>74.56999999999999</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="K13" s="6" t="n">
         <v>74.68000000000001</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="6" t="n">
         <v>74.41</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="M13" s="6" t="n">
         <v>74.92</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="N13" s="6" t="n">
         <v>74.76000000000001</v>
       </c>
-      <c r="O13" s="7" t="n">
+      <c r="O13" s="6" t="n">
         <v>74.81999999999999</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="P13" s="6" t="n">
         <v>73.83</v>
       </c>
-      <c r="Q13" s="7" t="n">
+      <c r="Q13" s="6" t="n">
         <v>74.08</v>
       </c>
-      <c r="R13" s="7" t="n">
+      <c r="R13" s="6" t="n">
         <v>72.84999999999999</v>
       </c>
-      <c r="S13" s="7" t="n">
+      <c r="S13" s="6" t="n">
         <v>74.43000000000001</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="T13" s="6" t="n">
         <v>74.48</v>
       </c>
-      <c r="U13" s="7" t="n">
+      <c r="U13" s="6" t="n">
         <v>74.27</v>
       </c>
-      <c r="V13" s="7" t="n">
+      <c r="V13" s="6" t="n">
         <v>74.08</v>
       </c>
-      <c r="W13" s="7" t="n">
+      <c r="W13" s="6" t="n">
         <v>73.83</v>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="X13" s="6" t="n">
         <v>74.39</v>
       </c>
-      <c r="Y13" s="7" t="n">
+      <c r="Y13" s="6" t="n">
         <v>74.2</v>
       </c>
-      <c r="Z13" s="7" t="n">
+      <c r="Z13" s="6" t="n">
         <v>73.31999999999999</v>
       </c>
       <c r="AA13" s="6" t="inlineStr">
@@ -1255,16 +1222,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD13" s="7" t="n">
+      <c r="AD13" s="6" t="n">
         <v>74.47</v>
       </c>
-      <c r="AE13" s="7" t="n">
+      <c r="AE13" s="6" t="n">
         <v>73.42</v>
       </c>
-      <c r="AF13" s="7" t="n">
+      <c r="AF13" s="6" t="n">
         <v>72.95999999999999</v>
       </c>
-      <c r="AG13" s="7" t="n">
+      <c r="AG13" s="6" t="n">
         <v>73.36</v>
       </c>
       <c r="AH13" s="6" t="n">
@@ -1274,7 +1241,7 @@
         <v>381.82</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1285,76 +1252,76 @@
       <c r="B14" s="6" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="6" t="n">
         <v>96.93000000000001</v>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D14" s="6" t="n">
         <v>97.09</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="6" t="n">
         <v>96.54000000000001</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F14" s="6" t="n">
         <v>97.12</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="6" t="n">
         <v>97.09</v>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="6" t="n">
         <v>97.7</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="6" t="n">
         <v>97.28</v>
       </c>
-      <c r="J14" s="7" t="n">
+      <c r="J14" s="6" t="n">
         <v>97.02</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="K14" s="6" t="n">
         <v>97.08</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="6" t="n">
         <v>96.45</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="M14" s="6" t="n">
         <v>96.55</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="N14" s="6" t="n">
         <v>96.68000000000001</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="O14" s="6" t="n">
         <v>97.84999999999999</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="P14" s="6" t="n">
         <v>97.26000000000001</v>
       </c>
-      <c r="Q14" s="7" t="n">
+      <c r="Q14" s="6" t="n">
         <v>97.52</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="R14" s="6" t="n">
         <v>96.83</v>
       </c>
-      <c r="S14" s="7" t="n">
+      <c r="S14" s="6" t="n">
         <v>95.88</v>
       </c>
-      <c r="T14" s="7" t="n">
+      <c r="T14" s="6" t="n">
         <v>96.89</v>
       </c>
-      <c r="U14" s="7" t="n">
+      <c r="U14" s="6" t="n">
         <v>96.91</v>
       </c>
-      <c r="V14" s="7" t="n">
+      <c r="V14" s="6" t="n">
         <v>96.95</v>
       </c>
-      <c r="W14" s="7" t="n">
+      <c r="W14" s="6" t="n">
         <v>97.84</v>
       </c>
-      <c r="X14" s="7" t="n">
+      <c r="X14" s="6" t="n">
         <v>96.5</v>
       </c>
-      <c r="Y14" s="7" t="n">
+      <c r="Y14" s="6" t="n">
         <v>96.29000000000001</v>
       </c>
-      <c r="Z14" s="7" t="n">
+      <c r="Z14" s="6" t="n">
         <v>97.41</v>
       </c>
       <c r="AA14" s="6" t="inlineStr">
@@ -1372,16 +1339,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD14" s="7" t="n">
+      <c r="AD14" s="6" t="n">
         <v>97.31999999999999</v>
       </c>
-      <c r="AE14" s="7" t="n">
+      <c r="AE14" s="6" t="n">
         <v>96.86</v>
       </c>
-      <c r="AF14" s="7" t="n">
+      <c r="AF14" s="6" t="n">
         <v>97.02</v>
       </c>
-      <c r="AG14" s="7" t="n">
+      <c r="AG14" s="6" t="n">
         <v>96.36</v>
       </c>
       <c r="AH14" s="6" t="n">
@@ -1391,7 +1358,7 @@
         <v>394.82</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1402,76 +1369,76 @@
       <c r="B15" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="6" t="n">
         <v>51.91</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="6" t="n">
         <v>51.91</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="6" t="n">
         <v>53.71</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="6" t="n">
         <v>53.19</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="6" t="n">
         <v>52.31</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="6" t="n">
         <v>52.02</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="6" t="n">
         <v>51.63</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="6" t="n">
         <v>51.38</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="6" t="n">
         <v>52.8</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="6" t="n">
         <v>52.85</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="6" t="n">
         <v>52.05</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="N15" s="6" t="n">
         <v>51.7</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="6" t="n">
         <v>51.64</v>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="P15" s="6" t="n">
         <v>51.52</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="6" t="n">
         <v>51.34</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="6" t="n">
         <v>51.23</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="6" t="n">
         <v>51.05</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="6" t="n">
         <v>51.93</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="6" t="n">
         <v>51.36</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="6" t="n">
         <v>51.27</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="6" t="n">
         <v>51.31</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="6" t="n">
         <v>51.83</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="6" t="n">
         <v>51.24</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="6" t="n">
         <v>52.94</v>
       </c>
       <c r="AA15" s="6" t="inlineStr">
@@ -1489,16 +1456,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD15" s="9" t="n">
+      <c r="AD15" s="6" t="n">
         <v>51.04</v>
       </c>
-      <c r="AE15" s="9" t="n">
+      <c r="AE15" s="6" t="n">
         <v>50.71</v>
       </c>
-      <c r="AF15" s="9" t="n">
+      <c r="AF15" s="6" t="n">
         <v>50.56</v>
       </c>
-      <c r="AG15" s="9" t="n">
+      <c r="AG15" s="6" t="n">
         <v>51.09</v>
       </c>
       <c r="AH15" s="6" t="n">
@@ -1508,7 +1475,7 @@
         <v>489.28</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1519,76 +1486,76 @@
       <c r="B16" s="6" t="n">
         <v>92.09999999999999</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="6" t="n">
         <v>87.31</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="6" t="n">
         <v>87.98999999999999</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="6" t="n">
         <v>88.61</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="6" t="n">
         <v>88.18000000000001</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="6" t="n">
         <v>87.95999999999999</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="6" t="n">
         <v>87.73</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="6" t="n">
         <v>87.54000000000001</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="6" t="n">
         <v>88.2</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="6" t="n">
         <v>89.23</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="6" t="n">
         <v>89.13</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="6" t="n">
         <v>89.14</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="N16" s="6" t="n">
         <v>89.18000000000001</v>
       </c>
-      <c r="O16" s="7" t="n">
+      <c r="O16" s="6" t="n">
         <v>88.27</v>
       </c>
-      <c r="P16" s="7" t="n">
+      <c r="P16" s="6" t="n">
         <v>88.66</v>
       </c>
-      <c r="Q16" s="7" t="n">
+      <c r="Q16" s="6" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="R16" s="7" t="n">
+      <c r="R16" s="6" t="n">
         <v>87.81999999999999</v>
       </c>
-      <c r="S16" s="7" t="n">
+      <c r="S16" s="6" t="n">
         <v>88.15000000000001</v>
       </c>
-      <c r="T16" s="7" t="n">
+      <c r="T16" s="6" t="n">
         <v>88.48</v>
       </c>
-      <c r="U16" s="7" t="n">
+      <c r="U16" s="6" t="n">
         <v>87.94</v>
       </c>
-      <c r="V16" s="7" t="n">
+      <c r="V16" s="6" t="n">
         <v>87.94</v>
       </c>
-      <c r="W16" s="7" t="n">
+      <c r="W16" s="6" t="n">
         <v>88.13</v>
       </c>
-      <c r="X16" s="7" t="n">
+      <c r="X16" s="6" t="n">
         <v>88.29000000000001</v>
       </c>
-      <c r="Y16" s="7" t="n">
+      <c r="Y16" s="6" t="n">
         <v>88.23</v>
       </c>
-      <c r="Z16" s="7" t="n">
+      <c r="Z16" s="6" t="n">
         <v>87.55</v>
       </c>
       <c r="AA16" s="6" t="inlineStr">
@@ -1606,16 +1573,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD16" s="7" t="n">
+      <c r="AD16" s="6" t="n">
         <v>88.03</v>
       </c>
-      <c r="AE16" s="7" t="n">
+      <c r="AE16" s="6" t="n">
         <v>88.34</v>
       </c>
-      <c r="AF16" s="7" t="n">
+      <c r="AF16" s="6" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="AG16" s="7" t="n">
+      <c r="AG16" s="6" t="n">
         <v>87.69</v>
       </c>
       <c r="AH16" s="6" t="n">
@@ -1625,7 +1592,7 @@
         <v>214.98</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1636,76 +1603,76 @@
       <c r="B17" s="6" t="n">
         <v>92.5</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="6" t="n">
         <v>83.66</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="6" t="n">
         <v>82.89</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="6" t="n">
         <v>79.54000000000001</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="6" t="n">
         <v>78.98999999999999</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="6" t="n">
         <v>78.14</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="6" t="n">
         <v>77.03</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="6" t="n">
         <v>78.29000000000001</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="6" t="n">
         <v>78.98</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="6" t="n">
         <v>78.91</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="6" t="n">
         <v>79.91</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="N17" s="6" t="n">
         <v>79.66</v>
       </c>
-      <c r="O17" s="7" t="n">
+      <c r="O17" s="6" t="n">
         <v>78.11</v>
       </c>
-      <c r="P17" s="7" t="n">
+      <c r="P17" s="6" t="n">
         <v>78.31</v>
       </c>
-      <c r="Q17" s="7" t="n">
+      <c r="Q17" s="6" t="n">
         <v>78.04000000000001</v>
       </c>
-      <c r="R17" s="7" t="n">
+      <c r="R17" s="6" t="n">
         <v>77.95</v>
       </c>
-      <c r="S17" s="7" t="n">
+      <c r="S17" s="6" t="n">
         <v>79.06</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="T17" s="6" t="n">
         <v>79.84</v>
       </c>
-      <c r="U17" s="7" t="n">
+      <c r="U17" s="6" t="n">
         <v>78.34</v>
       </c>
-      <c r="V17" s="7" t="n">
+      <c r="V17" s="6" t="n">
         <v>79.08</v>
       </c>
-      <c r="W17" s="7" t="n">
+      <c r="W17" s="6" t="n">
         <v>79.27</v>
       </c>
-      <c r="X17" s="7" t="n">
+      <c r="X17" s="6" t="n">
         <v>78.29000000000001</v>
       </c>
-      <c r="Y17" s="7" t="n">
+      <c r="Y17" s="6" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="Z17" s="7" t="n">
+      <c r="Z17" s="6" t="n">
         <v>77.91</v>
       </c>
       <c r="AA17" s="6" t="inlineStr">
@@ -1723,16 +1690,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="n">
+      <c r="AD17" s="6" t="n">
         <v>78.19</v>
       </c>
-      <c r="AE17" s="7" t="n">
+      <c r="AE17" s="6" t="n">
         <v>78.01000000000001</v>
       </c>
-      <c r="AF17" s="7" t="n">
+      <c r="AF17" s="6" t="n">
         <v>77.29000000000001</v>
       </c>
-      <c r="AG17" s="7" t="n">
+      <c r="AG17" s="6" t="n">
         <v>77.31</v>
       </c>
       <c r="AH17" s="6" t="n">
@@ -1742,7 +1709,7 @@
         <v>362.77</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1753,76 +1720,76 @@
       <c r="B18" s="6" t="n">
         <v>93.3</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="6" t="n">
         <v>87.48999999999999</v>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D18" s="6" t="n">
         <v>89.48</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E18" s="6" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="6" t="n">
         <v>82.76000000000001</v>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="6" t="n">
         <v>82.14</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="6" t="n">
         <v>83.81999999999999</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="6" t="n">
         <v>82.84999999999999</v>
       </c>
-      <c r="J18" s="7" t="n">
+      <c r="J18" s="6" t="n">
         <v>82.92</v>
       </c>
-      <c r="K18" s="7" t="n">
+      <c r="K18" s="6" t="n">
         <v>82.92</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="6" t="n">
         <v>83.93000000000001</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="M18" s="6" t="n">
         <v>81.26000000000001</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="N18" s="6" t="n">
         <v>79.93000000000001</v>
       </c>
-      <c r="O18" s="7" t="n">
+      <c r="O18" s="6" t="n">
         <v>77.94</v>
       </c>
-      <c r="P18" s="7" t="n">
+      <c r="P18" s="6" t="n">
         <v>77.83</v>
       </c>
-      <c r="Q18" s="7" t="n">
+      <c r="Q18" s="6" t="n">
         <v>77.65000000000001</v>
       </c>
-      <c r="R18" s="7" t="n">
+      <c r="R18" s="6" t="n">
         <v>76.88</v>
       </c>
-      <c r="S18" s="7" t="n">
+      <c r="S18" s="6" t="n">
         <v>79.18000000000001</v>
       </c>
-      <c r="T18" s="7" t="n">
+      <c r="T18" s="6" t="n">
         <v>81.59</v>
       </c>
-      <c r="U18" s="7" t="n">
+      <c r="U18" s="6" t="n">
         <v>77.73999999999999</v>
       </c>
-      <c r="V18" s="7" t="n">
+      <c r="V18" s="6" t="n">
         <v>78.68000000000001</v>
       </c>
-      <c r="W18" s="7" t="n">
+      <c r="W18" s="6" t="n">
         <v>77.12</v>
       </c>
-      <c r="X18" s="7" t="n">
+      <c r="X18" s="6" t="n">
         <v>78.59</v>
       </c>
-      <c r="Y18" s="7" t="n">
+      <c r="Y18" s="6" t="n">
         <v>78.06999999999999</v>
       </c>
-      <c r="Z18" s="7" t="n">
+      <c r="Z18" s="6" t="n">
         <v>83.88</v>
       </c>
       <c r="AA18" s="6" t="inlineStr">
@@ -1840,16 +1807,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD18" s="7" t="n">
+      <c r="AD18" s="6" t="n">
         <v>84.56</v>
       </c>
-      <c r="AE18" s="7" t="n">
+      <c r="AE18" s="6" t="n">
         <v>83.56999999999999</v>
       </c>
-      <c r="AF18" s="7" t="n">
+      <c r="AF18" s="6" t="n">
         <v>83.16</v>
       </c>
-      <c r="AG18" s="7" t="n">
+      <c r="AG18" s="6" t="n">
         <v>84.08</v>
       </c>
       <c r="AH18" s="6" t="n">
@@ -1859,7 +1826,7 @@
         <v>219.91</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1870,76 +1837,76 @@
       <c r="B19" s="6" t="n">
         <v>94.09999999999999</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="6" t="n">
         <v>63.41</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="6" t="n">
         <v>60.13</v>
       </c>
-      <c r="E19" s="7" t="n">
+      <c r="E19" s="6" t="n">
         <v>59.7</v>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F19" s="6" t="n">
         <v>57.16</v>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="6" t="n">
         <v>56.34</v>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="6" t="n">
         <v>57.07</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="6" t="n">
         <v>57.27</v>
       </c>
-      <c r="J19" s="7" t="n">
+      <c r="J19" s="6" t="n">
         <v>56.95</v>
       </c>
-      <c r="K19" s="7" t="n">
+      <c r="K19" s="6" t="n">
         <v>55.98</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="6" t="n">
         <v>54.59</v>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="M19" s="6" t="n">
         <v>58.17</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="N19" s="6" t="n">
         <v>57.62</v>
       </c>
-      <c r="O19" s="7" t="n">
+      <c r="O19" s="6" t="n">
         <v>56.08</v>
       </c>
-      <c r="P19" s="7" t="n">
+      <c r="P19" s="6" t="n">
         <v>55.72</v>
       </c>
-      <c r="Q19" s="7" t="n">
+      <c r="Q19" s="6" t="n">
         <v>54.92</v>
       </c>
-      <c r="R19" s="7" t="n">
+      <c r="R19" s="6" t="n">
         <v>54.94</v>
       </c>
-      <c r="S19" s="7" t="n">
+      <c r="S19" s="6" t="n">
         <v>59.31</v>
       </c>
-      <c r="T19" s="7" t="n">
+      <c r="T19" s="6" t="n">
         <v>57.59</v>
       </c>
-      <c r="U19" s="7" t="n">
+      <c r="U19" s="6" t="n">
         <v>56.86</v>
       </c>
-      <c r="V19" s="7" t="n">
+      <c r="V19" s="6" t="n">
         <v>57.49</v>
       </c>
-      <c r="W19" s="7" t="n">
+      <c r="W19" s="6" t="n">
         <v>55.42</v>
       </c>
-      <c r="X19" s="7" t="n">
+      <c r="X19" s="6" t="n">
         <v>56.76</v>
       </c>
-      <c r="Y19" s="7" t="n">
+      <c r="Y19" s="6" t="n">
         <v>56.06</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="6" t="n">
         <v>53.79</v>
       </c>
       <c r="AA19" s="6" t="inlineStr">
@@ -1957,16 +1924,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD19" s="9" t="n">
+      <c r="AD19" s="6" t="n">
         <v>52.48</v>
       </c>
-      <c r="AE19" s="7" t="n">
+      <c r="AE19" s="6" t="n">
         <v>54.38</v>
       </c>
-      <c r="AF19" s="7" t="n">
+      <c r="AF19" s="6" t="n">
         <v>55.62</v>
       </c>
-      <c r="AG19" s="7" t="n">
+      <c r="AG19" s="6" t="n">
         <v>55.96</v>
       </c>
       <c r="AH19" s="6" t="n">
@@ -1976,7 +1943,7 @@
         <v>489.91</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1987,76 +1954,76 @@
       <c r="B20" s="6" t="n">
         <v>94.5</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="6" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="6" t="n">
         <v>87.55</v>
       </c>
-      <c r="E20" s="7" t="n">
+      <c r="E20" s="6" t="n">
         <v>87.76000000000001</v>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F20" s="6" t="n">
         <v>87.17</v>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="6" t="n">
         <v>87.51000000000001</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="6" t="n">
         <v>87.17</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="6" t="n">
         <v>87.18000000000001</v>
       </c>
-      <c r="J20" s="7" t="n">
+      <c r="J20" s="6" t="n">
         <v>87.56999999999999</v>
       </c>
-      <c r="K20" s="7" t="n">
+      <c r="K20" s="6" t="n">
         <v>87.29000000000001</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="6" t="n">
         <v>87.41</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="M20" s="6" t="n">
         <v>87.76000000000001</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="N20" s="6" t="n">
         <v>87.13</v>
       </c>
-      <c r="O20" s="7" t="n">
+      <c r="O20" s="6" t="n">
         <v>87.53</v>
       </c>
-      <c r="P20" s="7" t="n">
+      <c r="P20" s="6" t="n">
         <v>87.48999999999999</v>
       </c>
-      <c r="Q20" s="7" t="n">
+      <c r="Q20" s="6" t="n">
         <v>87.55</v>
       </c>
-      <c r="R20" s="7" t="n">
+      <c r="R20" s="6" t="n">
         <v>87.04000000000001</v>
       </c>
-      <c r="S20" s="7" t="n">
+      <c r="S20" s="6" t="n">
         <v>87.28</v>
       </c>
-      <c r="T20" s="7" t="n">
+      <c r="T20" s="6" t="n">
         <v>87.66</v>
       </c>
-      <c r="U20" s="7" t="n">
+      <c r="U20" s="6" t="n">
         <v>87.26000000000001</v>
       </c>
-      <c r="V20" s="7" t="n">
+      <c r="V20" s="6" t="n">
         <v>87.17</v>
       </c>
-      <c r="W20" s="7" t="n">
+      <c r="W20" s="6" t="n">
         <v>88.13</v>
       </c>
-      <c r="X20" s="7" t="n">
+      <c r="X20" s="6" t="n">
         <v>86.91</v>
       </c>
-      <c r="Y20" s="7" t="n">
+      <c r="Y20" s="6" t="n">
         <v>87.19</v>
       </c>
-      <c r="Z20" s="7" t="n">
+      <c r="Z20" s="6" t="n">
         <v>87.05</v>
       </c>
       <c r="AA20" s="6" t="inlineStr">
@@ -2074,16 +2041,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD20" s="7" t="n">
+      <c r="AD20" s="6" t="n">
         <v>87.63</v>
       </c>
-      <c r="AE20" s="7" t="n">
+      <c r="AE20" s="6" t="n">
         <v>87.11</v>
       </c>
-      <c r="AF20" s="7" t="n">
+      <c r="AF20" s="6" t="n">
         <v>87.04000000000001</v>
       </c>
-      <c r="AG20" s="7" t="n">
+      <c r="AG20" s="6" t="n">
         <v>87.14</v>
       </c>
       <c r="AH20" s="6" t="n">
@@ -2093,7 +2060,7 @@
         <v>196.8</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2104,76 +2071,76 @@
       <c r="B21" s="6" t="n">
         <v>95.3</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="6" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="6" t="n">
         <v>94.76000000000001</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="6" t="n">
         <v>94.06999999999999</v>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F21" s="6" t="n">
         <v>94.17</v>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="6" t="n">
         <v>94.72</v>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="6" t="n">
         <v>94.16</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="6" t="n">
         <v>94.15000000000001</v>
       </c>
-      <c r="J21" s="7" t="n">
+      <c r="J21" s="6" t="n">
         <v>94.31</v>
       </c>
-      <c r="K21" s="7" t="n">
+      <c r="K21" s="6" t="n">
         <v>94.03</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="6" t="n">
         <v>93.81</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="M21" s="6" t="n">
         <v>93.7</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="N21" s="6" t="n">
         <v>94.93000000000001</v>
       </c>
-      <c r="O21" s="7" t="n">
+      <c r="O21" s="6" t="n">
         <v>94.28</v>
       </c>
-      <c r="P21" s="7" t="n">
+      <c r="P21" s="6" t="n">
         <v>94.02</v>
       </c>
-      <c r="Q21" s="7" t="n">
+      <c r="Q21" s="6" t="n">
         <v>94.45</v>
       </c>
-      <c r="R21" s="7" t="n">
+      <c r="R21" s="6" t="n">
         <v>93.68000000000001</v>
       </c>
-      <c r="S21" s="7" t="n">
+      <c r="S21" s="6" t="n">
         <v>94.22</v>
       </c>
-      <c r="T21" s="7" t="n">
+      <c r="T21" s="6" t="n">
         <v>94.33</v>
       </c>
-      <c r="U21" s="7" t="n">
+      <c r="U21" s="6" t="n">
         <v>94.87</v>
       </c>
-      <c r="V21" s="7" t="n">
+      <c r="V21" s="6" t="n">
         <v>94.43000000000001</v>
       </c>
-      <c r="W21" s="7" t="n">
+      <c r="W21" s="6" t="n">
         <v>94.41</v>
       </c>
-      <c r="X21" s="7" t="n">
+      <c r="X21" s="6" t="n">
         <v>93.66</v>
       </c>
-      <c r="Y21" s="7" t="n">
+      <c r="Y21" s="6" t="n">
         <v>94.48</v>
       </c>
-      <c r="Z21" s="7" t="n">
+      <c r="Z21" s="6" t="n">
         <v>94.44</v>
       </c>
       <c r="AA21" s="6" t="inlineStr">
@@ -2191,16 +2158,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD21" s="7" t="n">
+      <c r="AD21" s="6" t="n">
         <v>94.86</v>
       </c>
-      <c r="AE21" s="7" t="n">
+      <c r="AE21" s="6" t="n">
         <v>93.95999999999999</v>
       </c>
-      <c r="AF21" s="7" t="n">
+      <c r="AF21" s="6" t="n">
         <v>93.87</v>
       </c>
-      <c r="AG21" s="7" t="n">
+      <c r="AG21" s="6" t="n">
         <v>94.06999999999999</v>
       </c>
       <c r="AH21" s="6" t="n">
@@ -2210,7 +2177,7 @@
         <v>230.95</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2221,76 +2188,76 @@
       <c r="B22" s="6" t="n">
         <v>95.7</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="6" t="n">
         <v>79.19</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="6" t="n">
         <v>78.02</v>
       </c>
-      <c r="E22" s="7" t="n">
+      <c r="E22" s="6" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F22" s="6" t="n">
         <v>78.19</v>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="6" t="n">
         <v>77.61</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="6" t="n">
         <v>78.34</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="6" t="n">
         <v>77.91</v>
       </c>
-      <c r="J22" s="7" t="n">
+      <c r="J22" s="6" t="n">
         <v>77.88</v>
       </c>
-      <c r="K22" s="7" t="n">
+      <c r="K22" s="6" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="6" t="n">
         <v>78.09</v>
       </c>
-      <c r="M22" s="7" t="n">
+      <c r="M22" s="6" t="n">
         <v>76.56</v>
       </c>
-      <c r="N22" s="7" t="n">
+      <c r="N22" s="6" t="n">
         <v>78.29000000000001</v>
       </c>
-      <c r="O22" s="7" t="n">
+      <c r="O22" s="6" t="n">
         <v>78.41</v>
       </c>
-      <c r="P22" s="7" t="n">
+      <c r="P22" s="6" t="n">
         <v>76.47</v>
       </c>
-      <c r="Q22" s="7" t="n">
+      <c r="Q22" s="6" t="n">
         <v>75.29000000000001</v>
       </c>
-      <c r="R22" s="7" t="n">
+      <c r="R22" s="6" t="n">
         <v>76.73999999999999</v>
       </c>
-      <c r="S22" s="7" t="n">
+      <c r="S22" s="6" t="n">
         <v>77.23</v>
       </c>
-      <c r="T22" s="7" t="n">
+      <c r="T22" s="6" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="U22" s="7" t="n">
+      <c r="U22" s="6" t="n">
         <v>78.76000000000001</v>
       </c>
-      <c r="V22" s="7" t="n">
+      <c r="V22" s="6" t="n">
         <v>78.73</v>
       </c>
-      <c r="W22" s="7" t="n">
+      <c r="W22" s="6" t="n">
         <v>77.31999999999999</v>
       </c>
-      <c r="X22" s="7" t="n">
+      <c r="X22" s="6" t="n">
         <v>77.84999999999999</v>
       </c>
-      <c r="Y22" s="7" t="n">
+      <c r="Y22" s="6" t="n">
         <v>76.91</v>
       </c>
-      <c r="Z22" s="7" t="n">
+      <c r="Z22" s="6" t="n">
         <v>77.48999999999999</v>
       </c>
       <c r="AA22" s="6" t="inlineStr">
@@ -2308,16 +2275,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD22" s="7" t="n">
+      <c r="AD22" s="6" t="n">
         <v>76.88</v>
       </c>
-      <c r="AE22" s="7" t="n">
+      <c r="AE22" s="6" t="n">
         <v>76.61</v>
       </c>
-      <c r="AF22" s="7" t="n">
+      <c r="AF22" s="6" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="AG22" s="7" t="n">
+      <c r="AG22" s="6" t="n">
         <v>76.23</v>
       </c>
       <c r="AH22" s="6" t="n">
@@ -2327,7 +2294,7 @@
         <v>436.64</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2338,76 +2305,76 @@
       <c r="B23" s="6" t="n">
         <v>97.3</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="6" t="n">
         <v>70.97</v>
       </c>
-      <c r="D23" s="7" t="n">
+      <c r="D23" s="6" t="n">
         <v>71.63</v>
       </c>
-      <c r="E23" s="7" t="n">
+      <c r="E23" s="6" t="n">
         <v>70.72</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="6" t="n">
         <v>72.53</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="6" t="n">
         <v>70.94</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="6" t="n">
         <v>71.58</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="6" t="n">
         <v>70.19</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="6" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" s="6" t="n">
         <v>71.48999999999999</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="6" t="n">
         <v>72.37</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="6" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="N23" s="6" t="n">
         <v>69.26000000000001</v>
       </c>
-      <c r="O23" s="7" t="n">
+      <c r="O23" s="6" t="n">
         <v>69.84</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="P23" s="6" t="n">
         <v>70.48</v>
       </c>
-      <c r="Q23" s="7" t="n">
+      <c r="Q23" s="6" t="n">
         <v>69.34999999999999</v>
       </c>
-      <c r="R23" s="7" t="n">
+      <c r="R23" s="6" t="n">
         <v>69.12</v>
       </c>
-      <c r="S23" s="7" t="n">
+      <c r="S23" s="6" t="n">
         <v>68.91</v>
       </c>
-      <c r="T23" s="7" t="n">
+      <c r="T23" s="6" t="n">
         <v>71.76000000000001</v>
       </c>
-      <c r="U23" s="7" t="n">
+      <c r="U23" s="6" t="n">
         <v>71.72</v>
       </c>
-      <c r="V23" s="7" t="n">
+      <c r="V23" s="6" t="n">
         <v>73.87</v>
       </c>
-      <c r="W23" s="7" t="n">
+      <c r="W23" s="6" t="n">
         <v>72.70999999999999</v>
       </c>
-      <c r="X23" s="7" t="n">
+      <c r="X23" s="6" t="n">
         <v>69.89</v>
       </c>
-      <c r="Y23" s="7" t="n">
+      <c r="Y23" s="6" t="n">
         <v>72.15000000000001</v>
       </c>
-      <c r="Z23" s="7" t="n">
+      <c r="Z23" s="6" t="n">
         <v>69.72</v>
       </c>
       <c r="AA23" s="6" t="inlineStr">
@@ -2425,16 +2392,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD23" s="7" t="n">
+      <c r="AD23" s="6" t="n">
         <v>75.16</v>
       </c>
-      <c r="AE23" s="7" t="n">
+      <c r="AE23" s="6" t="n">
         <v>77.33</v>
       </c>
-      <c r="AF23" s="7" t="n">
+      <c r="AF23" s="6" t="n">
         <v>76.20999999999999</v>
       </c>
-      <c r="AG23" s="7" t="n">
+      <c r="AG23" s="6" t="n">
         <v>84.45</v>
       </c>
       <c r="AH23" s="6" t="n">
@@ -2444,7 +2411,7 @@
         <v>257.14</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2455,76 +2422,76 @@
       <c r="B24" s="6" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="6" t="n">
         <v>82.16</v>
       </c>
-      <c r="D24" s="7" t="n">
+      <c r="D24" s="6" t="n">
         <v>82.04000000000001</v>
       </c>
-      <c r="E24" s="7" t="n">
+      <c r="E24" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F24" s="6" t="n">
         <v>83.72</v>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="6" t="n">
         <v>81.56</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="6" t="n">
         <v>82.06999999999999</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="6" t="n">
         <v>81.31999999999999</v>
       </c>
-      <c r="J24" s="7" t="n">
+      <c r="J24" s="6" t="n">
         <v>81.45999999999999</v>
       </c>
-      <c r="K24" s="7" t="n">
+      <c r="K24" s="6" t="n">
         <v>82.41</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="6" t="n">
         <v>82.11</v>
       </c>
-      <c r="M24" s="7" t="n">
+      <c r="M24" s="6" t="n">
         <v>81.54000000000001</v>
       </c>
-      <c r="N24" s="7" t="n">
+      <c r="N24" s="6" t="n">
         <v>81.65000000000001</v>
       </c>
-      <c r="O24" s="7" t="n">
+      <c r="O24" s="6" t="n">
         <v>81.03</v>
       </c>
-      <c r="P24" s="7" t="n">
+      <c r="P24" s="6" t="n">
         <v>79.18000000000001</v>
       </c>
-      <c r="Q24" s="7" t="n">
+      <c r="Q24" s="6" t="n">
         <v>80.03</v>
       </c>
-      <c r="R24" s="7" t="n">
+      <c r="R24" s="6" t="n">
         <v>80.20999999999999</v>
       </c>
-      <c r="S24" s="7" t="n">
+      <c r="S24" s="6" t="n">
         <v>80.44</v>
       </c>
-      <c r="T24" s="7" t="n">
+      <c r="T24" s="6" t="n">
         <v>82.08</v>
       </c>
-      <c r="U24" s="7" t="n">
+      <c r="U24" s="6" t="n">
         <v>80.15000000000001</v>
       </c>
-      <c r="V24" s="7" t="n">
+      <c r="V24" s="6" t="n">
         <v>80.55</v>
       </c>
-      <c r="W24" s="7" t="n">
+      <c r="W24" s="6" t="n">
         <v>79.08</v>
       </c>
-      <c r="X24" s="7" t="n">
+      <c r="X24" s="6" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="Y24" s="7" t="n">
+      <c r="Y24" s="6" t="n">
         <v>81.37</v>
       </c>
-      <c r="Z24" s="7" t="n">
+      <c r="Z24" s="6" t="n">
         <v>80.8</v>
       </c>
       <c r="AA24" s="6" t="inlineStr">
@@ -2542,16 +2509,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD24" s="7" t="n">
+      <c r="AD24" s="6" t="n">
         <v>80.97</v>
       </c>
-      <c r="AE24" s="7" t="n">
+      <c r="AE24" s="6" t="n">
         <v>80.06</v>
       </c>
-      <c r="AF24" s="7" t="n">
+      <c r="AF24" s="6" t="n">
         <v>80.63</v>
       </c>
-      <c r="AG24" s="7" t="n">
+      <c r="AG24" s="6" t="n">
         <v>81.16</v>
       </c>
       <c r="AH24" s="6" t="n">
@@ -2561,7 +2528,7 @@
         <v>197.27</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2572,76 +2539,76 @@
       <c r="B25" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="6" t="n">
         <v>46.88</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="6" t="n">
         <v>46.81</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="6" t="n">
         <v>45.97</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="6" t="n">
         <v>47.78</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="6" t="n">
         <v>48.08</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="6" t="n">
         <v>47.05</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="6" t="n">
         <v>46.67</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" s="6" t="n">
         <v>47.12</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="6" t="n">
         <v>46.84</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="6" t="n">
         <v>46.88</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="6" t="n">
         <v>46.33</v>
       </c>
-      <c r="N25" s="9" t="n">
+      <c r="N25" s="6" t="n">
         <v>49.66</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="O25" s="6" t="n">
         <v>48.7</v>
       </c>
-      <c r="P25" s="9" t="n">
+      <c r="P25" s="6" t="n">
         <v>49.31</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="6" t="n">
         <v>47.73</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="6" t="n">
         <v>49.23</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="6" t="n">
         <v>47.98</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="6" t="n">
         <v>46.88</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="6" t="n">
         <v>45.82</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="6" t="n">
         <v>46.52</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="6" t="n">
         <v>47.44</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" s="6" t="n">
         <v>46.51</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="6" t="n">
         <v>46.15</v>
       </c>
-      <c r="Z25" s="9" t="n">
+      <c r="Z25" s="6" t="n">
         <v>45.64</v>
       </c>
       <c r="AA25" s="6" t="inlineStr">
@@ -2659,16 +2626,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD25" s="9" t="n">
+      <c r="AD25" s="6" t="n">
         <v>44.54</v>
       </c>
-      <c r="AE25" s="9" t="n">
+      <c r="AE25" s="6" t="n">
         <v>46.63</v>
       </c>
-      <c r="AF25" s="9" t="n">
+      <c r="AF25" s="6" t="n">
         <v>46.59</v>
       </c>
-      <c r="AG25" s="9" t="n">
+      <c r="AG25" s="6" t="n">
         <v>47.18</v>
       </c>
       <c r="AH25" s="6" t="n">
@@ -2678,7 +2645,7 @@
         <v>490</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2689,76 +2656,76 @@
       <c r="B26" s="6" t="n">
         <v>99.3</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="6" t="n">
         <v>91.44</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D26" s="6" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E26" s="6" t="n">
         <v>90.98999999999999</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F26" s="6" t="n">
         <v>92.53</v>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="6" t="n">
         <v>90.17</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H26" s="6" t="n">
         <v>92.02</v>
       </c>
-      <c r="I26" s="7" t="n">
+      <c r="I26" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="J26" s="7" t="n">
+      <c r="J26" s="6" t="n">
         <v>89.87</v>
       </c>
-      <c r="K26" s="7" t="n">
+      <c r="K26" s="6" t="n">
         <v>91.92</v>
       </c>
-      <c r="L26" s="7" t="n">
+      <c r="L26" s="6" t="n">
         <v>91.45</v>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="M26" s="6" t="n">
         <v>91.73999999999999</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="N26" s="6" t="n">
         <v>90.67</v>
       </c>
-      <c r="O26" s="7" t="n">
+      <c r="O26" s="6" t="n">
         <v>82.06999999999999</v>
       </c>
-      <c r="P26" s="7" t="n">
+      <c r="P26" s="6" t="n">
         <v>89.36</v>
       </c>
-      <c r="Q26" s="7" t="n">
+      <c r="Q26" s="6" t="n">
         <v>89.47</v>
       </c>
-      <c r="R26" s="7" t="n">
+      <c r="R26" s="6" t="n">
         <v>89.79000000000001</v>
       </c>
-      <c r="S26" s="7" t="n">
+      <c r="S26" s="6" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="T26" s="7" t="n">
+      <c r="T26" s="6" t="n">
         <v>91.59</v>
       </c>
-      <c r="U26" s="7" t="n">
+      <c r="U26" s="6" t="n">
         <v>91.81</v>
       </c>
-      <c r="V26" s="7" t="n">
+      <c r="V26" s="6" t="n">
         <v>90.04000000000001</v>
       </c>
-      <c r="W26" s="7" t="n">
+      <c r="W26" s="6" t="n">
         <v>87.87</v>
       </c>
-      <c r="X26" s="7" t="n">
+      <c r="X26" s="6" t="n">
         <v>91.38</v>
       </c>
-      <c r="Y26" s="7" t="n">
+      <c r="Y26" s="6" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="Z26" s="7" t="n">
+      <c r="Z26" s="6" t="n">
         <v>91.66</v>
       </c>
       <c r="AA26" s="6" t="inlineStr">
@@ -2776,16 +2743,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD26" s="7" t="n">
+      <c r="AD26" s="6" t="n">
         <v>89.04000000000001</v>
       </c>
-      <c r="AE26" s="7" t="n">
+      <c r="AE26" s="6" t="n">
         <v>90.68000000000001</v>
       </c>
-      <c r="AF26" s="7" t="n">
+      <c r="AF26" s="6" t="n">
         <v>89.98</v>
       </c>
-      <c r="AG26" s="7" t="n">
+      <c r="AG26" s="6" t="n">
         <v>91.37</v>
       </c>
       <c r="AH26" s="6" t="n">
@@ -2795,7 +2762,7 @@
         <v>371.19</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2806,76 +2773,76 @@
       <c r="B27" s="6" t="n">
         <v>99.7</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="6" t="n">
         <v>88.66</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D27" s="6" t="n">
         <v>89.05</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="6" t="n">
         <v>88.14</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="6" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="6" t="n">
         <v>88.63</v>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="H27" s="6" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="6" t="n">
         <v>88.69</v>
       </c>
-      <c r="J27" s="7" t="n">
+      <c r="J27" s="6" t="n">
         <v>88.92</v>
       </c>
-      <c r="K27" s="7" t="n">
+      <c r="K27" s="6" t="n">
         <v>90.20999999999999</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" s="6" t="n">
         <v>89.76000000000001</v>
       </c>
-      <c r="M27" s="7" t="n">
+      <c r="M27" s="6" t="n">
         <v>89.08</v>
       </c>
-      <c r="N27" s="7" t="n">
+      <c r="N27" s="6" t="n">
         <v>89.7</v>
       </c>
-      <c r="O27" s="7" t="n">
+      <c r="O27" s="6" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="P27" s="7" t="n">
+      <c r="P27" s="6" t="n">
         <v>88.95999999999999</v>
       </c>
-      <c r="Q27" s="7" t="n">
+      <c r="Q27" s="6" t="n">
         <v>89.70999999999999</v>
       </c>
-      <c r="R27" s="7" t="n">
+      <c r="R27" s="6" t="n">
         <v>89.22</v>
       </c>
-      <c r="S27" s="7" t="n">
+      <c r="S27" s="6" t="n">
         <v>89.31999999999999</v>
       </c>
-      <c r="T27" s="7" t="n">
+      <c r="T27" s="6" t="n">
         <v>90.02</v>
       </c>
-      <c r="U27" s="7" t="n">
+      <c r="U27" s="6" t="n">
         <v>90.06</v>
       </c>
-      <c r="V27" s="7" t="n">
+      <c r="V27" s="6" t="n">
         <v>89.88</v>
       </c>
-      <c r="W27" s="7" t="n">
+      <c r="W27" s="6" t="n">
         <v>89.81</v>
       </c>
-      <c r="X27" s="7" t="n">
+      <c r="X27" s="6" t="n">
         <v>89.81999999999999</v>
       </c>
-      <c r="Y27" s="7" t="n">
+      <c r="Y27" s="6" t="n">
         <v>89.81</v>
       </c>
-      <c r="Z27" s="7" t="n">
+      <c r="Z27" s="6" t="n">
         <v>89.56</v>
       </c>
       <c r="AA27" s="6" t="inlineStr">
@@ -2893,16 +2860,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD27" s="7" t="n">
+      <c r="AD27" s="6" t="n">
         <v>90.26000000000001</v>
       </c>
-      <c r="AE27" s="7" t="n">
+      <c r="AE27" s="6" t="n">
         <v>89.19</v>
       </c>
-      <c r="AF27" s="7" t="n">
+      <c r="AF27" s="6" t="n">
         <v>89.26000000000001</v>
       </c>
-      <c r="AG27" s="7" t="n">
+      <c r="AG27" s="6" t="n">
         <v>89.41</v>
       </c>
       <c r="AH27" s="6" t="n">
@@ -2912,7 +2879,7 @@
         <v>315.07</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -2923,76 +2890,76 @@
       <c r="B28" s="6" t="n">
         <v>101.7</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="6" t="n">
         <v>95.06999999999999</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D28" s="6" t="n">
         <v>95.45</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E28" s="6" t="n">
         <v>95.17</v>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F28" s="6" t="n">
         <v>96.01000000000001</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>95.23999999999999</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="6" t="n">
         <v>95.89</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="6" t="n">
         <v>95.45999999999999</v>
       </c>
-      <c r="J28" s="7" t="n">
+      <c r="J28" s="6" t="n">
         <v>95.34</v>
       </c>
-      <c r="K28" s="7" t="n">
+      <c r="K28" s="6" t="n">
         <v>95.73999999999999</v>
       </c>
-      <c r="L28" s="7" t="n">
+      <c r="L28" s="6" t="n">
         <v>95.16</v>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="M28" s="6" t="n">
         <v>93.95999999999999</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="N28" s="6" t="n">
         <v>94.33</v>
       </c>
-      <c r="O28" s="7" t="n">
+      <c r="O28" s="6" t="n">
         <v>94.28</v>
       </c>
-      <c r="P28" s="7" t="n">
+      <c r="P28" s="6" t="n">
         <v>93.86</v>
       </c>
-      <c r="Q28" s="7" t="n">
+      <c r="Q28" s="6" t="n">
         <v>93.70999999999999</v>
       </c>
-      <c r="R28" s="7" t="n">
+      <c r="R28" s="6" t="n">
         <v>93.66</v>
       </c>
-      <c r="S28" s="7" t="n">
+      <c r="S28" s="6" t="n">
         <v>93.48</v>
       </c>
-      <c r="T28" s="7" t="n">
+      <c r="T28" s="6" t="n">
         <v>92.98999999999999</v>
       </c>
-      <c r="U28" s="7" t="n">
+      <c r="U28" s="6" t="n">
         <v>93.19</v>
       </c>
-      <c r="V28" s="7" t="n">
+      <c r="V28" s="6" t="n">
         <v>93.31999999999999</v>
       </c>
-      <c r="W28" s="7" t="n">
+      <c r="W28" s="6" t="n">
         <v>93.22</v>
       </c>
-      <c r="X28" s="7" t="n">
+      <c r="X28" s="6" t="n">
         <v>92.98</v>
       </c>
-      <c r="Y28" s="7" t="n">
+      <c r="Y28" s="6" t="n">
         <v>93.08</v>
       </c>
-      <c r="Z28" s="7" t="n">
+      <c r="Z28" s="6" t="n">
         <v>92.95999999999999</v>
       </c>
       <c r="AA28" s="6" t="inlineStr">
@@ -3010,16 +2977,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD28" s="7" t="n">
+      <c r="AD28" s="6" t="n">
         <v>88.22</v>
       </c>
-      <c r="AE28" s="7" t="n">
+      <c r="AE28" s="6" t="n">
         <v>94.93000000000001</v>
       </c>
-      <c r="AF28" s="7" t="n">
+      <c r="AF28" s="6" t="n">
         <v>95.78</v>
       </c>
-      <c r="AG28" s="7" t="n">
+      <c r="AG28" s="6" t="n">
         <v>95.53</v>
       </c>
       <c r="AH28" s="6" t="n">
@@ -3029,7 +2996,7 @@
         <v>244.12</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3040,76 +3007,76 @@
       <c r="B29" s="6" t="n">
         <v>105.7</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="6" t="n">
         <v>44.26</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="6" t="n">
         <v>43.4</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="6" t="n">
         <v>42.87</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="6" t="n">
         <v>43.78</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="6" t="n">
         <v>45.04</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="6" t="n">
         <v>43.91</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" s="6" t="n">
         <v>44.14</v>
       </c>
-      <c r="J29" s="10" t="n">
+      <c r="J29" s="6" t="n">
         <v>42.84</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="6" t="n">
         <v>44.14</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="6" t="n">
         <v>43.75</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="6" t="n">
         <v>48.48</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="6" t="n">
         <v>47.18</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="6" t="n">
         <v>44.35</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="6" t="n">
         <v>45.84</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="6" t="n">
         <v>46.76</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="6" t="n">
         <v>47.58</v>
       </c>
-      <c r="S29" s="9" t="n">
+      <c r="S29" s="6" t="n">
         <v>45.74</v>
       </c>
-      <c r="T29" s="10" t="n">
+      <c r="T29" s="6" t="n">
         <v>42.89</v>
       </c>
-      <c r="U29" s="10" t="n">
+      <c r="U29" s="6" t="n">
         <v>41.15</v>
       </c>
-      <c r="V29" s="10" t="n">
+      <c r="V29" s="6" t="n">
         <v>42.51</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="6" t="n">
         <v>43.88</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="X29" s="6" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y29" s="10" t="n">
+      <c r="Y29" s="6" t="n">
         <v>42.28</v>
       </c>
-      <c r="Z29" s="9" t="n">
+      <c r="Z29" s="6" t="n">
         <v>44.64</v>
       </c>
       <c r="AA29" s="6" t="inlineStr">
@@ -3127,16 +3094,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD29" s="10" t="n">
+      <c r="AD29" s="6" t="n">
         <v>41.87</v>
       </c>
-      <c r="AE29" s="10" t="n">
+      <c r="AE29" s="6" t="n">
         <v>42.42</v>
       </c>
-      <c r="AF29" s="10" t="n">
+      <c r="AF29" s="6" t="n">
         <v>41.86</v>
       </c>
-      <c r="AG29" s="9" t="n">
+      <c r="AG29" s="6" t="n">
         <v>43.46</v>
       </c>
       <c r="AH29" s="6" t="n">
@@ -3146,7 +3113,7 @@
         <v>483.6</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3157,76 +3124,76 @@
       <c r="B30" s="6" t="n">
         <v>106.1</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="6" t="n">
         <v>93.23</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D30" s="6" t="n">
         <v>93.48999999999999</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E30" s="6" t="n">
         <v>93.69</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F30" s="6" t="n">
         <v>93.81</v>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="6" t="n">
         <v>93.94</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H30" s="6" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="6" t="n">
         <v>93.86</v>
       </c>
-      <c r="J30" s="7" t="n">
+      <c r="J30" s="6" t="n">
         <v>93.83</v>
       </c>
-      <c r="K30" s="7" t="n">
+      <c r="K30" s="6" t="n">
         <v>93.98999999999999</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="L30" s="6" t="n">
         <v>93.70999999999999</v>
       </c>
-      <c r="M30" s="7" t="n">
+      <c r="M30" s="6" t="n">
         <v>93.76000000000001</v>
       </c>
-      <c r="N30" s="7" t="n">
+      <c r="N30" s="6" t="n">
         <v>93.42</v>
       </c>
-      <c r="O30" s="7" t="n">
+      <c r="O30" s="6" t="n">
         <v>93.77</v>
       </c>
-      <c r="P30" s="7" t="n">
+      <c r="P30" s="6" t="n">
         <v>94.01000000000001</v>
       </c>
-      <c r="Q30" s="7" t="n">
+      <c r="Q30" s="6" t="n">
         <v>93.72</v>
       </c>
-      <c r="R30" s="7" t="n">
+      <c r="R30" s="6" t="n">
         <v>93.48</v>
       </c>
-      <c r="S30" s="7" t="n">
+      <c r="S30" s="6" t="n">
         <v>93.78</v>
       </c>
-      <c r="T30" s="7" t="n">
+      <c r="T30" s="6" t="n">
         <v>93.89</v>
       </c>
-      <c r="U30" s="7" t="n">
+      <c r="U30" s="6" t="n">
         <v>94.01000000000001</v>
       </c>
-      <c r="V30" s="7" t="n">
+      <c r="V30" s="6" t="n">
         <v>93.81999999999999</v>
       </c>
-      <c r="W30" s="7" t="n">
+      <c r="W30" s="6" t="n">
         <v>94.14</v>
       </c>
-      <c r="X30" s="7" t="n">
+      <c r="X30" s="6" t="n">
         <v>93.48999999999999</v>
       </c>
-      <c r="Y30" s="7" t="n">
+      <c r="Y30" s="6" t="n">
         <v>93.56</v>
       </c>
-      <c r="Z30" s="7" t="n">
+      <c r="Z30" s="6" t="n">
         <v>93.34999999999999</v>
       </c>
       <c r="AA30" s="6" t="inlineStr">
@@ -3244,16 +3211,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD30" s="7" t="n">
+      <c r="AD30" s="6" t="n">
         <v>93.14</v>
       </c>
-      <c r="AE30" s="7" t="n">
+      <c r="AE30" s="6" t="n">
         <v>93.41</v>
       </c>
-      <c r="AF30" s="7" t="n">
+      <c r="AF30" s="6" t="n">
         <v>93.56999999999999</v>
       </c>
-      <c r="AG30" s="7" t="n">
+      <c r="AG30" s="6" t="n">
         <v>93.66</v>
       </c>
       <c r="AH30" s="6" t="n">
@@ -3263,7 +3230,7 @@
         <v>165.25</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3274,76 +3241,76 @@
       <c r="B31" s="6" t="n">
         <v>106.9</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="6" t="n">
         <v>95.87</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="6" t="n">
         <v>92.8</v>
       </c>
-      <c r="E31" s="7" t="n">
+      <c r="E31" s="6" t="n">
         <v>89.73</v>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F31" s="6" t="n">
         <v>95.20999999999999</v>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="6" t="n">
         <v>91.89</v>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="6" t="n">
         <v>91.70999999999999</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="6" t="n">
         <v>92.11</v>
       </c>
-      <c r="J31" s="7" t="n">
+      <c r="J31" s="6" t="n">
         <v>91.36</v>
       </c>
-      <c r="K31" s="7" t="n">
+      <c r="K31" s="6" t="n">
         <v>91.63</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="L31" s="6" t="n">
         <v>91.56999999999999</v>
       </c>
-      <c r="M31" s="7" t="n">
+      <c r="M31" s="6" t="n">
         <v>91.55</v>
       </c>
-      <c r="N31" s="7" t="n">
+      <c r="N31" s="6" t="n">
         <v>92.47</v>
       </c>
-      <c r="O31" s="7" t="n">
+      <c r="O31" s="6" t="n">
         <v>92.87</v>
       </c>
-      <c r="P31" s="7" t="n">
+      <c r="P31" s="6" t="n">
         <v>92.89</v>
       </c>
-      <c r="Q31" s="7" t="n">
+      <c r="Q31" s="6" t="n">
         <v>92.98</v>
       </c>
-      <c r="R31" s="7" t="n">
+      <c r="R31" s="6" t="n">
         <v>92.31999999999999</v>
       </c>
-      <c r="S31" s="7" t="n">
+      <c r="S31" s="6" t="n">
         <v>92.94</v>
       </c>
-      <c r="T31" s="7" t="n">
+      <c r="T31" s="6" t="n">
         <v>95.68000000000001</v>
       </c>
-      <c r="U31" s="7" t="n">
+      <c r="U31" s="6" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="V31" s="7" t="n">
+      <c r="V31" s="6" t="n">
         <v>92.45999999999999</v>
       </c>
-      <c r="W31" s="7" t="n">
+      <c r="W31" s="6" t="n">
         <v>92.95</v>
       </c>
-      <c r="X31" s="7" t="n">
+      <c r="X31" s="6" t="n">
         <v>92.76000000000001</v>
       </c>
-      <c r="Y31" s="7" t="n">
+      <c r="Y31" s="6" t="n">
         <v>92.53</v>
       </c>
-      <c r="Z31" s="7" t="n">
+      <c r="Z31" s="6" t="n">
         <v>95.41</v>
       </c>
       <c r="AA31" s="6" t="inlineStr">
@@ -3361,16 +3328,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD31" s="7" t="n">
+      <c r="AD31" s="6" t="n">
         <v>95.22</v>
       </c>
-      <c r="AE31" s="7" t="n">
+      <c r="AE31" s="6" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="AF31" s="7" t="n">
+      <c r="AF31" s="6" t="n">
         <v>92.39</v>
       </c>
-      <c r="AG31" s="7" t="n">
+      <c r="AG31" s="6" t="n">
         <v>92.54000000000001</v>
       </c>
       <c r="AH31" s="6" t="n">
@@ -3380,7 +3347,7 @@
         <v>243.85</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3391,76 +3358,76 @@
       <c r="B32" s="6" t="n">
         <v>107.3</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="6" t="n">
         <v>89.27</v>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D32" s="6" t="n">
         <v>88.7</v>
       </c>
-      <c r="E32" s="7" t="n">
+      <c r="E32" s="6" t="n">
         <v>88.43000000000001</v>
       </c>
-      <c r="F32" s="7" t="n">
+      <c r="F32" s="6" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="6" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="6" t="n">
         <v>89.02</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="6" t="n">
         <v>68.03</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="6" t="n">
         <v>46.18</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="K32" s="6" t="n">
         <v>88.91</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="L32" s="6" t="n">
         <v>88.97</v>
       </c>
-      <c r="M32" s="7" t="n">
+      <c r="M32" s="6" t="n">
         <v>88.75</v>
       </c>
-      <c r="N32" s="7" t="n">
+      <c r="N32" s="6" t="n">
         <v>88.88</v>
       </c>
-      <c r="O32" s="7" t="n">
+      <c r="O32" s="6" t="n">
         <v>89.19</v>
       </c>
-      <c r="P32" s="7" t="n">
+      <c r="P32" s="6" t="n">
         <v>89.51000000000001</v>
       </c>
-      <c r="Q32" s="7" t="n">
+      <c r="Q32" s="6" t="n">
         <v>89.79000000000001</v>
       </c>
-      <c r="R32" s="7" t="n">
+      <c r="R32" s="6" t="n">
         <v>89.64</v>
       </c>
-      <c r="S32" s="7" t="n">
+      <c r="S32" s="6" t="n">
         <v>89.63</v>
       </c>
-      <c r="T32" s="7" t="n">
+      <c r="T32" s="6" t="n">
         <v>89.18000000000001</v>
       </c>
-      <c r="U32" s="7" t="n">
+      <c r="U32" s="6" t="n">
         <v>89.20999999999999</v>
       </c>
-      <c r="V32" s="7" t="n">
+      <c r="V32" s="6" t="n">
         <v>89.44</v>
       </c>
-      <c r="W32" s="7" t="n">
+      <c r="W32" s="6" t="n">
         <v>90.08</v>
       </c>
-      <c r="X32" s="7" t="n">
+      <c r="X32" s="6" t="n">
         <v>89.84999999999999</v>
       </c>
-      <c r="Y32" s="7" t="n">
+      <c r="Y32" s="6" t="n">
         <v>89.40000000000001</v>
       </c>
-      <c r="Z32" s="7" t="n">
+      <c r="Z32" s="6" t="n">
         <v>89.25</v>
       </c>
       <c r="AA32" s="6" t="inlineStr">
@@ -3478,16 +3445,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD32" s="7" t="n">
+      <c r="AD32" s="6" t="n">
         <v>89.64</v>
       </c>
-      <c r="AE32" s="7" t="n">
+      <c r="AE32" s="6" t="n">
         <v>89.58</v>
       </c>
-      <c r="AF32" s="7" t="n">
+      <c r="AF32" s="6" t="n">
         <v>90.16</v>
       </c>
-      <c r="AG32" s="7" t="n">
+      <c r="AG32" s="6" t="n">
         <v>89.7</v>
       </c>
       <c r="AH32" s="6" t="n">
@@ -3497,124 +3464,124 @@
         <v>332.07</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>RADIO CAÑARI</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="9" t="n">
         <v>107.7</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="9" t="n">
         <v>92.8</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="9" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="9" t="n">
         <v>91.36</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="9" t="n">
         <v>91.81</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="9" t="n">
         <v>92.20999999999999</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="9" t="n">
         <v>92.84999999999999</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="I33" s="9" t="n">
         <v>92.97</v>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="9" t="n">
         <v>92.06</v>
       </c>
-      <c r="K33" s="13" t="n">
+      <c r="K33" s="9" t="n">
         <v>92.05</v>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="9" t="n">
         <v>91.97</v>
       </c>
-      <c r="M33" s="13" t="n">
+      <c r="M33" s="9" t="n">
         <v>91.98</v>
       </c>
-      <c r="N33" s="13" t="n">
+      <c r="N33" s="9" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="O33" s="13" t="n">
+      <c r="O33" s="9" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="P33" s="13" t="n">
+      <c r="P33" s="9" t="n">
         <v>92.14</v>
       </c>
-      <c r="Q33" s="13" t="n">
+      <c r="Q33" s="9" t="n">
         <v>92.78</v>
       </c>
-      <c r="R33" s="13" t="n">
+      <c r="R33" s="9" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="S33" s="13" t="n">
+      <c r="S33" s="9" t="n">
         <v>92.78</v>
       </c>
-      <c r="T33" s="13" t="n">
+      <c r="T33" s="9" t="n">
         <v>92.92</v>
       </c>
-      <c r="U33" s="13" t="n">
+      <c r="U33" s="9" t="n">
         <v>91.84</v>
       </c>
-      <c r="V33" s="13" t="n">
+      <c r="V33" s="9" t="n">
         <v>92.84</v>
       </c>
-      <c r="W33" s="13" t="n">
+      <c r="W33" s="9" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="X33" s="13" t="n">
+      <c r="X33" s="9" t="n">
         <v>92.89</v>
       </c>
-      <c r="Y33" s="13" t="n">
+      <c r="Y33" s="9" t="n">
         <v>92.36</v>
       </c>
-      <c r="Z33" s="13" t="n">
+      <c r="Z33" s="9" t="n">
         <v>93.11</v>
       </c>
-      <c r="AA33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD33" s="13" t="n">
+      <c r="AA33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="9" t="n">
         <v>93.01000000000001</v>
       </c>
-      <c r="AE33" s="13" t="n">
+      <c r="AE33" s="9" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="AF33" s="13" t="n">
+      <c r="AF33" s="9" t="n">
         <v>92.98</v>
       </c>
-      <c r="AG33" s="13" t="n">
+      <c r="AG33" s="9" t="n">
         <v>93.02</v>
       </c>
-      <c r="AH33" s="12" t="n">
+      <c r="AH33" s="9" t="n">
         <v>92.45</v>
       </c>
-      <c r="AI33" s="12" t="n">
+      <c r="AI33" s="9" t="n">
         <v>269.05</v>
       </c>
-      <c r="AJ33" s="12" t="inlineStr"/>
-      <c r="AK33" s="14" t="inlineStr"/>
+      <c r="AJ33" s="9" t="inlineStr"/>
+      <c r="AK33" s="10" t="inlineStr"/>
     </row>
     <row r="34"/>
     <row r="35"/>
@@ -3649,7 +3616,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>CIUDAD:tambo</t>
+          <t>CIUDAD:CAÑAR</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3630,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 27/08/2025</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3756,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK43" s="15" t="n"/>
+      <c r="AK43" s="11" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3800,76 +3767,76 @@
       <c r="B44" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="6" t="n">
         <v>54.45</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="6" t="n">
         <v>54.48</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="6" t="n">
         <v>57.77</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="6" t="n">
         <v>54.82</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="6" t="n">
         <v>55.26</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="6" t="n">
         <v>56.32</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="I44" s="6" t="n">
         <v>56.04</v>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="J44" s="6" t="n">
         <v>55.54</v>
       </c>
-      <c r="K44" s="7" t="n">
+      <c r="K44" s="6" t="n">
         <v>56.45</v>
       </c>
-      <c r="L44" s="7" t="n">
+      <c r="L44" s="6" t="n">
         <v>56.89</v>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="6" t="n">
         <v>56.92</v>
       </c>
-      <c r="N44" s="7" t="n">
+      <c r="N44" s="6" t="n">
         <v>57.59</v>
       </c>
-      <c r="O44" s="7" t="n">
+      <c r="O44" s="6" t="n">
         <v>57.66</v>
       </c>
-      <c r="P44" s="7" t="n">
+      <c r="P44" s="6" t="n">
         <v>55.07</v>
       </c>
-      <c r="Q44" s="7" t="n">
+      <c r="Q44" s="6" t="n">
         <v>54.17</v>
       </c>
-      <c r="R44" s="7" t="n">
+      <c r="R44" s="6" t="n">
         <v>56.31</v>
       </c>
-      <c r="S44" s="7" t="n">
+      <c r="S44" s="6" t="n">
         <v>55.18</v>
       </c>
-      <c r="T44" s="7" t="n">
+      <c r="T44" s="6" t="n">
         <v>56.62</v>
       </c>
-      <c r="U44" s="7" t="n">
+      <c r="U44" s="6" t="n">
         <v>55.28</v>
       </c>
-      <c r="V44" s="7" t="n">
+      <c r="V44" s="6" t="n">
         <v>54.73</v>
       </c>
-      <c r="W44" s="7" t="n">
+      <c r="W44" s="6" t="n">
         <v>55.07</v>
       </c>
-      <c r="X44" s="7" t="n">
+      <c r="X44" s="6" t="n">
         <v>54.94</v>
       </c>
-      <c r="Y44" s="7" t="n">
+      <c r="Y44" s="6" t="n">
         <v>57.08</v>
       </c>
-      <c r="Z44" s="7" t="n">
+      <c r="Z44" s="6" t="n">
         <v>54.75</v>
       </c>
       <c r="AA44" s="6" t="inlineStr">
@@ -3887,16 +3854,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD44" s="9" t="n">
+      <c r="AD44" s="6" t="n">
         <v>52.19</v>
       </c>
-      <c r="AE44" s="7" t="n">
+      <c r="AE44" s="6" t="n">
         <v>54.52</v>
       </c>
-      <c r="AF44" s="7" t="n">
+      <c r="AF44" s="6" t="n">
         <v>54.88</v>
       </c>
-      <c r="AG44" s="7" t="n">
+      <c r="AG44" s="6" t="n">
         <v>54.43</v>
       </c>
       <c r="AH44" s="6" t="n">
@@ -3904,7 +3871,7 @@
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="16" t="n"/>
+      <c r="AK44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3915,76 +3882,76 @@
       <c r="B45" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="6" t="n">
         <v>62.47</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="6" t="n">
         <v>60.99</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="6" t="n">
         <v>59.32</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="6" t="n">
         <v>61.95</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="6" t="n">
         <v>61.42</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="6" t="n">
         <v>61.35</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="6" t="n">
         <v>60.77</v>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="J45" s="6" t="n">
         <v>60.27</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="K45" s="6" t="n">
         <v>59.26</v>
       </c>
-      <c r="L45" s="7" t="n">
+      <c r="L45" s="6" t="n">
         <v>59.13</v>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="6" t="n">
         <v>59.08</v>
       </c>
-      <c r="N45" s="7" t="n">
+      <c r="N45" s="6" t="n">
         <v>57.83</v>
       </c>
-      <c r="O45" s="7" t="n">
+      <c r="O45" s="6" t="n">
         <v>58.15</v>
       </c>
-      <c r="P45" s="7" t="n">
+      <c r="P45" s="6" t="n">
         <v>62.37</v>
       </c>
-      <c r="Q45" s="7" t="n">
+      <c r="Q45" s="6" t="n">
         <v>62.44</v>
       </c>
-      <c r="R45" s="7" t="n">
+      <c r="R45" s="6" t="n">
         <v>59.07</v>
       </c>
-      <c r="S45" s="7" t="n">
+      <c r="S45" s="6" t="n">
         <v>61.21</v>
       </c>
-      <c r="T45" s="7" t="n">
+      <c r="T45" s="6" t="n">
         <v>58.95</v>
       </c>
-      <c r="U45" s="7" t="n">
+      <c r="U45" s="6" t="n">
         <v>61.47</v>
       </c>
-      <c r="V45" s="7" t="n">
+      <c r="V45" s="6" t="n">
         <v>62.25</v>
       </c>
-      <c r="W45" s="7" t="n">
+      <c r="W45" s="6" t="n">
         <v>62</v>
       </c>
-      <c r="X45" s="7" t="n">
+      <c r="X45" s="6" t="n">
         <v>62.32</v>
       </c>
-      <c r="Y45" s="7" t="n">
+      <c r="Y45" s="6" t="n">
         <v>60.83</v>
       </c>
-      <c r="Z45" s="7" t="n">
+      <c r="Z45" s="6" t="n">
         <v>62.26</v>
       </c>
       <c r="AA45" s="6" t="inlineStr">
@@ -4002,16 +3969,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD45" s="7" t="n">
+      <c r="AD45" s="6" t="n">
         <v>62.62</v>
       </c>
-      <c r="AE45" s="7" t="n">
+      <c r="AE45" s="6" t="n">
         <v>62.34</v>
       </c>
-      <c r="AF45" s="7" t="n">
+      <c r="AF45" s="6" t="n">
         <v>62.65</v>
       </c>
-      <c r="AG45" s="7" t="n">
+      <c r="AG45" s="6" t="n">
         <v>63.19</v>
       </c>
       <c r="AH45" s="6" t="n">
@@ -4019,7 +3986,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="16" t="n"/>
+      <c r="AK45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4030,76 +3997,76 @@
       <c r="B46" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="6" t="n">
         <v>30.76</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="6" t="n">
         <v>31.32</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="6" t="n">
         <v>32.11</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="6" t="n">
         <v>30.86</v>
       </c>
-      <c r="G46" s="10" t="n">
+      <c r="G46" s="6" t="n">
         <v>28.58</v>
       </c>
-      <c r="H46" s="10" t="n">
+      <c r="H46" s="6" t="n">
         <v>29.81</v>
       </c>
-      <c r="I46" s="10" t="n">
+      <c r="I46" s="6" t="n">
         <v>27.63</v>
       </c>
-      <c r="J46" s="10" t="n">
+      <c r="J46" s="6" t="n">
         <v>31.39</v>
       </c>
-      <c r="K46" s="10" t="n">
+      <c r="K46" s="6" t="n">
         <v>31.98</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" s="6" t="n">
         <v>31.91</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="6" t="n">
         <v>33.47</v>
       </c>
-      <c r="N46" s="10" t="n">
+      <c r="N46" s="6" t="n">
         <v>31.81</v>
       </c>
-      <c r="O46" s="10" t="n">
+      <c r="O46" s="6" t="n">
         <v>28.62</v>
       </c>
-      <c r="P46" s="10" t="n">
+      <c r="P46" s="6" t="n">
         <v>24.98</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="6" t="n">
         <v>27.11</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="6" t="n">
         <v>27.55</v>
       </c>
-      <c r="S46" s="10" t="n">
+      <c r="S46" s="6" t="n">
         <v>29.39</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="T46" s="6" t="n">
         <v>30.03</v>
       </c>
-      <c r="U46" s="10" t="n">
+      <c r="U46" s="6" t="n">
         <v>29.37</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="6" t="n">
         <v>27.43</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="6" t="n">
         <v>24.95</v>
       </c>
-      <c r="X46" s="10" t="n">
+      <c r="X46" s="6" t="n">
         <v>28.58</v>
       </c>
-      <c r="Y46" s="10" t="n">
+      <c r="Y46" s="6" t="n">
         <v>30.77</v>
       </c>
-      <c r="Z46" s="10" t="n">
+      <c r="Z46" s="6" t="n">
         <v>28.12</v>
       </c>
       <c r="AA46" s="6" t="inlineStr">
@@ -4117,16 +4084,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD46" s="10" t="n">
+      <c r="AD46" s="6" t="n">
         <v>27.18</v>
       </c>
-      <c r="AE46" s="10" t="n">
+      <c r="AE46" s="6" t="n">
         <v>27.85</v>
       </c>
-      <c r="AF46" s="10" t="n">
+      <c r="AF46" s="6" t="n">
         <v>26.6</v>
       </c>
-      <c r="AG46" s="10" t="n">
+      <c r="AG46" s="6" t="n">
         <v>26.24</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4134,7 +4101,7 @@
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="16" t="n"/>
+      <c r="AK46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4145,76 +4112,76 @@
       <c r="B47" s="6" t="n">
         <v>193.25</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="6" t="n">
         <v>46.3</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D47" s="6" t="n">
         <v>46.33</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="6" t="n">
         <v>46.39</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="6" t="n">
         <v>47.05</v>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="G47" s="6" t="n">
         <v>47.51</v>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="H47" s="6" t="n">
         <v>48.13</v>
       </c>
-      <c r="I47" s="9" t="n">
+      <c r="I47" s="6" t="n">
         <v>46.25</v>
       </c>
-      <c r="J47" s="9" t="n">
+      <c r="J47" s="6" t="n">
         <v>47.56</v>
       </c>
-      <c r="K47" s="9" t="n">
+      <c r="K47" s="6" t="n">
         <v>49.26</v>
       </c>
-      <c r="L47" s="9" t="n">
+      <c r="L47" s="6" t="n">
         <v>47.54</v>
       </c>
-      <c r="M47" s="9" t="n">
+      <c r="M47" s="6" t="n">
         <v>48.23</v>
       </c>
-      <c r="N47" s="9" t="n">
+      <c r="N47" s="6" t="n">
         <v>46.86</v>
       </c>
-      <c r="O47" s="9" t="n">
+      <c r="O47" s="6" t="n">
         <v>45.58</v>
       </c>
-      <c r="P47" s="9" t="n">
+      <c r="P47" s="6" t="n">
         <v>45.14</v>
       </c>
-      <c r="Q47" s="9" t="n">
+      <c r="Q47" s="6" t="n">
         <v>46.13</v>
       </c>
-      <c r="R47" s="9" t="n">
+      <c r="R47" s="6" t="n">
         <v>46.38</v>
       </c>
-      <c r="S47" s="9" t="n">
+      <c r="S47" s="6" t="n">
         <v>46.3</v>
       </c>
-      <c r="T47" s="9" t="n">
+      <c r="T47" s="6" t="n">
         <v>49.68</v>
       </c>
-      <c r="U47" s="9" t="n">
+      <c r="U47" s="6" t="n">
         <v>49.32</v>
       </c>
-      <c r="V47" s="9" t="n">
+      <c r="V47" s="6" t="n">
         <v>47.83</v>
       </c>
-      <c r="W47" s="9" t="n">
+      <c r="W47" s="6" t="n">
         <v>45.16</v>
       </c>
-      <c r="X47" s="9" t="n">
+      <c r="X47" s="6" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y47" s="9" t="n">
+      <c r="Y47" s="6" t="n">
         <v>48.44</v>
       </c>
-      <c r="Z47" s="9" t="n">
+      <c r="Z47" s="6" t="n">
         <v>46.78</v>
       </c>
       <c r="AA47" s="6" t="inlineStr">
@@ -4232,16 +4199,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD47" s="9" t="n">
+      <c r="AD47" s="6" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE47" s="9" t="n">
+      <c r="AE47" s="6" t="n">
         <v>47.77</v>
       </c>
-      <c r="AF47" s="9" t="n">
+      <c r="AF47" s="6" t="n">
         <v>47.22</v>
       </c>
-      <c r="AG47" s="9" t="n">
+      <c r="AG47" s="6" t="n">
         <v>47.83</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -4249,7 +4216,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="16" t="n"/>
+      <c r="AK47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4260,76 +4227,76 @@
       <c r="B48" s="6" t="n">
         <v>205.25</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="6" t="n">
         <v>20.25</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="6" t="n">
         <v>19.44</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E48" s="6" t="n">
         <v>18.66</v>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="6" t="n">
         <v>21.06</v>
       </c>
-      <c r="G48" s="10" t="n">
+      <c r="G48" s="6" t="n">
         <v>19.93</v>
       </c>
-      <c r="H48" s="10" t="n">
+      <c r="H48" s="6" t="n">
         <v>20.95</v>
       </c>
-      <c r="I48" s="10" t="n">
+      <c r="I48" s="6" t="n">
         <v>21.35</v>
       </c>
-      <c r="J48" s="10" t="n">
+      <c r="J48" s="6" t="n">
         <v>19.73</v>
       </c>
-      <c r="K48" s="10" t="n">
+      <c r="K48" s="6" t="n">
         <v>20.03</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L48" s="6" t="n">
         <v>19.83</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="6" t="n">
         <v>19.34</v>
       </c>
-      <c r="N48" s="10" t="n">
+      <c r="N48" s="6" t="n">
         <v>20.03</v>
       </c>
-      <c r="O48" s="10" t="n">
+      <c r="O48" s="6" t="n">
         <v>20.25</v>
       </c>
-      <c r="P48" s="10" t="n">
+      <c r="P48" s="6" t="n">
         <v>19.31</v>
       </c>
-      <c r="Q48" s="10" t="n">
+      <c r="Q48" s="6" t="n">
         <v>21.73</v>
       </c>
-      <c r="R48" s="10" t="n">
+      <c r="R48" s="6" t="n">
         <v>21.23</v>
       </c>
-      <c r="S48" s="10" t="n">
+      <c r="S48" s="6" t="n">
         <v>19.64</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="T48" s="6" t="n">
         <v>20.19</v>
       </c>
-      <c r="U48" s="10" t="n">
+      <c r="U48" s="6" t="n">
         <v>20.4</v>
       </c>
-      <c r="V48" s="10" t="n">
+      <c r="V48" s="6" t="n">
         <v>20.01</v>
       </c>
-      <c r="W48" s="10" t="n">
+      <c r="W48" s="6" t="n">
         <v>20.09</v>
       </c>
-      <c r="X48" s="10" t="n">
+      <c r="X48" s="6" t="n">
         <v>19.82</v>
       </c>
-      <c r="Y48" s="10" t="n">
+      <c r="Y48" s="6" t="n">
         <v>20.22</v>
       </c>
-      <c r="Z48" s="10" t="n">
+      <c r="Z48" s="6" t="n">
         <v>20.75</v>
       </c>
       <c r="AA48" s="6" t="inlineStr">
@@ -4347,16 +4314,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD48" s="10" t="n">
+      <c r="AD48" s="6" t="n">
         <v>20.72</v>
       </c>
-      <c r="AE48" s="10" t="n">
+      <c r="AE48" s="6" t="n">
         <v>19.91</v>
       </c>
-      <c r="AF48" s="10" t="n">
+      <c r="AF48" s="6" t="n">
         <v>20.74</v>
       </c>
-      <c r="AG48" s="10" t="n">
+      <c r="AG48" s="6" t="n">
         <v>20.32</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -4364,7 +4331,7 @@
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="16" t="n"/>
+      <c r="AK48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4375,76 +4342,76 @@
       <c r="B49" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="6" t="n">
         <v>17.22</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D49" s="6" t="n">
         <v>17.16</v>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="E49" s="6" t="n">
         <v>16.48</v>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="F49" s="6" t="n">
         <v>20.09</v>
       </c>
-      <c r="G49" s="10" t="n">
+      <c r="G49" s="6" t="n">
         <v>17.15</v>
       </c>
-      <c r="H49" s="10" t="n">
+      <c r="H49" s="6" t="n">
         <v>16.65</v>
       </c>
-      <c r="I49" s="10" t="n">
+      <c r="I49" s="6" t="n">
         <v>17.38</v>
       </c>
-      <c r="J49" s="10" t="n">
+      <c r="J49" s="6" t="n">
         <v>17.17</v>
       </c>
-      <c r="K49" s="10" t="n">
+      <c r="K49" s="6" t="n">
         <v>16.77</v>
       </c>
-      <c r="L49" s="10" t="n">
+      <c r="L49" s="6" t="n">
         <v>16.8</v>
       </c>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="6" t="n">
         <v>16.85</v>
       </c>
-      <c r="N49" s="10" t="n">
+      <c r="N49" s="6" t="n">
         <v>16.67</v>
       </c>
-      <c r="O49" s="10" t="n">
+      <c r="O49" s="6" t="n">
         <v>16.78</v>
       </c>
-      <c r="P49" s="10" t="n">
+      <c r="P49" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="6" t="n">
         <v>16.78</v>
       </c>
-      <c r="R49" s="10" t="n">
+      <c r="R49" s="6" t="n">
         <v>16.69</v>
       </c>
-      <c r="S49" s="10" t="n">
+      <c r="S49" s="6" t="n">
         <v>17.09</v>
       </c>
-      <c r="T49" s="10" t="n">
+      <c r="T49" s="6" t="n">
         <v>16.92</v>
       </c>
-      <c r="U49" s="10" t="n">
+      <c r="U49" s="6" t="n">
         <v>16.91</v>
       </c>
-      <c r="V49" s="10" t="n">
+      <c r="V49" s="6" t="n">
         <v>17.3</v>
       </c>
-      <c r="W49" s="10" t="n">
+      <c r="W49" s="6" t="n">
         <v>17.05</v>
       </c>
-      <c r="X49" s="10" t="n">
+      <c r="X49" s="6" t="n">
         <v>16.87</v>
       </c>
-      <c r="Y49" s="10" t="n">
+      <c r="Y49" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="Z49" s="10" t="n">
+      <c r="Z49" s="6" t="n">
         <v>16.9</v>
       </c>
       <c r="AA49" s="6" t="inlineStr">
@@ -4462,16 +4429,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD49" s="10" t="n">
+      <c r="AD49" s="6" t="n">
         <v>16.85</v>
       </c>
-      <c r="AE49" s="10" t="n">
+      <c r="AE49" s="6" t="n">
         <v>16.5</v>
       </c>
-      <c r="AF49" s="10" t="n">
+      <c r="AF49" s="6" t="n">
         <v>16.61</v>
       </c>
-      <c r="AG49" s="10" t="n">
+      <c r="AG49" s="6" t="n">
         <v>16.54</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -4479,7 +4446,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="16" t="n"/>
+      <c r="AK49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4490,76 +4457,76 @@
       <c r="B50" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="6" t="n">
         <v>64.31999999999999</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="6" t="n">
         <v>65.59</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" s="6" t="n">
         <v>65.7</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="6" t="n">
         <v>29.7</v>
       </c>
-      <c r="G50" s="10" t="n">
+      <c r="G50" s="6" t="n">
         <v>31.15</v>
       </c>
-      <c r="H50" s="10" t="n">
+      <c r="H50" s="6" t="n">
         <v>30.96</v>
       </c>
-      <c r="I50" s="10" t="n">
+      <c r="I50" s="6" t="n">
         <v>30.68</v>
       </c>
-      <c r="J50" s="10" t="n">
+      <c r="J50" s="6" t="n">
         <v>30.74</v>
       </c>
-      <c r="K50" s="10" t="n">
+      <c r="K50" s="6" t="n">
         <v>30.38</v>
       </c>
-      <c r="L50" s="10" t="n">
+      <c r="L50" s="6" t="n">
         <v>30.17</v>
       </c>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="6" t="n">
         <v>30.75</v>
       </c>
-      <c r="N50" s="10" t="n">
+      <c r="N50" s="6" t="n">
         <v>29.89</v>
       </c>
-      <c r="O50" s="10" t="n">
+      <c r="O50" s="6" t="n">
         <v>30.15</v>
       </c>
-      <c r="P50" s="10" t="n">
+      <c r="P50" s="6" t="n">
         <v>31.64</v>
       </c>
-      <c r="Q50" s="10" t="n">
+      <c r="Q50" s="6" t="n">
         <v>30.28</v>
       </c>
-      <c r="R50" s="10" t="n">
+      <c r="R50" s="6" t="n">
         <v>31.09</v>
       </c>
-      <c r="S50" s="10" t="n">
+      <c r="S50" s="6" t="n">
         <v>30.65</v>
       </c>
-      <c r="T50" s="10" t="n">
+      <c r="T50" s="6" t="n">
         <v>32.47</v>
       </c>
-      <c r="U50" s="10" t="n">
+      <c r="U50" s="6" t="n">
         <v>31.51</v>
       </c>
-      <c r="V50" s="10" t="n">
+      <c r="V50" s="6" t="n">
         <v>30.9</v>
       </c>
-      <c r="W50" s="10" t="n">
+      <c r="W50" s="6" t="n">
         <v>32.99</v>
       </c>
-      <c r="X50" s="10" t="n">
+      <c r="X50" s="6" t="n">
         <v>27.85</v>
       </c>
-      <c r="Y50" s="10" t="n">
+      <c r="Y50" s="6" t="n">
         <v>28.3</v>
       </c>
-      <c r="Z50" s="10" t="n">
+      <c r="Z50" s="6" t="n">
         <v>28.28</v>
       </c>
       <c r="AA50" s="6" t="inlineStr">
@@ -4577,16 +4544,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD50" s="10" t="n">
+      <c r="AD50" s="6" t="n">
         <v>28.19</v>
       </c>
-      <c r="AE50" s="9" t="n">
+      <c r="AE50" s="6" t="n">
         <v>44.75</v>
       </c>
-      <c r="AF50" s="7" t="n">
+      <c r="AF50" s="6" t="n">
         <v>60.62</v>
       </c>
-      <c r="AG50" s="7" t="n">
+      <c r="AG50" s="6" t="n">
         <v>61.05</v>
       </c>
       <c r="AH50" s="6" t="n">
@@ -4594,7 +4561,7 @@
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="16" t="n"/>
+      <c r="AK50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -4605,76 +4572,76 @@
       <c r="B51" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="6" t="n">
         <v>22.82</v>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D51" s="6" t="n">
         <v>19.78</v>
       </c>
-      <c r="E51" s="10" t="n">
+      <c r="E51" s="6" t="n">
         <v>19.33</v>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="6" t="n">
         <v>20.23</v>
       </c>
-      <c r="G51" s="10" t="n">
+      <c r="G51" s="6" t="n">
         <v>20.96</v>
       </c>
-      <c r="H51" s="10" t="n">
+      <c r="H51" s="6" t="n">
         <v>21.43</v>
       </c>
-      <c r="I51" s="10" t="n">
+      <c r="I51" s="6" t="n">
         <v>20.83</v>
       </c>
-      <c r="J51" s="10" t="n">
+      <c r="J51" s="6" t="n">
         <v>20.46</v>
       </c>
-      <c r="K51" s="10" t="n">
+      <c r="K51" s="6" t="n">
         <v>20.8</v>
       </c>
-      <c r="L51" s="10" t="n">
+      <c r="L51" s="6" t="n">
         <v>19.84</v>
       </c>
-      <c r="M51" s="10" t="n">
+      <c r="M51" s="6" t="n">
         <v>19.92</v>
       </c>
-      <c r="N51" s="10" t="n">
+      <c r="N51" s="6" t="n">
         <v>20.16</v>
       </c>
-      <c r="O51" s="10" t="n">
+      <c r="O51" s="6" t="n">
         <v>20.13</v>
       </c>
-      <c r="P51" s="10" t="n">
+      <c r="P51" s="6" t="n">
         <v>22.75</v>
       </c>
-      <c r="Q51" s="10" t="n">
+      <c r="Q51" s="6" t="n">
         <v>20.9</v>
       </c>
-      <c r="R51" s="10" t="n">
+      <c r="R51" s="6" t="n">
         <v>20.58</v>
       </c>
-      <c r="S51" s="10" t="n">
+      <c r="S51" s="6" t="n">
         <v>20.58</v>
       </c>
-      <c r="T51" s="10" t="n">
+      <c r="T51" s="6" t="n">
         <v>22.65</v>
       </c>
-      <c r="U51" s="10" t="n">
+      <c r="U51" s="6" t="n">
         <v>21.7</v>
       </c>
-      <c r="V51" s="10" t="n">
+      <c r="V51" s="6" t="n">
         <v>19.97</v>
       </c>
-      <c r="W51" s="10" t="n">
+      <c r="W51" s="6" t="n">
         <v>20.77</v>
       </c>
-      <c r="X51" s="10" t="n">
+      <c r="X51" s="6" t="n">
         <v>20.33</v>
       </c>
-      <c r="Y51" s="10" t="n">
+      <c r="Y51" s="6" t="n">
         <v>20.74</v>
       </c>
-      <c r="Z51" s="10" t="n">
+      <c r="Z51" s="6" t="n">
         <v>21.79</v>
       </c>
       <c r="AA51" s="6" t="inlineStr">
@@ -4692,16 +4659,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD51" s="10" t="n">
+      <c r="AD51" s="6" t="n">
         <v>20.5</v>
       </c>
-      <c r="AE51" s="10" t="n">
+      <c r="AE51" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="AF51" s="10" t="n">
+      <c r="AF51" s="6" t="n">
         <v>20.99</v>
       </c>
-      <c r="AG51" s="10" t="n">
+      <c r="AG51" s="6" t="n">
         <v>21.88</v>
       </c>
       <c r="AH51" s="6" t="n">
@@ -4709,7 +4676,7 @@
       </c>
       <c r="AI51" s="6" t="inlineStr"/>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="16" t="n"/>
+      <c r="AK51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -4720,76 +4687,76 @@
       <c r="B52" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="6" t="n">
         <v>18.53</v>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E52" s="10" t="n">
+      <c r="E52" s="6" t="n">
         <v>17.98</v>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" s="6" t="n">
         <v>18.24</v>
       </c>
-      <c r="G52" s="10" t="n">
+      <c r="G52" s="6" t="n">
         <v>18.19</v>
       </c>
-      <c r="H52" s="10" t="n">
+      <c r="H52" s="6" t="n">
         <v>17.79</v>
       </c>
-      <c r="I52" s="10" t="n">
+      <c r="I52" s="6" t="n">
         <v>18.05</v>
       </c>
-      <c r="J52" s="10" t="n">
+      <c r="J52" s="6" t="n">
         <v>18.3</v>
       </c>
-      <c r="K52" s="10" t="n">
+      <c r="K52" s="6" t="n">
         <v>18.22</v>
       </c>
-      <c r="L52" s="10" t="n">
+      <c r="L52" s="6" t="n">
         <v>17.98</v>
       </c>
-      <c r="M52" s="10" t="n">
+      <c r="M52" s="6" t="n">
         <v>18.44</v>
       </c>
-      <c r="N52" s="10" t="n">
+      <c r="N52" s="6" t="n">
         <v>18.26</v>
       </c>
-      <c r="O52" s="10" t="n">
+      <c r="O52" s="6" t="n">
         <v>18.29</v>
       </c>
-      <c r="P52" s="10" t="n">
+      <c r="P52" s="6" t="n">
         <v>18.67</v>
       </c>
-      <c r="Q52" s="10" t="n">
+      <c r="Q52" s="6" t="n">
         <v>18.47</v>
       </c>
-      <c r="R52" s="10" t="n">
+      <c r="R52" s="6" t="n">
         <v>18.01</v>
       </c>
-      <c r="S52" s="10" t="n">
+      <c r="S52" s="6" t="n">
         <v>18.22</v>
       </c>
-      <c r="T52" s="10" t="n">
+      <c r="T52" s="6" t="n">
         <v>18.26</v>
       </c>
-      <c r="U52" s="10" t="n">
+      <c r="U52" s="6" t="n">
         <v>17.86</v>
       </c>
-      <c r="V52" s="10" t="n">
+      <c r="V52" s="6" t="n">
         <v>18.4</v>
       </c>
-      <c r="W52" s="10" t="n">
+      <c r="W52" s="6" t="n">
         <v>18.1</v>
       </c>
-      <c r="X52" s="10" t="n">
+      <c r="X52" s="6" t="n">
         <v>17.84</v>
       </c>
-      <c r="Y52" s="10" t="n">
+      <c r="Y52" s="6" t="n">
         <v>18.21</v>
       </c>
-      <c r="Z52" s="10" t="n">
+      <c r="Z52" s="6" t="n">
         <v>18.21</v>
       </c>
       <c r="AA52" s="6" t="inlineStr">
@@ -4807,16 +4774,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD52" s="10" t="n">
+      <c r="AD52" s="6" t="n">
         <v>18.28</v>
       </c>
-      <c r="AE52" s="10" t="n">
+      <c r="AE52" s="6" t="n">
         <v>17.92</v>
       </c>
-      <c r="AF52" s="10" t="n">
+      <c r="AF52" s="6" t="n">
         <v>19.01</v>
       </c>
-      <c r="AG52" s="10" t="n">
+      <c r="AG52" s="6" t="n">
         <v>17.87</v>
       </c>
       <c r="AH52" s="6" t="n">
@@ -4824,122 +4791,122 @@
       </c>
       <c r="AI52" s="6" t="inlineStr"/>
       <c r="AJ52" s="6" t="inlineStr"/>
-      <c r="AK52" s="16" t="n"/>
+      <c r="AK52" s="12" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="9" t="n">
         <v>621.25</v>
       </c>
-      <c r="C53" s="17" t="n">
+      <c r="C53" s="9" t="n">
         <v>17.95</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="9" t="n">
         <v>18.92</v>
       </c>
-      <c r="E53" s="17" t="n">
+      <c r="E53" s="9" t="n">
         <v>18.01</v>
       </c>
-      <c r="F53" s="17" t="n">
+      <c r="F53" s="9" t="n">
         <v>19.62</v>
       </c>
-      <c r="G53" s="17" t="n">
+      <c r="G53" s="9" t="n">
         <v>18.31</v>
       </c>
-      <c r="H53" s="17" t="n">
+      <c r="H53" s="9" t="n">
         <v>18.65</v>
       </c>
-      <c r="I53" s="17" t="n">
+      <c r="I53" s="9" t="n">
         <v>17.95</v>
       </c>
-      <c r="J53" s="17" t="n">
+      <c r="J53" s="9" t="n">
         <v>18.35</v>
       </c>
-      <c r="K53" s="17" t="n">
+      <c r="K53" s="9" t="n">
         <v>17.77</v>
       </c>
-      <c r="L53" s="17" t="n">
+      <c r="L53" s="9" t="n">
         <v>17.89</v>
       </c>
-      <c r="M53" s="17" t="n">
+      <c r="M53" s="9" t="n">
         <v>18.63</v>
       </c>
-      <c r="N53" s="17" t="n">
+      <c r="N53" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="O53" s="17" t="n">
+      <c r="O53" s="9" t="n">
         <v>18.66</v>
       </c>
-      <c r="P53" s="17" t="n">
+      <c r="P53" s="9" t="n">
         <v>18.17</v>
       </c>
-      <c r="Q53" s="17" t="n">
+      <c r="Q53" s="9" t="n">
         <v>17.78</v>
       </c>
-      <c r="R53" s="17" t="n">
+      <c r="R53" s="9" t="n">
         <v>17.77</v>
       </c>
-      <c r="S53" s="17" t="n">
+      <c r="S53" s="9" t="n">
         <v>18.17</v>
       </c>
-      <c r="T53" s="17" t="n">
+      <c r="T53" s="9" t="n">
         <v>18.65</v>
       </c>
-      <c r="U53" s="17" t="n">
+      <c r="U53" s="9" t="n">
         <v>18.15</v>
       </c>
-      <c r="V53" s="17" t="n">
+      <c r="V53" s="9" t="n">
         <v>18.39</v>
       </c>
-      <c r="W53" s="17" t="n">
+      <c r="W53" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="X53" s="17" t="n">
+      <c r="X53" s="9" t="n">
         <v>17.88</v>
       </c>
-      <c r="Y53" s="17" t="n">
+      <c r="Y53" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="Z53" s="17" t="n">
+      <c r="Z53" s="9" t="n">
         <v>17.42</v>
       </c>
-      <c r="AA53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD53" s="17" t="n">
+      <c r="AA53" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD53" s="9" t="n">
         <v>17.28</v>
       </c>
-      <c r="AE53" s="17" t="n">
+      <c r="AE53" s="9" t="n">
         <v>17.95</v>
       </c>
-      <c r="AF53" s="17" t="n">
+      <c r="AF53" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="AG53" s="17" t="n">
+      <c r="AG53" s="9" t="n">
         <v>17.93</v>
       </c>
-      <c r="AH53" s="12" t="n">
+      <c r="AH53" s="9" t="n">
         <v>18.18</v>
       </c>
-      <c r="AI53" s="12" t="inlineStr"/>
-      <c r="AJ53" s="12" t="inlineStr"/>
-      <c r="AK53" s="18" t="n"/>
+      <c r="AI53" s="9" t="inlineStr"/>
+      <c r="AJ53" s="9" t="inlineStr"/>
+      <c r="AK53" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFD9BCB"/>
         <bgColor rgb="FFFD9BCB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6666"/>
+        <bgColor rgb="FFFF6666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,6 +206,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -210,6 +228,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1033,14 +1057,14 @@
       <c r="AG11" s="7" t="n">
         <v>71.11</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="8" t="n">
         <v>70.79000000000001</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="9" t="n">
         <v>339.89</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1150,14 +1174,14 @@
       <c r="AG12" s="7" t="n">
         <v>93.13</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="8" t="n">
         <v>93.33</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="9" t="n">
         <v>215.38</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1267,14 +1291,14 @@
       <c r="AG13" s="7" t="n">
         <v>73.36</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="8" t="n">
         <v>74.42</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="9" t="n">
         <v>381.82</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1384,14 +1408,14 @@
       <c r="AG14" s="7" t="n">
         <v>96.36</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="8" t="n">
         <v>96.97</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="9" t="n">
         <v>394.82</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1402,76 +1426,76 @@
       <c r="B15" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="11" t="n">
         <v>51.91</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="11" t="n">
         <v>51.91</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="11" t="n">
         <v>53.71</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="11" t="n">
         <v>53.19</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="11" t="n">
         <v>52.31</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="11" t="n">
         <v>52.02</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="11" t="n">
         <v>51.63</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="11" t="n">
         <v>51.38</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="11" t="n">
         <v>52.8</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="11" t="n">
         <v>52.85</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="11" t="n">
         <v>52.05</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="N15" s="11" t="n">
         <v>51.7</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="11" t="n">
         <v>51.64</v>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="P15" s="11" t="n">
         <v>51.52</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="11" t="n">
         <v>51.34</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="11" t="n">
         <v>51.23</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="11" t="n">
         <v>51.05</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="11" t="n">
         <v>51.93</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="11" t="n">
         <v>51.36</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="11" t="n">
         <v>51.27</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="11" t="n">
         <v>51.31</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="11" t="n">
         <v>51.83</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="11" t="n">
         <v>51.24</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="11" t="n">
         <v>52.94</v>
       </c>
       <c r="AA15" s="6" t="inlineStr">
@@ -1489,26 +1513,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD15" s="9" t="n">
+      <c r="AD15" s="11" t="n">
         <v>51.04</v>
       </c>
-      <c r="AE15" s="9" t="n">
+      <c r="AE15" s="11" t="n">
         <v>50.71</v>
       </c>
-      <c r="AF15" s="9" t="n">
+      <c r="AF15" s="11" t="n">
         <v>50.56</v>
       </c>
-      <c r="AG15" s="9" t="n">
+      <c r="AG15" s="11" t="n">
         <v>51.09</v>
       </c>
       <c r="AH15" s="6" t="n">
         <v>51.77</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="9" t="n">
         <v>489.28</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1618,14 +1642,14 @@
       <c r="AG16" s="7" t="n">
         <v>87.69</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="8" t="n">
         <v>88.22</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="9" t="n">
         <v>214.98</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1735,14 +1759,14 @@
       <c r="AG17" s="7" t="n">
         <v>77.31</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="8" t="n">
         <v>78.98</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="9" t="n">
         <v>362.77</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1852,14 +1876,14 @@
       <c r="AG18" s="7" t="n">
         <v>84.08</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="8" t="n">
         <v>81.7</v>
       </c>
-      <c r="AI18" s="6" t="n">
+      <c r="AI18" s="9" t="n">
         <v>219.91</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1939,7 +1963,7 @@
       <c r="Y19" s="7" t="n">
         <v>56.06</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="11" t="n">
         <v>53.79</v>
       </c>
       <c r="AA19" s="6" t="inlineStr">
@@ -1957,7 +1981,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD19" s="9" t="n">
+      <c r="AD19" s="11" t="n">
         <v>52.48</v>
       </c>
       <c r="AE19" s="7" t="n">
@@ -1972,11 +1996,11 @@
       <c r="AH19" s="6" t="n">
         <v>56.71</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="9" t="n">
         <v>489.91</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2086,14 +2110,14 @@
       <c r="AG20" s="7" t="n">
         <v>87.14</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="8" t="n">
         <v>87.34</v>
       </c>
       <c r="AI20" s="6" t="n">
         <v>196.8</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2203,14 +2227,14 @@
       <c r="AG21" s="7" t="n">
         <v>94.06999999999999</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="8" t="n">
         <v>94.26000000000001</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="9" t="n">
         <v>230.95</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2320,14 +2344,14 @@
       <c r="AG22" s="7" t="n">
         <v>76.23</v>
       </c>
-      <c r="AH22" s="6" t="n">
+      <c r="AH22" s="8" t="n">
         <v>77.55</v>
       </c>
-      <c r="AI22" s="6" t="n">
+      <c r="AI22" s="9" t="n">
         <v>436.64</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2437,14 +2461,14 @@
       <c r="AG23" s="7" t="n">
         <v>84.45</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH23" s="8" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="AI23" s="6" t="n">
+      <c r="AI23" s="9" t="n">
         <v>257.14</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2554,14 +2578,14 @@
       <c r="AG24" s="7" t="n">
         <v>81.16</v>
       </c>
-      <c r="AH24" s="6" t="n">
+      <c r="AH24" s="8" t="n">
         <v>81.17</v>
       </c>
       <c r="AI24" s="6" t="n">
         <v>197.27</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2572,76 +2596,76 @@
       <c r="B25" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="11" t="n">
         <v>46.88</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="11" t="n">
         <v>46.81</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="11" t="n">
         <v>45.97</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="11" t="n">
         <v>47.78</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="11" t="n">
         <v>48.08</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="11" t="n">
         <v>47.05</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="11" t="n">
         <v>46.67</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" s="11" t="n">
         <v>47.12</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="11" t="n">
         <v>46.84</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="11" t="n">
         <v>46.88</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="11" t="n">
         <v>46.33</v>
       </c>
-      <c r="N25" s="9" t="n">
+      <c r="N25" s="11" t="n">
         <v>49.66</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="O25" s="11" t="n">
         <v>48.7</v>
       </c>
-      <c r="P25" s="9" t="n">
+      <c r="P25" s="11" t="n">
         <v>49.31</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="11" t="n">
         <v>47.73</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="11" t="n">
         <v>49.23</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="11" t="n">
         <v>47.98</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="11" t="n">
         <v>46.88</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="11" t="n">
         <v>45.82</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="11" t="n">
         <v>46.52</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="11" t="n">
         <v>47.44</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" s="11" t="n">
         <v>46.51</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="11" t="n">
         <v>46.15</v>
       </c>
-      <c r="Z25" s="9" t="n">
+      <c r="Z25" s="11" t="n">
         <v>45.64</v>
       </c>
       <c r="AA25" s="6" t="inlineStr">
@@ -2659,26 +2683,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD25" s="9" t="n">
+      <c r="AD25" s="11" t="n">
         <v>44.54</v>
       </c>
-      <c r="AE25" s="9" t="n">
+      <c r="AE25" s="11" t="n">
         <v>46.63</v>
       </c>
-      <c r="AF25" s="9" t="n">
+      <c r="AF25" s="11" t="n">
         <v>46.59</v>
       </c>
-      <c r="AG25" s="9" t="n">
+      <c r="AG25" s="11" t="n">
         <v>47.18</v>
       </c>
       <c r="AH25" s="6" t="n">
         <v>47.1</v>
       </c>
-      <c r="AI25" s="6" t="n">
+      <c r="AI25" s="9" t="n">
         <v>490</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2788,14 +2812,14 @@
       <c r="AG26" s="7" t="n">
         <v>91.37</v>
       </c>
-      <c r="AH26" s="6" t="n">
+      <c r="AH26" s="8" t="n">
         <v>90.45999999999999</v>
       </c>
-      <c r="AI26" s="6" t="n">
+      <c r="AI26" s="9" t="n">
         <v>371.19</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2905,14 +2929,14 @@
       <c r="AG27" s="7" t="n">
         <v>89.41</v>
       </c>
-      <c r="AH27" s="6" t="n">
+      <c r="AH27" s="8" t="n">
         <v>89.45</v>
       </c>
-      <c r="AI27" s="6" t="n">
+      <c r="AI27" s="9" t="n">
         <v>315.07</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -3022,14 +3046,14 @@
       <c r="AG28" s="7" t="n">
         <v>95.53</v>
       </c>
-      <c r="AH28" s="6" t="n">
+      <c r="AH28" s="8" t="n">
         <v>94.22</v>
       </c>
-      <c r="AI28" s="6" t="n">
+      <c r="AI28" s="9" t="n">
         <v>244.12</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3040,76 +3064,76 @@
       <c r="B29" s="6" t="n">
         <v>105.7</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="11" t="n">
         <v>44.26</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="11" t="n">
         <v>43.4</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="12" t="n">
         <v>42.87</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="11" t="n">
         <v>43.78</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="11" t="n">
         <v>45.04</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="11" t="n">
         <v>43.91</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" s="11" t="n">
         <v>44.14</v>
       </c>
-      <c r="J29" s="10" t="n">
+      <c r="J29" s="12" t="n">
         <v>42.84</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="11" t="n">
         <v>44.14</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="11" t="n">
         <v>43.75</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="11" t="n">
         <v>48.48</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="11" t="n">
         <v>47.18</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="11" t="n">
         <v>44.35</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="11" t="n">
         <v>45.84</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="11" t="n">
         <v>46.76</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="11" t="n">
         <v>47.58</v>
       </c>
-      <c r="S29" s="9" t="n">
+      <c r="S29" s="11" t="n">
         <v>45.74</v>
       </c>
-      <c r="T29" s="10" t="n">
+      <c r="T29" s="12" t="n">
         <v>42.89</v>
       </c>
-      <c r="U29" s="10" t="n">
+      <c r="U29" s="12" t="n">
         <v>41.15</v>
       </c>
-      <c r="V29" s="10" t="n">
+      <c r="V29" s="12" t="n">
         <v>42.51</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="11" t="n">
         <v>43.88</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="X29" s="11" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y29" s="10" t="n">
+      <c r="Y29" s="12" t="n">
         <v>42.28</v>
       </c>
-      <c r="Z29" s="9" t="n">
+      <c r="Z29" s="11" t="n">
         <v>44.64</v>
       </c>
       <c r="AA29" s="6" t="inlineStr">
@@ -3127,26 +3151,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD29" s="10" t="n">
+      <c r="AD29" s="12" t="n">
         <v>41.87</v>
       </c>
-      <c r="AE29" s="10" t="n">
+      <c r="AE29" s="12" t="n">
         <v>42.42</v>
       </c>
-      <c r="AF29" s="10" t="n">
+      <c r="AF29" s="12" t="n">
         <v>41.86</v>
       </c>
-      <c r="AG29" s="9" t="n">
+      <c r="AG29" s="11" t="n">
         <v>43.46</v>
       </c>
       <c r="AH29" s="6" t="n">
         <v>44.09</v>
       </c>
-      <c r="AI29" s="6" t="n">
+      <c r="AI29" s="9" t="n">
         <v>483.6</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3256,14 +3280,14 @@
       <c r="AG30" s="7" t="n">
         <v>93.66</v>
       </c>
-      <c r="AH30" s="6" t="n">
+      <c r="AH30" s="8" t="n">
         <v>93.70999999999999</v>
       </c>
       <c r="AI30" s="6" t="n">
         <v>165.25</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3373,14 +3397,14 @@
       <c r="AG31" s="7" t="n">
         <v>92.54000000000001</v>
       </c>
-      <c r="AH31" s="6" t="n">
+      <c r="AH31" s="8" t="n">
         <v>92.83</v>
       </c>
-      <c r="AI31" s="6" t="n">
+      <c r="AI31" s="9" t="n">
         <v>243.85</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3412,7 +3436,7 @@
       <c r="I32" s="7" t="n">
         <v>68.03</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="11" t="n">
         <v>46.18</v>
       </c>
       <c r="K32" s="7" t="n">
@@ -3490,131 +3514,131 @@
       <c r="AG32" s="7" t="n">
         <v>89.7</v>
       </c>
-      <c r="AH32" s="6" t="n">
+      <c r="AH32" s="8" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="AI32" s="6" t="n">
+      <c r="AI32" s="9" t="n">
         <v>332.07</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>RADIO CAÑARI</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="14" t="n">
         <v>107.7</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="15" t="n">
         <v>92.8</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="15" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="15" t="n">
         <v>91.36</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="15" t="n">
         <v>91.81</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="15" t="n">
         <v>92.20999999999999</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="15" t="n">
         <v>92.84999999999999</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="I33" s="15" t="n">
         <v>92.97</v>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="15" t="n">
         <v>92.06</v>
       </c>
-      <c r="K33" s="13" t="n">
+      <c r="K33" s="15" t="n">
         <v>92.05</v>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="15" t="n">
         <v>91.97</v>
       </c>
-      <c r="M33" s="13" t="n">
+      <c r="M33" s="15" t="n">
         <v>91.98</v>
       </c>
-      <c r="N33" s="13" t="n">
+      <c r="N33" s="15" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="O33" s="13" t="n">
+      <c r="O33" s="15" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="P33" s="13" t="n">
+      <c r="P33" s="15" t="n">
         <v>92.14</v>
       </c>
-      <c r="Q33" s="13" t="n">
+      <c r="Q33" s="15" t="n">
         <v>92.78</v>
       </c>
-      <c r="R33" s="13" t="n">
+      <c r="R33" s="15" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="S33" s="13" t="n">
+      <c r="S33" s="15" t="n">
         <v>92.78</v>
       </c>
-      <c r="T33" s="13" t="n">
+      <c r="T33" s="15" t="n">
         <v>92.92</v>
       </c>
-      <c r="U33" s="13" t="n">
+      <c r="U33" s="15" t="n">
         <v>91.84</v>
       </c>
-      <c r="V33" s="13" t="n">
+      <c r="V33" s="15" t="n">
         <v>92.84</v>
       </c>
-      <c r="W33" s="13" t="n">
+      <c r="W33" s="15" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="X33" s="13" t="n">
+      <c r="X33" s="15" t="n">
         <v>92.89</v>
       </c>
-      <c r="Y33" s="13" t="n">
+      <c r="Y33" s="15" t="n">
         <v>92.36</v>
       </c>
-      <c r="Z33" s="13" t="n">
+      <c r="Z33" s="15" t="n">
         <v>93.11</v>
       </c>
-      <c r="AA33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD33" s="13" t="n">
+      <c r="AA33" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="15" t="n">
         <v>93.01000000000001</v>
       </c>
-      <c r="AE33" s="13" t="n">
+      <c r="AE33" s="15" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="AF33" s="13" t="n">
+      <c r="AF33" s="15" t="n">
         <v>92.98</v>
       </c>
-      <c r="AG33" s="13" t="n">
+      <c r="AG33" s="15" t="n">
         <v>93.02</v>
       </c>
-      <c r="AH33" s="12" t="n">
+      <c r="AH33" s="16" t="n">
         <v>92.45</v>
       </c>
-      <c r="AI33" s="12" t="n">
+      <c r="AI33" s="17" t="n">
         <v>269.05</v>
       </c>
-      <c r="AJ33" s="12" t="inlineStr"/>
-      <c r="AK33" s="14" t="inlineStr"/>
+      <c r="AJ33" s="14" t="inlineStr"/>
+      <c r="AK33" s="18" t="inlineStr"/>
     </row>
     <row r="34"/>
     <row r="35"/>
@@ -3789,7 +3813,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK43" s="15" t="n"/>
+      <c r="AK43" s="19" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3887,7 +3911,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD44" s="9" t="n">
+      <c r="AD44" s="11" t="n">
         <v>52.19</v>
       </c>
       <c r="AE44" s="7" t="n">
@@ -3904,7 +3928,7 @@
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="16" t="n"/>
+      <c r="AK44" s="20" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4014,12 +4038,12 @@
       <c r="AG45" s="7" t="n">
         <v>63.19</v>
       </c>
-      <c r="AH45" s="6" t="n">
+      <c r="AH45" s="8" t="n">
         <v>61</v>
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="16" t="n"/>
+      <c r="AK45" s="20" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4030,76 +4054,76 @@
       <c r="B46" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="12" t="n">
         <v>30.76</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="12" t="n">
         <v>31.32</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="12" t="n">
         <v>32.11</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="12" t="n">
         <v>30.86</v>
       </c>
-      <c r="G46" s="10" t="n">
+      <c r="G46" s="12" t="n">
         <v>28.58</v>
       </c>
-      <c r="H46" s="10" t="n">
+      <c r="H46" s="12" t="n">
         <v>29.81</v>
       </c>
-      <c r="I46" s="10" t="n">
+      <c r="I46" s="12" t="n">
         <v>27.63</v>
       </c>
-      <c r="J46" s="10" t="n">
+      <c r="J46" s="12" t="n">
         <v>31.39</v>
       </c>
-      <c r="K46" s="10" t="n">
+      <c r="K46" s="12" t="n">
         <v>31.98</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" s="12" t="n">
         <v>31.91</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="12" t="n">
         <v>33.47</v>
       </c>
-      <c r="N46" s="10" t="n">
+      <c r="N46" s="12" t="n">
         <v>31.81</v>
       </c>
-      <c r="O46" s="10" t="n">
+      <c r="O46" s="12" t="n">
         <v>28.62</v>
       </c>
-      <c r="P46" s="10" t="n">
+      <c r="P46" s="12" t="n">
         <v>24.98</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="12" t="n">
         <v>27.11</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="12" t="n">
         <v>27.55</v>
       </c>
-      <c r="S46" s="10" t="n">
+      <c r="S46" s="12" t="n">
         <v>29.39</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="T46" s="12" t="n">
         <v>30.03</v>
       </c>
-      <c r="U46" s="10" t="n">
+      <c r="U46" s="12" t="n">
         <v>29.37</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="12" t="n">
         <v>27.43</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="12" t="n">
         <v>24.95</v>
       </c>
-      <c r="X46" s="10" t="n">
+      <c r="X46" s="12" t="n">
         <v>28.58</v>
       </c>
-      <c r="Y46" s="10" t="n">
+      <c r="Y46" s="12" t="n">
         <v>30.77</v>
       </c>
-      <c r="Z46" s="10" t="n">
+      <c r="Z46" s="12" t="n">
         <v>28.12</v>
       </c>
       <c r="AA46" s="6" t="inlineStr">
@@ -4117,16 +4141,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD46" s="10" t="n">
+      <c r="AD46" s="12" t="n">
         <v>27.18</v>
       </c>
-      <c r="AE46" s="10" t="n">
+      <c r="AE46" s="12" t="n">
         <v>27.85</v>
       </c>
-      <c r="AF46" s="10" t="n">
+      <c r="AF46" s="12" t="n">
         <v>26.6</v>
       </c>
-      <c r="AG46" s="10" t="n">
+      <c r="AG46" s="12" t="n">
         <v>26.24</v>
       </c>
       <c r="AH46" s="6" t="n">
@@ -4134,7 +4158,7 @@
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="16" t="n"/>
+      <c r="AK46" s="20" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4145,76 +4169,76 @@
       <c r="B47" s="6" t="n">
         <v>193.25</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="11" t="n">
         <v>46.3</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D47" s="11" t="n">
         <v>46.33</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="11" t="n">
         <v>46.39</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="11" t="n">
         <v>47.05</v>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="G47" s="11" t="n">
         <v>47.51</v>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="H47" s="11" t="n">
         <v>48.13</v>
       </c>
-      <c r="I47" s="9" t="n">
+      <c r="I47" s="11" t="n">
         <v>46.25</v>
       </c>
-      <c r="J47" s="9" t="n">
+      <c r="J47" s="11" t="n">
         <v>47.56</v>
       </c>
-      <c r="K47" s="9" t="n">
+      <c r="K47" s="11" t="n">
         <v>49.26</v>
       </c>
-      <c r="L47" s="9" t="n">
+      <c r="L47" s="11" t="n">
         <v>47.54</v>
       </c>
-      <c r="M47" s="9" t="n">
+      <c r="M47" s="11" t="n">
         <v>48.23</v>
       </c>
-      <c r="N47" s="9" t="n">
+      <c r="N47" s="11" t="n">
         <v>46.86</v>
       </c>
-      <c r="O47" s="9" t="n">
+      <c r="O47" s="11" t="n">
         <v>45.58</v>
       </c>
-      <c r="P47" s="9" t="n">
+      <c r="P47" s="11" t="n">
         <v>45.14</v>
       </c>
-      <c r="Q47" s="9" t="n">
+      <c r="Q47" s="11" t="n">
         <v>46.13</v>
       </c>
-      <c r="R47" s="9" t="n">
+      <c r="R47" s="11" t="n">
         <v>46.38</v>
       </c>
-      <c r="S47" s="9" t="n">
+      <c r="S47" s="11" t="n">
         <v>46.3</v>
       </c>
-      <c r="T47" s="9" t="n">
+      <c r="T47" s="11" t="n">
         <v>49.68</v>
       </c>
-      <c r="U47" s="9" t="n">
+      <c r="U47" s="11" t="n">
         <v>49.32</v>
       </c>
-      <c r="V47" s="9" t="n">
+      <c r="V47" s="11" t="n">
         <v>47.83</v>
       </c>
-      <c r="W47" s="9" t="n">
+      <c r="W47" s="11" t="n">
         <v>45.16</v>
       </c>
-      <c r="X47" s="9" t="n">
+      <c r="X47" s="11" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y47" s="9" t="n">
+      <c r="Y47" s="11" t="n">
         <v>48.44</v>
       </c>
-      <c r="Z47" s="9" t="n">
+      <c r="Z47" s="11" t="n">
         <v>46.78</v>
       </c>
       <c r="AA47" s="6" t="inlineStr">
@@ -4232,16 +4256,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD47" s="9" t="n">
+      <c r="AD47" s="11" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE47" s="9" t="n">
+      <c r="AE47" s="11" t="n">
         <v>47.77</v>
       </c>
-      <c r="AF47" s="9" t="n">
+      <c r="AF47" s="11" t="n">
         <v>47.22</v>
       </c>
-      <c r="AG47" s="9" t="n">
+      <c r="AG47" s="11" t="n">
         <v>47.83</v>
       </c>
       <c r="AH47" s="6" t="n">
@@ -4249,7 +4273,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="16" t="n"/>
+      <c r="AK47" s="20" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4260,76 +4284,76 @@
       <c r="B48" s="6" t="n">
         <v>205.25</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="12" t="n">
         <v>20.25</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="12" t="n">
         <v>19.44</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E48" s="12" t="n">
         <v>18.66</v>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="12" t="n">
         <v>21.06</v>
       </c>
-      <c r="G48" s="10" t="n">
+      <c r="G48" s="12" t="n">
         <v>19.93</v>
       </c>
-      <c r="H48" s="10" t="n">
+      <c r="H48" s="12" t="n">
         <v>20.95</v>
       </c>
-      <c r="I48" s="10" t="n">
+      <c r="I48" s="12" t="n">
         <v>21.35</v>
       </c>
-      <c r="J48" s="10" t="n">
+      <c r="J48" s="12" t="n">
         <v>19.73</v>
       </c>
-      <c r="K48" s="10" t="n">
+      <c r="K48" s="12" t="n">
         <v>20.03</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L48" s="12" t="n">
         <v>19.83</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="12" t="n">
         <v>19.34</v>
       </c>
-      <c r="N48" s="10" t="n">
+      <c r="N48" s="12" t="n">
         <v>20.03</v>
       </c>
-      <c r="O48" s="10" t="n">
+      <c r="O48" s="12" t="n">
         <v>20.25</v>
       </c>
-      <c r="P48" s="10" t="n">
+      <c r="P48" s="12" t="n">
         <v>19.31</v>
       </c>
-      <c r="Q48" s="10" t="n">
+      <c r="Q48" s="12" t="n">
         <v>21.73</v>
       </c>
-      <c r="R48" s="10" t="n">
+      <c r="R48" s="12" t="n">
         <v>21.23</v>
       </c>
-      <c r="S48" s="10" t="n">
+      <c r="S48" s="12" t="n">
         <v>19.64</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="T48" s="12" t="n">
         <v>20.19</v>
       </c>
-      <c r="U48" s="10" t="n">
+      <c r="U48" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="V48" s="10" t="n">
+      <c r="V48" s="12" t="n">
         <v>20.01</v>
       </c>
-      <c r="W48" s="10" t="n">
+      <c r="W48" s="12" t="n">
         <v>20.09</v>
       </c>
-      <c r="X48" s="10" t="n">
+      <c r="X48" s="12" t="n">
         <v>19.82</v>
       </c>
-      <c r="Y48" s="10" t="n">
+      <c r="Y48" s="12" t="n">
         <v>20.22</v>
       </c>
-      <c r="Z48" s="10" t="n">
+      <c r="Z48" s="12" t="n">
         <v>20.75</v>
       </c>
       <c r="AA48" s="6" t="inlineStr">
@@ -4347,16 +4371,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD48" s="10" t="n">
+      <c r="AD48" s="12" t="n">
         <v>20.72</v>
       </c>
-      <c r="AE48" s="10" t="n">
+      <c r="AE48" s="12" t="n">
         <v>19.91</v>
       </c>
-      <c r="AF48" s="10" t="n">
+      <c r="AF48" s="12" t="n">
         <v>20.74</v>
       </c>
-      <c r="AG48" s="10" t="n">
+      <c r="AG48" s="12" t="n">
         <v>20.32</v>
       </c>
       <c r="AH48" s="6" t="n">
@@ -4364,7 +4388,7 @@
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="16" t="n"/>
+      <c r="AK48" s="20" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4375,76 +4399,76 @@
       <c r="B49" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="12" t="n">
         <v>17.22</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D49" s="12" t="n">
         <v>17.16</v>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="E49" s="12" t="n">
         <v>16.48</v>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="F49" s="12" t="n">
         <v>20.09</v>
       </c>
-      <c r="G49" s="10" t="n">
+      <c r="G49" s="12" t="n">
         <v>17.15</v>
       </c>
-      <c r="H49" s="10" t="n">
+      <c r="H49" s="12" t="n">
         <v>16.65</v>
       </c>
-      <c r="I49" s="10" t="n">
+      <c r="I49" s="12" t="n">
         <v>17.38</v>
       </c>
-      <c r="J49" s="10" t="n">
+      <c r="J49" s="12" t="n">
         <v>17.17</v>
       </c>
-      <c r="K49" s="10" t="n">
+      <c r="K49" s="12" t="n">
         <v>16.77</v>
       </c>
-      <c r="L49" s="10" t="n">
+      <c r="L49" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="12" t="n">
         <v>16.85</v>
       </c>
-      <c r="N49" s="10" t="n">
+      <c r="N49" s="12" t="n">
         <v>16.67</v>
       </c>
-      <c r="O49" s="10" t="n">
+      <c r="O49" s="12" t="n">
         <v>16.78</v>
       </c>
-      <c r="P49" s="10" t="n">
+      <c r="P49" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="12" t="n">
         <v>16.78</v>
       </c>
-      <c r="R49" s="10" t="n">
+      <c r="R49" s="12" t="n">
         <v>16.69</v>
       </c>
-      <c r="S49" s="10" t="n">
+      <c r="S49" s="12" t="n">
         <v>17.09</v>
       </c>
-      <c r="T49" s="10" t="n">
+      <c r="T49" s="12" t="n">
         <v>16.92</v>
       </c>
-      <c r="U49" s="10" t="n">
+      <c r="U49" s="12" t="n">
         <v>16.91</v>
       </c>
-      <c r="V49" s="10" t="n">
+      <c r="V49" s="12" t="n">
         <v>17.3</v>
       </c>
-      <c r="W49" s="10" t="n">
+      <c r="W49" s="12" t="n">
         <v>17.05</v>
       </c>
-      <c r="X49" s="10" t="n">
+      <c r="X49" s="12" t="n">
         <v>16.87</v>
       </c>
-      <c r="Y49" s="10" t="n">
+      <c r="Y49" s="12" t="n">
         <v>16.7</v>
       </c>
-      <c r="Z49" s="10" t="n">
+      <c r="Z49" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="AA49" s="6" t="inlineStr">
@@ -4462,16 +4486,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD49" s="10" t="n">
+      <c r="AD49" s="12" t="n">
         <v>16.85</v>
       </c>
-      <c r="AE49" s="10" t="n">
+      <c r="AE49" s="12" t="n">
         <v>16.5</v>
       </c>
-      <c r="AF49" s="10" t="n">
+      <c r="AF49" s="12" t="n">
         <v>16.61</v>
       </c>
-      <c r="AG49" s="10" t="n">
+      <c r="AG49" s="12" t="n">
         <v>16.54</v>
       </c>
       <c r="AH49" s="6" t="n">
@@ -4479,7 +4503,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="16" t="n"/>
+      <c r="AK49" s="20" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4499,67 +4523,67 @@
       <c r="E50" s="7" t="n">
         <v>65.7</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="12" t="n">
         <v>29.7</v>
       </c>
-      <c r="G50" s="10" t="n">
+      <c r="G50" s="12" t="n">
         <v>31.15</v>
       </c>
-      <c r="H50" s="10" t="n">
+      <c r="H50" s="12" t="n">
         <v>30.96</v>
       </c>
-      <c r="I50" s="10" t="n">
+      <c r="I50" s="12" t="n">
         <v>30.68</v>
       </c>
-      <c r="J50" s="10" t="n">
+      <c r="J50" s="12" t="n">
         <v>30.74</v>
       </c>
-      <c r="K50" s="10" t="n">
+      <c r="K50" s="12" t="n">
         <v>30.38</v>
       </c>
-      <c r="L50" s="10" t="n">
+      <c r="L50" s="12" t="n">
         <v>30.17</v>
       </c>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="12" t="n">
         <v>30.75</v>
       </c>
-      <c r="N50" s="10" t="n">
+      <c r="N50" s="12" t="n">
         <v>29.89</v>
       </c>
-      <c r="O50" s="10" t="n">
+      <c r="O50" s="12" t="n">
         <v>30.15</v>
       </c>
-      <c r="P50" s="10" t="n">
+      <c r="P50" s="12" t="n">
         <v>31.64</v>
       </c>
-      <c r="Q50" s="10" t="n">
+      <c r="Q50" s="12" t="n">
         <v>30.28</v>
       </c>
-      <c r="R50" s="10" t="n">
+      <c r="R50" s="12" t="n">
         <v>31.09</v>
       </c>
-      <c r="S50" s="10" t="n">
+      <c r="S50" s="12" t="n">
         <v>30.65</v>
       </c>
-      <c r="T50" s="10" t="n">
+      <c r="T50" s="12" t="n">
         <v>32.47</v>
       </c>
-      <c r="U50" s="10" t="n">
+      <c r="U50" s="12" t="n">
         <v>31.51</v>
       </c>
-      <c r="V50" s="10" t="n">
+      <c r="V50" s="12" t="n">
         <v>30.9</v>
       </c>
-      <c r="W50" s="10" t="n">
+      <c r="W50" s="12" t="n">
         <v>32.99</v>
       </c>
-      <c r="X50" s="10" t="n">
+      <c r="X50" s="12" t="n">
         <v>27.85</v>
       </c>
-      <c r="Y50" s="10" t="n">
+      <c r="Y50" s="12" t="n">
         <v>28.3</v>
       </c>
-      <c r="Z50" s="10" t="n">
+      <c r="Z50" s="12" t="n">
         <v>28.28</v>
       </c>
       <c r="AA50" s="6" t="inlineStr">
@@ -4577,10 +4601,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD50" s="10" t="n">
+      <c r="AD50" s="12" t="n">
         <v>28.19</v>
       </c>
-      <c r="AE50" s="9" t="n">
+      <c r="AE50" s="11" t="n">
         <v>44.75</v>
       </c>
       <c r="AF50" s="7" t="n">
@@ -4594,7 +4618,7 @@
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="16" t="n"/>
+      <c r="AK50" s="20" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -4605,76 +4629,76 @@
       <c r="B51" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="12" t="n">
         <v>22.82</v>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D51" s="12" t="n">
         <v>19.78</v>
       </c>
-      <c r="E51" s="10" t="n">
+      <c r="E51" s="12" t="n">
         <v>19.33</v>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="12" t="n">
         <v>20.23</v>
       </c>
-      <c r="G51" s="10" t="n">
+      <c r="G51" s="12" t="n">
         <v>20.96</v>
       </c>
-      <c r="H51" s="10" t="n">
+      <c r="H51" s="12" t="n">
         <v>21.43</v>
       </c>
-      <c r="I51" s="10" t="n">
+      <c r="I51" s="12" t="n">
         <v>20.83</v>
       </c>
-      <c r="J51" s="10" t="n">
+      <c r="J51" s="12" t="n">
         <v>20.46</v>
       </c>
-      <c r="K51" s="10" t="n">
+      <c r="K51" s="12" t="n">
         <v>20.8</v>
       </c>
-      <c r="L51" s="10" t="n">
+      <c r="L51" s="12" t="n">
         <v>19.84</v>
       </c>
-      <c r="M51" s="10" t="n">
+      <c r="M51" s="12" t="n">
         <v>19.92</v>
       </c>
-      <c r="N51" s="10" t="n">
+      <c r="N51" s="12" t="n">
         <v>20.16</v>
       </c>
-      <c r="O51" s="10" t="n">
+      <c r="O51" s="12" t="n">
         <v>20.13</v>
       </c>
-      <c r="P51" s="10" t="n">
+      <c r="P51" s="12" t="n">
         <v>22.75</v>
       </c>
-      <c r="Q51" s="10" t="n">
+      <c r="Q51" s="12" t="n">
         <v>20.9</v>
       </c>
-      <c r="R51" s="10" t="n">
+      <c r="R51" s="12" t="n">
         <v>20.58</v>
       </c>
-      <c r="S51" s="10" t="n">
+      <c r="S51" s="12" t="n">
         <v>20.58</v>
       </c>
-      <c r="T51" s="10" t="n">
+      <c r="T51" s="12" t="n">
         <v>22.65</v>
       </c>
-      <c r="U51" s="10" t="n">
+      <c r="U51" s="12" t="n">
         <v>21.7</v>
       </c>
-      <c r="V51" s="10" t="n">
+      <c r="V51" s="12" t="n">
         <v>19.97</v>
       </c>
-      <c r="W51" s="10" t="n">
+      <c r="W51" s="12" t="n">
         <v>20.77</v>
       </c>
-      <c r="X51" s="10" t="n">
+      <c r="X51" s="12" t="n">
         <v>20.33</v>
       </c>
-      <c r="Y51" s="10" t="n">
+      <c r="Y51" s="12" t="n">
         <v>20.74</v>
       </c>
-      <c r="Z51" s="10" t="n">
+      <c r="Z51" s="12" t="n">
         <v>21.79</v>
       </c>
       <c r="AA51" s="6" t="inlineStr">
@@ -4692,16 +4716,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD51" s="10" t="n">
+      <c r="AD51" s="12" t="n">
         <v>20.5</v>
       </c>
-      <c r="AE51" s="10" t="n">
+      <c r="AE51" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="AF51" s="10" t="n">
+      <c r="AF51" s="12" t="n">
         <v>20.99</v>
       </c>
-      <c r="AG51" s="10" t="n">
+      <c r="AG51" s="12" t="n">
         <v>21.88</v>
       </c>
       <c r="AH51" s="6" t="n">
@@ -4709,7 +4733,7 @@
       </c>
       <c r="AI51" s="6" t="inlineStr"/>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="16" t="n"/>
+      <c r="AK51" s="20" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -4720,76 +4744,76 @@
       <c r="B52" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="12" t="n">
         <v>18.53</v>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="E52" s="10" t="n">
+      <c r="E52" s="12" t="n">
         <v>17.98</v>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" s="12" t="n">
         <v>18.24</v>
       </c>
-      <c r="G52" s="10" t="n">
+      <c r="G52" s="12" t="n">
         <v>18.19</v>
       </c>
-      <c r="H52" s="10" t="n">
+      <c r="H52" s="12" t="n">
         <v>17.79</v>
       </c>
-      <c r="I52" s="10" t="n">
+      <c r="I52" s="12" t="n">
         <v>18.05</v>
       </c>
-      <c r="J52" s="10" t="n">
+      <c r="J52" s="12" t="n">
         <v>18.3</v>
       </c>
-      <c r="K52" s="10" t="n">
+      <c r="K52" s="12" t="n">
         <v>18.22</v>
       </c>
-      <c r="L52" s="10" t="n">
+      <c r="L52" s="12" t="n">
         <v>17.98</v>
       </c>
-      <c r="M52" s="10" t="n">
+      <c r="M52" s="12" t="n">
         <v>18.44</v>
       </c>
-      <c r="N52" s="10" t="n">
+      <c r="N52" s="12" t="n">
         <v>18.26</v>
       </c>
-      <c r="O52" s="10" t="n">
+      <c r="O52" s="12" t="n">
         <v>18.29</v>
       </c>
-      <c r="P52" s="10" t="n">
+      <c r="P52" s="12" t="n">
         <v>18.67</v>
       </c>
-      <c r="Q52" s="10" t="n">
+      <c r="Q52" s="12" t="n">
         <v>18.47</v>
       </c>
-      <c r="R52" s="10" t="n">
+      <c r="R52" s="12" t="n">
         <v>18.01</v>
       </c>
-      <c r="S52" s="10" t="n">
+      <c r="S52" s="12" t="n">
         <v>18.22</v>
       </c>
-      <c r="T52" s="10" t="n">
+      <c r="T52" s="12" t="n">
         <v>18.26</v>
       </c>
-      <c r="U52" s="10" t="n">
+      <c r="U52" s="12" t="n">
         <v>17.86</v>
       </c>
-      <c r="V52" s="10" t="n">
+      <c r="V52" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="W52" s="10" t="n">
+      <c r="W52" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="X52" s="10" t="n">
+      <c r="X52" s="12" t="n">
         <v>17.84</v>
       </c>
-      <c r="Y52" s="10" t="n">
+      <c r="Y52" s="12" t="n">
         <v>18.21</v>
       </c>
-      <c r="Z52" s="10" t="n">
+      <c r="Z52" s="12" t="n">
         <v>18.21</v>
       </c>
       <c r="AA52" s="6" t="inlineStr">
@@ -4807,16 +4831,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD52" s="10" t="n">
+      <c r="AD52" s="12" t="n">
         <v>18.28</v>
       </c>
-      <c r="AE52" s="10" t="n">
+      <c r="AE52" s="12" t="n">
         <v>17.92</v>
       </c>
-      <c r="AF52" s="10" t="n">
+      <c r="AF52" s="12" t="n">
         <v>19.01</v>
       </c>
-      <c r="AG52" s="10" t="n">
+      <c r="AG52" s="12" t="n">
         <v>17.87</v>
       </c>
       <c r="AH52" s="6" t="n">
@@ -4824,122 +4848,122 @@
       </c>
       <c r="AI52" s="6" t="inlineStr"/>
       <c r="AJ52" s="6" t="inlineStr"/>
-      <c r="AK52" s="16" t="n"/>
+      <c r="AK52" s="20" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="14" t="n">
         <v>621.25</v>
       </c>
-      <c r="C53" s="17" t="n">
+      <c r="C53" s="21" t="n">
         <v>17.95</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="21" t="n">
         <v>18.92</v>
       </c>
-      <c r="E53" s="17" t="n">
+      <c r="E53" s="21" t="n">
         <v>18.01</v>
       </c>
-      <c r="F53" s="17" t="n">
+      <c r="F53" s="21" t="n">
         <v>19.62</v>
       </c>
-      <c r="G53" s="17" t="n">
+      <c r="G53" s="21" t="n">
         <v>18.31</v>
       </c>
-      <c r="H53" s="17" t="n">
+      <c r="H53" s="21" t="n">
         <v>18.65</v>
       </c>
-      <c r="I53" s="17" t="n">
+      <c r="I53" s="21" t="n">
         <v>17.95</v>
       </c>
-      <c r="J53" s="17" t="n">
+      <c r="J53" s="21" t="n">
         <v>18.35</v>
       </c>
-      <c r="K53" s="17" t="n">
+      <c r="K53" s="21" t="n">
         <v>17.77</v>
       </c>
-      <c r="L53" s="17" t="n">
+      <c r="L53" s="21" t="n">
         <v>17.89</v>
       </c>
-      <c r="M53" s="17" t="n">
+      <c r="M53" s="21" t="n">
         <v>18.63</v>
       </c>
-      <c r="N53" s="17" t="n">
+      <c r="N53" s="21" t="n">
         <v>18.2</v>
       </c>
-      <c r="O53" s="17" t="n">
+      <c r="O53" s="21" t="n">
         <v>18.66</v>
       </c>
-      <c r="P53" s="17" t="n">
+      <c r="P53" s="21" t="n">
         <v>18.17</v>
       </c>
-      <c r="Q53" s="17" t="n">
+      <c r="Q53" s="21" t="n">
         <v>17.78</v>
       </c>
-      <c r="R53" s="17" t="n">
+      <c r="R53" s="21" t="n">
         <v>17.77</v>
       </c>
-      <c r="S53" s="17" t="n">
+      <c r="S53" s="21" t="n">
         <v>18.17</v>
       </c>
-      <c r="T53" s="17" t="n">
+      <c r="T53" s="21" t="n">
         <v>18.65</v>
       </c>
-      <c r="U53" s="17" t="n">
+      <c r="U53" s="21" t="n">
         <v>18.15</v>
       </c>
-      <c r="V53" s="17" t="n">
+      <c r="V53" s="21" t="n">
         <v>18.39</v>
       </c>
-      <c r="W53" s="17" t="n">
+      <c r="W53" s="21" t="n">
         <v>18.8</v>
       </c>
-      <c r="X53" s="17" t="n">
+      <c r="X53" s="21" t="n">
         <v>17.88</v>
       </c>
-      <c r="Y53" s="17" t="n">
+      <c r="Y53" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="Z53" s="17" t="n">
+      <c r="Z53" s="21" t="n">
         <v>17.42</v>
       </c>
-      <c r="AA53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD53" s="17" t="n">
+      <c r="AA53" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD53" s="21" t="n">
         <v>17.28</v>
       </c>
-      <c r="AE53" s="17" t="n">
+      <c r="AE53" s="21" t="n">
         <v>17.95</v>
       </c>
-      <c r="AF53" s="17" t="n">
+      <c r="AF53" s="21" t="n">
         <v>17.8</v>
       </c>
-      <c r="AG53" s="17" t="n">
+      <c r="AG53" s="21" t="n">
         <v>17.93</v>
       </c>
-      <c r="AH53" s="12" t="n">
+      <c r="AH53" s="14" t="n">
         <v>18.18</v>
       </c>
-      <c r="AI53" s="12" t="inlineStr"/>
-      <c r="AJ53" s="12" t="inlineStr"/>
-      <c r="AK53" s="18" t="n"/>
+      <c r="AI53" s="14" t="inlineStr"/>
+      <c r="AJ53" s="14" t="inlineStr"/>
+      <c r="AK53" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -303,7 +303,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4762500" cy="952500"/>
@@ -326,9 +326,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2476500" cy="1143000"/>
@@ -376,7 +376,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>33</col>
+      <col>35</col>
       <colOff>0</colOff>
       <row>37</row>
       <rowOff>0</rowOff>

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -30,12 +30,18 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -171,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,22 +197,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,7 +229,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -792,7 +804,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -1036,11 +1048,11 @@
       <c r="AH11" s="6" t="n">
         <v>70.79000000000001</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="8" t="n">
         <v>339.89</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="8" t="inlineStr"/>
+      <c r="AK11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1157,7 +1169,7 @@
         <v>215.38</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="8" t="inlineStr"/>
+      <c r="AK12" s="9" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1270,11 +1282,11 @@
       <c r="AH13" s="6" t="n">
         <v>74.42</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="8" t="n">
         <v>381.82</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="8" t="inlineStr"/>
+      <c r="AK13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1387,11 +1399,11 @@
       <c r="AH14" s="6" t="n">
         <v>96.97</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="8" t="n">
         <v>394.82</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="8" t="inlineStr"/>
+      <c r="AK14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1402,76 +1414,76 @@
       <c r="B15" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="10" t="n">
         <v>51.91</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="10" t="n">
         <v>51.91</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="10" t="n">
         <v>53.71</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="10" t="n">
         <v>53.19</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="10" t="n">
         <v>52.31</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="10" t="n">
         <v>52.02</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="10" t="n">
         <v>51.63</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="10" t="n">
         <v>51.38</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="10" t="n">
         <v>52.8</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="10" t="n">
         <v>52.85</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="10" t="n">
         <v>52.05</v>
       </c>
-      <c r="N15" s="9" t="n">
+      <c r="N15" s="10" t="n">
         <v>51.7</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="10" t="n">
         <v>51.64</v>
       </c>
-      <c r="P15" s="9" t="n">
+      <c r="P15" s="10" t="n">
         <v>51.52</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="10" t="n">
         <v>51.34</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="10" t="n">
         <v>51.23</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="10" t="n">
         <v>51.05</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="10" t="n">
         <v>51.93</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="10" t="n">
         <v>51.36</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="10" t="n">
         <v>51.27</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="10" t="n">
         <v>51.31</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="10" t="n">
         <v>51.83</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="10" t="n">
         <v>51.24</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="10" t="n">
         <v>52.94</v>
       </c>
       <c r="AA15" s="6" t="inlineStr">
@@ -1489,26 +1501,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD15" s="9" t="n">
+      <c r="AD15" s="10" t="n">
         <v>51.04</v>
       </c>
-      <c r="AE15" s="9" t="n">
+      <c r="AE15" s="10" t="n">
         <v>50.71</v>
       </c>
-      <c r="AF15" s="9" t="n">
+      <c r="AF15" s="10" t="n">
         <v>50.56</v>
       </c>
-      <c r="AG15" s="9" t="n">
+      <c r="AG15" s="10" t="n">
         <v>51.09</v>
       </c>
-      <c r="AH15" s="6" t="n">
+      <c r="AH15" s="8" t="n">
         <v>51.77</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="8" t="n">
         <v>489.28</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="8" t="inlineStr"/>
+      <c r="AK15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1625,7 +1637,7 @@
         <v>214.98</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="8" t="inlineStr"/>
+      <c r="AK16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1738,11 +1750,11 @@
       <c r="AH17" s="6" t="n">
         <v>78.98</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AI17" s="8" t="n">
         <v>362.77</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="8" t="inlineStr"/>
+      <c r="AK17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1859,7 +1871,7 @@
         <v>219.91</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="8" t="inlineStr"/>
+      <c r="AK18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1939,7 +1951,7 @@
       <c r="Y19" s="7" t="n">
         <v>56.06</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="10" t="n">
         <v>53.79</v>
       </c>
       <c r="AA19" s="6" t="inlineStr">
@@ -1957,7 +1969,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD19" s="9" t="n">
+      <c r="AD19" s="10" t="n">
         <v>52.48</v>
       </c>
       <c r="AE19" s="7" t="n">
@@ -1972,11 +1984,11 @@
       <c r="AH19" s="6" t="n">
         <v>56.71</v>
       </c>
-      <c r="AI19" s="6" t="n">
+      <c r="AI19" s="8" t="n">
         <v>489.91</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="8" t="inlineStr"/>
+      <c r="AK19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2093,7 +2105,7 @@
         <v>196.8</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="8" t="inlineStr"/>
+      <c r="AK20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2206,11 +2218,11 @@
       <c r="AH21" s="6" t="n">
         <v>94.26000000000001</v>
       </c>
-      <c r="AI21" s="6" t="n">
+      <c r="AI21" s="8" t="n">
         <v>230.95</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="8" t="inlineStr"/>
+      <c r="AK21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2323,11 +2335,11 @@
       <c r="AH22" s="6" t="n">
         <v>77.55</v>
       </c>
-      <c r="AI22" s="6" t="n">
+      <c r="AI22" s="8" t="n">
         <v>436.64</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="8" t="inlineStr"/>
+      <c r="AK22" s="9" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2440,11 +2452,11 @@
       <c r="AH23" s="6" t="n">
         <v>71.95999999999999</v>
       </c>
-      <c r="AI23" s="6" t="n">
+      <c r="AI23" s="8" t="n">
         <v>257.14</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="8" t="inlineStr"/>
+      <c r="AK23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2561,7 +2573,7 @@
         <v>197.27</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="8" t="inlineStr"/>
+      <c r="AK24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2572,76 +2584,76 @@
       <c r="B25" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C25" s="10" t="n">
         <v>46.88</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="10" t="n">
         <v>46.81</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="10" t="n">
         <v>45.97</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="10" t="n">
         <v>47.78</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="10" t="n">
         <v>48.08</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="10" t="n">
         <v>47.05</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="10" t="n">
         <v>46.67</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" s="10" t="n">
         <v>47.12</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="10" t="n">
         <v>46.84</v>
       </c>
-      <c r="L25" s="9" t="n">
+      <c r="L25" s="10" t="n">
         <v>46.88</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10" t="n">
         <v>46.33</v>
       </c>
-      <c r="N25" s="9" t="n">
+      <c r="N25" s="10" t="n">
         <v>49.66</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="O25" s="10" t="n">
         <v>48.7</v>
       </c>
-      <c r="P25" s="9" t="n">
+      <c r="P25" s="10" t="n">
         <v>49.31</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="10" t="n">
         <v>47.73</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="10" t="n">
         <v>49.23</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="10" t="n">
         <v>47.98</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="10" t="n">
         <v>46.88</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="10" t="n">
         <v>45.82</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="10" t="n">
         <v>46.52</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="10" t="n">
         <v>47.44</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" s="10" t="n">
         <v>46.51</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="10" t="n">
         <v>46.15</v>
       </c>
-      <c r="Z25" s="9" t="n">
+      <c r="Z25" s="10" t="n">
         <v>45.64</v>
       </c>
       <c r="AA25" s="6" t="inlineStr">
@@ -2659,26 +2671,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD25" s="9" t="n">
+      <c r="AD25" s="10" t="n">
         <v>44.54</v>
       </c>
-      <c r="AE25" s="9" t="n">
+      <c r="AE25" s="10" t="n">
         <v>46.63</v>
       </c>
-      <c r="AF25" s="9" t="n">
+      <c r="AF25" s="10" t="n">
         <v>46.59</v>
       </c>
-      <c r="AG25" s="9" t="n">
+      <c r="AG25" s="10" t="n">
         <v>47.18</v>
       </c>
-      <c r="AH25" s="6" t="n">
+      <c r="AH25" s="8" t="n">
         <v>47.1</v>
       </c>
-      <c r="AI25" s="6" t="n">
+      <c r="AI25" s="8" t="n">
         <v>490</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="8" t="inlineStr"/>
+      <c r="AK25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2791,11 +2803,11 @@
       <c r="AH26" s="6" t="n">
         <v>90.45999999999999</v>
       </c>
-      <c r="AI26" s="6" t="n">
+      <c r="AI26" s="8" t="n">
         <v>371.19</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="8" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2908,11 +2920,11 @@
       <c r="AH27" s="6" t="n">
         <v>89.45</v>
       </c>
-      <c r="AI27" s="6" t="n">
+      <c r="AI27" s="8" t="n">
         <v>315.07</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="8" t="inlineStr"/>
+      <c r="AK27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -3025,11 +3037,11 @@
       <c r="AH28" s="6" t="n">
         <v>94.22</v>
       </c>
-      <c r="AI28" s="6" t="n">
+      <c r="AI28" s="8" t="n">
         <v>244.12</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="8" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3040,76 +3052,76 @@
       <c r="B29" s="6" t="n">
         <v>105.7</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C29" s="10" t="n">
         <v>44.26</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="10" t="n">
         <v>43.4</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="11" t="n">
         <v>42.87</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="10" t="n">
         <v>43.78</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="10" t="n">
         <v>45.04</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="10" t="n">
         <v>43.91</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" s="10" t="n">
         <v>44.14</v>
       </c>
-      <c r="J29" s="10" t="n">
+      <c r="J29" s="11" t="n">
         <v>42.84</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="10" t="n">
         <v>44.14</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="10" t="n">
         <v>43.75</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="10" t="n">
         <v>48.48</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="10" t="n">
         <v>47.18</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="10" t="n">
         <v>44.35</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="10" t="n">
         <v>45.84</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="10" t="n">
         <v>46.76</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="10" t="n">
         <v>47.58</v>
       </c>
-      <c r="S29" s="9" t="n">
+      <c r="S29" s="10" t="n">
         <v>45.74</v>
       </c>
-      <c r="T29" s="10" t="n">
+      <c r="T29" s="11" t="n">
         <v>42.89</v>
       </c>
-      <c r="U29" s="10" t="n">
+      <c r="U29" s="11" t="n">
         <v>41.15</v>
       </c>
-      <c r="V29" s="10" t="n">
+      <c r="V29" s="11" t="n">
         <v>42.51</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="10" t="n">
         <v>43.88</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="X29" s="10" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y29" s="10" t="n">
+      <c r="Y29" s="11" t="n">
         <v>42.28</v>
       </c>
-      <c r="Z29" s="9" t="n">
+      <c r="Z29" s="10" t="n">
         <v>44.64</v>
       </c>
       <c r="AA29" s="6" t="inlineStr">
@@ -3127,26 +3139,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD29" s="10" t="n">
+      <c r="AD29" s="11" t="n">
         <v>41.87</v>
       </c>
-      <c r="AE29" s="10" t="n">
+      <c r="AE29" s="11" t="n">
         <v>42.42</v>
       </c>
-      <c r="AF29" s="10" t="n">
+      <c r="AF29" s="11" t="n">
         <v>41.86</v>
       </c>
-      <c r="AG29" s="9" t="n">
+      <c r="AG29" s="10" t="n">
         <v>43.46</v>
       </c>
-      <c r="AH29" s="6" t="n">
+      <c r="AH29" s="8" t="n">
         <v>44.09</v>
       </c>
-      <c r="AI29" s="6" t="n">
+      <c r="AI29" s="8" t="n">
         <v>483.6</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="8" t="inlineStr"/>
+      <c r="AK29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3263,7 +3275,7 @@
         <v>165.25</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="8" t="inlineStr"/>
+      <c r="AK30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3376,11 +3388,11 @@
       <c r="AH31" s="6" t="n">
         <v>92.83</v>
       </c>
-      <c r="AI31" s="6" t="n">
+      <c r="AI31" s="8" t="n">
         <v>243.85</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="8" t="inlineStr"/>
+      <c r="AK31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3412,7 +3424,7 @@
       <c r="I32" s="7" t="n">
         <v>68.03</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="10" t="n">
         <v>46.18</v>
       </c>
       <c r="K32" s="7" t="n">
@@ -3493,128 +3505,128 @@
       <c r="AH32" s="6" t="n">
         <v>87.01000000000001</v>
       </c>
-      <c r="AI32" s="6" t="n">
+      <c r="AI32" s="8" t="n">
         <v>332.07</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="8" t="inlineStr"/>
+      <c r="AK32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>RADIO CAÑARI</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>107.7</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="14" t="n">
         <v>92.8</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>91.36</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="14" t="n">
         <v>91.81</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="14" t="n">
         <v>92.20999999999999</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="14" t="n">
         <v>92.84999999999999</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="I33" s="14" t="n">
         <v>92.97</v>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="14" t="n">
         <v>92.06</v>
       </c>
-      <c r="K33" s="13" t="n">
+      <c r="K33" s="14" t="n">
         <v>92.05</v>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="14" t="n">
         <v>91.97</v>
       </c>
-      <c r="M33" s="13" t="n">
+      <c r="M33" s="14" t="n">
         <v>91.98</v>
       </c>
-      <c r="N33" s="13" t="n">
+      <c r="N33" s="14" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="O33" s="13" t="n">
+      <c r="O33" s="14" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="P33" s="13" t="n">
+      <c r="P33" s="14" t="n">
         <v>92.14</v>
       </c>
-      <c r="Q33" s="13" t="n">
+      <c r="Q33" s="14" t="n">
         <v>92.78</v>
       </c>
-      <c r="R33" s="13" t="n">
+      <c r="R33" s="14" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="S33" s="13" t="n">
+      <c r="S33" s="14" t="n">
         <v>92.78</v>
       </c>
-      <c r="T33" s="13" t="n">
+      <c r="T33" s="14" t="n">
         <v>92.92</v>
       </c>
-      <c r="U33" s="13" t="n">
+      <c r="U33" s="14" t="n">
         <v>91.84</v>
       </c>
-      <c r="V33" s="13" t="n">
+      <c r="V33" s="14" t="n">
         <v>92.84</v>
       </c>
-      <c r="W33" s="13" t="n">
+      <c r="W33" s="14" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="X33" s="13" t="n">
+      <c r="X33" s="14" t="n">
         <v>92.89</v>
       </c>
-      <c r="Y33" s="13" t="n">
+      <c r="Y33" s="14" t="n">
         <v>92.36</v>
       </c>
-      <c r="Z33" s="13" t="n">
+      <c r="Z33" s="14" t="n">
         <v>93.11</v>
       </c>
-      <c r="AA33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD33" s="13" t="n">
+      <c r="AA33" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="14" t="n">
         <v>93.01000000000001</v>
       </c>
-      <c r="AE33" s="13" t="n">
+      <c r="AE33" s="14" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="AF33" s="13" t="n">
+      <c r="AF33" s="14" t="n">
         <v>92.98</v>
       </c>
-      <c r="AG33" s="13" t="n">
+      <c r="AG33" s="14" t="n">
         <v>93.02</v>
       </c>
-      <c r="AH33" s="12" t="n">
+      <c r="AH33" s="13" t="n">
         <v>92.45</v>
       </c>
-      <c r="AI33" s="12" t="n">
+      <c r="AI33" s="15" t="n">
         <v>269.05</v>
       </c>
-      <c r="AJ33" s="12" t="inlineStr"/>
-      <c r="AK33" s="14" t="inlineStr"/>
+      <c r="AJ33" s="13" t="inlineStr"/>
+      <c r="AK33" s="16" t="inlineStr"/>
     </row>
     <row r="34"/>
     <row r="35"/>
@@ -3663,7 +3675,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 28/08/2025</t>
+          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3801,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK43" s="15" t="n"/>
+      <c r="AK43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3800,76 +3812,76 @@
       <c r="B44" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="11" t="n">
         <v>54.45</v>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D44" s="11" t="n">
         <v>54.48</v>
       </c>
-      <c r="E44" s="7" t="n">
+      <c r="E44" s="10" t="n">
         <v>57.77</v>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F44" s="11" t="n">
         <v>54.82</v>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="11" t="n">
         <v>55.26</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H44" s="10" t="n">
         <v>56.32</v>
       </c>
-      <c r="I44" s="7" t="n">
+      <c r="I44" s="10" t="n">
         <v>56.04</v>
       </c>
-      <c r="J44" s="7" t="n">
+      <c r="J44" s="11" t="n">
         <v>55.54</v>
       </c>
-      <c r="K44" s="7" t="n">
+      <c r="K44" s="10" t="n">
         <v>56.45</v>
       </c>
-      <c r="L44" s="7" t="n">
+      <c r="L44" s="10" t="n">
         <v>56.89</v>
       </c>
-      <c r="M44" s="7" t="n">
+      <c r="M44" s="10" t="n">
         <v>56.92</v>
       </c>
-      <c r="N44" s="7" t="n">
+      <c r="N44" s="10" t="n">
         <v>57.59</v>
       </c>
-      <c r="O44" s="7" t="n">
+      <c r="O44" s="10" t="n">
         <v>57.66</v>
       </c>
-      <c r="P44" s="7" t="n">
+      <c r="P44" s="11" t="n">
         <v>55.07</v>
       </c>
-      <c r="Q44" s="7" t="n">
+      <c r="Q44" s="11" t="n">
         <v>54.17</v>
       </c>
-      <c r="R44" s="7" t="n">
+      <c r="R44" s="10" t="n">
         <v>56.31</v>
       </c>
-      <c r="S44" s="7" t="n">
+      <c r="S44" s="11" t="n">
         <v>55.18</v>
       </c>
-      <c r="T44" s="7" t="n">
+      <c r="T44" s="10" t="n">
         <v>56.62</v>
       </c>
-      <c r="U44" s="7" t="n">
+      <c r="U44" s="11" t="n">
         <v>55.28</v>
       </c>
-      <c r="V44" s="7" t="n">
+      <c r="V44" s="11" t="n">
         <v>54.73</v>
       </c>
-      <c r="W44" s="7" t="n">
+      <c r="W44" s="11" t="n">
         <v>55.07</v>
       </c>
-      <c r="X44" s="7" t="n">
+      <c r="X44" s="11" t="n">
         <v>54.94</v>
       </c>
-      <c r="Y44" s="7" t="n">
+      <c r="Y44" s="10" t="n">
         <v>57.08</v>
       </c>
-      <c r="Z44" s="7" t="n">
+      <c r="Z44" s="11" t="n">
         <v>54.75</v>
       </c>
       <c r="AA44" s="6" t="inlineStr">
@@ -3887,24 +3899,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD44" s="9" t="n">
+      <c r="AD44" s="11" t="n">
         <v>52.19</v>
       </c>
-      <c r="AE44" s="7" t="n">
+      <c r="AE44" s="11" t="n">
         <v>54.52</v>
       </c>
-      <c r="AF44" s="7" t="n">
+      <c r="AF44" s="11" t="n">
         <v>54.88</v>
       </c>
-      <c r="AG44" s="7" t="n">
+      <c r="AG44" s="11" t="n">
         <v>54.43</v>
       </c>
-      <c r="AH44" s="6" t="n">
+      <c r="AH44" s="8" t="n">
         <v>55.55</v>
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="16" t="n"/>
+      <c r="AK44" s="18" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3915,76 +3927,76 @@
       <c r="B45" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="10" t="n">
         <v>62.47</v>
       </c>
-      <c r="D45" s="7" t="n">
+      <c r="D45" s="10" t="n">
         <v>60.99</v>
       </c>
-      <c r="E45" s="7" t="n">
+      <c r="E45" s="10" t="n">
         <v>59.32</v>
       </c>
-      <c r="F45" s="7" t="n">
+      <c r="F45" s="10" t="n">
         <v>61.95</v>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="10" t="n">
         <v>61.42</v>
       </c>
-      <c r="H45" s="7" t="n">
+      <c r="H45" s="10" t="n">
         <v>61.35</v>
       </c>
-      <c r="I45" s="7" t="n">
+      <c r="I45" s="10" t="n">
         <v>60.77</v>
       </c>
-      <c r="J45" s="7" t="n">
+      <c r="J45" s="10" t="n">
         <v>60.27</v>
       </c>
-      <c r="K45" s="7" t="n">
+      <c r="K45" s="10" t="n">
         <v>59.26</v>
       </c>
-      <c r="L45" s="7" t="n">
+      <c r="L45" s="10" t="n">
         <v>59.13</v>
       </c>
-      <c r="M45" s="7" t="n">
+      <c r="M45" s="10" t="n">
         <v>59.08</v>
       </c>
-      <c r="N45" s="7" t="n">
+      <c r="N45" s="10" t="n">
         <v>57.83</v>
       </c>
-      <c r="O45" s="7" t="n">
+      <c r="O45" s="10" t="n">
         <v>58.15</v>
       </c>
-      <c r="P45" s="7" t="n">
+      <c r="P45" s="10" t="n">
         <v>62.37</v>
       </c>
-      <c r="Q45" s="7" t="n">
+      <c r="Q45" s="10" t="n">
         <v>62.44</v>
       </c>
-      <c r="R45" s="7" t="n">
+      <c r="R45" s="10" t="n">
         <v>59.07</v>
       </c>
-      <c r="S45" s="7" t="n">
+      <c r="S45" s="10" t="n">
         <v>61.21</v>
       </c>
-      <c r="T45" s="7" t="n">
+      <c r="T45" s="10" t="n">
         <v>58.95</v>
       </c>
-      <c r="U45" s="7" t="n">
+      <c r="U45" s="10" t="n">
         <v>61.47</v>
       </c>
-      <c r="V45" s="7" t="n">
+      <c r="V45" s="10" t="n">
         <v>62.25</v>
       </c>
-      <c r="W45" s="7" t="n">
+      <c r="W45" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="X45" s="7" t="n">
+      <c r="X45" s="10" t="n">
         <v>62.32</v>
       </c>
-      <c r="Y45" s="7" t="n">
+      <c r="Y45" s="10" t="n">
         <v>60.83</v>
       </c>
-      <c r="Z45" s="7" t="n">
+      <c r="Z45" s="10" t="n">
         <v>62.26</v>
       </c>
       <c r="AA45" s="6" t="inlineStr">
@@ -4002,24 +4014,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD45" s="7" t="n">
+      <c r="AD45" s="10" t="n">
         <v>62.62</v>
       </c>
-      <c r="AE45" s="7" t="n">
+      <c r="AE45" s="10" t="n">
         <v>62.34</v>
       </c>
-      <c r="AF45" s="7" t="n">
+      <c r="AF45" s="10" t="n">
         <v>62.65</v>
       </c>
-      <c r="AG45" s="7" t="n">
+      <c r="AG45" s="10" t="n">
         <v>63.19</v>
       </c>
-      <c r="AH45" s="6" t="n">
+      <c r="AH45" s="10" t="n">
         <v>61</v>
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="16" t="n"/>
+      <c r="AK45" s="18" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4030,76 +4042,76 @@
       <c r="B46" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="11" t="n">
         <v>30.76</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="11" t="n">
         <v>31.32</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="11" t="n">
         <v>32.11</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="11" t="n">
         <v>30.86</v>
       </c>
-      <c r="G46" s="10" t="n">
+      <c r="G46" s="11" t="n">
         <v>28.58</v>
       </c>
-      <c r="H46" s="10" t="n">
+      <c r="H46" s="11" t="n">
         <v>29.81</v>
       </c>
-      <c r="I46" s="10" t="n">
+      <c r="I46" s="11" t="n">
         <v>27.63</v>
       </c>
-      <c r="J46" s="10" t="n">
+      <c r="J46" s="11" t="n">
         <v>31.39</v>
       </c>
-      <c r="K46" s="10" t="n">
+      <c r="K46" s="11" t="n">
         <v>31.98</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L46" s="11" t="n">
         <v>31.91</v>
       </c>
-      <c r="M46" s="10" t="n">
+      <c r="M46" s="11" t="n">
         <v>33.47</v>
       </c>
-      <c r="N46" s="10" t="n">
+      <c r="N46" s="11" t="n">
         <v>31.81</v>
       </c>
-      <c r="O46" s="10" t="n">
+      <c r="O46" s="11" t="n">
         <v>28.62</v>
       </c>
-      <c r="P46" s="10" t="n">
+      <c r="P46" s="11" t="n">
         <v>24.98</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="11" t="n">
         <v>27.11</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="11" t="n">
         <v>27.55</v>
       </c>
-      <c r="S46" s="10" t="n">
+      <c r="S46" s="11" t="n">
         <v>29.39</v>
       </c>
-      <c r="T46" s="10" t="n">
+      <c r="T46" s="11" t="n">
         <v>30.03</v>
       </c>
-      <c r="U46" s="10" t="n">
+      <c r="U46" s="11" t="n">
         <v>29.37</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="11" t="n">
         <v>27.43</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="11" t="n">
         <v>24.95</v>
       </c>
-      <c r="X46" s="10" t="n">
+      <c r="X46" s="11" t="n">
         <v>28.58</v>
       </c>
-      <c r="Y46" s="10" t="n">
+      <c r="Y46" s="11" t="n">
         <v>30.77</v>
       </c>
-      <c r="Z46" s="10" t="n">
+      <c r="Z46" s="11" t="n">
         <v>28.12</v>
       </c>
       <c r="AA46" s="6" t="inlineStr">
@@ -4117,24 +4129,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD46" s="10" t="n">
+      <c r="AD46" s="11" t="n">
         <v>27.18</v>
       </c>
-      <c r="AE46" s="10" t="n">
+      <c r="AE46" s="11" t="n">
         <v>27.85</v>
       </c>
-      <c r="AF46" s="10" t="n">
+      <c r="AF46" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="AG46" s="10" t="n">
+      <c r="AG46" s="11" t="n">
         <v>26.24</v>
       </c>
-      <c r="AH46" s="6" t="n">
+      <c r="AH46" s="8" t="n">
         <v>29.16</v>
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="16" t="n"/>
+      <c r="AK46" s="18" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4145,76 +4157,76 @@
       <c r="B47" s="6" t="n">
         <v>193.25</v>
       </c>
-      <c r="C47" s="9" t="n">
+      <c r="C47" s="11" t="n">
         <v>46.3</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D47" s="11" t="n">
         <v>46.33</v>
       </c>
-      <c r="E47" s="9" t="n">
+      <c r="E47" s="11" t="n">
         <v>46.39</v>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F47" s="11" t="n">
         <v>47.05</v>
       </c>
-      <c r="G47" s="9" t="n">
+      <c r="G47" s="11" t="n">
         <v>47.51</v>
       </c>
-      <c r="H47" s="9" t="n">
+      <c r="H47" s="11" t="n">
         <v>48.13</v>
       </c>
-      <c r="I47" s="9" t="n">
+      <c r="I47" s="11" t="n">
         <v>46.25</v>
       </c>
-      <c r="J47" s="9" t="n">
+      <c r="J47" s="11" t="n">
         <v>47.56</v>
       </c>
-      <c r="K47" s="9" t="n">
+      <c r="K47" s="11" t="n">
         <v>49.26</v>
       </c>
-      <c r="L47" s="9" t="n">
+      <c r="L47" s="11" t="n">
         <v>47.54</v>
       </c>
-      <c r="M47" s="9" t="n">
+      <c r="M47" s="11" t="n">
         <v>48.23</v>
       </c>
-      <c r="N47" s="9" t="n">
+      <c r="N47" s="11" t="n">
         <v>46.86</v>
       </c>
-      <c r="O47" s="9" t="n">
+      <c r="O47" s="11" t="n">
         <v>45.58</v>
       </c>
-      <c r="P47" s="9" t="n">
+      <c r="P47" s="11" t="n">
         <v>45.14</v>
       </c>
-      <c r="Q47" s="9" t="n">
+      <c r="Q47" s="11" t="n">
         <v>46.13</v>
       </c>
-      <c r="R47" s="9" t="n">
+      <c r="R47" s="11" t="n">
         <v>46.38</v>
       </c>
-      <c r="S47" s="9" t="n">
+      <c r="S47" s="11" t="n">
         <v>46.3</v>
       </c>
-      <c r="T47" s="9" t="n">
+      <c r="T47" s="11" t="n">
         <v>49.68</v>
       </c>
-      <c r="U47" s="9" t="n">
+      <c r="U47" s="11" t="n">
         <v>49.32</v>
       </c>
-      <c r="V47" s="9" t="n">
+      <c r="V47" s="11" t="n">
         <v>47.83</v>
       </c>
-      <c r="W47" s="9" t="n">
+      <c r="W47" s="11" t="n">
         <v>45.16</v>
       </c>
-      <c r="X47" s="9" t="n">
+      <c r="X47" s="11" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y47" s="9" t="n">
+      <c r="Y47" s="11" t="n">
         <v>48.44</v>
       </c>
-      <c r="Z47" s="9" t="n">
+      <c r="Z47" s="11" t="n">
         <v>46.78</v>
       </c>
       <c r="AA47" s="6" t="inlineStr">
@@ -4232,24 +4244,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD47" s="9" t="n">
+      <c r="AD47" s="11" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE47" s="9" t="n">
+      <c r="AE47" s="11" t="n">
         <v>47.77</v>
       </c>
-      <c r="AF47" s="9" t="n">
+      <c r="AF47" s="11" t="n">
         <v>47.22</v>
       </c>
-      <c r="AG47" s="9" t="n">
+      <c r="AG47" s="11" t="n">
         <v>47.83</v>
       </c>
-      <c r="AH47" s="6" t="n">
+      <c r="AH47" s="8" t="n">
         <v>47.15</v>
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="16" t="n"/>
+      <c r="AK47" s="18" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4260,76 +4272,76 @@
       <c r="B48" s="6" t="n">
         <v>205.25</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="11" t="n">
         <v>20.25</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="11" t="n">
         <v>19.44</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E48" s="11" t="n">
         <v>18.66</v>
       </c>
-      <c r="F48" s="10" t="n">
+      <c r="F48" s="11" t="n">
         <v>21.06</v>
       </c>
-      <c r="G48" s="10" t="n">
+      <c r="G48" s="11" t="n">
         <v>19.93</v>
       </c>
-      <c r="H48" s="10" t="n">
+      <c r="H48" s="11" t="n">
         <v>20.95</v>
       </c>
-      <c r="I48" s="10" t="n">
+      <c r="I48" s="11" t="n">
         <v>21.35</v>
       </c>
-      <c r="J48" s="10" t="n">
+      <c r="J48" s="11" t="n">
         <v>19.73</v>
       </c>
-      <c r="K48" s="10" t="n">
+      <c r="K48" s="11" t="n">
         <v>20.03</v>
       </c>
-      <c r="L48" s="10" t="n">
+      <c r="L48" s="11" t="n">
         <v>19.83</v>
       </c>
-      <c r="M48" s="10" t="n">
+      <c r="M48" s="11" t="n">
         <v>19.34</v>
       </c>
-      <c r="N48" s="10" t="n">
+      <c r="N48" s="11" t="n">
         <v>20.03</v>
       </c>
-      <c r="O48" s="10" t="n">
+      <c r="O48" s="11" t="n">
         <v>20.25</v>
       </c>
-      <c r="P48" s="10" t="n">
+      <c r="P48" s="11" t="n">
         <v>19.31</v>
       </c>
-      <c r="Q48" s="10" t="n">
+      <c r="Q48" s="11" t="n">
         <v>21.73</v>
       </c>
-      <c r="R48" s="10" t="n">
+      <c r="R48" s="11" t="n">
         <v>21.23</v>
       </c>
-      <c r="S48" s="10" t="n">
+      <c r="S48" s="11" t="n">
         <v>19.64</v>
       </c>
-      <c r="T48" s="10" t="n">
+      <c r="T48" s="11" t="n">
         <v>20.19</v>
       </c>
-      <c r="U48" s="10" t="n">
+      <c r="U48" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="V48" s="10" t="n">
+      <c r="V48" s="11" t="n">
         <v>20.01</v>
       </c>
-      <c r="W48" s="10" t="n">
+      <c r="W48" s="11" t="n">
         <v>20.09</v>
       </c>
-      <c r="X48" s="10" t="n">
+      <c r="X48" s="11" t="n">
         <v>19.82</v>
       </c>
-      <c r="Y48" s="10" t="n">
+      <c r="Y48" s="11" t="n">
         <v>20.22</v>
       </c>
-      <c r="Z48" s="10" t="n">
+      <c r="Z48" s="11" t="n">
         <v>20.75</v>
       </c>
       <c r="AA48" s="6" t="inlineStr">
@@ -4347,24 +4359,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD48" s="10" t="n">
+      <c r="AD48" s="11" t="n">
         <v>20.72</v>
       </c>
-      <c r="AE48" s="10" t="n">
+      <c r="AE48" s="11" t="n">
         <v>19.91</v>
       </c>
-      <c r="AF48" s="10" t="n">
+      <c r="AF48" s="11" t="n">
         <v>20.74</v>
       </c>
-      <c r="AG48" s="10" t="n">
+      <c r="AG48" s="11" t="n">
         <v>20.32</v>
       </c>
-      <c r="AH48" s="6" t="n">
+      <c r="AH48" s="8" t="n">
         <v>20.21</v>
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="16" t="n"/>
+      <c r="AK48" s="18" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4375,76 +4387,76 @@
       <c r="B49" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C49" s="11" t="n">
         <v>17.22</v>
       </c>
-      <c r="D49" s="10" t="n">
+      <c r="D49" s="11" t="n">
         <v>17.16</v>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="E49" s="11" t="n">
         <v>16.48</v>
       </c>
-      <c r="F49" s="10" t="n">
+      <c r="F49" s="11" t="n">
         <v>20.09</v>
       </c>
-      <c r="G49" s="10" t="n">
+      <c r="G49" s="11" t="n">
         <v>17.15</v>
       </c>
-      <c r="H49" s="10" t="n">
+      <c r="H49" s="11" t="n">
         <v>16.65</v>
       </c>
-      <c r="I49" s="10" t="n">
+      <c r="I49" s="11" t="n">
         <v>17.38</v>
       </c>
-      <c r="J49" s="10" t="n">
+      <c r="J49" s="11" t="n">
         <v>17.17</v>
       </c>
-      <c r="K49" s="10" t="n">
+      <c r="K49" s="11" t="n">
         <v>16.77</v>
       </c>
-      <c r="L49" s="10" t="n">
+      <c r="L49" s="11" t="n">
         <v>16.8</v>
       </c>
-      <c r="M49" s="10" t="n">
+      <c r="M49" s="11" t="n">
         <v>16.85</v>
       </c>
-      <c r="N49" s="10" t="n">
+      <c r="N49" s="11" t="n">
         <v>16.67</v>
       </c>
-      <c r="O49" s="10" t="n">
+      <c r="O49" s="11" t="n">
         <v>16.78</v>
       </c>
-      <c r="P49" s="10" t="n">
+      <c r="P49" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="Q49" s="10" t="n">
+      <c r="Q49" s="11" t="n">
         <v>16.78</v>
       </c>
-      <c r="R49" s="10" t="n">
+      <c r="R49" s="11" t="n">
         <v>16.69</v>
       </c>
-      <c r="S49" s="10" t="n">
+      <c r="S49" s="11" t="n">
         <v>17.09</v>
       </c>
-      <c r="T49" s="10" t="n">
+      <c r="T49" s="11" t="n">
         <v>16.92</v>
       </c>
-      <c r="U49" s="10" t="n">
+      <c r="U49" s="11" t="n">
         <v>16.91</v>
       </c>
-      <c r="V49" s="10" t="n">
+      <c r="V49" s="11" t="n">
         <v>17.3</v>
       </c>
-      <c r="W49" s="10" t="n">
+      <c r="W49" s="11" t="n">
         <v>17.05</v>
       </c>
-      <c r="X49" s="10" t="n">
+      <c r="X49" s="11" t="n">
         <v>16.87</v>
       </c>
-      <c r="Y49" s="10" t="n">
+      <c r="Y49" s="11" t="n">
         <v>16.7</v>
       </c>
-      <c r="Z49" s="10" t="n">
+      <c r="Z49" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="AA49" s="6" t="inlineStr">
@@ -4462,24 +4474,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD49" s="10" t="n">
+      <c r="AD49" s="11" t="n">
         <v>16.85</v>
       </c>
-      <c r="AE49" s="10" t="n">
+      <c r="AE49" s="11" t="n">
         <v>16.5</v>
       </c>
-      <c r="AF49" s="10" t="n">
+      <c r="AF49" s="11" t="n">
         <v>16.61</v>
       </c>
-      <c r="AG49" s="10" t="n">
+      <c r="AG49" s="11" t="n">
         <v>16.54</v>
       </c>
-      <c r="AH49" s="6" t="n">
+      <c r="AH49" s="8" t="n">
         <v>17</v>
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="16" t="n"/>
+      <c r="AK49" s="18" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4490,76 +4502,76 @@
       <c r="B50" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="10" t="n">
         <v>64.31999999999999</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="10" t="n">
         <v>65.59</v>
       </c>
-      <c r="E50" s="7" t="n">
+      <c r="E50" s="10" t="n">
         <v>65.7</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="11" t="n">
         <v>29.7</v>
       </c>
-      <c r="G50" s="10" t="n">
+      <c r="G50" s="11" t="n">
         <v>31.15</v>
       </c>
-      <c r="H50" s="10" t="n">
+      <c r="H50" s="11" t="n">
         <v>30.96</v>
       </c>
-      <c r="I50" s="10" t="n">
+      <c r="I50" s="11" t="n">
         <v>30.68</v>
       </c>
-      <c r="J50" s="10" t="n">
+      <c r="J50" s="11" t="n">
         <v>30.74</v>
       </c>
-      <c r="K50" s="10" t="n">
+      <c r="K50" s="11" t="n">
         <v>30.38</v>
       </c>
-      <c r="L50" s="10" t="n">
+      <c r="L50" s="11" t="n">
         <v>30.17</v>
       </c>
-      <c r="M50" s="10" t="n">
+      <c r="M50" s="11" t="n">
         <v>30.75</v>
       </c>
-      <c r="N50" s="10" t="n">
+      <c r="N50" s="11" t="n">
         <v>29.89</v>
       </c>
-      <c r="O50" s="10" t="n">
+      <c r="O50" s="11" t="n">
         <v>30.15</v>
       </c>
-      <c r="P50" s="10" t="n">
+      <c r="P50" s="11" t="n">
         <v>31.64</v>
       </c>
-      <c r="Q50" s="10" t="n">
+      <c r="Q50" s="11" t="n">
         <v>30.28</v>
       </c>
-      <c r="R50" s="10" t="n">
+      <c r="R50" s="11" t="n">
         <v>31.09</v>
       </c>
-      <c r="S50" s="10" t="n">
+      <c r="S50" s="11" t="n">
         <v>30.65</v>
       </c>
-      <c r="T50" s="10" t="n">
+      <c r="T50" s="11" t="n">
         <v>32.47</v>
       </c>
-      <c r="U50" s="10" t="n">
+      <c r="U50" s="11" t="n">
         <v>31.51</v>
       </c>
-      <c r="V50" s="10" t="n">
+      <c r="V50" s="11" t="n">
         <v>30.9</v>
       </c>
-      <c r="W50" s="10" t="n">
+      <c r="W50" s="11" t="n">
         <v>32.99</v>
       </c>
-      <c r="X50" s="10" t="n">
+      <c r="X50" s="11" t="n">
         <v>27.85</v>
       </c>
-      <c r="Y50" s="10" t="n">
+      <c r="Y50" s="11" t="n">
         <v>28.3</v>
       </c>
-      <c r="Z50" s="10" t="n">
+      <c r="Z50" s="11" t="n">
         <v>28.28</v>
       </c>
       <c r="AA50" s="6" t="inlineStr">
@@ -4577,24 +4589,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD50" s="10" t="n">
+      <c r="AD50" s="11" t="n">
         <v>28.19</v>
       </c>
-      <c r="AE50" s="9" t="n">
+      <c r="AE50" s="11" t="n">
         <v>44.75</v>
       </c>
-      <c r="AF50" s="7" t="n">
+      <c r="AF50" s="10" t="n">
         <v>60.62</v>
       </c>
-      <c r="AG50" s="7" t="n">
+      <c r="AG50" s="10" t="n">
         <v>61.05</v>
       </c>
-      <c r="AH50" s="6" t="n">
+      <c r="AH50" s="8" t="n">
         <v>36.81</v>
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="16" t="n"/>
+      <c r="AK50" s="18" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -4605,76 +4617,76 @@
       <c r="B51" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="11" t="n">
         <v>22.82</v>
       </c>
-      <c r="D51" s="10" t="n">
+      <c r="D51" s="11" t="n">
         <v>19.78</v>
       </c>
-      <c r="E51" s="10" t="n">
+      <c r="E51" s="11" t="n">
         <v>19.33</v>
       </c>
-      <c r="F51" s="10" t="n">
+      <c r="F51" s="11" t="n">
         <v>20.23</v>
       </c>
-      <c r="G51" s="10" t="n">
+      <c r="G51" s="11" t="n">
         <v>20.96</v>
       </c>
-      <c r="H51" s="10" t="n">
+      <c r="H51" s="11" t="n">
         <v>21.43</v>
       </c>
-      <c r="I51" s="10" t="n">
+      <c r="I51" s="11" t="n">
         <v>20.83</v>
       </c>
-      <c r="J51" s="10" t="n">
+      <c r="J51" s="11" t="n">
         <v>20.46</v>
       </c>
-      <c r="K51" s="10" t="n">
+      <c r="K51" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="L51" s="10" t="n">
+      <c r="L51" s="11" t="n">
         <v>19.84</v>
       </c>
-      <c r="M51" s="10" t="n">
+      <c r="M51" s="11" t="n">
         <v>19.92</v>
       </c>
-      <c r="N51" s="10" t="n">
+      <c r="N51" s="11" t="n">
         <v>20.16</v>
       </c>
-      <c r="O51" s="10" t="n">
+      <c r="O51" s="11" t="n">
         <v>20.13</v>
       </c>
-      <c r="P51" s="10" t="n">
+      <c r="P51" s="11" t="n">
         <v>22.75</v>
       </c>
-      <c r="Q51" s="10" t="n">
+      <c r="Q51" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="R51" s="10" t="n">
+      <c r="R51" s="11" t="n">
         <v>20.58</v>
       </c>
-      <c r="S51" s="10" t="n">
+      <c r="S51" s="11" t="n">
         <v>20.58</v>
       </c>
-      <c r="T51" s="10" t="n">
+      <c r="T51" s="11" t="n">
         <v>22.65</v>
       </c>
-      <c r="U51" s="10" t="n">
+      <c r="U51" s="11" t="n">
         <v>21.7</v>
       </c>
-      <c r="V51" s="10" t="n">
+      <c r="V51" s="11" t="n">
         <v>19.97</v>
       </c>
-      <c r="W51" s="10" t="n">
+      <c r="W51" s="11" t="n">
         <v>20.77</v>
       </c>
-      <c r="X51" s="10" t="n">
+      <c r="X51" s="11" t="n">
         <v>20.33</v>
       </c>
-      <c r="Y51" s="10" t="n">
+      <c r="Y51" s="11" t="n">
         <v>20.74</v>
       </c>
-      <c r="Z51" s="10" t="n">
+      <c r="Z51" s="11" t="n">
         <v>21.79</v>
       </c>
       <c r="AA51" s="6" t="inlineStr">
@@ -4692,24 +4704,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD51" s="10" t="n">
+      <c r="AD51" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="AE51" s="10" t="n">
+      <c r="AE51" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="AF51" s="10" t="n">
+      <c r="AF51" s="11" t="n">
         <v>20.99</v>
       </c>
-      <c r="AG51" s="10" t="n">
+      <c r="AG51" s="11" t="n">
         <v>21.88</v>
       </c>
-      <c r="AH51" s="6" t="n">
+      <c r="AH51" s="8" t="n">
         <v>20.81</v>
       </c>
       <c r="AI51" s="6" t="inlineStr"/>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="16" t="n"/>
+      <c r="AK51" s="18" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -4720,76 +4732,76 @@
       <c r="B52" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="11" t="n">
         <v>18.53</v>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="E52" s="10" t="n">
+      <c r="E52" s="11" t="n">
         <v>17.98</v>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" s="11" t="n">
         <v>18.24</v>
       </c>
-      <c r="G52" s="10" t="n">
+      <c r="G52" s="11" t="n">
         <v>18.19</v>
       </c>
-      <c r="H52" s="10" t="n">
+      <c r="H52" s="11" t="n">
         <v>17.79</v>
       </c>
-      <c r="I52" s="10" t="n">
+      <c r="I52" s="11" t="n">
         <v>18.05</v>
       </c>
-      <c r="J52" s="10" t="n">
+      <c r="J52" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="K52" s="10" t="n">
+      <c r="K52" s="11" t="n">
         <v>18.22</v>
       </c>
-      <c r="L52" s="10" t="n">
+      <c r="L52" s="11" t="n">
         <v>17.98</v>
       </c>
-      <c r="M52" s="10" t="n">
+      <c r="M52" s="11" t="n">
         <v>18.44</v>
       </c>
-      <c r="N52" s="10" t="n">
+      <c r="N52" s="11" t="n">
         <v>18.26</v>
       </c>
-      <c r="O52" s="10" t="n">
+      <c r="O52" s="11" t="n">
         <v>18.29</v>
       </c>
-      <c r="P52" s="10" t="n">
+      <c r="P52" s="11" t="n">
         <v>18.67</v>
       </c>
-      <c r="Q52" s="10" t="n">
+      <c r="Q52" s="11" t="n">
         <v>18.47</v>
       </c>
-      <c r="R52" s="10" t="n">
+      <c r="R52" s="11" t="n">
         <v>18.01</v>
       </c>
-      <c r="S52" s="10" t="n">
+      <c r="S52" s="11" t="n">
         <v>18.22</v>
       </c>
-      <c r="T52" s="10" t="n">
+      <c r="T52" s="11" t="n">
         <v>18.26</v>
       </c>
-      <c r="U52" s="10" t="n">
+      <c r="U52" s="11" t="n">
         <v>17.86</v>
       </c>
-      <c r="V52" s="10" t="n">
+      <c r="V52" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="W52" s="10" t="n">
+      <c r="W52" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="X52" s="10" t="n">
+      <c r="X52" s="11" t="n">
         <v>17.84</v>
       </c>
-      <c r="Y52" s="10" t="n">
+      <c r="Y52" s="11" t="n">
         <v>18.21</v>
       </c>
-      <c r="Z52" s="10" t="n">
+      <c r="Z52" s="11" t="n">
         <v>18.21</v>
       </c>
       <c r="AA52" s="6" t="inlineStr">
@@ -4807,139 +4819,139 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD52" s="10" t="n">
+      <c r="AD52" s="11" t="n">
         <v>18.28</v>
       </c>
-      <c r="AE52" s="10" t="n">
+      <c r="AE52" s="11" t="n">
         <v>17.92</v>
       </c>
-      <c r="AF52" s="10" t="n">
+      <c r="AF52" s="11" t="n">
         <v>19.01</v>
       </c>
-      <c r="AG52" s="10" t="n">
+      <c r="AG52" s="11" t="n">
         <v>17.87</v>
       </c>
-      <c r="AH52" s="6" t="n">
+      <c r="AH52" s="8" t="n">
         <v>18.2</v>
       </c>
       <c r="AI52" s="6" t="inlineStr"/>
       <c r="AJ52" s="6" t="inlineStr"/>
-      <c r="AK52" s="16" t="n"/>
+      <c r="AK52" s="18" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="13" t="n">
         <v>621.25</v>
       </c>
-      <c r="C53" s="17" t="n">
+      <c r="C53" s="19" t="n">
         <v>17.95</v>
       </c>
-      <c r="D53" s="17" t="n">
+      <c r="D53" s="19" t="n">
         <v>18.92</v>
       </c>
-      <c r="E53" s="17" t="n">
+      <c r="E53" s="19" t="n">
         <v>18.01</v>
       </c>
-      <c r="F53" s="17" t="n">
+      <c r="F53" s="19" t="n">
         <v>19.62</v>
       </c>
-      <c r="G53" s="17" t="n">
+      <c r="G53" s="19" t="n">
         <v>18.31</v>
       </c>
-      <c r="H53" s="17" t="n">
+      <c r="H53" s="19" t="n">
         <v>18.65</v>
       </c>
-      <c r="I53" s="17" t="n">
+      <c r="I53" s="19" t="n">
         <v>17.95</v>
       </c>
-      <c r="J53" s="17" t="n">
+      <c r="J53" s="19" t="n">
         <v>18.35</v>
       </c>
-      <c r="K53" s="17" t="n">
+      <c r="K53" s="19" t="n">
         <v>17.77</v>
       </c>
-      <c r="L53" s="17" t="n">
+      <c r="L53" s="19" t="n">
         <v>17.89</v>
       </c>
-      <c r="M53" s="17" t="n">
+      <c r="M53" s="19" t="n">
         <v>18.63</v>
       </c>
-      <c r="N53" s="17" t="n">
+      <c r="N53" s="19" t="n">
         <v>18.2</v>
       </c>
-      <c r="O53" s="17" t="n">
+      <c r="O53" s="19" t="n">
         <v>18.66</v>
       </c>
-      <c r="P53" s="17" t="n">
+      <c r="P53" s="19" t="n">
         <v>18.17</v>
       </c>
-      <c r="Q53" s="17" t="n">
+      <c r="Q53" s="19" t="n">
         <v>17.78</v>
       </c>
-      <c r="R53" s="17" t="n">
+      <c r="R53" s="19" t="n">
         <v>17.77</v>
       </c>
-      <c r="S53" s="17" t="n">
+      <c r="S53" s="19" t="n">
         <v>18.17</v>
       </c>
-      <c r="T53" s="17" t="n">
+      <c r="T53" s="19" t="n">
         <v>18.65</v>
       </c>
-      <c r="U53" s="17" t="n">
+      <c r="U53" s="19" t="n">
         <v>18.15</v>
       </c>
-      <c r="V53" s="17" t="n">
+      <c r="V53" s="19" t="n">
         <v>18.39</v>
       </c>
-      <c r="W53" s="17" t="n">
+      <c r="W53" s="19" t="n">
         <v>18.8</v>
       </c>
-      <c r="X53" s="17" t="n">
+      <c r="X53" s="19" t="n">
         <v>17.88</v>
       </c>
-      <c r="Y53" s="17" t="n">
+      <c r="Y53" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="Z53" s="17" t="n">
+      <c r="Z53" s="19" t="n">
         <v>17.42</v>
       </c>
-      <c r="AA53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD53" s="17" t="n">
+      <c r="AA53" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD53" s="19" t="n">
         <v>17.28</v>
       </c>
-      <c r="AE53" s="17" t="n">
+      <c r="AE53" s="19" t="n">
         <v>17.95</v>
       </c>
-      <c r="AF53" s="17" t="n">
+      <c r="AF53" s="19" t="n">
         <v>17.8</v>
       </c>
-      <c r="AG53" s="17" t="n">
+      <c r="AG53" s="19" t="n">
         <v>17.93</v>
       </c>
-      <c r="AH53" s="12" t="n">
+      <c r="AH53" s="15" t="n">
         <v>18.18</v>
       </c>
-      <c r="AI53" s="12" t="inlineStr"/>
-      <c r="AJ53" s="12" t="inlineStr"/>
-      <c r="AK53" s="18" t="n"/>
+      <c r="AI53" s="13" t="inlineStr"/>
+      <c r="AJ53" s="13" t="inlineStr"/>
+      <c r="AK53" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -39,14 +39,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFC4A2C"/>
-        <bgColor rgb="FFFC4A2C"/>
+        <fgColor rgb="FFCDFECE"/>
+        <bgColor rgb="FFCDFECE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCDFECE"/>
-        <bgColor rgb="FFCDFECE"/>
+        <fgColor rgb="FFFC4A2C"/>
+        <bgColor rgb="FFFC4A2C"/>
       </patternFill>
     </fill>
     <fill>
@@ -197,10 +197,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,10 +218,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -804,7 +804,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       <c r="AG11" s="7" t="n">
         <v>71.11</v>
       </c>
-      <c r="AH11" s="6" t="n">
+      <c r="AH11" s="7" t="n">
         <v>70.79000000000001</v>
       </c>
       <c r="AI11" s="8" t="n">
@@ -1162,10 +1162,10 @@
       <c r="AG12" s="7" t="n">
         <v>93.13</v>
       </c>
-      <c r="AH12" s="6" t="n">
+      <c r="AH12" s="7" t="n">
         <v>93.33</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="7" t="n">
         <v>215.38</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       <c r="AG13" s="7" t="n">
         <v>73.36</v>
       </c>
-      <c r="AH13" s="6" t="n">
+      <c r="AH13" s="7" t="n">
         <v>74.42</v>
       </c>
       <c r="AI13" s="8" t="n">
@@ -1396,7 +1396,7 @@
       <c r="AG14" s="7" t="n">
         <v>96.36</v>
       </c>
-      <c r="AH14" s="6" t="n">
+      <c r="AH14" s="7" t="n">
         <v>96.97</v>
       </c>
       <c r="AI14" s="8" t="n">
@@ -1513,7 +1513,7 @@
       <c r="AG15" s="10" t="n">
         <v>51.09</v>
       </c>
-      <c r="AH15" s="8" t="n">
+      <c r="AH15" s="10" t="n">
         <v>51.77</v>
       </c>
       <c r="AI15" s="8" t="n">
@@ -1630,10 +1630,10 @@
       <c r="AG16" s="7" t="n">
         <v>87.69</v>
       </c>
-      <c r="AH16" s="6" t="n">
+      <c r="AH16" s="7" t="n">
         <v>88.22</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="7" t="n">
         <v>214.98</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       <c r="AG17" s="7" t="n">
         <v>77.31</v>
       </c>
-      <c r="AH17" s="6" t="n">
+      <c r="AH17" s="7" t="n">
         <v>78.98</v>
       </c>
       <c r="AI17" s="8" t="n">
@@ -1864,10 +1864,10 @@
       <c r="AG18" s="7" t="n">
         <v>84.08</v>
       </c>
-      <c r="AH18" s="6" t="n">
+      <c r="AH18" s="7" t="n">
         <v>81.7</v>
       </c>
-      <c r="AI18" s="6" t="n">
+      <c r="AI18" s="7" t="n">
         <v>219.91</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
       <c r="AG19" s="7" t="n">
         <v>55.96</v>
       </c>
-      <c r="AH19" s="6" t="n">
+      <c r="AH19" s="7" t="n">
         <v>56.71</v>
       </c>
       <c r="AI19" s="8" t="n">
@@ -2098,10 +2098,10 @@
       <c r="AG20" s="7" t="n">
         <v>87.14</v>
       </c>
-      <c r="AH20" s="6" t="n">
+      <c r="AH20" s="7" t="n">
         <v>87.34</v>
       </c>
-      <c r="AI20" s="6" t="n">
+      <c r="AI20" s="7" t="n">
         <v>196.8</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
@@ -2215,7 +2215,7 @@
       <c r="AG21" s="7" t="n">
         <v>94.06999999999999</v>
       </c>
-      <c r="AH21" s="6" t="n">
+      <c r="AH21" s="7" t="n">
         <v>94.26000000000001</v>
       </c>
       <c r="AI21" s="8" t="n">
@@ -2332,7 +2332,7 @@
       <c r="AG22" s="7" t="n">
         <v>76.23</v>
       </c>
-      <c r="AH22" s="6" t="n">
+      <c r="AH22" s="7" t="n">
         <v>77.55</v>
       </c>
       <c r="AI22" s="8" t="n">
@@ -2449,7 +2449,7 @@
       <c r="AG23" s="7" t="n">
         <v>84.45</v>
       </c>
-      <c r="AH23" s="6" t="n">
+      <c r="AH23" s="7" t="n">
         <v>71.95999999999999</v>
       </c>
       <c r="AI23" s="8" t="n">
@@ -2566,10 +2566,10 @@
       <c r="AG24" s="7" t="n">
         <v>81.16</v>
       </c>
-      <c r="AH24" s="6" t="n">
+      <c r="AH24" s="7" t="n">
         <v>81.17</v>
       </c>
-      <c r="AI24" s="6" t="n">
+      <c r="AI24" s="7" t="n">
         <v>197.27</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
@@ -2683,7 +2683,7 @@
       <c r="AG25" s="10" t="n">
         <v>47.18</v>
       </c>
-      <c r="AH25" s="8" t="n">
+      <c r="AH25" s="10" t="n">
         <v>47.1</v>
       </c>
       <c r="AI25" s="8" t="n">
@@ -2800,7 +2800,7 @@
       <c r="AG26" s="7" t="n">
         <v>91.37</v>
       </c>
-      <c r="AH26" s="6" t="n">
+      <c r="AH26" s="7" t="n">
         <v>90.45999999999999</v>
       </c>
       <c r="AI26" s="8" t="n">
@@ -2917,7 +2917,7 @@
       <c r="AG27" s="7" t="n">
         <v>89.41</v>
       </c>
-      <c r="AH27" s="6" t="n">
+      <c r="AH27" s="7" t="n">
         <v>89.45</v>
       </c>
       <c r="AI27" s="8" t="n">
@@ -3034,7 +3034,7 @@
       <c r="AG28" s="7" t="n">
         <v>95.53</v>
       </c>
-      <c r="AH28" s="6" t="n">
+      <c r="AH28" s="7" t="n">
         <v>94.22</v>
       </c>
       <c r="AI28" s="8" t="n">
@@ -3151,7 +3151,7 @@
       <c r="AG29" s="10" t="n">
         <v>43.46</v>
       </c>
-      <c r="AH29" s="8" t="n">
+      <c r="AH29" s="10" t="n">
         <v>44.09</v>
       </c>
       <c r="AI29" s="8" t="n">
@@ -3268,10 +3268,10 @@
       <c r="AG30" s="7" t="n">
         <v>93.66</v>
       </c>
-      <c r="AH30" s="6" t="n">
+      <c r="AH30" s="7" t="n">
         <v>93.70999999999999</v>
       </c>
-      <c r="AI30" s="6" t="n">
+      <c r="AI30" s="7" t="n">
         <v>165.25</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
@@ -3385,7 +3385,7 @@
       <c r="AG31" s="7" t="n">
         <v>92.54000000000001</v>
       </c>
-      <c r="AH31" s="6" t="n">
+      <c r="AH31" s="7" t="n">
         <v>92.83</v>
       </c>
       <c r="AI31" s="8" t="n">
@@ -3502,7 +3502,7 @@
       <c r="AG32" s="7" t="n">
         <v>89.7</v>
       </c>
-      <c r="AH32" s="6" t="n">
+      <c r="AH32" s="7" t="n">
         <v>87.01000000000001</v>
       </c>
       <c r="AI32" s="8" t="n">
@@ -3619,7 +3619,7 @@
       <c r="AG33" s="14" t="n">
         <v>93.02</v>
       </c>
-      <c r="AH33" s="13" t="n">
+      <c r="AH33" s="14" t="n">
         <v>92.45</v>
       </c>
       <c r="AI33" s="15" t="n">
@@ -3675,7 +3675,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 01/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
         </is>
       </c>
     </row>

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -209,9 +209,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -229,6 +226,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3058,7 +3058,7 @@
       <c r="D29" s="10" t="n">
         <v>43.4</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="10" t="n">
         <v>42.87</v>
       </c>
       <c r="F29" s="10" t="n">
@@ -3073,7 +3073,7 @@
       <c r="I29" s="10" t="n">
         <v>44.14</v>
       </c>
-      <c r="J29" s="11" t="n">
+      <c r="J29" s="10" t="n">
         <v>42.84</v>
       </c>
       <c r="K29" s="10" t="n">
@@ -3103,13 +3103,13 @@
       <c r="S29" s="10" t="n">
         <v>45.74</v>
       </c>
-      <c r="T29" s="11" t="n">
+      <c r="T29" s="10" t="n">
         <v>42.89</v>
       </c>
-      <c r="U29" s="11" t="n">
+      <c r="U29" s="10" t="n">
         <v>41.15</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="10" t="n">
         <v>42.51</v>
       </c>
       <c r="W29" s="10" t="n">
@@ -3118,7 +3118,7 @@
       <c r="X29" s="10" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y29" s="11" t="n">
+      <c r="Y29" s="10" t="n">
         <v>42.28</v>
       </c>
       <c r="Z29" s="10" t="n">
@@ -3139,13 +3139,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD29" s="11" t="n">
+      <c r="AD29" s="10" t="n">
         <v>41.87</v>
       </c>
-      <c r="AE29" s="11" t="n">
+      <c r="AE29" s="10" t="n">
         <v>42.42</v>
       </c>
-      <c r="AF29" s="11" t="n">
+      <c r="AF29" s="10" t="n">
         <v>41.86</v>
       </c>
       <c r="AG29" s="10" t="n">
@@ -3512,121 +3512,121 @@
       <c r="AK32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>RADIO CAÑARI</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="12" t="n">
         <v>107.7</v>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="13" t="n">
         <v>92.8</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="13" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="13" t="n">
         <v>91.36</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="13" t="n">
         <v>91.81</v>
       </c>
-      <c r="G33" s="14" t="n">
+      <c r="G33" s="13" t="n">
         <v>92.20999999999999</v>
       </c>
-      <c r="H33" s="14" t="n">
+      <c r="H33" s="13" t="n">
         <v>92.84999999999999</v>
       </c>
-      <c r="I33" s="14" t="n">
+      <c r="I33" s="13" t="n">
         <v>92.97</v>
       </c>
-      <c r="J33" s="14" t="n">
+      <c r="J33" s="13" t="n">
         <v>92.06</v>
       </c>
-      <c r="K33" s="14" t="n">
+      <c r="K33" s="13" t="n">
         <v>92.05</v>
       </c>
-      <c r="L33" s="14" t="n">
+      <c r="L33" s="13" t="n">
         <v>91.97</v>
       </c>
-      <c r="M33" s="14" t="n">
+      <c r="M33" s="13" t="n">
         <v>91.98</v>
       </c>
-      <c r="N33" s="14" t="n">
+      <c r="N33" s="13" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="O33" s="14" t="n">
+      <c r="O33" s="13" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="P33" s="14" t="n">
+      <c r="P33" s="13" t="n">
         <v>92.14</v>
       </c>
-      <c r="Q33" s="14" t="n">
+      <c r="Q33" s="13" t="n">
         <v>92.78</v>
       </c>
-      <c r="R33" s="14" t="n">
+      <c r="R33" s="13" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="S33" s="14" t="n">
+      <c r="S33" s="13" t="n">
         <v>92.78</v>
       </c>
-      <c r="T33" s="14" t="n">
+      <c r="T33" s="13" t="n">
         <v>92.92</v>
       </c>
-      <c r="U33" s="14" t="n">
+      <c r="U33" s="13" t="n">
         <v>91.84</v>
       </c>
-      <c r="V33" s="14" t="n">
+      <c r="V33" s="13" t="n">
         <v>92.84</v>
       </c>
-      <c r="W33" s="14" t="n">
+      <c r="W33" s="13" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="X33" s="14" t="n">
+      <c r="X33" s="13" t="n">
         <v>92.89</v>
       </c>
-      <c r="Y33" s="14" t="n">
+      <c r="Y33" s="13" t="n">
         <v>92.36</v>
       </c>
-      <c r="Z33" s="14" t="n">
+      <c r="Z33" s="13" t="n">
         <v>93.11</v>
       </c>
-      <c r="AA33" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB33" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC33" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD33" s="14" t="n">
+      <c r="AA33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="13" t="n">
         <v>93.01000000000001</v>
       </c>
-      <c r="AE33" s="14" t="n">
+      <c r="AE33" s="13" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="AF33" s="14" t="n">
+      <c r="AF33" s="13" t="n">
         <v>92.98</v>
       </c>
-      <c r="AG33" s="14" t="n">
+      <c r="AG33" s="13" t="n">
         <v>93.02</v>
       </c>
-      <c r="AH33" s="14" t="n">
+      <c r="AH33" s="13" t="n">
         <v>92.45</v>
       </c>
-      <c r="AI33" s="15" t="n">
+      <c r="AI33" s="14" t="n">
         <v>269.05</v>
       </c>
-      <c r="AJ33" s="13" t="inlineStr"/>
-      <c r="AK33" s="16" t="inlineStr"/>
+      <c r="AJ33" s="12" t="inlineStr"/>
+      <c r="AK33" s="15" t="inlineStr"/>
     </row>
     <row r="34"/>
     <row r="35"/>
@@ -3801,7 +3801,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK43" s="17" t="n"/>
+      <c r="AK43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3812,19 +3812,19 @@
       <c r="B44" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C44" s="10" t="n">
         <v>54.45</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D44" s="10" t="n">
         <v>54.48</v>
       </c>
       <c r="E44" s="10" t="n">
         <v>57.77</v>
       </c>
-      <c r="F44" s="11" t="n">
+      <c r="F44" s="10" t="n">
         <v>54.82</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="G44" s="10" t="n">
         <v>55.26</v>
       </c>
       <c r="H44" s="10" t="n">
@@ -3833,7 +3833,7 @@
       <c r="I44" s="10" t="n">
         <v>56.04</v>
       </c>
-      <c r="J44" s="11" t="n">
+      <c r="J44" s="10" t="n">
         <v>55.54</v>
       </c>
       <c r="K44" s="10" t="n">
@@ -3851,37 +3851,37 @@
       <c r="O44" s="10" t="n">
         <v>57.66</v>
       </c>
-      <c r="P44" s="11" t="n">
+      <c r="P44" s="10" t="n">
         <v>55.07</v>
       </c>
-      <c r="Q44" s="11" t="n">
+      <c r="Q44" s="10" t="n">
         <v>54.17</v>
       </c>
       <c r="R44" s="10" t="n">
         <v>56.31</v>
       </c>
-      <c r="S44" s="11" t="n">
+      <c r="S44" s="10" t="n">
         <v>55.18</v>
       </c>
       <c r="T44" s="10" t="n">
         <v>56.62</v>
       </c>
-      <c r="U44" s="11" t="n">
+      <c r="U44" s="10" t="n">
         <v>55.28</v>
       </c>
-      <c r="V44" s="11" t="n">
+      <c r="V44" s="10" t="n">
         <v>54.73</v>
       </c>
-      <c r="W44" s="11" t="n">
+      <c r="W44" s="10" t="n">
         <v>55.07</v>
       </c>
-      <c r="X44" s="11" t="n">
+      <c r="X44" s="10" t="n">
         <v>54.94</v>
       </c>
       <c r="Y44" s="10" t="n">
         <v>57.08</v>
       </c>
-      <c r="Z44" s="11" t="n">
+      <c r="Z44" s="10" t="n">
         <v>54.75</v>
       </c>
       <c r="AA44" s="6" t="inlineStr">
@@ -3899,24 +3899,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD44" s="11" t="n">
+      <c r="AD44" s="10" t="n">
         <v>52.19</v>
       </c>
-      <c r="AE44" s="11" t="n">
+      <c r="AE44" s="10" t="n">
         <v>54.52</v>
       </c>
-      <c r="AF44" s="11" t="n">
+      <c r="AF44" s="10" t="n">
         <v>54.88</v>
       </c>
-      <c r="AG44" s="11" t="n">
+      <c r="AG44" s="10" t="n">
         <v>54.43</v>
       </c>
-      <c r="AH44" s="8" t="n">
+      <c r="AH44" s="10" t="n">
         <v>55.55</v>
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="18" t="n"/>
+      <c r="AK44" s="17" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="18" t="n"/>
+      <c r="AK45" s="17" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4042,76 +4042,76 @@
       <c r="B46" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C46" s="11" t="n">
+      <c r="C46" s="18" t="n">
         <v>30.76</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="18" t="n">
         <v>31.32</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="18" t="n">
         <v>32.11</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="18" t="n">
         <v>30.86</v>
       </c>
-      <c r="G46" s="11" t="n">
+      <c r="G46" s="18" t="n">
         <v>28.58</v>
       </c>
-      <c r="H46" s="11" t="n">
+      <c r="H46" s="18" t="n">
         <v>29.81</v>
       </c>
-      <c r="I46" s="11" t="n">
+      <c r="I46" s="18" t="n">
         <v>27.63</v>
       </c>
-      <c r="J46" s="11" t="n">
+      <c r="J46" s="18" t="n">
         <v>31.39</v>
       </c>
-      <c r="K46" s="11" t="n">
+      <c r="K46" s="18" t="n">
         <v>31.98</v>
       </c>
-      <c r="L46" s="11" t="n">
+      <c r="L46" s="18" t="n">
         <v>31.91</v>
       </c>
-      <c r="M46" s="11" t="n">
+      <c r="M46" s="18" t="n">
         <v>33.47</v>
       </c>
-      <c r="N46" s="11" t="n">
+      <c r="N46" s="18" t="n">
         <v>31.81</v>
       </c>
-      <c r="O46" s="11" t="n">
+      <c r="O46" s="18" t="n">
         <v>28.62</v>
       </c>
-      <c r="P46" s="11" t="n">
+      <c r="P46" s="18" t="n">
         <v>24.98</v>
       </c>
-      <c r="Q46" s="11" t="n">
+      <c r="Q46" s="18" t="n">
         <v>27.11</v>
       </c>
-      <c r="R46" s="11" t="n">
+      <c r="R46" s="18" t="n">
         <v>27.55</v>
       </c>
-      <c r="S46" s="11" t="n">
+      <c r="S46" s="18" t="n">
         <v>29.39</v>
       </c>
-      <c r="T46" s="11" t="n">
+      <c r="T46" s="18" t="n">
         <v>30.03</v>
       </c>
-      <c r="U46" s="11" t="n">
+      <c r="U46" s="18" t="n">
         <v>29.37</v>
       </c>
-      <c r="V46" s="11" t="n">
+      <c r="V46" s="18" t="n">
         <v>27.43</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="18" t="n">
         <v>24.95</v>
       </c>
-      <c r="X46" s="11" t="n">
+      <c r="X46" s="18" t="n">
         <v>28.58</v>
       </c>
-      <c r="Y46" s="11" t="n">
+      <c r="Y46" s="18" t="n">
         <v>30.77</v>
       </c>
-      <c r="Z46" s="11" t="n">
+      <c r="Z46" s="18" t="n">
         <v>28.12</v>
       </c>
       <c r="AA46" s="6" t="inlineStr">
@@ -4129,24 +4129,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD46" s="11" t="n">
+      <c r="AD46" s="18" t="n">
         <v>27.18</v>
       </c>
-      <c r="AE46" s="11" t="n">
+      <c r="AE46" s="18" t="n">
         <v>27.85</v>
       </c>
-      <c r="AF46" s="11" t="n">
+      <c r="AF46" s="18" t="n">
         <v>26.6</v>
       </c>
-      <c r="AG46" s="11" t="n">
+      <c r="AG46" s="18" t="n">
         <v>26.24</v>
       </c>
-      <c r="AH46" s="8" t="n">
+      <c r="AH46" s="18" t="n">
         <v>29.16</v>
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
       <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="18" t="n"/>
+      <c r="AK46" s="17" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4157,76 +4157,76 @@
       <c r="B47" s="6" t="n">
         <v>193.25</v>
       </c>
-      <c r="C47" s="11" t="n">
+      <c r="C47" s="18" t="n">
         <v>46.3</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="18" t="n">
         <v>46.33</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E47" s="18" t="n">
         <v>46.39</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="F47" s="18" t="n">
         <v>47.05</v>
       </c>
-      <c r="G47" s="11" t="n">
+      <c r="G47" s="18" t="n">
         <v>47.51</v>
       </c>
-      <c r="H47" s="11" t="n">
+      <c r="H47" s="18" t="n">
         <v>48.13</v>
       </c>
-      <c r="I47" s="11" t="n">
+      <c r="I47" s="18" t="n">
         <v>46.25</v>
       </c>
-      <c r="J47" s="11" t="n">
+      <c r="J47" s="18" t="n">
         <v>47.56</v>
       </c>
-      <c r="K47" s="11" t="n">
+      <c r="K47" s="18" t="n">
         <v>49.26</v>
       </c>
-      <c r="L47" s="11" t="n">
+      <c r="L47" s="18" t="n">
         <v>47.54</v>
       </c>
-      <c r="M47" s="11" t="n">
+      <c r="M47" s="18" t="n">
         <v>48.23</v>
       </c>
-      <c r="N47" s="11" t="n">
+      <c r="N47" s="18" t="n">
         <v>46.86</v>
       </c>
-      <c r="O47" s="11" t="n">
+      <c r="O47" s="18" t="n">
         <v>45.58</v>
       </c>
-      <c r="P47" s="11" t="n">
+      <c r="P47" s="18" t="n">
         <v>45.14</v>
       </c>
-      <c r="Q47" s="11" t="n">
+      <c r="Q47" s="18" t="n">
         <v>46.13</v>
       </c>
-      <c r="R47" s="11" t="n">
+      <c r="R47" s="18" t="n">
         <v>46.38</v>
       </c>
-      <c r="S47" s="11" t="n">
+      <c r="S47" s="18" t="n">
         <v>46.3</v>
       </c>
-      <c r="T47" s="11" t="n">
+      <c r="T47" s="18" t="n">
         <v>49.68</v>
       </c>
-      <c r="U47" s="11" t="n">
+      <c r="U47" s="18" t="n">
         <v>49.32</v>
       </c>
-      <c r="V47" s="11" t="n">
+      <c r="V47" s="18" t="n">
         <v>47.83</v>
       </c>
-      <c r="W47" s="11" t="n">
+      <c r="W47" s="18" t="n">
         <v>45.16</v>
       </c>
-      <c r="X47" s="11" t="n">
+      <c r="X47" s="18" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y47" s="11" t="n">
+      <c r="Y47" s="18" t="n">
         <v>48.44</v>
       </c>
-      <c r="Z47" s="11" t="n">
+      <c r="Z47" s="18" t="n">
         <v>46.78</v>
       </c>
       <c r="AA47" s="6" t="inlineStr">
@@ -4244,24 +4244,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD47" s="11" t="n">
+      <c r="AD47" s="18" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE47" s="11" t="n">
+      <c r="AE47" s="18" t="n">
         <v>47.77</v>
       </c>
-      <c r="AF47" s="11" t="n">
+      <c r="AF47" s="18" t="n">
         <v>47.22</v>
       </c>
-      <c r="AG47" s="11" t="n">
+      <c r="AG47" s="18" t="n">
         <v>47.83</v>
       </c>
-      <c r="AH47" s="8" t="n">
+      <c r="AH47" s="18" t="n">
         <v>47.15</v>
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
       <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="18" t="n"/>
+      <c r="AK47" s="17" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4272,76 +4272,76 @@
       <c r="B48" s="6" t="n">
         <v>205.25</v>
       </c>
-      <c r="C48" s="11" t="n">
+      <c r="C48" s="18" t="n">
         <v>20.25</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="18" t="n">
         <v>19.44</v>
       </c>
-      <c r="E48" s="11" t="n">
+      <c r="E48" s="18" t="n">
         <v>18.66</v>
       </c>
-      <c r="F48" s="11" t="n">
+      <c r="F48" s="18" t="n">
         <v>21.06</v>
       </c>
-      <c r="G48" s="11" t="n">
+      <c r="G48" s="18" t="n">
         <v>19.93</v>
       </c>
-      <c r="H48" s="11" t="n">
+      <c r="H48" s="18" t="n">
         <v>20.95</v>
       </c>
-      <c r="I48" s="11" t="n">
+      <c r="I48" s="18" t="n">
         <v>21.35</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="J48" s="18" t="n">
         <v>19.73</v>
       </c>
-      <c r="K48" s="11" t="n">
+      <c r="K48" s="18" t="n">
         <v>20.03</v>
       </c>
-      <c r="L48" s="11" t="n">
+      <c r="L48" s="18" t="n">
         <v>19.83</v>
       </c>
-      <c r="M48" s="11" t="n">
+      <c r="M48" s="18" t="n">
         <v>19.34</v>
       </c>
-      <c r="N48" s="11" t="n">
+      <c r="N48" s="18" t="n">
         <v>20.03</v>
       </c>
-      <c r="O48" s="11" t="n">
+      <c r="O48" s="18" t="n">
         <v>20.25</v>
       </c>
-      <c r="P48" s="11" t="n">
+      <c r="P48" s="18" t="n">
         <v>19.31</v>
       </c>
-      <c r="Q48" s="11" t="n">
+      <c r="Q48" s="18" t="n">
         <v>21.73</v>
       </c>
-      <c r="R48" s="11" t="n">
+      <c r="R48" s="18" t="n">
         <v>21.23</v>
       </c>
-      <c r="S48" s="11" t="n">
+      <c r="S48" s="18" t="n">
         <v>19.64</v>
       </c>
-      <c r="T48" s="11" t="n">
+      <c r="T48" s="18" t="n">
         <v>20.19</v>
       </c>
-      <c r="U48" s="11" t="n">
+      <c r="U48" s="18" t="n">
         <v>20.4</v>
       </c>
-      <c r="V48" s="11" t="n">
+      <c r="V48" s="18" t="n">
         <v>20.01</v>
       </c>
-      <c r="W48" s="11" t="n">
+      <c r="W48" s="18" t="n">
         <v>20.09</v>
       </c>
-      <c r="X48" s="11" t="n">
+      <c r="X48" s="18" t="n">
         <v>19.82</v>
       </c>
-      <c r="Y48" s="11" t="n">
+      <c r="Y48" s="18" t="n">
         <v>20.22</v>
       </c>
-      <c r="Z48" s="11" t="n">
+      <c r="Z48" s="18" t="n">
         <v>20.75</v>
       </c>
       <c r="AA48" s="6" t="inlineStr">
@@ -4359,24 +4359,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD48" s="11" t="n">
+      <c r="AD48" s="18" t="n">
         <v>20.72</v>
       </c>
-      <c r="AE48" s="11" t="n">
+      <c r="AE48" s="18" t="n">
         <v>19.91</v>
       </c>
-      <c r="AF48" s="11" t="n">
+      <c r="AF48" s="18" t="n">
         <v>20.74</v>
       </c>
-      <c r="AG48" s="11" t="n">
+      <c r="AG48" s="18" t="n">
         <v>20.32</v>
       </c>
-      <c r="AH48" s="8" t="n">
+      <c r="AH48" s="18" t="n">
         <v>20.21</v>
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
       <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="18" t="n"/>
+      <c r="AK48" s="17" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4387,76 +4387,76 @@
       <c r="B49" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C49" s="11" t="n">
+      <c r="C49" s="18" t="n">
         <v>17.22</v>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="18" t="n">
         <v>17.16</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E49" s="18" t="n">
         <v>16.48</v>
       </c>
-      <c r="F49" s="11" t="n">
+      <c r="F49" s="18" t="n">
         <v>20.09</v>
       </c>
-      <c r="G49" s="11" t="n">
+      <c r="G49" s="18" t="n">
         <v>17.15</v>
       </c>
-      <c r="H49" s="11" t="n">
+      <c r="H49" s="18" t="n">
         <v>16.65</v>
       </c>
-      <c r="I49" s="11" t="n">
+      <c r="I49" s="18" t="n">
         <v>17.38</v>
       </c>
-      <c r="J49" s="11" t="n">
+      <c r="J49" s="18" t="n">
         <v>17.17</v>
       </c>
-      <c r="K49" s="11" t="n">
+      <c r="K49" s="18" t="n">
         <v>16.77</v>
       </c>
-      <c r="L49" s="11" t="n">
+      <c r="L49" s="18" t="n">
         <v>16.8</v>
       </c>
-      <c r="M49" s="11" t="n">
+      <c r="M49" s="18" t="n">
         <v>16.85</v>
       </c>
-      <c r="N49" s="11" t="n">
+      <c r="N49" s="18" t="n">
         <v>16.67</v>
       </c>
-      <c r="O49" s="11" t="n">
+      <c r="O49" s="18" t="n">
         <v>16.78</v>
       </c>
-      <c r="P49" s="11" t="n">
+      <c r="P49" s="18" t="n">
         <v>17</v>
       </c>
-      <c r="Q49" s="11" t="n">
+      <c r="Q49" s="18" t="n">
         <v>16.78</v>
       </c>
-      <c r="R49" s="11" t="n">
+      <c r="R49" s="18" t="n">
         <v>16.69</v>
       </c>
-      <c r="S49" s="11" t="n">
+      <c r="S49" s="18" t="n">
         <v>17.09</v>
       </c>
-      <c r="T49" s="11" t="n">
+      <c r="T49" s="18" t="n">
         <v>16.92</v>
       </c>
-      <c r="U49" s="11" t="n">
+      <c r="U49" s="18" t="n">
         <v>16.91</v>
       </c>
-      <c r="V49" s="11" t="n">
+      <c r="V49" s="18" t="n">
         <v>17.3</v>
       </c>
-      <c r="W49" s="11" t="n">
+      <c r="W49" s="18" t="n">
         <v>17.05</v>
       </c>
-      <c r="X49" s="11" t="n">
+      <c r="X49" s="18" t="n">
         <v>16.87</v>
       </c>
-      <c r="Y49" s="11" t="n">
+      <c r="Y49" s="18" t="n">
         <v>16.7</v>
       </c>
-      <c r="Z49" s="11" t="n">
+      <c r="Z49" s="18" t="n">
         <v>16.9</v>
       </c>
       <c r="AA49" s="6" t="inlineStr">
@@ -4474,24 +4474,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD49" s="11" t="n">
+      <c r="AD49" s="18" t="n">
         <v>16.85</v>
       </c>
-      <c r="AE49" s="11" t="n">
+      <c r="AE49" s="18" t="n">
         <v>16.5</v>
       </c>
-      <c r="AF49" s="11" t="n">
+      <c r="AF49" s="18" t="n">
         <v>16.61</v>
       </c>
-      <c r="AG49" s="11" t="n">
+      <c r="AG49" s="18" t="n">
         <v>16.54</v>
       </c>
-      <c r="AH49" s="8" t="n">
+      <c r="AH49" s="18" t="n">
         <v>17</v>
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
       <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="18" t="n"/>
+      <c r="AK49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -4511,67 +4511,67 @@
       <c r="E50" s="10" t="n">
         <v>65.7</v>
       </c>
-      <c r="F50" s="11" t="n">
+      <c r="F50" s="18" t="n">
         <v>29.7</v>
       </c>
-      <c r="G50" s="11" t="n">
+      <c r="G50" s="18" t="n">
         <v>31.15</v>
       </c>
-      <c r="H50" s="11" t="n">
+      <c r="H50" s="18" t="n">
         <v>30.96</v>
       </c>
-      <c r="I50" s="11" t="n">
+      <c r="I50" s="18" t="n">
         <v>30.68</v>
       </c>
-      <c r="J50" s="11" t="n">
+      <c r="J50" s="18" t="n">
         <v>30.74</v>
       </c>
-      <c r="K50" s="11" t="n">
+      <c r="K50" s="18" t="n">
         <v>30.38</v>
       </c>
-      <c r="L50" s="11" t="n">
+      <c r="L50" s="18" t="n">
         <v>30.17</v>
       </c>
-      <c r="M50" s="11" t="n">
+      <c r="M50" s="18" t="n">
         <v>30.75</v>
       </c>
-      <c r="N50" s="11" t="n">
+      <c r="N50" s="18" t="n">
         <v>29.89</v>
       </c>
-      <c r="O50" s="11" t="n">
+      <c r="O50" s="18" t="n">
         <v>30.15</v>
       </c>
-      <c r="P50" s="11" t="n">
+      <c r="P50" s="18" t="n">
         <v>31.64</v>
       </c>
-      <c r="Q50" s="11" t="n">
+      <c r="Q50" s="18" t="n">
         <v>30.28</v>
       </c>
-      <c r="R50" s="11" t="n">
+      <c r="R50" s="18" t="n">
         <v>31.09</v>
       </c>
-      <c r="S50" s="11" t="n">
+      <c r="S50" s="18" t="n">
         <v>30.65</v>
       </c>
-      <c r="T50" s="11" t="n">
+      <c r="T50" s="18" t="n">
         <v>32.47</v>
       </c>
-      <c r="U50" s="11" t="n">
+      <c r="U50" s="18" t="n">
         <v>31.51</v>
       </c>
-      <c r="V50" s="11" t="n">
+      <c r="V50" s="18" t="n">
         <v>30.9</v>
       </c>
-      <c r="W50" s="11" t="n">
+      <c r="W50" s="18" t="n">
         <v>32.99</v>
       </c>
-      <c r="X50" s="11" t="n">
+      <c r="X50" s="18" t="n">
         <v>27.85</v>
       </c>
-      <c r="Y50" s="11" t="n">
+      <c r="Y50" s="18" t="n">
         <v>28.3</v>
       </c>
-      <c r="Z50" s="11" t="n">
+      <c r="Z50" s="18" t="n">
         <v>28.28</v>
       </c>
       <c r="AA50" s="6" t="inlineStr">
@@ -4589,24 +4589,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD50" s="11" t="n">
+      <c r="AD50" s="18" t="n">
         <v>28.19</v>
       </c>
-      <c r="AE50" s="11" t="n">
+      <c r="AE50" s="18" t="n">
         <v>44.75</v>
       </c>
-      <c r="AF50" s="10" t="n">
+      <c r="AF50" s="18" t="n">
         <v>60.62</v>
       </c>
-      <c r="AG50" s="10" t="n">
+      <c r="AG50" s="18" t="n">
         <v>61.05</v>
       </c>
-      <c r="AH50" s="8" t="n">
+      <c r="AH50" s="18" t="n">
         <v>36.81</v>
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
       <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="18" t="n"/>
+      <c r="AK50" s="17" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -4617,76 +4617,76 @@
       <c r="B51" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C51" s="11" t="n">
+      <c r="C51" s="18" t="n">
         <v>22.82</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="18" t="n">
         <v>19.78</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E51" s="18" t="n">
         <v>19.33</v>
       </c>
-      <c r="F51" s="11" t="n">
+      <c r="F51" s="18" t="n">
         <v>20.23</v>
       </c>
-      <c r="G51" s="11" t="n">
+      <c r="G51" s="18" t="n">
         <v>20.96</v>
       </c>
-      <c r="H51" s="11" t="n">
+      <c r="H51" s="18" t="n">
         <v>21.43</v>
       </c>
-      <c r="I51" s="11" t="n">
+      <c r="I51" s="18" t="n">
         <v>20.83</v>
       </c>
-      <c r="J51" s="11" t="n">
+      <c r="J51" s="18" t="n">
         <v>20.46</v>
       </c>
-      <c r="K51" s="11" t="n">
+      <c r="K51" s="18" t="n">
         <v>20.8</v>
       </c>
-      <c r="L51" s="11" t="n">
+      <c r="L51" s="18" t="n">
         <v>19.84</v>
       </c>
-      <c r="M51" s="11" t="n">
+      <c r="M51" s="18" t="n">
         <v>19.92</v>
       </c>
-      <c r="N51" s="11" t="n">
+      <c r="N51" s="18" t="n">
         <v>20.16</v>
       </c>
-      <c r="O51" s="11" t="n">
+      <c r="O51" s="18" t="n">
         <v>20.13</v>
       </c>
-      <c r="P51" s="11" t="n">
+      <c r="P51" s="18" t="n">
         <v>22.75</v>
       </c>
-      <c r="Q51" s="11" t="n">
+      <c r="Q51" s="18" t="n">
         <v>20.9</v>
       </c>
-      <c r="R51" s="11" t="n">
+      <c r="R51" s="18" t="n">
         <v>20.58</v>
       </c>
-      <c r="S51" s="11" t="n">
+      <c r="S51" s="18" t="n">
         <v>20.58</v>
       </c>
-      <c r="T51" s="11" t="n">
+      <c r="T51" s="18" t="n">
         <v>22.65</v>
       </c>
-      <c r="U51" s="11" t="n">
+      <c r="U51" s="18" t="n">
         <v>21.7</v>
       </c>
-      <c r="V51" s="11" t="n">
+      <c r="V51" s="18" t="n">
         <v>19.97</v>
       </c>
-      <c r="W51" s="11" t="n">
+      <c r="W51" s="18" t="n">
         <v>20.77</v>
       </c>
-      <c r="X51" s="11" t="n">
+      <c r="X51" s="18" t="n">
         <v>20.33</v>
       </c>
-      <c r="Y51" s="11" t="n">
+      <c r="Y51" s="18" t="n">
         <v>20.74</v>
       </c>
-      <c r="Z51" s="11" t="n">
+      <c r="Z51" s="18" t="n">
         <v>21.79</v>
       </c>
       <c r="AA51" s="6" t="inlineStr">
@@ -4704,24 +4704,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD51" s="11" t="n">
+      <c r="AD51" s="18" t="n">
         <v>20.5</v>
       </c>
-      <c r="AE51" s="11" t="n">
+      <c r="AE51" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="AF51" s="11" t="n">
+      <c r="AF51" s="18" t="n">
         <v>20.99</v>
       </c>
-      <c r="AG51" s="11" t="n">
+      <c r="AG51" s="18" t="n">
         <v>21.88</v>
       </c>
-      <c r="AH51" s="8" t="n">
+      <c r="AH51" s="18" t="n">
         <v>20.81</v>
       </c>
       <c r="AI51" s="6" t="inlineStr"/>
       <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="18" t="n"/>
+      <c r="AK51" s="17" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -4732,76 +4732,76 @@
       <c r="B52" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C52" s="18" t="n">
         <v>18.53</v>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D52" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="E52" s="11" t="n">
+      <c r="E52" s="18" t="n">
         <v>17.98</v>
       </c>
-      <c r="F52" s="11" t="n">
+      <c r="F52" s="18" t="n">
         <v>18.24</v>
       </c>
-      <c r="G52" s="11" t="n">
+      <c r="G52" s="18" t="n">
         <v>18.19</v>
       </c>
-      <c r="H52" s="11" t="n">
+      <c r="H52" s="18" t="n">
         <v>17.79</v>
       </c>
-      <c r="I52" s="11" t="n">
+      <c r="I52" s="18" t="n">
         <v>18.05</v>
       </c>
-      <c r="J52" s="11" t="n">
+      <c r="J52" s="18" t="n">
         <v>18.3</v>
       </c>
-      <c r="K52" s="11" t="n">
+      <c r="K52" s="18" t="n">
         <v>18.22</v>
       </c>
-      <c r="L52" s="11" t="n">
+      <c r="L52" s="18" t="n">
         <v>17.98</v>
       </c>
-      <c r="M52" s="11" t="n">
+      <c r="M52" s="18" t="n">
         <v>18.44</v>
       </c>
-      <c r="N52" s="11" t="n">
+      <c r="N52" s="18" t="n">
         <v>18.26</v>
       </c>
-      <c r="O52" s="11" t="n">
+      <c r="O52" s="18" t="n">
         <v>18.29</v>
       </c>
-      <c r="P52" s="11" t="n">
+      <c r="P52" s="18" t="n">
         <v>18.67</v>
       </c>
-      <c r="Q52" s="11" t="n">
+      <c r="Q52" s="18" t="n">
         <v>18.47</v>
       </c>
-      <c r="R52" s="11" t="n">
+      <c r="R52" s="18" t="n">
         <v>18.01</v>
       </c>
-      <c r="S52" s="11" t="n">
+      <c r="S52" s="18" t="n">
         <v>18.22</v>
       </c>
-      <c r="T52" s="11" t="n">
+      <c r="T52" s="18" t="n">
         <v>18.26</v>
       </c>
-      <c r="U52" s="11" t="n">
+      <c r="U52" s="18" t="n">
         <v>17.86</v>
       </c>
-      <c r="V52" s="11" t="n">
+      <c r="V52" s="18" t="n">
         <v>18.4</v>
       </c>
-      <c r="W52" s="11" t="n">
+      <c r="W52" s="18" t="n">
         <v>18.1</v>
       </c>
-      <c r="X52" s="11" t="n">
+      <c r="X52" s="18" t="n">
         <v>17.84</v>
       </c>
-      <c r="Y52" s="11" t="n">
+      <c r="Y52" s="18" t="n">
         <v>18.21</v>
       </c>
-      <c r="Z52" s="11" t="n">
+      <c r="Z52" s="18" t="n">
         <v>18.21</v>
       </c>
       <c r="AA52" s="6" t="inlineStr">
@@ -4819,32 +4819,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD52" s="11" t="n">
+      <c r="AD52" s="18" t="n">
         <v>18.28</v>
       </c>
-      <c r="AE52" s="11" t="n">
+      <c r="AE52" s="18" t="n">
         <v>17.92</v>
       </c>
-      <c r="AF52" s="11" t="n">
+      <c r="AF52" s="18" t="n">
         <v>19.01</v>
       </c>
-      <c r="AG52" s="11" t="n">
+      <c r="AG52" s="18" t="n">
         <v>17.87</v>
       </c>
-      <c r="AH52" s="8" t="n">
+      <c r="AH52" s="18" t="n">
         <v>18.2</v>
       </c>
       <c r="AI52" s="6" t="inlineStr"/>
       <c r="AJ52" s="6" t="inlineStr"/>
-      <c r="AK52" s="18" t="n"/>
+      <c r="AK52" s="17" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B53" s="13" t="n">
+      <c r="B53" s="12" t="n">
         <v>621.25</v>
       </c>
       <c r="C53" s="19" t="n">
@@ -4919,17 +4919,17 @@
       <c r="Z53" s="19" t="n">
         <v>17.42</v>
       </c>
-      <c r="AA53" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB53" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC53" s="13" t="inlineStr">
+      <c r="AA53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4946,11 +4946,11 @@
       <c r="AG53" s="19" t="n">
         <v>17.93</v>
       </c>
-      <c r="AH53" s="15" t="n">
+      <c r="AH53" s="19" t="n">
         <v>18.18</v>
       </c>
-      <c r="AI53" s="13" t="inlineStr"/>
-      <c r="AJ53" s="13" t="inlineStr"/>
+      <c r="AI53" s="12" t="inlineStr"/>
+      <c r="AJ53" s="12" t="inlineStr"/>
       <c r="AK53" s="20" t="n"/>
     </row>
   </sheetData>

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -177,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,6 +204,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,15 +225,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1052,7 +1061,12 @@
         <v>339.89</v>
       </c>
       <c r="AJ11" s="6" t="inlineStr"/>
-      <c r="AK11" s="9" t="inlineStr"/>
+      <c r="AK11" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1169,7 +1183,7 @@
         <v>215.38</v>
       </c>
       <c r="AJ12" s="6" t="inlineStr"/>
-      <c r="AK12" s="9" t="inlineStr"/>
+      <c r="AK12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1286,7 +1300,12 @@
         <v>381.82</v>
       </c>
       <c r="AJ13" s="6" t="inlineStr"/>
-      <c r="AK13" s="9" t="inlineStr"/>
+      <c r="AK13" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1403,7 +1422,12 @@
         <v>394.82</v>
       </c>
       <c r="AJ14" s="6" t="inlineStr"/>
-      <c r="AK14" s="9" t="inlineStr"/>
+      <c r="AK14" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1414,76 +1438,76 @@
       <c r="B15" s="6" t="n">
         <v>91.7</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="11" t="n">
         <v>51.91</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <v>51.91</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="11" t="n">
         <v>53.71</v>
       </c>
-      <c r="F15" s="10" t="n">
+      <c r="F15" s="11" t="n">
         <v>53.19</v>
       </c>
-      <c r="G15" s="10" t="n">
+      <c r="G15" s="11" t="n">
         <v>52.31</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H15" s="11" t="n">
         <v>52.02</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I15" s="11" t="n">
         <v>51.63</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J15" s="11" t="n">
         <v>51.38</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="K15" s="11" t="n">
         <v>52.8</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="L15" s="11" t="n">
         <v>52.85</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="M15" s="11" t="n">
         <v>52.05</v>
       </c>
-      <c r="N15" s="10" t="n">
+      <c r="N15" s="11" t="n">
         <v>51.7</v>
       </c>
-      <c r="O15" s="10" t="n">
+      <c r="O15" s="11" t="n">
         <v>51.64</v>
       </c>
-      <c r="P15" s="10" t="n">
+      <c r="P15" s="11" t="n">
         <v>51.52</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="Q15" s="11" t="n">
         <v>51.34</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="R15" s="11" t="n">
         <v>51.23</v>
       </c>
-      <c r="S15" s="10" t="n">
+      <c r="S15" s="11" t="n">
         <v>51.05</v>
       </c>
-      <c r="T15" s="10" t="n">
+      <c r="T15" s="11" t="n">
         <v>51.93</v>
       </c>
-      <c r="U15" s="10" t="n">
+      <c r="U15" s="11" t="n">
         <v>51.36</v>
       </c>
-      <c r="V15" s="10" t="n">
+      <c r="V15" s="11" t="n">
         <v>51.27</v>
       </c>
-      <c r="W15" s="10" t="n">
+      <c r="W15" s="11" t="n">
         <v>51.31</v>
       </c>
-      <c r="X15" s="10" t="n">
+      <c r="X15" s="11" t="n">
         <v>51.83</v>
       </c>
-      <c r="Y15" s="10" t="n">
+      <c r="Y15" s="11" t="n">
         <v>51.24</v>
       </c>
-      <c r="Z15" s="10" t="n">
+      <c r="Z15" s="11" t="n">
         <v>52.94</v>
       </c>
       <c r="AA15" s="6" t="inlineStr">
@@ -1501,26 +1525,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD15" s="10" t="n">
+      <c r="AD15" s="11" t="n">
         <v>51.04</v>
       </c>
-      <c r="AE15" s="10" t="n">
+      <c r="AE15" s="11" t="n">
         <v>50.71</v>
       </c>
-      <c r="AF15" s="10" t="n">
+      <c r="AF15" s="11" t="n">
         <v>50.56</v>
       </c>
-      <c r="AG15" s="10" t="n">
+      <c r="AG15" s="11" t="n">
         <v>51.09</v>
       </c>
-      <c r="AH15" s="10" t="n">
+      <c r="AH15" s="11" t="n">
         <v>51.77</v>
       </c>
       <c r="AI15" s="8" t="n">
         <v>489.28</v>
       </c>
       <c r="AJ15" s="6" t="inlineStr"/>
-      <c r="AK15" s="9" t="inlineStr"/>
+      <c r="AK15" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1637,7 +1666,7 @@
         <v>214.98</v>
       </c>
       <c r="AJ16" s="6" t="inlineStr"/>
-      <c r="AK16" s="9" t="inlineStr"/>
+      <c r="AK16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1754,7 +1783,12 @@
         <v>362.77</v>
       </c>
       <c r="AJ17" s="6" t="inlineStr"/>
-      <c r="AK17" s="9" t="inlineStr"/>
+      <c r="AK17" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1871,7 +1905,7 @@
         <v>219.91</v>
       </c>
       <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="9" t="inlineStr"/>
+      <c r="AK18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1951,7 +1985,7 @@
       <c r="Y19" s="7" t="n">
         <v>56.06</v>
       </c>
-      <c r="Z19" s="10" t="n">
+      <c r="Z19" s="11" t="n">
         <v>53.79</v>
       </c>
       <c r="AA19" s="6" t="inlineStr">
@@ -1969,7 +2003,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD19" s="10" t="n">
+      <c r="AD19" s="11" t="n">
         <v>52.48</v>
       </c>
       <c r="AE19" s="7" t="n">
@@ -1988,7 +2022,12 @@
         <v>489.91</v>
       </c>
       <c r="AJ19" s="6" t="inlineStr"/>
-      <c r="AK19" s="9" t="inlineStr"/>
+      <c r="AK19" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2105,7 +2144,7 @@
         <v>196.8</v>
       </c>
       <c r="AJ20" s="6" t="inlineStr"/>
-      <c r="AK20" s="9" t="inlineStr"/>
+      <c r="AK20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2222,7 +2261,12 @@
         <v>230.95</v>
       </c>
       <c r="AJ21" s="6" t="inlineStr"/>
-      <c r="AK21" s="9" t="inlineStr"/>
+      <c r="AK21" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2339,7 +2383,12 @@
         <v>436.64</v>
       </c>
       <c r="AJ22" s="6" t="inlineStr"/>
-      <c r="AK22" s="9" t="inlineStr"/>
+      <c r="AK22" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2456,7 +2505,12 @@
         <v>257.14</v>
       </c>
       <c r="AJ23" s="6" t="inlineStr"/>
-      <c r="AK23" s="9" t="inlineStr"/>
+      <c r="AK23" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2573,7 +2627,7 @@
         <v>197.27</v>
       </c>
       <c r="AJ24" s="6" t="inlineStr"/>
-      <c r="AK24" s="9" t="inlineStr"/>
+      <c r="AK24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2584,76 +2638,76 @@
       <c r="B25" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="C25" s="10" t="n">
+      <c r="C25" s="11" t="n">
         <v>46.88</v>
       </c>
-      <c r="D25" s="10" t="n">
+      <c r="D25" s="11" t="n">
         <v>46.81</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="E25" s="11" t="n">
         <v>45.97</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="11" t="n">
         <v>47.78</v>
       </c>
-      <c r="G25" s="10" t="n">
+      <c r="G25" s="11" t="n">
         <v>48.08</v>
       </c>
-      <c r="H25" s="10" t="n">
+      <c r="H25" s="11" t="n">
         <v>47.05</v>
       </c>
-      <c r="I25" s="10" t="n">
+      <c r="I25" s="11" t="n">
         <v>46.67</v>
       </c>
-      <c r="J25" s="10" t="n">
+      <c r="J25" s="11" t="n">
         <v>47.12</v>
       </c>
-      <c r="K25" s="10" t="n">
+      <c r="K25" s="11" t="n">
         <v>46.84</v>
       </c>
-      <c r="L25" s="10" t="n">
+      <c r="L25" s="11" t="n">
         <v>46.88</v>
       </c>
-      <c r="M25" s="10" t="n">
+      <c r="M25" s="11" t="n">
         <v>46.33</v>
       </c>
-      <c r="N25" s="10" t="n">
+      <c r="N25" s="11" t="n">
         <v>49.66</v>
       </c>
-      <c r="O25" s="10" t="n">
+      <c r="O25" s="11" t="n">
         <v>48.7</v>
       </c>
-      <c r="P25" s="10" t="n">
+      <c r="P25" s="11" t="n">
         <v>49.31</v>
       </c>
-      <c r="Q25" s="10" t="n">
+      <c r="Q25" s="11" t="n">
         <v>47.73</v>
       </c>
-      <c r="R25" s="10" t="n">
+      <c r="R25" s="11" t="n">
         <v>49.23</v>
       </c>
-      <c r="S25" s="10" t="n">
+      <c r="S25" s="11" t="n">
         <v>47.98</v>
       </c>
-      <c r="T25" s="10" t="n">
+      <c r="T25" s="11" t="n">
         <v>46.88</v>
       </c>
-      <c r="U25" s="10" t="n">
+      <c r="U25" s="11" t="n">
         <v>45.82</v>
       </c>
-      <c r="V25" s="10" t="n">
+      <c r="V25" s="11" t="n">
         <v>46.52</v>
       </c>
-      <c r="W25" s="10" t="n">
+      <c r="W25" s="11" t="n">
         <v>47.44</v>
       </c>
-      <c r="X25" s="10" t="n">
+      <c r="X25" s="11" t="n">
         <v>46.51</v>
       </c>
-      <c r="Y25" s="10" t="n">
+      <c r="Y25" s="11" t="n">
         <v>46.15</v>
       </c>
-      <c r="Z25" s="10" t="n">
+      <c r="Z25" s="11" t="n">
         <v>45.64</v>
       </c>
       <c r="AA25" s="6" t="inlineStr">
@@ -2671,26 +2725,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD25" s="10" t="n">
+      <c r="AD25" s="11" t="n">
         <v>44.54</v>
       </c>
-      <c r="AE25" s="10" t="n">
+      <c r="AE25" s="11" t="n">
         <v>46.63</v>
       </c>
-      <c r="AF25" s="10" t="n">
+      <c r="AF25" s="11" t="n">
         <v>46.59</v>
       </c>
-      <c r="AG25" s="10" t="n">
+      <c r="AG25" s="11" t="n">
         <v>47.18</v>
       </c>
-      <c r="AH25" s="10" t="n">
+      <c r="AH25" s="11" t="n">
         <v>47.1</v>
       </c>
       <c r="AI25" s="8" t="n">
         <v>490</v>
       </c>
       <c r="AJ25" s="6" t="inlineStr"/>
-      <c r="AK25" s="9" t="inlineStr"/>
+      <c r="AK25" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2807,7 +2866,12 @@
         <v>371.19</v>
       </c>
       <c r="AJ26" s="6" t="inlineStr"/>
-      <c r="AK26" s="9" t="inlineStr"/>
+      <c r="AK26" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2924,7 +2988,12 @@
         <v>315.07</v>
       </c>
       <c r="AJ27" s="6" t="inlineStr"/>
-      <c r="AK27" s="9" t="inlineStr"/>
+      <c r="AK27" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -3041,7 +3110,12 @@
         <v>244.12</v>
       </c>
       <c r="AJ28" s="6" t="inlineStr"/>
-      <c r="AK28" s="9" t="inlineStr"/>
+      <c r="AK28" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3052,76 +3126,76 @@
       <c r="B29" s="6" t="n">
         <v>105.7</v>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C29" s="11" t="n">
         <v>44.26</v>
       </c>
-      <c r="D29" s="10" t="n">
+      <c r="D29" s="11" t="n">
         <v>43.4</v>
       </c>
-      <c r="E29" s="10" t="n">
+      <c r="E29" s="11" t="n">
         <v>42.87</v>
       </c>
-      <c r="F29" s="10" t="n">
+      <c r="F29" s="11" t="n">
         <v>43.78</v>
       </c>
-      <c r="G29" s="10" t="n">
+      <c r="G29" s="11" t="n">
         <v>45.04</v>
       </c>
-      <c r="H29" s="10" t="n">
+      <c r="H29" s="11" t="n">
         <v>43.91</v>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="I29" s="11" t="n">
         <v>44.14</v>
       </c>
-      <c r="J29" s="10" t="n">
+      <c r="J29" s="11" t="n">
         <v>42.84</v>
       </c>
-      <c r="K29" s="10" t="n">
+      <c r="K29" s="11" t="n">
         <v>44.14</v>
       </c>
-      <c r="L29" s="10" t="n">
+      <c r="L29" s="11" t="n">
         <v>43.75</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M29" s="11" t="n">
         <v>48.48</v>
       </c>
-      <c r="N29" s="10" t="n">
+      <c r="N29" s="11" t="n">
         <v>47.18</v>
       </c>
-      <c r="O29" s="10" t="n">
+      <c r="O29" s="11" t="n">
         <v>44.35</v>
       </c>
-      <c r="P29" s="10" t="n">
+      <c r="P29" s="11" t="n">
         <v>45.84</v>
       </c>
-      <c r="Q29" s="10" t="n">
+      <c r="Q29" s="11" t="n">
         <v>46.76</v>
       </c>
-      <c r="R29" s="10" t="n">
+      <c r="R29" s="11" t="n">
         <v>47.58</v>
       </c>
-      <c r="S29" s="10" t="n">
+      <c r="S29" s="11" t="n">
         <v>45.74</v>
       </c>
-      <c r="T29" s="10" t="n">
+      <c r="T29" s="11" t="n">
         <v>42.89</v>
       </c>
-      <c r="U29" s="10" t="n">
+      <c r="U29" s="11" t="n">
         <v>41.15</v>
       </c>
-      <c r="V29" s="10" t="n">
+      <c r="V29" s="11" t="n">
         <v>42.51</v>
       </c>
-      <c r="W29" s="10" t="n">
+      <c r="W29" s="11" t="n">
         <v>43.88</v>
       </c>
-      <c r="X29" s="10" t="n">
+      <c r="X29" s="11" t="n">
         <v>43.55</v>
       </c>
-      <c r="Y29" s="10" t="n">
+      <c r="Y29" s="11" t="n">
         <v>42.28</v>
       </c>
-      <c r="Z29" s="10" t="n">
+      <c r="Z29" s="11" t="n">
         <v>44.64</v>
       </c>
       <c r="AA29" s="6" t="inlineStr">
@@ -3139,26 +3213,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD29" s="10" t="n">
+      <c r="AD29" s="11" t="n">
         <v>41.87</v>
       </c>
-      <c r="AE29" s="10" t="n">
+      <c r="AE29" s="11" t="n">
         <v>42.42</v>
       </c>
-      <c r="AF29" s="10" t="n">
+      <c r="AF29" s="11" t="n">
         <v>41.86</v>
       </c>
-      <c r="AG29" s="10" t="n">
+      <c r="AG29" s="11" t="n">
         <v>43.46</v>
       </c>
-      <c r="AH29" s="10" t="n">
+      <c r="AH29" s="11" t="n">
         <v>44.09</v>
       </c>
       <c r="AI29" s="8" t="n">
         <v>483.6</v>
       </c>
       <c r="AJ29" s="6" t="inlineStr"/>
-      <c r="AK29" s="9" t="inlineStr"/>
+      <c r="AK29" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3275,7 +3354,7 @@
         <v>165.25</v>
       </c>
       <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="9" t="inlineStr"/>
+      <c r="AK30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3392,7 +3471,12 @@
         <v>243.85</v>
       </c>
       <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="9" t="inlineStr"/>
+      <c r="AK31" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3424,7 +3508,7 @@
       <c r="I32" s="7" t="n">
         <v>68.03</v>
       </c>
-      <c r="J32" s="10" t="n">
+      <c r="J32" s="11" t="n">
         <v>46.18</v>
       </c>
       <c r="K32" s="7" t="n">
@@ -3509,124 +3593,134 @@
         <v>332.07</v>
       </c>
       <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="9" t="inlineStr"/>
+      <c r="AK32" s="9" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>RADIO CAÑARI</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>107.7</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="14" t="n">
         <v>92.8</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>91.36</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="14" t="n">
         <v>91.81</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="14" t="n">
         <v>92.20999999999999</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="14" t="n">
         <v>92.84999999999999</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="I33" s="14" t="n">
         <v>92.97</v>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="J33" s="14" t="n">
         <v>92.06</v>
       </c>
-      <c r="K33" s="13" t="n">
+      <c r="K33" s="14" t="n">
         <v>92.05</v>
       </c>
-      <c r="L33" s="13" t="n">
+      <c r="L33" s="14" t="n">
         <v>91.97</v>
       </c>
-      <c r="M33" s="13" t="n">
+      <c r="M33" s="14" t="n">
         <v>91.98</v>
       </c>
-      <c r="N33" s="13" t="n">
+      <c r="N33" s="14" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="O33" s="13" t="n">
+      <c r="O33" s="14" t="n">
         <v>91.81999999999999</v>
       </c>
-      <c r="P33" s="13" t="n">
+      <c r="P33" s="14" t="n">
         <v>92.14</v>
       </c>
-      <c r="Q33" s="13" t="n">
+      <c r="Q33" s="14" t="n">
         <v>92.78</v>
       </c>
-      <c r="R33" s="13" t="n">
+      <c r="R33" s="14" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="S33" s="13" t="n">
+      <c r="S33" s="14" t="n">
         <v>92.78</v>
       </c>
-      <c r="T33" s="13" t="n">
+      <c r="T33" s="14" t="n">
         <v>92.92</v>
       </c>
-      <c r="U33" s="13" t="n">
+      <c r="U33" s="14" t="n">
         <v>91.84</v>
       </c>
-      <c r="V33" s="13" t="n">
+      <c r="V33" s="14" t="n">
         <v>92.84</v>
       </c>
-      <c r="W33" s="13" t="n">
+      <c r="W33" s="14" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="X33" s="13" t="n">
+      <c r="X33" s="14" t="n">
         <v>92.89</v>
       </c>
-      <c r="Y33" s="13" t="n">
+      <c r="Y33" s="14" t="n">
         <v>92.36</v>
       </c>
-      <c r="Z33" s="13" t="n">
+      <c r="Z33" s="14" t="n">
         <v>93.11</v>
       </c>
-      <c r="AA33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC33" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD33" s="13" t="n">
+      <c r="AA33" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" s="14" t="n">
         <v>93.01000000000001</v>
       </c>
-      <c r="AE33" s="13" t="n">
+      <c r="AE33" s="14" t="n">
         <v>92.70999999999999</v>
       </c>
-      <c r="AF33" s="13" t="n">
+      <c r="AF33" s="14" t="n">
         <v>92.98</v>
       </c>
-      <c r="AG33" s="13" t="n">
+      <c r="AG33" s="14" t="n">
         <v>93.02</v>
       </c>
-      <c r="AH33" s="13" t="n">
+      <c r="AH33" s="14" t="n">
         <v>92.45</v>
       </c>
-      <c r="AI33" s="14" t="n">
+      <c r="AI33" s="15" t="n">
         <v>269.05</v>
       </c>
-      <c r="AJ33" s="12" t="inlineStr"/>
-      <c r="AK33" s="15" t="inlineStr"/>
+      <c r="AJ33" s="13" t="inlineStr"/>
+      <c r="AK33" s="16" t="inlineStr">
+        <is>
+          <t>Opera con ancho de banda mayor a lo
+autorizado(medición automática)</t>
+        </is>
+      </c>
     </row>
     <row r="34"/>
     <row r="35"/>
@@ -3801,7 +3895,7 @@
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="AK43" s="16" t="n"/>
+      <c r="AK43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -3812,76 +3906,76 @@
       <c r="B44" s="6" t="n">
         <v>61.25</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="11" t="n">
         <v>54.45</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="11" t="n">
         <v>54.48</v>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E44" s="11" t="n">
         <v>57.77</v>
       </c>
-      <c r="F44" s="10" t="n">
+      <c r="F44" s="11" t="n">
         <v>54.82</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G44" s="11" t="n">
         <v>55.26</v>
       </c>
-      <c r="H44" s="10" t="n">
+      <c r="H44" s="11" t="n">
         <v>56.32</v>
       </c>
-      <c r="I44" s="10" t="n">
+      <c r="I44" s="11" t="n">
         <v>56.04</v>
       </c>
-      <c r="J44" s="10" t="n">
+      <c r="J44" s="11" t="n">
         <v>55.54</v>
       </c>
-      <c r="K44" s="10" t="n">
+      <c r="K44" s="11" t="n">
         <v>56.45</v>
       </c>
-      <c r="L44" s="10" t="n">
+      <c r="L44" s="11" t="n">
         <v>56.89</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M44" s="11" t="n">
         <v>56.92</v>
       </c>
-      <c r="N44" s="10" t="n">
+      <c r="N44" s="11" t="n">
         <v>57.59</v>
       </c>
-      <c r="O44" s="10" t="n">
+      <c r="O44" s="11" t="n">
         <v>57.66</v>
       </c>
-      <c r="P44" s="10" t="n">
+      <c r="P44" s="11" t="n">
         <v>55.07</v>
       </c>
-      <c r="Q44" s="10" t="n">
+      <c r="Q44" s="11" t="n">
         <v>54.17</v>
       </c>
-      <c r="R44" s="10" t="n">
+      <c r="R44" s="11" t="n">
         <v>56.31</v>
       </c>
-      <c r="S44" s="10" t="n">
+      <c r="S44" s="11" t="n">
         <v>55.18</v>
       </c>
-      <c r="T44" s="10" t="n">
+      <c r="T44" s="11" t="n">
         <v>56.62</v>
       </c>
-      <c r="U44" s="10" t="n">
+      <c r="U44" s="11" t="n">
         <v>55.28</v>
       </c>
-      <c r="V44" s="10" t="n">
+      <c r="V44" s="11" t="n">
         <v>54.73</v>
       </c>
-      <c r="W44" s="10" t="n">
+      <c r="W44" s="11" t="n">
         <v>55.07</v>
       </c>
-      <c r="X44" s="10" t="n">
+      <c r="X44" s="11" t="n">
         <v>54.94</v>
       </c>
-      <c r="Y44" s="10" t="n">
+      <c r="Y44" s="11" t="n">
         <v>57.08</v>
       </c>
-      <c r="Z44" s="10" t="n">
+      <c r="Z44" s="11" t="n">
         <v>54.75</v>
       </c>
       <c r="AA44" s="6" t="inlineStr">
@@ -3899,24 +3993,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD44" s="10" t="n">
+      <c r="AD44" s="11" t="n">
         <v>52.19</v>
       </c>
-      <c r="AE44" s="10" t="n">
+      <c r="AE44" s="11" t="n">
         <v>54.52</v>
       </c>
-      <c r="AF44" s="10" t="n">
+      <c r="AF44" s="11" t="n">
         <v>54.88</v>
       </c>
-      <c r="AG44" s="10" t="n">
+      <c r="AG44" s="11" t="n">
         <v>54.43</v>
       </c>
-      <c r="AH44" s="10" t="n">
+      <c r="AH44" s="11" t="n">
         <v>55.55</v>
       </c>
       <c r="AI44" s="6" t="inlineStr"/>
       <c r="AJ44" s="6" t="inlineStr"/>
-      <c r="AK44" s="17" t="n"/>
+      <c r="AK44" s="18" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -3927,76 +4021,76 @@
       <c r="B45" s="6" t="n">
         <v>83.25</v>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C45" s="11" t="n">
         <v>62.47</v>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="11" t="n">
         <v>60.99</v>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E45" s="11" t="n">
         <v>59.32</v>
       </c>
-      <c r="F45" s="10" t="n">
+      <c r="F45" s="11" t="n">
         <v>61.95</v>
       </c>
-      <c r="G45" s="10" t="n">
+      <c r="G45" s="11" t="n">
         <v>61.42</v>
       </c>
-      <c r="H45" s="10" t="n">
+      <c r="H45" s="11" t="n">
         <v>61.35</v>
       </c>
-      <c r="I45" s="10" t="n">
+      <c r="I45" s="11" t="n">
         <v>60.77</v>
       </c>
-      <c r="J45" s="10" t="n">
+      <c r="J45" s="11" t="n">
         <v>60.27</v>
       </c>
-      <c r="K45" s="10" t="n">
+      <c r="K45" s="11" t="n">
         <v>59.26</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L45" s="11" t="n">
         <v>59.13</v>
       </c>
-      <c r="M45" s="10" t="n">
+      <c r="M45" s="11" t="n">
         <v>59.08</v>
       </c>
-      <c r="N45" s="10" t="n">
+      <c r="N45" s="11" t="n">
         <v>57.83</v>
       </c>
-      <c r="O45" s="10" t="n">
+      <c r="O45" s="11" t="n">
         <v>58.15</v>
       </c>
-      <c r="P45" s="10" t="n">
+      <c r="P45" s="11" t="n">
         <v>62.37</v>
       </c>
-      <c r="Q45" s="10" t="n">
+      <c r="Q45" s="11" t="n">
         <v>62.44</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="11" t="n">
         <v>59.07</v>
       </c>
-      <c r="S45" s="10" t="n">
+      <c r="S45" s="11" t="n">
         <v>61.21</v>
       </c>
-      <c r="T45" s="10" t="n">
+      <c r="T45" s="11" t="n">
         <v>58.95</v>
       </c>
-      <c r="U45" s="10" t="n">
+      <c r="U45" s="11" t="n">
         <v>61.47</v>
       </c>
-      <c r="V45" s="10" t="n">
+      <c r="V45" s="11" t="n">
         <v>62.25</v>
       </c>
-      <c r="W45" s="10" t="n">
+      <c r="W45" s="11" t="n">
         <v>62</v>
       </c>
-      <c r="X45" s="10" t="n">
+      <c r="X45" s="11" t="n">
         <v>62.32</v>
       </c>
-      <c r="Y45" s="10" t="n">
+      <c r="Y45" s="11" t="n">
         <v>60.83</v>
       </c>
-      <c r="Z45" s="10" t="n">
+      <c r="Z45" s="11" t="n">
         <v>62.26</v>
       </c>
       <c r="AA45" s="6" t="inlineStr">
@@ -4014,26 +4108,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD45" s="10" t="n">
+      <c r="AD45" s="11" t="n">
         <v>62.62</v>
       </c>
-      <c r="AE45" s="10" t="n">
+      <c r="AE45" s="11" t="n">
         <v>62.34</v>
       </c>
-      <c r="AF45" s="10" t="n">
+      <c r="AF45" s="11" t="n">
         <v>62.65</v>
       </c>
-      <c r="AG45" s="10" t="n">
+      <c r="AG45" s="11" t="n">
         <v>63.19</v>
       </c>
-      <c r="AH45" s="10" t="n">
+      <c r="AH45" s="11" t="n">
         <v>61</v>
       </c>
       <c r="AI45" s="6" t="inlineStr"/>
       <c r="AJ45" s="6" t="inlineStr"/>
-      <c r="AK45" s="17" t="n"/>
+      <c r="AK45" s="18" t="n"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>TELEVISION DEL PACIFICO</t>
@@ -4042,76 +4136,76 @@
       <c r="B46" s="6" t="n">
         <v>181.25</v>
       </c>
-      <c r="C46" s="18" t="n">
+      <c r="C46" s="19" t="n">
         <v>30.76</v>
       </c>
-      <c r="D46" s="18" t="n">
+      <c r="D46" s="19" t="n">
         <v>31.32</v>
       </c>
-      <c r="E46" s="18" t="n">
+      <c r="E46" s="19" t="n">
         <v>32.11</v>
       </c>
-      <c r="F46" s="18" t="n">
+      <c r="F46" s="19" t="n">
         <v>30.86</v>
       </c>
-      <c r="G46" s="18" t="n">
+      <c r="G46" s="19" t="n">
         <v>28.58</v>
       </c>
-      <c r="H46" s="18" t="n">
+      <c r="H46" s="19" t="n">
         <v>29.81</v>
       </c>
-      <c r="I46" s="18" t="n">
+      <c r="I46" s="19" t="n">
         <v>27.63</v>
       </c>
-      <c r="J46" s="18" t="n">
+      <c r="J46" s="19" t="n">
         <v>31.39</v>
       </c>
-      <c r="K46" s="18" t="n">
+      <c r="K46" s="19" t="n">
         <v>31.98</v>
       </c>
-      <c r="L46" s="18" t="n">
+      <c r="L46" s="19" t="n">
         <v>31.91</v>
       </c>
-      <c r="M46" s="18" t="n">
+      <c r="M46" s="19" t="n">
         <v>33.47</v>
       </c>
-      <c r="N46" s="18" t="n">
+      <c r="N46" s="19" t="n">
         <v>31.81</v>
       </c>
-      <c r="O46" s="18" t="n">
+      <c r="O46" s="19" t="n">
         <v>28.62</v>
       </c>
-      <c r="P46" s="18" t="n">
+      <c r="P46" s="19" t="n">
         <v>24.98</v>
       </c>
-      <c r="Q46" s="18" t="n">
+      <c r="Q46" s="19" t="n">
         <v>27.11</v>
       </c>
-      <c r="R46" s="18" t="n">
+      <c r="R46" s="19" t="n">
         <v>27.55</v>
       </c>
-      <c r="S46" s="18" t="n">
+      <c r="S46" s="19" t="n">
         <v>29.39</v>
       </c>
-      <c r="T46" s="18" t="n">
+      <c r="T46" s="19" t="n">
         <v>30.03</v>
       </c>
-      <c r="U46" s="18" t="n">
+      <c r="U46" s="19" t="n">
         <v>29.37</v>
       </c>
-      <c r="V46" s="18" t="n">
+      <c r="V46" s="19" t="n">
         <v>27.43</v>
       </c>
-      <c r="W46" s="18" t="n">
+      <c r="W46" s="19" t="n">
         <v>24.95</v>
       </c>
-      <c r="X46" s="18" t="n">
+      <c r="X46" s="19" t="n">
         <v>28.58</v>
       </c>
-      <c r="Y46" s="18" t="n">
+      <c r="Y46" s="19" t="n">
         <v>30.77</v>
       </c>
-      <c r="Z46" s="18" t="n">
+      <c r="Z46" s="19" t="n">
         <v>28.12</v>
       </c>
       <c r="AA46" s="6" t="inlineStr">
@@ -4129,26 +4223,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD46" s="18" t="n">
+      <c r="AD46" s="19" t="n">
         <v>27.18</v>
       </c>
-      <c r="AE46" s="18" t="n">
+      <c r="AE46" s="19" t="n">
         <v>27.85</v>
       </c>
-      <c r="AF46" s="18" t="n">
+      <c r="AF46" s="19" t="n">
         <v>26.6</v>
       </c>
-      <c r="AG46" s="18" t="n">
+      <c r="AG46" s="19" t="n">
         <v>26.24</v>
       </c>
-      <c r="AH46" s="18" t="n">
+      <c r="AH46" s="19" t="n">
         <v>29.16</v>
       </c>
       <c r="AI46" s="6" t="inlineStr"/>
-      <c r="AJ46" s="6" t="inlineStr"/>
-      <c r="AK46" s="17" t="n"/>
+      <c r="AJ46" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK46" s="18" t="n"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>RED TELESISTEMA (R.T.S)</t>
@@ -4157,76 +4255,76 @@
       <c r="B47" s="6" t="n">
         <v>193.25</v>
       </c>
-      <c r="C47" s="18" t="n">
+      <c r="C47" s="19" t="n">
         <v>46.3</v>
       </c>
-      <c r="D47" s="18" t="n">
+      <c r="D47" s="19" t="n">
         <v>46.33</v>
       </c>
-      <c r="E47" s="18" t="n">
+      <c r="E47" s="19" t="n">
         <v>46.39</v>
       </c>
-      <c r="F47" s="18" t="n">
+      <c r="F47" s="19" t="n">
         <v>47.05</v>
       </c>
-      <c r="G47" s="18" t="n">
+      <c r="G47" s="19" t="n">
         <v>47.51</v>
       </c>
-      <c r="H47" s="18" t="n">
+      <c r="H47" s="19" t="n">
         <v>48.13</v>
       </c>
-      <c r="I47" s="18" t="n">
+      <c r="I47" s="19" t="n">
         <v>46.25</v>
       </c>
-      <c r="J47" s="18" t="n">
+      <c r="J47" s="19" t="n">
         <v>47.56</v>
       </c>
-      <c r="K47" s="18" t="n">
+      <c r="K47" s="19" t="n">
         <v>49.26</v>
       </c>
-      <c r="L47" s="18" t="n">
+      <c r="L47" s="19" t="n">
         <v>47.54</v>
       </c>
-      <c r="M47" s="18" t="n">
+      <c r="M47" s="19" t="n">
         <v>48.23</v>
       </c>
-      <c r="N47" s="18" t="n">
+      <c r="N47" s="19" t="n">
         <v>46.86</v>
       </c>
-      <c r="O47" s="18" t="n">
+      <c r="O47" s="19" t="n">
         <v>45.58</v>
       </c>
-      <c r="P47" s="18" t="n">
+      <c r="P47" s="19" t="n">
         <v>45.14</v>
       </c>
-      <c r="Q47" s="18" t="n">
+      <c r="Q47" s="19" t="n">
         <v>46.13</v>
       </c>
-      <c r="R47" s="18" t="n">
+      <c r="R47" s="19" t="n">
         <v>46.38</v>
       </c>
-      <c r="S47" s="18" t="n">
+      <c r="S47" s="19" t="n">
         <v>46.3</v>
       </c>
-      <c r="T47" s="18" t="n">
+      <c r="T47" s="19" t="n">
         <v>49.68</v>
       </c>
-      <c r="U47" s="18" t="n">
+      <c r="U47" s="19" t="n">
         <v>49.32</v>
       </c>
-      <c r="V47" s="18" t="n">
+      <c r="V47" s="19" t="n">
         <v>47.83</v>
       </c>
-      <c r="W47" s="18" t="n">
+      <c r="W47" s="19" t="n">
         <v>45.16</v>
       </c>
-      <c r="X47" s="18" t="n">
+      <c r="X47" s="19" t="n">
         <v>47.52</v>
       </c>
-      <c r="Y47" s="18" t="n">
+      <c r="Y47" s="19" t="n">
         <v>48.44</v>
       </c>
-      <c r="Z47" s="18" t="n">
+      <c r="Z47" s="19" t="n">
         <v>46.78</v>
       </c>
       <c r="AA47" s="6" t="inlineStr">
@@ -4244,26 +4342,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD47" s="18" t="n">
+      <c r="AD47" s="19" t="n">
         <v>45.82</v>
       </c>
-      <c r="AE47" s="18" t="n">
+      <c r="AE47" s="19" t="n">
         <v>47.77</v>
       </c>
-      <c r="AF47" s="18" t="n">
+      <c r="AF47" s="19" t="n">
         <v>47.22</v>
       </c>
-      <c r="AG47" s="18" t="n">
+      <c r="AG47" s="19" t="n">
         <v>47.83</v>
       </c>
-      <c r="AH47" s="18" t="n">
+      <c r="AH47" s="19" t="n">
         <v>47.15</v>
       </c>
       <c r="AI47" s="6" t="inlineStr"/>
-      <c r="AJ47" s="6" t="inlineStr"/>
-      <c r="AK47" s="17" t="n"/>
+      <c r="AJ47" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK47" s="18" t="n"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
           <t>CADENA ECUATORIANA DE TELE</t>
@@ -4272,76 +4374,76 @@
       <c r="B48" s="6" t="n">
         <v>205.25</v>
       </c>
-      <c r="C48" s="18" t="n">
+      <c r="C48" s="19" t="n">
         <v>20.25</v>
       </c>
-      <c r="D48" s="18" t="n">
+      <c r="D48" s="19" t="n">
         <v>19.44</v>
       </c>
-      <c r="E48" s="18" t="n">
+      <c r="E48" s="19" t="n">
         <v>18.66</v>
       </c>
-      <c r="F48" s="18" t="n">
+      <c r="F48" s="19" t="n">
         <v>21.06</v>
       </c>
-      <c r="G48" s="18" t="n">
+      <c r="G48" s="19" t="n">
         <v>19.93</v>
       </c>
-      <c r="H48" s="18" t="n">
+      <c r="H48" s="19" t="n">
         <v>20.95</v>
       </c>
-      <c r="I48" s="18" t="n">
+      <c r="I48" s="19" t="n">
         <v>21.35</v>
       </c>
-      <c r="J48" s="18" t="n">
+      <c r="J48" s="19" t="n">
         <v>19.73</v>
       </c>
-      <c r="K48" s="18" t="n">
+      <c r="K48" s="19" t="n">
         <v>20.03</v>
       </c>
-      <c r="L48" s="18" t="n">
+      <c r="L48" s="19" t="n">
         <v>19.83</v>
       </c>
-      <c r="M48" s="18" t="n">
+      <c r="M48" s="19" t="n">
         <v>19.34</v>
       </c>
-      <c r="N48" s="18" t="n">
+      <c r="N48" s="19" t="n">
         <v>20.03</v>
       </c>
-      <c r="O48" s="18" t="n">
+      <c r="O48" s="19" t="n">
         <v>20.25</v>
       </c>
-      <c r="P48" s="18" t="n">
+      <c r="P48" s="19" t="n">
         <v>19.31</v>
       </c>
-      <c r="Q48" s="18" t="n">
+      <c r="Q48" s="19" t="n">
         <v>21.73</v>
       </c>
-      <c r="R48" s="18" t="n">
+      <c r="R48" s="19" t="n">
         <v>21.23</v>
       </c>
-      <c r="S48" s="18" t="n">
+      <c r="S48" s="19" t="n">
         <v>19.64</v>
       </c>
-      <c r="T48" s="18" t="n">
+      <c r="T48" s="19" t="n">
         <v>20.19</v>
       </c>
-      <c r="U48" s="18" t="n">
+      <c r="U48" s="19" t="n">
         <v>20.4</v>
       </c>
-      <c r="V48" s="18" t="n">
+      <c r="V48" s="19" t="n">
         <v>20.01</v>
       </c>
-      <c r="W48" s="18" t="n">
+      <c r="W48" s="19" t="n">
         <v>20.09</v>
       </c>
-      <c r="X48" s="18" t="n">
+      <c r="X48" s="19" t="n">
         <v>19.82</v>
       </c>
-      <c r="Y48" s="18" t="n">
+      <c r="Y48" s="19" t="n">
         <v>20.22</v>
       </c>
-      <c r="Z48" s="18" t="n">
+      <c r="Z48" s="19" t="n">
         <v>20.75</v>
       </c>
       <c r="AA48" s="6" t="inlineStr">
@@ -4359,26 +4461,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD48" s="18" t="n">
+      <c r="AD48" s="19" t="n">
         <v>20.72</v>
       </c>
-      <c r="AE48" s="18" t="n">
+      <c r="AE48" s="19" t="n">
         <v>19.91</v>
       </c>
-      <c r="AF48" s="18" t="n">
+      <c r="AF48" s="19" t="n">
         <v>20.74</v>
       </c>
-      <c r="AG48" s="18" t="n">
+      <c r="AG48" s="19" t="n">
         <v>20.32</v>
       </c>
-      <c r="AH48" s="18" t="n">
+      <c r="AH48" s="19" t="n">
         <v>20.21</v>
       </c>
       <c r="AI48" s="6" t="inlineStr"/>
-      <c r="AJ48" s="6" t="inlineStr"/>
-      <c r="AK48" s="17" t="n"/>
+      <c r="AJ48" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK48" s="18" t="n"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
           <t>CANAL UNO (NO AUTORIZADO)</t>
@@ -4387,76 +4493,76 @@
       <c r="B49" s="6" t="n">
         <v>519.25</v>
       </c>
-      <c r="C49" s="18" t="n">
+      <c r="C49" s="19" t="n">
         <v>17.22</v>
       </c>
-      <c r="D49" s="18" t="n">
+      <c r="D49" s="19" t="n">
         <v>17.16</v>
       </c>
-      <c r="E49" s="18" t="n">
+      <c r="E49" s="19" t="n">
         <v>16.48</v>
       </c>
-      <c r="F49" s="18" t="n">
+      <c r="F49" s="19" t="n">
         <v>20.09</v>
       </c>
-      <c r="G49" s="18" t="n">
+      <c r="G49" s="19" t="n">
         <v>17.15</v>
       </c>
-      <c r="H49" s="18" t="n">
+      <c r="H49" s="19" t="n">
         <v>16.65</v>
       </c>
-      <c r="I49" s="18" t="n">
+      <c r="I49" s="19" t="n">
         <v>17.38</v>
       </c>
-      <c r="J49" s="18" t="n">
+      <c r="J49" s="19" t="n">
         <v>17.17</v>
       </c>
-      <c r="K49" s="18" t="n">
+      <c r="K49" s="19" t="n">
         <v>16.77</v>
       </c>
-      <c r="L49" s="18" t="n">
+      <c r="L49" s="19" t="n">
         <v>16.8</v>
       </c>
-      <c r="M49" s="18" t="n">
+      <c r="M49" s="19" t="n">
         <v>16.85</v>
       </c>
-      <c r="N49" s="18" t="n">
+      <c r="N49" s="19" t="n">
         <v>16.67</v>
       </c>
-      <c r="O49" s="18" t="n">
+      <c r="O49" s="19" t="n">
         <v>16.78</v>
       </c>
-      <c r="P49" s="18" t="n">
+      <c r="P49" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="Q49" s="18" t="n">
+      <c r="Q49" s="19" t="n">
         <v>16.78</v>
       </c>
-      <c r="R49" s="18" t="n">
+      <c r="R49" s="19" t="n">
         <v>16.69</v>
       </c>
-      <c r="S49" s="18" t="n">
+      <c r="S49" s="19" t="n">
         <v>17.09</v>
       </c>
-      <c r="T49" s="18" t="n">
+      <c r="T49" s="19" t="n">
         <v>16.92</v>
       </c>
-      <c r="U49" s="18" t="n">
+      <c r="U49" s="19" t="n">
         <v>16.91</v>
       </c>
-      <c r="V49" s="18" t="n">
+      <c r="V49" s="19" t="n">
         <v>17.3</v>
       </c>
-      <c r="W49" s="18" t="n">
+      <c r="W49" s="19" t="n">
         <v>17.05</v>
       </c>
-      <c r="X49" s="18" t="n">
+      <c r="X49" s="19" t="n">
         <v>16.87</v>
       </c>
-      <c r="Y49" s="18" t="n">
+      <c r="Y49" s="19" t="n">
         <v>16.7</v>
       </c>
-      <c r="Z49" s="18" t="n">
+      <c r="Z49" s="19" t="n">
         <v>16.9</v>
       </c>
       <c r="AA49" s="6" t="inlineStr">
@@ -4474,26 +4580,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD49" s="18" t="n">
+      <c r="AD49" s="19" t="n">
         <v>16.85</v>
       </c>
-      <c r="AE49" s="18" t="n">
+      <c r="AE49" s="19" t="n">
         <v>16.5</v>
       </c>
-      <c r="AF49" s="18" t="n">
+      <c r="AF49" s="19" t="n">
         <v>16.61</v>
       </c>
-      <c r="AG49" s="18" t="n">
+      <c r="AG49" s="19" t="n">
         <v>16.54</v>
       </c>
-      <c r="AH49" s="18" t="n">
+      <c r="AH49" s="19" t="n">
         <v>17</v>
       </c>
       <c r="AI49" s="6" t="inlineStr"/>
-      <c r="AJ49" s="6" t="inlineStr"/>
-      <c r="AK49" s="17" t="n"/>
+      <c r="AJ49" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK49" s="18" t="n"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>TELEVICENTRO</t>
@@ -4502,76 +4612,76 @@
       <c r="B50" s="6" t="n">
         <v>567.25</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="11" t="n">
         <v>64.31999999999999</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="11" t="n">
         <v>65.59</v>
       </c>
-      <c r="E50" s="10" t="n">
+      <c r="E50" s="11" t="n">
         <v>65.7</v>
       </c>
-      <c r="F50" s="18" t="n">
+      <c r="F50" s="19" t="n">
         <v>29.7</v>
       </c>
-      <c r="G50" s="18" t="n">
+      <c r="G50" s="19" t="n">
         <v>31.15</v>
       </c>
-      <c r="H50" s="18" t="n">
+      <c r="H50" s="19" t="n">
         <v>30.96</v>
       </c>
-      <c r="I50" s="18" t="n">
+      <c r="I50" s="19" t="n">
         <v>30.68</v>
       </c>
-      <c r="J50" s="18" t="n">
+      <c r="J50" s="19" t="n">
         <v>30.74</v>
       </c>
-      <c r="K50" s="18" t="n">
+      <c r="K50" s="19" t="n">
         <v>30.38</v>
       </c>
-      <c r="L50" s="18" t="n">
+      <c r="L50" s="19" t="n">
         <v>30.17</v>
       </c>
-      <c r="M50" s="18" t="n">
+      <c r="M50" s="19" t="n">
         <v>30.75</v>
       </c>
-      <c r="N50" s="18" t="n">
+      <c r="N50" s="19" t="n">
         <v>29.89</v>
       </c>
-      <c r="O50" s="18" t="n">
+      <c r="O50" s="19" t="n">
         <v>30.15</v>
       </c>
-      <c r="P50" s="18" t="n">
+      <c r="P50" s="19" t="n">
         <v>31.64</v>
       </c>
-      <c r="Q50" s="18" t="n">
+      <c r="Q50" s="19" t="n">
         <v>30.28</v>
       </c>
-      <c r="R50" s="18" t="n">
+      <c r="R50" s="19" t="n">
         <v>31.09</v>
       </c>
-      <c r="S50" s="18" t="n">
+      <c r="S50" s="19" t="n">
         <v>30.65</v>
       </c>
-      <c r="T50" s="18" t="n">
+      <c r="T50" s="19" t="n">
         <v>32.47</v>
       </c>
-      <c r="U50" s="18" t="n">
+      <c r="U50" s="19" t="n">
         <v>31.51</v>
       </c>
-      <c r="V50" s="18" t="n">
+      <c r="V50" s="19" t="n">
         <v>30.9</v>
       </c>
-      <c r="W50" s="18" t="n">
+      <c r="W50" s="19" t="n">
         <v>32.99</v>
       </c>
-      <c r="X50" s="18" t="n">
+      <c r="X50" s="19" t="n">
         <v>27.85</v>
       </c>
-      <c r="Y50" s="18" t="n">
+      <c r="Y50" s="19" t="n">
         <v>28.3</v>
       </c>
-      <c r="Z50" s="18" t="n">
+      <c r="Z50" s="19" t="n">
         <v>28.28</v>
       </c>
       <c r="AA50" s="6" t="inlineStr">
@@ -4589,26 +4699,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD50" s="18" t="n">
+      <c r="AD50" s="19" t="n">
         <v>28.19</v>
       </c>
-      <c r="AE50" s="18" t="n">
+      <c r="AE50" s="19" t="n">
         <v>44.75</v>
       </c>
-      <c r="AF50" s="18" t="n">
+      <c r="AF50" s="19" t="n">
         <v>60.62</v>
       </c>
-      <c r="AG50" s="18" t="n">
+      <c r="AG50" s="19" t="n">
         <v>61.05</v>
       </c>
-      <c r="AH50" s="18" t="n">
+      <c r="AH50" s="19" t="n">
         <v>36.81</v>
       </c>
       <c r="AI50" s="6" t="inlineStr"/>
-      <c r="AJ50" s="6" t="inlineStr"/>
-      <c r="AK50" s="17" t="n"/>
+      <c r="AJ50" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK50" s="18" t="n"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>TV AUSTRAL</t>
@@ -4617,76 +4731,76 @@
       <c r="B51" s="6" t="n">
         <v>579.25</v>
       </c>
-      <c r="C51" s="18" t="n">
+      <c r="C51" s="19" t="n">
         <v>22.82</v>
       </c>
-      <c r="D51" s="18" t="n">
+      <c r="D51" s="19" t="n">
         <v>19.78</v>
       </c>
-      <c r="E51" s="18" t="n">
+      <c r="E51" s="19" t="n">
         <v>19.33</v>
       </c>
-      <c r="F51" s="18" t="n">
+      <c r="F51" s="19" t="n">
         <v>20.23</v>
       </c>
-      <c r="G51" s="18" t="n">
+      <c r="G51" s="19" t="n">
         <v>20.96</v>
       </c>
-      <c r="H51" s="18" t="n">
+      <c r="H51" s="19" t="n">
         <v>21.43</v>
       </c>
-      <c r="I51" s="18" t="n">
+      <c r="I51" s="19" t="n">
         <v>20.83</v>
       </c>
-      <c r="J51" s="18" t="n">
+      <c r="J51" s="19" t="n">
         <v>20.46</v>
       </c>
-      <c r="K51" s="18" t="n">
+      <c r="K51" s="19" t="n">
         <v>20.8</v>
       </c>
-      <c r="L51" s="18" t="n">
+      <c r="L51" s="19" t="n">
         <v>19.84</v>
       </c>
-      <c r="M51" s="18" t="n">
+      <c r="M51" s="19" t="n">
         <v>19.92</v>
       </c>
-      <c r="N51" s="18" t="n">
+      <c r="N51" s="19" t="n">
         <v>20.16</v>
       </c>
-      <c r="O51" s="18" t="n">
+      <c r="O51" s="19" t="n">
         <v>20.13</v>
       </c>
-      <c r="P51" s="18" t="n">
+      <c r="P51" s="19" t="n">
         <v>22.75</v>
       </c>
-      <c r="Q51" s="18" t="n">
+      <c r="Q51" s="19" t="n">
         <v>20.9</v>
       </c>
-      <c r="R51" s="18" t="n">
+      <c r="R51" s="19" t="n">
         <v>20.58</v>
       </c>
-      <c r="S51" s="18" t="n">
+      <c r="S51" s="19" t="n">
         <v>20.58</v>
       </c>
-      <c r="T51" s="18" t="n">
+      <c r="T51" s="19" t="n">
         <v>22.65</v>
       </c>
-      <c r="U51" s="18" t="n">
+      <c r="U51" s="19" t="n">
         <v>21.7</v>
       </c>
-      <c r="V51" s="18" t="n">
+      <c r="V51" s="19" t="n">
         <v>19.97</v>
       </c>
-      <c r="W51" s="18" t="n">
+      <c r="W51" s="19" t="n">
         <v>20.77</v>
       </c>
-      <c r="X51" s="18" t="n">
+      <c r="X51" s="19" t="n">
         <v>20.33</v>
       </c>
-      <c r="Y51" s="18" t="n">
+      <c r="Y51" s="19" t="n">
         <v>20.74</v>
       </c>
-      <c r="Z51" s="18" t="n">
+      <c r="Z51" s="19" t="n">
         <v>21.79</v>
       </c>
       <c r="AA51" s="6" t="inlineStr">
@@ -4704,26 +4818,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD51" s="18" t="n">
+      <c r="AD51" s="19" t="n">
         <v>20.5</v>
       </c>
-      <c r="AE51" s="18" t="n">
+      <c r="AE51" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="AF51" s="18" t="n">
+      <c r="AF51" s="19" t="n">
         <v>20.99</v>
       </c>
-      <c r="AG51" s="18" t="n">
+      <c r="AG51" s="19" t="n">
         <v>21.88</v>
       </c>
-      <c r="AH51" s="18" t="n">
+      <c r="AH51" s="19" t="n">
         <v>20.81</v>
       </c>
       <c r="AI51" s="6" t="inlineStr"/>
-      <c r="AJ51" s="6" t="inlineStr"/>
-      <c r="AK51" s="17" t="n"/>
+      <c r="AJ51" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK51" s="18" t="n"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
           <t>UCSG TELEVISION</t>
@@ -4732,76 +4850,76 @@
       <c r="B52" s="6" t="n">
         <v>591.25</v>
       </c>
-      <c r="C52" s="18" t="n">
+      <c r="C52" s="19" t="n">
         <v>18.53</v>
       </c>
-      <c r="D52" s="18" t="n">
+      <c r="D52" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="E52" s="19" t="n">
         <v>17.98</v>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="F52" s="19" t="n">
         <v>18.24</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="G52" s="19" t="n">
         <v>18.19</v>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="H52" s="19" t="n">
         <v>17.79</v>
       </c>
-      <c r="I52" s="18" t="n">
+      <c r="I52" s="19" t="n">
         <v>18.05</v>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="J52" s="19" t="n">
         <v>18.3</v>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="K52" s="19" t="n">
         <v>18.22</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="L52" s="19" t="n">
         <v>17.98</v>
       </c>
-      <c r="M52" s="18" t="n">
+      <c r="M52" s="19" t="n">
         <v>18.44</v>
       </c>
-      <c r="N52" s="18" t="n">
+      <c r="N52" s="19" t="n">
         <v>18.26</v>
       </c>
-      <c r="O52" s="18" t="n">
+      <c r="O52" s="19" t="n">
         <v>18.29</v>
       </c>
-      <c r="P52" s="18" t="n">
+      <c r="P52" s="19" t="n">
         <v>18.67</v>
       </c>
-      <c r="Q52" s="18" t="n">
+      <c r="Q52" s="19" t="n">
         <v>18.47</v>
       </c>
-      <c r="R52" s="18" t="n">
+      <c r="R52" s="19" t="n">
         <v>18.01</v>
       </c>
-      <c r="S52" s="18" t="n">
+      <c r="S52" s="19" t="n">
         <v>18.22</v>
       </c>
-      <c r="T52" s="18" t="n">
+      <c r="T52" s="19" t="n">
         <v>18.26</v>
       </c>
-      <c r="U52" s="18" t="n">
+      <c r="U52" s="19" t="n">
         <v>17.86</v>
       </c>
-      <c r="V52" s="18" t="n">
+      <c r="V52" s="19" t="n">
         <v>18.4</v>
       </c>
-      <c r="W52" s="18" t="n">
+      <c r="W52" s="19" t="n">
         <v>18.1</v>
       </c>
-      <c r="X52" s="18" t="n">
+      <c r="X52" s="19" t="n">
         <v>17.84</v>
       </c>
-      <c r="Y52" s="18" t="n">
+      <c r="Y52" s="19" t="n">
         <v>18.21</v>
       </c>
-      <c r="Z52" s="18" t="n">
+      <c r="Z52" s="19" t="n">
         <v>18.21</v>
       </c>
       <c r="AA52" s="6" t="inlineStr">
@@ -4819,139 +4937,147 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AD52" s="18" t="n">
+      <c r="AD52" s="19" t="n">
         <v>18.28</v>
       </c>
-      <c r="AE52" s="18" t="n">
+      <c r="AE52" s="19" t="n">
         <v>17.92</v>
       </c>
-      <c r="AF52" s="18" t="n">
+      <c r="AF52" s="19" t="n">
         <v>19.01</v>
       </c>
-      <c r="AG52" s="18" t="n">
+      <c r="AG52" s="19" t="n">
         <v>17.87</v>
       </c>
-      <c r="AH52" s="18" t="n">
+      <c r="AH52" s="19" t="n">
         <v>18.2</v>
       </c>
       <c r="AI52" s="6" t="inlineStr"/>
-      <c r="AJ52" s="6" t="inlineStr"/>
-      <c r="AK52" s="17" t="n"/>
+      <c r="AJ52" s="20" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK52" s="18" t="n"/>
     </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
         <is>
           <t>OROMAR</t>
         </is>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="13" t="n">
         <v>621.25</v>
       </c>
-      <c r="C53" s="19" t="n">
+      <c r="C53" s="21" t="n">
         <v>17.95</v>
       </c>
-      <c r="D53" s="19" t="n">
+      <c r="D53" s="21" t="n">
         <v>18.92</v>
       </c>
-      <c r="E53" s="19" t="n">
+      <c r="E53" s="21" t="n">
         <v>18.01</v>
       </c>
-      <c r="F53" s="19" t="n">
+      <c r="F53" s="21" t="n">
         <v>19.62</v>
       </c>
-      <c r="G53" s="19" t="n">
+      <c r="G53" s="21" t="n">
         <v>18.31</v>
       </c>
-      <c r="H53" s="19" t="n">
+      <c r="H53" s="21" t="n">
         <v>18.65</v>
       </c>
-      <c r="I53" s="19" t="n">
+      <c r="I53" s="21" t="n">
         <v>17.95</v>
       </c>
-      <c r="J53" s="19" t="n">
+      <c r="J53" s="21" t="n">
         <v>18.35</v>
       </c>
-      <c r="K53" s="19" t="n">
+      <c r="K53" s="21" t="n">
         <v>17.77</v>
       </c>
-      <c r="L53" s="19" t="n">
+      <c r="L53" s="21" t="n">
         <v>17.89</v>
       </c>
-      <c r="M53" s="19" t="n">
+      <c r="M53" s="21" t="n">
         <v>18.63</v>
       </c>
-      <c r="N53" s="19" t="n">
+      <c r="N53" s="21" t="n">
         <v>18.2</v>
       </c>
-      <c r="O53" s="19" t="n">
+      <c r="O53" s="21" t="n">
         <v>18.66</v>
       </c>
-      <c r="P53" s="19" t="n">
+      <c r="P53" s="21" t="n">
         <v>18.17</v>
       </c>
-      <c r="Q53" s="19" t="n">
+      <c r="Q53" s="21" t="n">
         <v>17.78</v>
       </c>
-      <c r="R53" s="19" t="n">
+      <c r="R53" s="21" t="n">
         <v>17.77</v>
       </c>
-      <c r="S53" s="19" t="n">
+      <c r="S53" s="21" t="n">
         <v>18.17</v>
       </c>
-      <c r="T53" s="19" t="n">
+      <c r="T53" s="21" t="n">
         <v>18.65</v>
       </c>
-      <c r="U53" s="19" t="n">
+      <c r="U53" s="21" t="n">
         <v>18.15</v>
       </c>
-      <c r="V53" s="19" t="n">
+      <c r="V53" s="21" t="n">
         <v>18.39</v>
       </c>
-      <c r="W53" s="19" t="n">
+      <c r="W53" s="21" t="n">
         <v>18.8</v>
       </c>
-      <c r="X53" s="19" t="n">
+      <c r="X53" s="21" t="n">
         <v>17.88</v>
       </c>
-      <c r="Y53" s="19" t="n">
+      <c r="Y53" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="Z53" s="19" t="n">
+      <c r="Z53" s="21" t="n">
         <v>17.42</v>
       </c>
-      <c r="AA53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AB53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC53" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD53" s="19" t="n">
+      <c r="AA53" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" s="13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD53" s="21" t="n">
         <v>17.28</v>
       </c>
-      <c r="AE53" s="19" t="n">
+      <c r="AE53" s="21" t="n">
         <v>17.95</v>
       </c>
-      <c r="AF53" s="19" t="n">
+      <c r="AF53" s="21" t="n">
         <v>17.8</v>
       </c>
-      <c r="AG53" s="19" t="n">
+      <c r="AG53" s="21" t="n">
         <v>17.93</v>
       </c>
-      <c r="AH53" s="19" t="n">
+      <c r="AH53" s="21" t="n">
         <v>18.18</v>
       </c>
-      <c r="AI53" s="12" t="inlineStr"/>
-      <c r="AJ53" s="12" t="inlineStr"/>
-      <c r="AK53" s="20" t="n"/>
+      <c r="AI53" s="13" t="inlineStr"/>
+      <c r="AJ53" s="22" t="inlineStr">
+        <is>
+          <t>Niveles por debajo del borde del área de cobertura principal y secundaria</t>
+        </is>
+      </c>
+      <c r="AK53" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="27">

--- a/ReportesUnificados/cañar_ReporteUnificado.xlsx
+++ b/ReportesUnificados/cañar_ReporteUnificado.xlsx
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>FECHA PRESENTACIÓN: 02/09/2025</t>
+          <t>FECHA PRESENTACIÓN: 03/09/2025</t>
         </is>
       </c>
     </row>
